--- a/docs/101_聲韻調對照表.xlsx
+++ b/docs/101_聲韻調對照表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F7369F-846A-4CED-8F07-4BBD9738B959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D547A410-1B2C-4FDF-809F-400790E8692E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5180" uniqueCount="1360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5180" uniqueCount="1362">
   <si>
     <t>識別號</t>
   </si>
@@ -5162,6 +5162,12 @@
   <si>
     <t>m</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>》e${1}i</t>
+  </si>
+  <si>
+    <t>》o${1}u</t>
   </si>
 </sst>
 </file>
@@ -24956,7 +24962,7 @@
     <col min="15" max="15" width="8.6640625" style="132"/>
     <col min="16" max="16" width="6" style="135" customWidth="1" outlineLevel="1"/>
     <col min="17" max="17" width="6.1640625" style="135" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="8.6640625" style="132"/>
+    <col min="18" max="18" width="11.1640625" style="132" customWidth="1"/>
     <col min="19" max="19" width="3" style="53" customWidth="1"/>
     <col min="20" max="20" width="34.5" style="133" customWidth="1"/>
     <col min="21" max="16384" width="8.6640625" style="53"/>
@@ -25095,13 +25101,13 @@
         <v>2</v>
       </c>
       <c r="R4" s="132" t="str">
-        <f t="shared" ref="R4:R50" si="0" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(L4,Q4), "${1}", RIGHT(L4, LEN(L4)-Q4)), "" )</f>
-        <v>ia${1}unnh</v>
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(L4,Q4-1), "》", MID(L4,Q4,1), "${1}", RIGHT(L4, LEN(L4)-Q4)), "" )</f>
+        <v>i》a${1}unnh</v>
       </c>
       <c r="S4" s="57"/>
       <c r="T4" s="58" t="str">
-        <f xml:space="preserve"> IF(AND(M4&lt;&gt;"", L4&lt;&gt;""), "    - xform/》" &amp; O4 &amp;  "/"  &amp; R4 &amp;  "》/", "")</f>
-        <v xml:space="preserve">    - xform/》iaunnh(\d)/ia${1}unnh》/</v>
+        <f xml:space="preserve"> IF(AND(M4&lt;&gt;"", L4&lt;&gt;""), "    - xform/》" &amp; O4 &amp;  "/"  &amp; R4 &amp;  "/", "")</f>
+        <v xml:space="preserve">    - xform/》iaunnh(\d)/i》a${1}unnh/</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="27.75" thickBot="1">
@@ -25148,28 +25154,28 @@
         <v>uainnh</v>
       </c>
       <c r="M5" s="59" t="str">
-        <f t="shared" ref="M5:M68" si="1">F5</f>
+        <f t="shared" ref="M5:M68" si="0">F5</f>
         <v>nuɑih</v>
       </c>
       <c r="O5" s="132" t="str">
-        <f t="shared" ref="O5:O68" si="2" xml:space="preserve"> _xlfn.CONCAT(L5, "(\d)")</f>
+        <f t="shared" ref="O5:O68" si="1" xml:space="preserve"> _xlfn.CONCAT(L5, "(\d)")</f>
         <v>uainnh(\d)</v>
       </c>
       <c r="P5" s="137" t="s">
         <v>1253</v>
       </c>
       <c r="Q5" s="135">
-        <f t="shared" ref="Q5:Q68" si="3" xml:space="preserve"> IFERROR( IF(P5="", "", SEARCH(P5, $L5)), "")</f>
+        <f t="shared" ref="Q5:Q68" si="2" xml:space="preserve"> IFERROR( IF(P5="", "", SEARCH(P5, $L5)), "")</f>
         <v>2</v>
       </c>
       <c r="R5" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ua${1}innh</v>
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(L5,Q5-1), "》", MID(L5,Q5,1), "${1}", RIGHT(L5, LEN(L5)-Q5)), "" )</f>
+        <v>u》a${1}innh</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="58" t="str">
-        <f t="shared" ref="T5:T68" si="4" xml:space="preserve"> IF(AND(M5&lt;&gt;"", L5&lt;&gt;""), "    - xform/》" &amp; O5 &amp;  "/"  &amp; R5 &amp;  "》/", "")</f>
-        <v xml:space="preserve">    - xform/》uainnh(\d)/ua${1}innh》/</v>
+        <f t="shared" ref="T5:T68" si="3" xml:space="preserve"> IF(AND(M5&lt;&gt;"", L5&lt;&gt;""), "    - xform/》" &amp; O5 &amp;  "/"  &amp; R5 &amp;  "/", "")</f>
+        <v xml:space="preserve">    - xform/》uainnh(\d)/u》a${1}innh/</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="27.75" thickBot="1">
@@ -25215,28 +25221,28 @@
         <v>aunnh</v>
       </c>
       <c r="M6" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>nɑoh</v>
+      </c>
+      <c r="O6" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>nɑoh</v>
-      </c>
-      <c r="O6" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>aunnh(\d)</v>
       </c>
       <c r="P6" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q6" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R6" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>a${1}unnh</v>
+        <f t="shared" ref="R6:R69" si="4" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(L6,Q6-1), "》", MID(L6,Q6,1), "${1}", RIGHT(L6, LEN(L6)-Q6)), "" )</f>
+        <v>》a${1}unnh</v>
       </c>
       <c r="S6" s="57"/>
       <c r="T6" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》aunnh(\d)/a${1}unnh》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》aunnh(\d)/》a${1}unnh/</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="27.75" thickBot="1">
@@ -25282,28 +25288,28 @@
         <v>iannh</v>
       </c>
       <c r="M7" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>niɑh</v>
+      </c>
+      <c r="O7" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>niɑh</v>
-      </c>
-      <c r="O7" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iannh(\d)</v>
       </c>
       <c r="P7" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q7" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R7" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ia${1}nnh</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}nnh</v>
       </c>
       <c r="S7" s="57"/>
       <c r="T7" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iannh(\d)/ia${1}nnh》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iannh(\d)/i》a${1}nnh/</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="27.75" thickBot="1">
@@ -25349,28 +25355,28 @@
         <v>iaunn</v>
       </c>
       <c r="M8" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>niɑo</v>
+      </c>
+      <c r="O8" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>niɑo</v>
-      </c>
-      <c r="O8" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iaunn(\d)</v>
       </c>
       <c r="P8" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q8" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R8" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ia${1}unn</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}unn</v>
       </c>
       <c r="S8" s="57"/>
       <c r="T8" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iaunn(\d)/ia${1}unn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iaunn(\d)/i》a${1}unn/</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="27.75" thickBot="1">
@@ -25417,28 +25423,28 @@
         <v>uainn</v>
       </c>
       <c r="M9" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>uɑi</v>
+      </c>
+      <c r="O9" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>uɑi</v>
-      </c>
-      <c r="O9" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>uainn(\d)</v>
       </c>
       <c r="P9" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q9" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R9" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ua${1}inn</v>
+        <f t="shared" si="4"/>
+        <v>u》a${1}inn</v>
       </c>
       <c r="S9" s="57"/>
       <c r="T9" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》uainn(\d)/ua${1}inn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》uainn(\d)/u》a${1}inn/</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="27.75" thickBot="1">
@@ -25484,28 +25490,28 @@
         <v>iang</v>
       </c>
       <c r="M10" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>iɑnɡ</v>
+      </c>
+      <c r="O10" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>iɑnɡ</v>
-      </c>
-      <c r="O10" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iang(\d)</v>
       </c>
       <c r="P10" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q10" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R10" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ia${1}ng</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}ng</v>
       </c>
       <c r="S10" s="57"/>
       <c r="T10" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iang(\d)/ia${1}ng》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iang(\d)/i》a${1}ng/</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="27.75" thickBot="1">
@@ -25551,28 +25557,28 @@
         <v>iauh</v>
       </c>
       <c r="M11" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>iaoh</v>
+      </c>
+      <c r="O11" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>iaoh</v>
-      </c>
-      <c r="O11" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iauh(\d)</v>
       </c>
       <c r="P11" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q11" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R11" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ia${1}uh</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}uh</v>
       </c>
       <c r="S11" s="57"/>
       <c r="T11" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iauh(\d)/ia${1}uh》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iauh(\d)/i》a${1}uh/</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="27.75" thickBot="1">
@@ -25618,28 +25624,28 @@
         <v>iong</v>
       </c>
       <c r="M12" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ionɡ</v>
+      </c>
+      <c r="O12" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ionɡ</v>
-      </c>
-      <c r="O12" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iong(\d)</v>
       </c>
       <c r="P12" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q12" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R12" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>io${1}ng</v>
+        <f t="shared" si="4"/>
+        <v>i》o${1}ng</v>
       </c>
       <c r="S12" s="57"/>
       <c r="T12" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iong(\d)/io${1}ng》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iong(\d)/i》o${1}ng/</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="27.75" thickBot="1">
@@ -25685,28 +25691,28 @@
         <v>ennh</v>
       </c>
       <c r="M13" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>nɑeh</v>
+      </c>
+      <c r="O13" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>nɑeh</v>
-      </c>
-      <c r="O13" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ennh(\d)</v>
       </c>
       <c r="P13" s="135" t="s">
         <v>1206</v>
       </c>
       <c r="Q13" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R13" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>e${1}nnh</v>
+        <f t="shared" si="4"/>
+        <v>》e${1}nnh</v>
       </c>
       <c r="S13" s="57"/>
       <c r="T13" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ennh(\d)/e${1}nnh》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ennh(\d)/》e${1}nnh/</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="27.75" thickBot="1">
@@ -25753,28 +25759,28 @@
         <v>onnh</v>
       </c>
       <c r="M14" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>nooh</v>
+      </c>
+      <c r="O14" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>nooh</v>
-      </c>
-      <c r="O14" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>onnh(\d)</v>
       </c>
       <c r="P14" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q14" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R14" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>o${1}nnh</v>
+        <f t="shared" si="4"/>
+        <v>》o${1}nnh</v>
       </c>
       <c r="S14" s="57"/>
       <c r="T14" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》onnh(\d)/o${1}nnh》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》onnh(\d)/》o${1}nnh/</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="27.75" thickBot="1">
@@ -25820,28 +25826,28 @@
         <v>annh</v>
       </c>
       <c r="M15" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>nɑh</v>
+      </c>
+      <c r="O15" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>nɑh</v>
-      </c>
-      <c r="O15" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>annh(\d)</v>
       </c>
       <c r="P15" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q15" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R15" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>a${1}nnh</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}nnh</v>
       </c>
       <c r="S15" s="57"/>
       <c r="T15" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》annh(\d)/a${1}nnh》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》annh(\d)/》a${1}nnh/</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="27.75" thickBot="1">
@@ -25887,28 +25893,28 @@
         <v>ainn</v>
       </c>
       <c r="M16" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>nɑi</v>
+      </c>
+      <c r="O16" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>nɑi</v>
-      </c>
-      <c r="O16" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ainn(\d)</v>
       </c>
       <c r="P16" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q16" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R16" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>a${1}inn</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}inn</v>
       </c>
       <c r="S16" s="57"/>
       <c r="T16" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ainn(\d)/a${1}inn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ainn(\d)/》a${1}inn/</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="27.75" thickBot="1">
@@ -25954,28 +25960,28 @@
         <v>aunn</v>
       </c>
       <c r="M17" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>nɑo</v>
+      </c>
+      <c r="O17" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>nɑo</v>
-      </c>
-      <c r="O17" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>aunn(\d)</v>
       </c>
       <c r="P17" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q17" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R17" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>a${1}unn</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}unn</v>
       </c>
       <c r="S17" s="57"/>
       <c r="T17" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》aunn(\d)/a${1}unn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》aunn(\d)/》a${1}unn/</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="27.75" thickBot="1">
@@ -26021,28 +26027,28 @@
         <v>iann</v>
       </c>
       <c r="M18" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>nia</v>
+      </c>
+      <c r="O18" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>nia</v>
-      </c>
-      <c r="O18" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iann(\d)</v>
       </c>
       <c r="P18" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q18" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R18" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ia${1}nn</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}nn</v>
       </c>
       <c r="S18" s="57"/>
       <c r="T18" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iann(\d)/ia${1}nn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iann(\d)/i》a${1}nn/</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="27.75" thickBot="1">
@@ -26089,27 +26095,28 @@
         <v>innh</v>
       </c>
       <c r="M19" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>nih</v>
+      </c>
+      <c r="O19" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>nih</v>
-      </c>
-      <c r="O19" s="132" t="str">
+        <v>innh(\d)</v>
+      </c>
+      <c r="P19" s="135" t="s">
+        <v>1254</v>
+      </c>
+      <c r="Q19" s="135">
         <f t="shared" si="2"/>
-        <v>innh(\d)</v>
-      </c>
-      <c r="P19" s="135" t="s">
-        <v>1253</v>
-      </c>
-      <c r="Q19" s="135" t="s">
-        <v>1254</v>
+        <v>1</v>
       </c>
       <c r="R19" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f t="shared" si="4"/>
+        <v>》i${1}nnh</v>
       </c>
       <c r="S19" s="57"/>
       <c r="T19" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》innh(\d)/》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》innh(\d)/》i${1}nnh/</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="27.75" thickBot="1">
@@ -26156,27 +26163,28 @@
         <v>iunn</v>
       </c>
       <c r="M20" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>niu</v>
+      </c>
+      <c r="O20" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>niu</v>
-      </c>
-      <c r="O20" s="132" t="str">
+        <v>iunn(\d)</v>
+      </c>
+      <c r="P20" s="135" t="s">
+        <v>1254</v>
+      </c>
+      <c r="Q20" s="135">
         <f t="shared" si="2"/>
-        <v>iunn(\d)</v>
-      </c>
-      <c r="P20" s="135" t="s">
-        <v>1253</v>
-      </c>
-      <c r="Q20" s="135" t="s">
-        <v>1254</v>
+        <v>1</v>
       </c>
       <c r="R20" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f t="shared" si="4"/>
+        <v>》i${1}unn</v>
       </c>
       <c r="S20" s="57"/>
       <c r="T20" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iunn(\d)/》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iunn(\d)/》i${1}unn/</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="27.75" thickBot="1">
@@ -26223,28 +26231,28 @@
         <v>uann</v>
       </c>
       <c r="M21" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>nua</v>
+      </c>
+      <c r="O21" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>nua</v>
-      </c>
-      <c r="O21" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>uann(\d)</v>
       </c>
       <c r="P21" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q21" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R21" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ua${1}nn</v>
+        <f t="shared" si="4"/>
+        <v>u》a${1}nn</v>
       </c>
       <c r="S21" s="57"/>
       <c r="T21" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》uann(\d)/ua${1}nn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》uann(\d)/u》a${1}nn/</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="27.75" thickBot="1">
@@ -26291,28 +26299,28 @@
         <v>uinn</v>
       </c>
       <c r="M22" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>nui</v>
+      </c>
+      <c r="O22" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>nui</v>
-      </c>
-      <c r="O22" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>uinn(\d)</v>
       </c>
       <c r="P22" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q22" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R22" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ui${1}nn</v>
+        <f t="shared" si="4"/>
+        <v>u》i${1}nn</v>
       </c>
       <c r="S22" s="57"/>
       <c r="T22" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》uinn(\d)/ui${1}nn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》uinn(\d)/u》i${1}nn/</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="27.75" thickBot="1">
@@ -26358,28 +26366,28 @@
         <v>ionn</v>
       </c>
       <c r="M23" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="O23" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="O23" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ionn(\d)</v>
       </c>
       <c r="P23" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q23" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R23" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>io${1}nn</v>
+        <f t="shared" si="4"/>
+        <v>i》o${1}nn</v>
       </c>
       <c r="S23" s="57"/>
       <c r="T23" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ionn(\d)/io${1}nn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ionn(\d)/i》o${1}nn/</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="27.75" thickBot="1">
@@ -26426,27 +26434,27 @@
         <v>iooh</v>
       </c>
       <c r="M24" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="O24" s="132" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O24" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iooh(\d)</v>
       </c>
       <c r="P24" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q24" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R24" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>io${1}oh</v>
+        <f t="shared" si="4"/>
+        <v>i》o${1}oh</v>
       </c>
       <c r="S24" s="57"/>
       <c r="T24" s="58" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -26494,28 +26502,28 @@
         <v>aenn</v>
       </c>
       <c r="M25" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>e</v>
+      </c>
+      <c r="O25" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>e</v>
-      </c>
-      <c r="O25" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>aenn(\d)</v>
       </c>
       <c r="P25" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q25" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R25" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>a${1}enn</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}enn</v>
       </c>
       <c r="S25" s="57"/>
       <c r="T25" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》aenn(\d)/a${1}enn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》aenn(\d)/》a${1}enn/</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="27.75" thickBot="1">
@@ -26558,28 +26566,28 @@
         <v>eeh</v>
       </c>
       <c r="M26" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ɑeh</v>
+      </c>
+      <c r="O26" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ɑeh</v>
-      </c>
-      <c r="O26" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>eeh(\d)</v>
       </c>
       <c r="P26" s="135" t="s">
         <v>1206</v>
       </c>
       <c r="Q26" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R26" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>e${1}eh</v>
+        <f t="shared" si="4"/>
+        <v>》e${1}eh</v>
       </c>
       <c r="S26" s="57"/>
       <c r="T26" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》eeh(\d)/e${1}eh》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》eeh(\d)/》e${1}eh/</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="27.75" thickBot="1">
@@ -26625,28 +26633,28 @@
         <v>ang</v>
       </c>
       <c r="M27" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>anɡ</v>
+      </c>
+      <c r="O27" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>anɡ</v>
-      </c>
-      <c r="O27" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ang(\d)</v>
       </c>
       <c r="P27" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q27" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R27" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>a${1}ng</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}ng</v>
       </c>
       <c r="S27" s="57"/>
       <c r="T27" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ang(\d)/a${1}ng》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ang(\d)/》a${1}ng/</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="27.75" thickBot="1">
@@ -26692,28 +26700,28 @@
         <v>auh</v>
       </c>
       <c r="M28" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ɑoh</v>
+      </c>
+      <c r="O28" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ɑoh</v>
-      </c>
-      <c r="O28" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>auh(\d)</v>
       </c>
       <c r="P28" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q28" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R28" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>a${1}uh</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}uh</v>
       </c>
       <c r="S28" s="57"/>
       <c r="T28" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》auh(\d)/a${1}uh》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》auh(\d)/》a${1}uh/</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="27.75" thickBot="1">
@@ -26759,28 +26767,28 @@
         <v>iah</v>
       </c>
       <c r="M29" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>iɑh</v>
+      </c>
+      <c r="O29" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>iɑh</v>
-      </c>
-      <c r="O29" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iah(\d)</v>
       </c>
       <c r="P29" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q29" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R29" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ia${1}h</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}h</v>
       </c>
       <c r="S29" s="57"/>
       <c r="T29" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iah(\d)/ia${1}h》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iah(\d)/i》a${1}h/</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="27.75" thickBot="1">
@@ -26826,28 +26834,28 @@
         <v>iak</v>
       </c>
       <c r="M30" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>iɑk</v>
+      </c>
+      <c r="O30" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>iɑk</v>
-      </c>
-      <c r="O30" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iak(\d)</v>
       </c>
       <c r="P30" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q30" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R30" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ia${1}k</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}k</v>
       </c>
       <c r="S30" s="57"/>
       <c r="T30" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iak(\d)/ia${1}k》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iak(\d)/i》a${1}k/</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="27.75" thickBot="1">
@@ -26893,28 +26901,28 @@
         <v>iam</v>
       </c>
       <c r="M31" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>iɑm</v>
+      </c>
+      <c r="O31" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>iɑm</v>
-      </c>
-      <c r="O31" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iam(\d)</v>
       </c>
       <c r="P31" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q31" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R31" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ia${1}m</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}m</v>
       </c>
       <c r="S31" s="57"/>
       <c r="T31" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iam(\d)/ia${1}m》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iam(\d)/i》a${1}m/</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="27.75" thickBot="1">
@@ -26960,28 +26968,28 @@
         <v>ian</v>
       </c>
       <c r="M32" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>iɑn</v>
+      </c>
+      <c r="O32" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>iɑn</v>
-      </c>
-      <c r="O32" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ian(\d)</v>
       </c>
       <c r="P32" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q32" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R32" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ia${1}n</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}n</v>
       </c>
       <c r="S32" s="57"/>
       <c r="T32" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ian(\d)/ia${1}n》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ian(\d)/i》a${1}n/</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="27.75" thickBot="1">
@@ -27027,28 +27035,28 @@
         <v>iau</v>
       </c>
       <c r="M33" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>iɑo</v>
+      </c>
+      <c r="O33" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>iɑo</v>
-      </c>
-      <c r="O33" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iau(\d)</v>
       </c>
       <c r="P33" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q33" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R33" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ia${1}u</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}u</v>
       </c>
       <c r="S33" s="57"/>
       <c r="T33" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iau(\d)/ia${1}u》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iau(\d)/i》a${1}u/</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="27.75" thickBot="1">
@@ -27094,28 +27102,28 @@
         <v>iap</v>
       </c>
       <c r="M34" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>iɑp</v>
+      </c>
+      <c r="O34" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>iɑp</v>
-      </c>
-      <c r="O34" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iap(\d)</v>
       </c>
       <c r="P34" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q34" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R34" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ia${1}p</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}p</v>
       </c>
       <c r="S34" s="57"/>
       <c r="T34" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iap(\d)/ia${1}p》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iap(\d)/i》a${1}p/</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="27.75" thickBot="1">
@@ -27161,28 +27169,28 @@
         <v>iat</v>
       </c>
       <c r="M35" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>iɑt</v>
+      </c>
+      <c r="O35" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>iɑt</v>
-      </c>
-      <c r="O35" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iat(\d)</v>
       </c>
       <c r="P35" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q35" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R35" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ia${1}t</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}t</v>
       </c>
       <c r="S35" s="57"/>
       <c r="T35" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iat(\d)/ia${1}t》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iat(\d)/i》a${1}t/</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="27.75" thickBot="1">
@@ -27228,28 +27236,28 @@
         <v>ing</v>
       </c>
       <c r="M36" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>inɡ</v>
+      </c>
+      <c r="O36" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>inɡ</v>
-      </c>
-      <c r="O36" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ing(\d)</v>
       </c>
       <c r="P36" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q36" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R36" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>i${1}ng</v>
+        <f t="shared" si="4"/>
+        <v>》i${1}ng</v>
       </c>
       <c r="S36" s="57"/>
       <c r="T36" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ing(\d)/i${1}ng》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ing(\d)/》i${1}ng/</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="27.75" thickBot="1">
@@ -27295,28 +27303,28 @@
         <v>ioh</v>
       </c>
       <c r="M37" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ioh</v>
+      </c>
+      <c r="O37" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ioh</v>
-      </c>
-      <c r="O37" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ioh(\d)</v>
       </c>
       <c r="P37" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q37" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R37" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>i${1}oh</v>
+        <f t="shared" si="4"/>
+        <v>》i${1}oh</v>
       </c>
       <c r="S37" s="57"/>
       <c r="T37" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ioh(\d)/i${1}oh》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ioh(\d)/》i${1}oh/</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="27.75" thickBot="1">
@@ -27362,28 +27370,28 @@
         <v>iok</v>
       </c>
       <c r="M38" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>iok</v>
+      </c>
+      <c r="O38" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>iok</v>
-      </c>
-      <c r="O38" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iok(\d)</v>
       </c>
       <c r="P38" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q38" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R38" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>i${1}ok</v>
+        <f t="shared" si="4"/>
+        <v>》i${1}ok</v>
       </c>
       <c r="S38" s="57"/>
       <c r="T38" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iok(\d)/i${1}ok》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iok(\d)/》i${1}ok/</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="27.75" thickBot="1">
@@ -27429,28 +27437,28 @@
         <v>iuh</v>
       </c>
       <c r="M39" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>iuh</v>
+      </c>
+      <c r="O39" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>iuh</v>
-      </c>
-      <c r="O39" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>iuh(\d)</v>
       </c>
       <c r="P39" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q39" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R39" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>i${1}uh</v>
+        <f t="shared" si="4"/>
+        <v>》i${1}uh</v>
       </c>
       <c r="S39" s="57"/>
       <c r="T39" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》iuh(\d)/i${1}uh》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》iuh(\d)/》i${1}uh/</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="27.75" thickBot="1">
@@ -27496,28 +27504,28 @@
         <v>enn</v>
       </c>
       <c r="M40" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>nɑe</v>
+      </c>
+      <c r="O40" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>nɑe</v>
-      </c>
-      <c r="O40" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>enn(\d)</v>
       </c>
       <c r="P40" s="135" t="s">
         <v>1206</v>
       </c>
       <c r="Q40" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R40" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>e${1}nn</v>
+        <f t="shared" si="4"/>
+        <v>》e${1}nn</v>
       </c>
       <c r="S40" s="57"/>
       <c r="T40" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》enn(\d)/e${1}nn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》enn(\d)/》e${1}nn/</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="27.75" thickBot="1">
@@ -27563,28 +27571,28 @@
         <v>ngh</v>
       </c>
       <c r="M41" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ngh</v>
+      </c>
+      <c r="O41" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ngh</v>
-      </c>
-      <c r="O41" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ngh(\d)</v>
       </c>
       <c r="P41" s="135" t="s">
         <v>1358</v>
       </c>
       <c r="Q41" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R41" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>n${1}gh</v>
+        <f t="shared" si="4"/>
+        <v>》n${1}gh</v>
       </c>
       <c r="S41" s="57"/>
       <c r="T41" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ngh(\d)/n${1}gh》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ngh(\d)/》n${1}gh/</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="27.75" thickBot="1">
@@ -27630,28 +27638,28 @@
         <v>onn</v>
       </c>
       <c r="M42" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>noo</v>
+      </c>
+      <c r="O42" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>noo</v>
-      </c>
-      <c r="O42" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>onn(\d)</v>
       </c>
       <c r="P42" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q42" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R42" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>o${1}nn</v>
+        <f t="shared" si="4"/>
+        <v>》o${1}nn</v>
       </c>
       <c r="S42" s="57"/>
       <c r="T42" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》onn(\d)/o${1}nn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》onn(\d)/》o${1}nn/</v>
       </c>
     </row>
     <row r="43" spans="1:20" ht="27.75" thickBot="1">
@@ -27697,28 +27705,28 @@
         <v>ong</v>
       </c>
       <c r="M43" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>onɡ</v>
+      </c>
+      <c r="O43" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>onɡ</v>
-      </c>
-      <c r="O43" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ong(\d)</v>
       </c>
       <c r="P43" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q43" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R43" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>o${1}ng</v>
+        <f t="shared" si="4"/>
+        <v>》o${1}ng</v>
       </c>
       <c r="S43" s="57"/>
       <c r="T43" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ong(\d)/o${1}ng》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ong(\d)/》o${1}ng/</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="27.75" thickBot="1">
@@ -27764,28 +27772,28 @@
         <v>ooh</v>
       </c>
       <c r="M44" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ooh</v>
+      </c>
+      <c r="O44" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ooh</v>
-      </c>
-      <c r="O44" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ooh(\d)</v>
       </c>
       <c r="P44" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q44" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R44" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>o${1}oh</v>
+        <f t="shared" si="4"/>
+        <v>》o${1}oh</v>
       </c>
       <c r="S44" s="57"/>
       <c r="T44" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ooh(\d)/o${1}oh》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ooh(\d)/》o${1}oh/</v>
       </c>
     </row>
     <row r="45" spans="1:20" ht="27.75" thickBot="1">
@@ -27831,28 +27839,28 @@
         <v>uah</v>
       </c>
       <c r="M45" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>uɑh</v>
+      </c>
+      <c r="O45" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>uɑh</v>
-      </c>
-      <c r="O45" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>uah(\d)</v>
       </c>
       <c r="P45" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q45" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R45" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ua${1}h</v>
+        <f t="shared" si="4"/>
+        <v>u》a${1}h</v>
       </c>
       <c r="S45" s="57"/>
       <c r="T45" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》uah(\d)/ua${1}h》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》uah(\d)/u》a${1}h/</v>
       </c>
     </row>
     <row r="46" spans="1:20" ht="27.75" thickBot="1">
@@ -27898,28 +27906,28 @@
         <v>uai</v>
       </c>
       <c r="M46" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>uai</v>
+      </c>
+      <c r="O46" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>uai</v>
-      </c>
-      <c r="O46" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>uai(\d)</v>
       </c>
       <c r="P46" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q46" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R46" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ua${1}i</v>
+        <f t="shared" si="4"/>
+        <v>u》a${1}i</v>
       </c>
       <c r="S46" s="57"/>
       <c r="T46" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》uai(\d)/ua${1}i》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》uai(\d)/u》a${1}i/</v>
       </c>
     </row>
     <row r="47" spans="1:20" ht="27.75" thickBot="1">
@@ -27965,28 +27973,28 @@
         <v>uan</v>
       </c>
       <c r="M47" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>uɑn</v>
+      </c>
+      <c r="O47" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>uɑn</v>
-      </c>
-      <c r="O47" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>uan(\d)</v>
       </c>
       <c r="P47" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q47" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R47" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ua${1}n</v>
+        <f t="shared" si="4"/>
+        <v>u》a${1}n</v>
       </c>
       <c r="S47" s="57"/>
       <c r="T47" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》uan(\d)/ua${1}n》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》uan(\d)/u》a${1}n/</v>
       </c>
     </row>
     <row r="48" spans="1:20" ht="27.75" thickBot="1">
@@ -28032,28 +28040,28 @@
         <v>uat</v>
       </c>
       <c r="M48" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>uɑt</v>
+      </c>
+      <c r="O48" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>uɑt</v>
-      </c>
-      <c r="O48" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>uat(\d)</v>
       </c>
       <c r="P48" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q48" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R48" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ua${1}t</v>
+        <f t="shared" si="4"/>
+        <v>u》a${1}t</v>
       </c>
       <c r="S48" s="57"/>
       <c r="T48" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》uat(\d)/ua${1}t》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》uat(\d)/u》a${1}t/</v>
       </c>
     </row>
     <row r="49" spans="1:20" ht="27.75" thickBot="1">
@@ -28099,28 +28107,28 @@
         <v>ueh</v>
       </c>
       <c r="M49" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ueh</v>
+      </c>
+      <c r="O49" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ueh</v>
-      </c>
-      <c r="O49" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ueh(\d)</v>
       </c>
       <c r="P49" s="135" t="s">
         <v>1206</v>
       </c>
       <c r="Q49" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R49" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>ue${1}h</v>
+        <f t="shared" si="4"/>
+        <v>u》e${1}h</v>
       </c>
       <c r="S49" s="57"/>
       <c r="T49" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ueh(\d)/ue${1}h》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ueh(\d)/u》e${1}h/</v>
       </c>
     </row>
     <row r="50" spans="1:20" ht="27.75" thickBot="1">
@@ -28166,28 +28174,28 @@
         <v>ann</v>
       </c>
       <c r="M50" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>na</v>
+      </c>
+      <c r="O50" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>na</v>
-      </c>
-      <c r="O50" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ann(\d)</v>
       </c>
       <c r="P50" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q50" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R50" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>a${1}nn</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}nn</v>
       </c>
       <c r="S50" s="57"/>
       <c r="T50" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ann(\d)/a${1}nn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ann(\d)/》a${1}nn/</v>
       </c>
     </row>
     <row r="51" spans="1:20" ht="27.75" thickBot="1">
@@ -28233,28 +28241,28 @@
         <v>inn</v>
       </c>
       <c r="M51" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ni</v>
+      </c>
+      <c r="O51" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ni</v>
-      </c>
-      <c r="O51" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>inn(\d)</v>
       </c>
       <c r="P51" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q51" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R51" s="132" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(L51,Q51), "${1}", RIGHT(L51, LEN(L51)-Q51)), "" )</f>
-        <v>i${1}nn</v>
+        <f t="shared" si="4"/>
+        <v>》i${1}nn</v>
       </c>
       <c r="S51" s="57"/>
       <c r="T51" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》inn(\d)/i${1}nn》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》inn(\d)/》i${1}nn/</v>
       </c>
     </row>
     <row r="52" spans="1:20" ht="27.75" thickBot="1">
@@ -28301,28 +28309,28 @@
         <v>uae</v>
       </c>
       <c r="M52" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>a</v>
+      </c>
+      <c r="O52" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="O52" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>uae(\d)</v>
       </c>
       <c r="P52" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q52" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R52" s="132" t="str">
-        <f t="shared" ref="R52:R99" si="5" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(L52,Q52), "${1}", RIGHT(L52, LEN(L52)-Q52)), "" )</f>
-        <v>ua${1}e</v>
+        <f t="shared" si="4"/>
+        <v>u》a${1}e</v>
       </c>
       <c r="S52" s="57"/>
       <c r="T52" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》uae(\d)/ua${1}e》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》uae(\d)/u》a${1}e/</v>
       </c>
     </row>
     <row r="53" spans="1:20" ht="27.75" thickBot="1">
@@ -28369,28 +28377,28 @@
         <v>ioo</v>
       </c>
       <c r="M53" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>m</v>
+      </c>
+      <c r="O53" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>m</v>
-      </c>
-      <c r="O53" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ioo(\d)</v>
       </c>
       <c r="P53" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q53" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R53" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>i${1}oo</v>
+        <f t="shared" si="4"/>
+        <v>》i${1}oo</v>
       </c>
       <c r="S53" s="57"/>
       <c r="T53" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ioo(\d)/i${1}oo》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ioo(\d)/》i${1}oo/</v>
       </c>
     </row>
     <row r="54" spans="1:20" ht="27.75" thickBot="1">
@@ -28437,28 +28445,28 @@
         <v>eng</v>
       </c>
       <c r="M54" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>o</v>
+      </c>
+      <c r="O54" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>o</v>
-      </c>
-      <c r="O54" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>eng(\d)</v>
       </c>
       <c r="P54" s="135" t="s">
         <v>1206</v>
       </c>
       <c r="Q54" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R54" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>e${1}ng</v>
+        <f t="shared" si="4"/>
+        <v>》e${1}ng</v>
       </c>
       <c r="S54" s="57"/>
       <c r="T54" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》eng(\d)/e${1}ng》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》eng(\d)/》e${1}ng/</v>
       </c>
     </row>
     <row r="55" spans="1:20" ht="27.75" thickBot="1">
@@ -28501,28 +28509,28 @@
         <v>ee</v>
       </c>
       <c r="M55" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ɑe</v>
+      </c>
+      <c r="O55" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ɑe</v>
-      </c>
-      <c r="O55" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ee(\d)</v>
       </c>
       <c r="P55" s="135" t="s">
         <v>1206</v>
       </c>
       <c r="Q55" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R55" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>e${1}e</v>
+        <f t="shared" si="4"/>
+        <v>》e${1}e</v>
       </c>
       <c r="S55" s="57"/>
       <c r="T55" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ee(\d)/e${1}e》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ee(\d)/》e${1}e/</v>
       </c>
     </row>
     <row r="56" spans="1:20" ht="27.75" thickBot="1">
@@ -28568,28 +28576,28 @@
         <v>ah</v>
       </c>
       <c r="M56" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ɑh</v>
+      </c>
+      <c r="O56" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ɑh</v>
-      </c>
-      <c r="O56" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ah(\d)</v>
       </c>
       <c r="P56" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q56" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R56" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>a${1}h</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}h</v>
       </c>
       <c r="S56" s="57"/>
       <c r="T56" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ah(\d)/a${1}h》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ah(\d)/》a${1}h/</v>
       </c>
     </row>
     <row r="57" spans="1:20" ht="27.75" thickBot="1">
@@ -28635,28 +28643,28 @@
         <v>ai</v>
       </c>
       <c r="M57" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ai</v>
+      </c>
+      <c r="O57" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ai</v>
-      </c>
-      <c r="O57" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ai(\d)</v>
       </c>
       <c r="P57" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q57" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R57" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>a${1}i</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}i</v>
       </c>
       <c r="S57" s="57"/>
       <c r="T57" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ai(\d)/a${1}i》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ai(\d)/》a${1}i/</v>
       </c>
     </row>
     <row r="58" spans="1:20" ht="27.75" thickBot="1">
@@ -28702,28 +28710,28 @@
         <v>ak</v>
       </c>
       <c r="M58" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ɑk</v>
+      </c>
+      <c r="O58" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ɑk</v>
-      </c>
-      <c r="O58" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ak(\d)</v>
       </c>
       <c r="P58" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q58" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R58" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>a${1}k</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}k</v>
       </c>
       <c r="S58" s="57"/>
       <c r="T58" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ak(\d)/a${1}k》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ak(\d)/》a${1}k/</v>
       </c>
     </row>
     <row r="59" spans="1:20" ht="27.75" thickBot="1">
@@ -28769,28 +28777,28 @@
         <v>am</v>
       </c>
       <c r="M59" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ɑm</v>
+      </c>
+      <c r="O59" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ɑm</v>
-      </c>
-      <c r="O59" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>am(\d)</v>
       </c>
       <c r="P59" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q59" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R59" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>a${1}m</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}m</v>
       </c>
       <c r="S59" s="57"/>
       <c r="T59" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》am(\d)/a${1}m》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》am(\d)/》a${1}m/</v>
       </c>
     </row>
     <row r="60" spans="1:20" ht="27.75" thickBot="1">
@@ -28836,28 +28844,28 @@
         <v>an</v>
       </c>
       <c r="M60" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ɑn</v>
+      </c>
+      <c r="O60" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ɑn</v>
-      </c>
-      <c r="O60" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>an(\d)</v>
       </c>
       <c r="P60" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q60" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R60" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>a${1}n</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}n</v>
       </c>
       <c r="S60" s="57"/>
       <c r="T60" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》an(\d)/a${1}n》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》an(\d)/》a${1}n/</v>
       </c>
     </row>
     <row r="61" spans="1:20" ht="27.75" thickBot="1">
@@ -28903,28 +28911,28 @@
         <v>au</v>
       </c>
       <c r="M61" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ao</v>
+      </c>
+      <c r="O61" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ao</v>
-      </c>
-      <c r="O61" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>au(\d)</v>
       </c>
       <c r="P61" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q61" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R61" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>a${1}u</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}u</v>
       </c>
       <c r="S61" s="57"/>
       <c r="T61" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》au(\d)/a${1}u》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》au(\d)/》a${1}u/</v>
       </c>
     </row>
     <row r="62" spans="1:20" ht="27.75" thickBot="1">
@@ -28970,28 +28978,28 @@
         <v>ap</v>
       </c>
       <c r="M62" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ɑp</v>
+      </c>
+      <c r="O62" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ɑp</v>
-      </c>
-      <c r="O62" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ap(\d)</v>
       </c>
       <c r="P62" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q62" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R62" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>a${1}p</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}p</v>
       </c>
       <c r="S62" s="57"/>
       <c r="T62" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ap(\d)/a${1}p》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ap(\d)/》a${1}p/</v>
       </c>
     </row>
     <row r="63" spans="1:20" ht="27.75" thickBot="1">
@@ -29037,28 +29045,28 @@
         <v>at</v>
       </c>
       <c r="M63" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ɑt</v>
+      </c>
+      <c r="O63" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ɑt</v>
-      </c>
-      <c r="O63" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>at(\d)</v>
       </c>
       <c r="P63" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q63" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R63" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>a${1}t</v>
+        <f t="shared" si="4"/>
+        <v>》a${1}t</v>
       </c>
       <c r="S63" s="57"/>
       <c r="T63" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》at(\d)/a${1}t》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》at(\d)/》a${1}t/</v>
       </c>
     </row>
     <row r="64" spans="1:20" ht="27.75" thickBot="1">
@@ -29104,28 +29112,28 @@
         <v>eh</v>
       </c>
       <c r="M64" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>eh</v>
+      </c>
+      <c r="O64" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>eh</v>
-      </c>
-      <c r="O64" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>eh(\d)</v>
       </c>
       <c r="P64" s="135" t="s">
         <v>1206</v>
       </c>
       <c r="Q64" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R64" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>e${1}h</v>
+        <f t="shared" si="4"/>
+        <v>》e${1}h</v>
       </c>
       <c r="S64" s="57"/>
       <c r="T64" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》eh(\d)/e${1}h》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》eh(\d)/》e${1}h/</v>
       </c>
     </row>
     <row r="65" spans="1:20" ht="27.75" thickBot="1">
@@ -29171,28 +29179,28 @@
         <v>ir</v>
       </c>
       <c r="M65" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>eu</v>
+      </c>
+      <c r="O65" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>eu</v>
-      </c>
-      <c r="O65" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ir(\d)</v>
       </c>
       <c r="P65" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q65" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R65" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>i${1}r</v>
+        <f t="shared" si="4"/>
+        <v>》i${1}r</v>
       </c>
       <c r="S65" s="57"/>
       <c r="T65" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ir(\d)/i${1}r》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ir(\d)/》i${1}r/</v>
       </c>
     </row>
     <row r="66" spans="1:20" ht="27.75" thickBot="1">
@@ -29238,28 +29246,28 @@
         <v>ia</v>
       </c>
       <c r="M66" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>iɑ</v>
+      </c>
+      <c r="O66" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>iɑ</v>
-      </c>
-      <c r="O66" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ia(\d)</v>
       </c>
       <c r="P66" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q66" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="R66" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>ia${1}</v>
+        <f t="shared" si="4"/>
+        <v>i》a${1}</v>
       </c>
       <c r="S66" s="57"/>
       <c r="T66" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ia(\d)/ia${1}》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ia(\d)/i》a${1}/</v>
       </c>
     </row>
     <row r="67" spans="1:20" ht="27.75" thickBot="1">
@@ -29305,28 +29313,28 @@
         <v>er</v>
       </c>
       <c r="M67" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ie</v>
+      </c>
+      <c r="O67" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ie</v>
-      </c>
-      <c r="O67" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>er(\d)</v>
       </c>
       <c r="P67" s="135" t="s">
         <v>1206</v>
       </c>
       <c r="Q67" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R67" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>e${1}r</v>
+        <f t="shared" si="4"/>
+        <v>》e${1}r</v>
       </c>
       <c r="S67" s="57"/>
       <c r="T67" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》er(\d)/e${1}r》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》er(\d)/》e${1}r/</v>
       </c>
     </row>
     <row r="68" spans="1:20" ht="27.75" thickBot="1">
@@ -29372,28 +29380,28 @@
         <v>ih</v>
       </c>
       <c r="M68" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v>ih</v>
+      </c>
+      <c r="O68" s="132" t="str">
         <f t="shared" si="1"/>
-        <v>ih</v>
-      </c>
-      <c r="O68" s="132" t="str">
-        <f t="shared" si="2"/>
         <v>ih(\d)</v>
       </c>
       <c r="P68" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q68" s="135">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R68" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>i${1}h</v>
+        <f t="shared" si="4"/>
+        <v>》i${1}h</v>
       </c>
       <c r="S68" s="57"/>
       <c r="T68" s="58" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    - xform/》ih(\d)/i${1}h》/</v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - xform/》ih(\d)/》i${1}h/</v>
       </c>
     </row>
     <row r="69" spans="1:20" ht="27.75" thickBot="1">
@@ -29439,28 +29447,28 @@
         <v>ik</v>
       </c>
       <c r="M69" s="59" t="str">
-        <f t="shared" ref="M69:M99" si="6">F69</f>
+        <f t="shared" ref="M69:M99" si="5">F69</f>
         <v>ik</v>
       </c>
       <c r="O69" s="132" t="str">
-        <f t="shared" ref="O69:O99" si="7" xml:space="preserve"> _xlfn.CONCAT(L69, "(\d)")</f>
+        <f t="shared" ref="O69:O99" si="6" xml:space="preserve"> _xlfn.CONCAT(L69, "(\d)")</f>
         <v>ik(\d)</v>
       </c>
       <c r="P69" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q69" s="135">
-        <f t="shared" ref="Q69:Q99" si="8" xml:space="preserve"> IFERROR( IF(P69="", "", SEARCH(P69, $L69)), "")</f>
+        <f t="shared" ref="Q69:Q99" si="7" xml:space="preserve"> IFERROR( IF(P69="", "", SEARCH(P69, $L69)), "")</f>
         <v>1</v>
       </c>
       <c r="R69" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>i${1}k</v>
+        <f t="shared" si="4"/>
+        <v>》i${1}k</v>
       </c>
       <c r="S69" s="57"/>
       <c r="T69" s="58" t="str">
-        <f t="shared" ref="T69:T99" si="9" xml:space="preserve"> IF(AND(M69&lt;&gt;"", L69&lt;&gt;""), "    - xform/》" &amp; O69 &amp;  "/"  &amp; R69 &amp;  "》/", "")</f>
-        <v xml:space="preserve">    - xform/》ik(\d)/i${1}k》/</v>
+        <f t="shared" ref="T69:T99" si="8" xml:space="preserve"> IF(AND(M69&lt;&gt;"", L69&lt;&gt;""), "    - xform/》" &amp; O69 &amp;  "/"  &amp; R69 &amp;  "/", "")</f>
+        <v xml:space="preserve">    - xform/》ik(\d)/》i${1}k/</v>
       </c>
     </row>
     <row r="70" spans="1:20" ht="27.75" thickBot="1">
@@ -29506,28 +29514,28 @@
         <v>im</v>
       </c>
       <c r="M70" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>im</v>
+      </c>
+      <c r="O70" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>im</v>
-      </c>
-      <c r="O70" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>im(\d)</v>
       </c>
       <c r="P70" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q70" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R70" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>i${1}m</v>
+        <f t="shared" ref="R70:R99" si="9" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(L70,Q70-1), "》", MID(L70,Q70,1), "${1}", RIGHT(L70, LEN(L70)-Q70)), "" )</f>
+        <v>》i${1}m</v>
       </c>
       <c r="S70" s="57"/>
       <c r="T70" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》im(\d)/i${1}m》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》im(\d)/》i${1}m/</v>
       </c>
     </row>
     <row r="71" spans="1:20" ht="27.75" thickBot="1">
@@ -29573,28 +29581,28 @@
         <v>in</v>
       </c>
       <c r="M71" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>in</v>
+      </c>
+      <c r="O71" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>in</v>
-      </c>
-      <c r="O71" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>in(\d)</v>
       </c>
       <c r="P71" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q71" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R71" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>i${1}n</v>
+        <f t="shared" si="9"/>
+        <v>》i${1}n</v>
       </c>
       <c r="S71" s="57"/>
       <c r="T71" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》in(\d)/i${1}n》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》in(\d)/》i${1}n/</v>
       </c>
     </row>
     <row r="72" spans="1:20" ht="27.75" thickBot="1">
@@ -29640,28 +29648,28 @@
         <v>io</v>
       </c>
       <c r="M72" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>io</v>
+      </c>
+      <c r="O72" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>io</v>
-      </c>
-      <c r="O72" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>io(\d)</v>
       </c>
       <c r="P72" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q72" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R72" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>i${1}o</v>
+        <f t="shared" si="9"/>
+        <v>》i${1}o</v>
       </c>
       <c r="S72" s="57"/>
       <c r="T72" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》io(\d)/i${1}o》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》io(\d)/》i${1}o/</v>
       </c>
     </row>
     <row r="73" spans="1:20" ht="27.75" thickBot="1">
@@ -29707,28 +29715,28 @@
         <v>ip</v>
       </c>
       <c r="M73" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>ip</v>
+      </c>
+      <c r="O73" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>ip</v>
-      </c>
-      <c r="O73" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>ip(\d)</v>
       </c>
       <c r="P73" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q73" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R73" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>i${1}p</v>
+        <f t="shared" si="9"/>
+        <v>》i${1}p</v>
       </c>
       <c r="S73" s="57"/>
       <c r="T73" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》ip(\d)/i${1}p》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ip(\d)/》i${1}p/</v>
       </c>
     </row>
     <row r="74" spans="1:20" ht="27.75" thickBot="1">
@@ -29774,28 +29782,28 @@
         <v>it</v>
       </c>
       <c r="M74" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>it</v>
+      </c>
+      <c r="O74" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>it</v>
-      </c>
-      <c r="O74" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>it(\d)</v>
       </c>
       <c r="P74" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q74" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R74" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>i${1}t</v>
+        <f t="shared" si="9"/>
+        <v>》i${1}t</v>
       </c>
       <c r="S74" s="57"/>
       <c r="T74" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》it(\d)/i${1}t》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》it(\d)/》i${1}t/</v>
       </c>
     </row>
     <row r="75" spans="1:20" ht="27.75" thickBot="1">
@@ -29841,28 +29849,28 @@
         <v>iu</v>
       </c>
       <c r="M75" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>iu</v>
+      </c>
+      <c r="O75" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>iu</v>
-      </c>
-      <c r="O75" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>iu(\d)</v>
       </c>
       <c r="P75" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q75" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R75" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>i${1}u</v>
+        <f t="shared" si="9"/>
+        <v>》i${1}u</v>
       </c>
       <c r="S75" s="57"/>
       <c r="T75" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》iu(\d)/i${1}u》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iu(\d)/》i${1}u/</v>
       </c>
     </row>
     <row r="76" spans="1:20" ht="27.75" thickBot="1">
@@ -29908,28 +29916,28 @@
         <v>mh</v>
       </c>
       <c r="M76" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>mh</v>
+      </c>
+      <c r="O76" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>mh</v>
-      </c>
-      <c r="O76" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>mh(\d)</v>
       </c>
       <c r="P76" s="135" t="s">
         <v>1359</v>
       </c>
       <c r="Q76" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R76" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>m${1}h</v>
+        <f t="shared" si="9"/>
+        <v>》m${1}h</v>
       </c>
       <c r="S76" s="57"/>
       <c r="T76" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》mh(\d)/m${1}h》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》mh(\d)/》m${1}h/</v>
       </c>
     </row>
     <row r="77" spans="1:20" ht="27.75" thickBot="1">
@@ -29975,28 +29983,28 @@
         <v>ng</v>
       </c>
       <c r="M77" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>ng</v>
+      </c>
+      <c r="O77" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>ng</v>
-      </c>
-      <c r="O77" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>ng(\d)</v>
       </c>
       <c r="P77" s="135" t="s">
         <v>1358</v>
       </c>
       <c r="Q77" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R77" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>n${1}g</v>
+        <f t="shared" si="9"/>
+        <v>》n${1}g</v>
       </c>
       <c r="S77" s="57"/>
       <c r="T77" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》ng(\d)/n${1}g》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ng(\d)/》n${1}g/</v>
       </c>
     </row>
     <row r="78" spans="1:20" ht="27.75" thickBot="1">
@@ -30042,28 +30050,28 @@
         <v>oh</v>
       </c>
       <c r="M78" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>oh</v>
+      </c>
+      <c r="O78" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>oh</v>
-      </c>
-      <c r="O78" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>oh(\d)</v>
       </c>
       <c r="P78" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q78" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R78" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>o${1}h</v>
+        <f t="shared" si="9"/>
+        <v>》o${1}h</v>
       </c>
       <c r="S78" s="57"/>
       <c r="T78" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》oh(\d)/o${1}h》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》oh(\d)/》o${1}h/</v>
       </c>
     </row>
     <row r="79" spans="1:20" ht="27.75" thickBot="1">
@@ -30109,28 +30117,28 @@
         <v>ok</v>
       </c>
       <c r="M79" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>ok</v>
+      </c>
+      <c r="O79" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>ok</v>
-      </c>
-      <c r="O79" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>ok(\d)</v>
       </c>
       <c r="P79" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q79" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R79" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>o${1}k</v>
+        <f t="shared" si="9"/>
+        <v>》o${1}k</v>
       </c>
       <c r="S79" s="57"/>
       <c r="T79" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》ok(\d)/o${1}k》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ok(\d)/》o${1}k/</v>
       </c>
     </row>
     <row r="80" spans="1:20" ht="27.75" thickBot="1">
@@ -30176,28 +30184,28 @@
         <v>oo</v>
       </c>
       <c r="M80" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>oo</v>
+      </c>
+      <c r="O80" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>oo</v>
-      </c>
-      <c r="O80" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>oo(\d)</v>
       </c>
       <c r="P80" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q80" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R80" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>o${1}o</v>
+        <f t="shared" si="9"/>
+        <v>》o${1}o</v>
       </c>
       <c r="S80" s="57"/>
       <c r="T80" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》oo(\d)/o${1}o》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》oo(\d)/》o${1}o/</v>
       </c>
     </row>
     <row r="81" spans="1:20" ht="27.75" thickBot="1">
@@ -30243,28 +30251,28 @@
         <v>op</v>
       </c>
       <c r="M81" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>op</v>
+      </c>
+      <c r="O81" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>op</v>
-      </c>
-      <c r="O81" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>op(\d)</v>
       </c>
       <c r="P81" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q81" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R81" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>o${1}p</v>
+        <f t="shared" si="9"/>
+        <v>》o${1}p</v>
       </c>
       <c r="S81" s="57"/>
       <c r="T81" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》op(\d)/o${1}p》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》op(\d)/》o${1}p/</v>
       </c>
     </row>
     <row r="82" spans="1:20" ht="27.75" thickBot="1">
@@ -30310,28 +30318,28 @@
         <v>ua</v>
       </c>
       <c r="M82" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>uɑ</v>
+      </c>
+      <c r="O82" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>uɑ</v>
-      </c>
-      <c r="O82" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>ua(\d)</v>
       </c>
       <c r="P82" s="135" t="s">
         <v>1252</v>
       </c>
       <c r="Q82" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R82" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>u${1}a</v>
+        <f t="shared" si="9"/>
+        <v>》u${1}a</v>
       </c>
       <c r="S82" s="57"/>
       <c r="T82" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》ua(\d)/u${1}a》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ua(\d)/》u${1}a/</v>
       </c>
     </row>
     <row r="83" spans="1:20" ht="27.75" thickBot="1">
@@ -30377,28 +30385,28 @@
         <v>ue</v>
       </c>
       <c r="M83" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>ue</v>
+      </c>
+      <c r="O83" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>ue</v>
-      </c>
-      <c r="O83" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>ue(\d)</v>
       </c>
       <c r="P83" s="135" t="s">
         <v>1252</v>
       </c>
       <c r="Q83" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R83" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>u${1}e</v>
+        <f t="shared" si="9"/>
+        <v>》u${1}e</v>
       </c>
       <c r="S83" s="57"/>
       <c r="T83" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》ue(\d)/u${1}e》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ue(\d)/》u${1}e/</v>
       </c>
     </row>
     <row r="84" spans="1:20" ht="27.75" thickBot="1">
@@ -30444,28 +30452,28 @@
         <v>uh</v>
       </c>
       <c r="M84" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>uh</v>
+      </c>
+      <c r="O84" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>uh</v>
-      </c>
-      <c r="O84" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>uh(\d)</v>
       </c>
       <c r="P84" s="135" t="s">
         <v>1252</v>
       </c>
       <c r="Q84" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R84" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>u${1}h</v>
+        <f t="shared" si="9"/>
+        <v>》u${1}h</v>
       </c>
       <c r="S84" s="57"/>
       <c r="T84" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》uh(\d)/u${1}h》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》uh(\d)/》u${1}h/</v>
       </c>
     </row>
     <row r="85" spans="1:20" ht="27.75" thickBot="1">
@@ -30511,28 +30519,28 @@
         <v>ui</v>
       </c>
       <c r="M85" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>ui</v>
+      </c>
+      <c r="O85" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>ui</v>
-      </c>
-      <c r="O85" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>ui(\d)</v>
       </c>
       <c r="P85" s="135" t="s">
         <v>1252</v>
       </c>
       <c r="Q85" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R85" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>u${1}i</v>
+        <f t="shared" si="9"/>
+        <v>》u${1}i</v>
       </c>
       <c r="S85" s="57"/>
       <c r="T85" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》ui(\d)/u${1}i》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ui(\d)/》u${1}i/</v>
       </c>
     </row>
     <row r="86" spans="1:20" ht="27.75" thickBot="1">
@@ -30578,28 +30586,28 @@
         <v>un</v>
       </c>
       <c r="M86" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>un</v>
+      </c>
+      <c r="O86" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>un</v>
-      </c>
-      <c r="O86" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>un(\d)</v>
       </c>
       <c r="P86" s="135" t="s">
         <v>1252</v>
       </c>
       <c r="Q86" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R86" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>u${1}n</v>
+        <f t="shared" si="9"/>
+        <v>》u${1}n</v>
       </c>
       <c r="S86" s="57"/>
       <c r="T86" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》un(\d)/u${1}n》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》un(\d)/》u${1}n/</v>
       </c>
     </row>
     <row r="87" spans="1:20" ht="27.75" thickBot="1">
@@ -30645,28 +30653,28 @@
         <v>ut</v>
       </c>
       <c r="M87" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>ut</v>
+      </c>
+      <c r="O87" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>ut</v>
-      </c>
-      <c r="O87" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>ut(\d)</v>
       </c>
       <c r="P87" s="135" t="s">
         <v>1252</v>
       </c>
       <c r="Q87" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R87" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>u${1}t</v>
+        <f t="shared" si="9"/>
+        <v>》u${1}t</v>
       </c>
       <c r="S87" s="57"/>
       <c r="T87" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》ut(\d)/u${1}t》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ut(\d)/》u${1}t/</v>
       </c>
     </row>
     <row r="88" spans="1:20" ht="27.75" thickBot="1">
@@ -30712,28 +30720,28 @@
         <v>om</v>
       </c>
       <c r="M88" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="O88" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="O88" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>om(\d)</v>
       </c>
       <c r="P88" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q88" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R88" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>o${1}m</v>
+        <f t="shared" si="9"/>
+        <v>》o${1}m</v>
       </c>
       <c r="S88" s="57"/>
       <c r="T88" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》om(\d)/o${1}m》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》om(\d)/》o${1}m/</v>
       </c>
     </row>
     <row r="89" spans="1:20" ht="27.75" thickBot="1">
@@ -30780,27 +30788,26 @@
         <v>ei</v>
       </c>
       <c r="M89" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O89" s="132" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O89" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>ei(\d)</v>
       </c>
       <c r="P89" s="135" t="s">
         <v>1206</v>
       </c>
       <c r="Q89" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="R89" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>e${1}i</v>
+      <c r="R89" s="132" t="s">
+        <v>1360</v>
       </c>
       <c r="S89" s="57"/>
       <c r="T89" s="58" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -30848,27 +30855,26 @@
         <v>ou</v>
       </c>
       <c r="M90" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O90" s="132" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O90" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>ou(\d)</v>
       </c>
       <c r="P90" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q90" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="R90" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>o${1}u</v>
+      <c r="R90" s="132" t="s">
+        <v>1361</v>
       </c>
       <c r="S90" s="57"/>
       <c r="T90" s="58" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -30916,27 +30922,27 @@
         <v>ae</v>
       </c>
       <c r="M91" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O91" s="132" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O91" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>ae(\d)</v>
       </c>
       <c r="P91" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q91" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R91" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>a${1}e</v>
+        <f t="shared" si="9"/>
+        <v>》a${1}e</v>
       </c>
       <c r="S91" s="57"/>
       <c r="T91" s="58" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -30984,28 +30990,28 @@
         <v>eu</v>
       </c>
       <c r="M92" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>i</v>
+      </c>
+      <c r="O92" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>i</v>
-      </c>
-      <c r="O92" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>eu(\d)</v>
       </c>
       <c r="P92" s="135" t="s">
         <v>1206</v>
       </c>
       <c r="Q92" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R92" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>e${1}u</v>
+        <f t="shared" si="9"/>
+        <v>》e${1}u</v>
       </c>
       <c r="S92" s="57"/>
       <c r="T92" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》eu(\d)/e${1}u》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》eu(\d)/》e${1}u/</v>
       </c>
     </row>
     <row r="93" spans="1:20" ht="27.75" thickBot="1">
@@ -31052,28 +31058,28 @@
         <v>ek</v>
       </c>
       <c r="M93" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>u</v>
+      </c>
+      <c r="O93" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>u</v>
-      </c>
-      <c r="O93" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>ek(\d)</v>
       </c>
       <c r="P93" s="135" t="s">
         <v>1206</v>
       </c>
       <c r="Q93" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R93" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>e${1}k</v>
+        <f t="shared" si="9"/>
+        <v>》e${1}k</v>
       </c>
       <c r="S93" s="57"/>
       <c r="T93" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》ek(\d)/e${1}k》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ek(\d)/》e${1}k/</v>
       </c>
     </row>
     <row r="94" spans="1:20" ht="27.75" thickBot="1">
@@ -31119,28 +31125,28 @@
         <v>a</v>
       </c>
       <c r="M94" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>ɑ</v>
+      </c>
+      <c r="O94" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>ɑ</v>
-      </c>
-      <c r="O94" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>a(\d)</v>
       </c>
       <c r="P94" s="135" t="s">
         <v>1253</v>
       </c>
       <c r="Q94" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R94" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>a${1}</v>
+        <f t="shared" si="9"/>
+        <v>》a${1}</v>
       </c>
       <c r="S94" s="57"/>
       <c r="T94" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》a(\d)/a${1}》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》a(\d)/》a${1}/</v>
       </c>
     </row>
     <row r="95" spans="1:20" ht="27.75" thickBot="1">
@@ -31186,28 +31192,28 @@
         <v>e</v>
       </c>
       <c r="M95" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>e</v>
+      </c>
+      <c r="O95" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>e</v>
-      </c>
-      <c r="O95" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>e(\d)</v>
       </c>
       <c r="P95" s="135" t="s">
         <v>1206</v>
       </c>
       <c r="Q95" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R95" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>e${1}</v>
+        <f t="shared" si="9"/>
+        <v>》e${1}</v>
       </c>
       <c r="S95" s="57"/>
       <c r="T95" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》e(\d)/e${1}》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》e(\d)/》e${1}/</v>
       </c>
     </row>
     <row r="96" spans="1:20" ht="27.75" thickBot="1">
@@ -31253,28 +31259,28 @@
         <v>i</v>
       </c>
       <c r="M96" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>i</v>
+      </c>
+      <c r="O96" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>i</v>
-      </c>
-      <c r="O96" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>i(\d)</v>
       </c>
       <c r="P96" s="135" t="s">
         <v>1254</v>
       </c>
       <c r="Q96" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R96" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>i${1}</v>
+        <f t="shared" si="9"/>
+        <v>》i${1}</v>
       </c>
       <c r="S96" s="57"/>
       <c r="T96" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》i(\d)/i${1}》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》i(\d)/》i${1}/</v>
       </c>
     </row>
     <row r="97" spans="1:20" ht="27.75" thickBot="1">
@@ -31320,28 +31326,28 @@
         <v>m</v>
       </c>
       <c r="M97" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>m</v>
+      </c>
+      <c r="O97" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>m</v>
-      </c>
-      <c r="O97" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>m(\d)</v>
       </c>
       <c r="P97" s="135" t="s">
         <v>1359</v>
       </c>
       <c r="Q97" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R97" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>m${1}</v>
+        <f t="shared" si="9"/>
+        <v>》m${1}</v>
       </c>
       <c r="S97" s="57"/>
       <c r="T97" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》m(\d)/m${1}》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》m(\d)/》m${1}/</v>
       </c>
     </row>
     <row r="98" spans="1:20" ht="27.75" thickBot="1">
@@ -31387,28 +31393,28 @@
         <v>o</v>
       </c>
       <c r="M98" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>o</v>
+      </c>
+      <c r="O98" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>o</v>
-      </c>
-      <c r="O98" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>o(\d)</v>
       </c>
       <c r="P98" s="135" t="s">
         <v>1241</v>
       </c>
       <c r="Q98" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R98" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>o${1}</v>
+        <f t="shared" si="9"/>
+        <v>》o${1}</v>
       </c>
       <c r="S98" s="57"/>
       <c r="T98" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》o(\d)/o${1}》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》o(\d)/》o${1}/</v>
       </c>
     </row>
     <row r="99" spans="1:20" ht="27.75" thickBot="1">
@@ -31454,28 +31460,28 @@
         <v>u</v>
       </c>
       <c r="M99" s="59" t="str">
+        <f t="shared" si="5"/>
+        <v>u</v>
+      </c>
+      <c r="O99" s="132" t="str">
         <f t="shared" si="6"/>
-        <v>u</v>
-      </c>
-      <c r="O99" s="132" t="str">
-        <f t="shared" si="7"/>
         <v>u(\d)</v>
       </c>
       <c r="P99" s="135" t="s">
         <v>1252</v>
       </c>
       <c r="Q99" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R99" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>u${1}</v>
+        <f t="shared" si="9"/>
+        <v>》u${1}</v>
       </c>
       <c r="S99" s="57"/>
       <c r="T99" s="58" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/》u(\d)/u${1}》/</v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》u(\d)/》u${1}/</v>
       </c>
     </row>
     <row r="103" spans="1:20">

--- a/docs/101_聲韻調對照表.xlsx
+++ b/docs/101_聲韻調對照表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105D5607-C4BD-4BC1-92BD-9EC4D288CD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51485D1-52C3-4438-871B-9F6CA02D7349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="811" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="811" activeTab="1" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
   </bookViews>
   <sheets>
     <sheet name="【聲】聲母對照表" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7424" uniqueCount="2260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7532" uniqueCount="2321">
   <si>
     <t>識別號</t>
   </si>
@@ -7976,6 +7976,189 @@
   <si>
     <t>:</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>台語注音</t>
+  </si>
+  <si>
+    <t>ㄖ</t>
+  </si>
+  <si>
+    <t>ㄙ</t>
+  </si>
+  <si>
+    <t>ㄪ</t>
+  </si>
+  <si>
+    <t>ㄘ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⁰ㄫ </t>
+  </si>
+  <si>
+    <t>ㄨㄉ</t>
+  </si>
+  <si>
+    <t>ㄧㄚㄉ</t>
+  </si>
+  <si>
+    <t>ㄧㄇ</t>
+  </si>
+  <si>
+    <t>ㄧㄅ</t>
+  </si>
+  <si>
+    <t>ㄝㄏ</t>
+  </si>
+  <si>
+    <t>ㄚㄉ</t>
+  </si>
+  <si>
+    <t>ㄛㄥ</t>
+  </si>
+  <si>
+    <t>ㄛㄍ</t>
+  </si>
+  <si>
+    <t>ㄨㄞㄏ</t>
+  </si>
+  <si>
+    <t>ㄧㄍ</t>
+  </si>
+  <si>
+    <t>ㄨㄚㄉ</t>
+  </si>
+  <si>
+    <t>ㄛ</t>
+  </si>
+  <si>
+    <t>ㄧㄠㄏ</t>
+  </si>
+  <si>
+    <t>ㄧㄛㄥ</t>
+  </si>
+  <si>
+    <t>ㄧㄛㄍ</t>
+  </si>
+  <si>
+    <t>ㄜㄏ</t>
+  </si>
+  <si>
+    <t>ㄧㄉ</t>
+  </si>
+  <si>
+    <t>ㄧㄚㄍ</t>
+  </si>
+  <si>
+    <t>ㄚㄇ</t>
+  </si>
+  <si>
+    <t>ㄚㄅ</t>
+  </si>
+  <si>
+    <t>ㄨㄚㄏ</t>
+  </si>
+  <si>
+    <t>ㄚㄍ</t>
+  </si>
+  <si>
+    <t>ㄧㄚㄇ</t>
+  </si>
+  <si>
+    <t>ㄧㄚㄅ</t>
+  </si>
+  <si>
+    <t>ㄠㄏ</t>
+  </si>
+  <si>
+    <t>ㄧㄚㄏ</t>
+  </si>
+  <si>
+    <t>ㄨㄝ</t>
+  </si>
+  <si>
+    <t>ㄨㄝㄏ</t>
+  </si>
+  <si>
+    <t>⁰ㄚ</t>
+  </si>
+  <si>
+    <t>⁰ㄚㄏ</t>
+  </si>
+  <si>
+    <t>ㄨㄏ</t>
+  </si>
+  <si>
+    <t>ㄚㄏ</t>
+  </si>
+  <si>
+    <t>ㄧㄏ</t>
+  </si>
+  <si>
+    <t>⁰ㄝ</t>
+  </si>
+  <si>
+    <t>⁰ㄝㄏ</t>
+  </si>
+  <si>
+    <t>⁰ㄨㄧ</t>
+  </si>
+  <si>
+    <t>ㄧㄜㄏ</t>
+  </si>
+  <si>
+    <t>⁰ㄧ</t>
+  </si>
+  <si>
+    <t>⁰ㄧㄏ</t>
+  </si>
+  <si>
+    <t>⁰ㄧㄛ</t>
+  </si>
+  <si>
+    <t>⁰ㄧㄚ</t>
+  </si>
+  <si>
+    <t>⁰ㄨㄚ</t>
+  </si>
+  <si>
+    <t>⁰ㄞ</t>
+  </si>
+  <si>
+    <t>⁰ㄛ</t>
+  </si>
+  <si>
+    <t>ㄨㄚㄍ</t>
+  </si>
+  <si>
+    <t>⁰ㄨㄞ</t>
+  </si>
+  <si>
+    <t>⁰ㄨㄞㄏ</t>
+  </si>
+  <si>
+    <t>⁰ㄨㄝ</t>
+  </si>
+  <si>
+    <t>⁰ㄧㄠ</t>
+  </si>
+  <si>
+    <t>⁰ㄧㄠㄏ</t>
+  </si>
+  <si>
+    <t>ㄛㄇ</t>
+  </si>
+  <si>
+    <t>ㄛㄅ</t>
+  </si>
+  <si>
+    <t>⁰ㄠ</t>
+  </si>
+  <si>
+    <t>⁰ㄛㄏ</t>
+  </si>
+  <si>
+    <t>⁰ㄧㆫ</t>
   </si>
 </sst>
 </file>
@@ -9353,17 +9536,17 @@
     <xf numFmtId="0" fontId="91" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -9373,84 +9556,7 @@
     <cellStyle name="一般 4" xfId="4" xr:uid="{E932D2E5-AF16-4FFA-AB0C-5F7E179E4D03}"/>
     <cellStyle name="一般 5" xfId="2" xr:uid="{8C9CBB70-72B8-491C-A1A5-535BA1FE1D69}"/>
   </cellStyles>
-  <dxfs count="34">
-    <dxf>
-      <font>
-        <sz val="24"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-        <name val="霞鶩文楷等寬 TC Medium"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="35">
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -9938,6 +10044,101 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <sz val="24"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+        <name val="霞鶩文楷等寬 TC Medium"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -10105,50 +10306,51 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{771C3941-9899-48C4-8E14-367017F7B2F5}" name="韻母對照表" displayName="韻母對照表" ref="A1:M85" totalsRowShown="0" headerRowDxfId="33" headerRowBorderDxfId="32" tableBorderDxfId="31" totalsRowBorderDxfId="30">
-  <autoFilter ref="A1:M85" xr:uid="{771C3941-9899-48C4-8E14-367017F7B2F5}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{93BCA6A2-508B-467B-95D1-473C97CCD52B}" name="識別號" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{C4E57A92-27A9-46F6-A864-9668B62AB3D8}" name="國際音標" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{D04A8FC9-DCA4-4643-AE3B-824F465B8E3A}" name="台羅拼音" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{DA98A1A1-49CA-4EC1-91D5-BF45045A4B18}" name="台語音標" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{E8D82139-523B-47F7-B0CC-47FDC35BBF0B}" name="注音二式" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{BDA4D6F0-BBAC-44DF-85B3-15A86E2ED416}" name="閩拼方案" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{972A94F9-A940-4172-AB75-0BE33372A5A6}" name="白話字" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{88460F28-F486-4EB3-974F-039F84D0E83A}" name="方音符號" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{8C99734F-A142-4FBD-96DD-463C060588A5}" name="漢字例" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{80F0C42C-C2BD-4707-8BE9-49A90C7647AB}" name="十五音" dataDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{77E72489-4845-4BE7-807E-50EDB35447E7}" name="十五音序" dataDxfId="23"/>
-    <tableColumn id="12" xr3:uid="{4D0E40DE-9C66-4BA2-B18D-2F564923928D}" name="舒促聲" dataDxfId="22"/>
-    <tableColumn id="13" xr3:uid="{1E5A033C-A3E4-47B2-8D3D-334C23BE852B}" name="十五音識別碼" dataDxfId="21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{771C3941-9899-48C4-8E14-367017F7B2F5}" name="韻母對照表" displayName="韻母對照表" ref="A1:N85" totalsRowShown="0" headerRowDxfId="34" headerRowBorderDxfId="33" tableBorderDxfId="32" totalsRowBorderDxfId="31">
+  <autoFilter ref="A1:N85" xr:uid="{771C3941-9899-48C4-8E14-367017F7B2F5}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{93BCA6A2-508B-467B-95D1-473C97CCD52B}" name="識別號" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{C4E57A92-27A9-46F6-A864-9668B62AB3D8}" name="國際音標" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{D04A8FC9-DCA4-4643-AE3B-824F465B8E3A}" name="台羅拼音" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{DA98A1A1-49CA-4EC1-91D5-BF45045A4B18}" name="台語音標" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{E8D82139-523B-47F7-B0CC-47FDC35BBF0B}" name="注音二式" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{BDA4D6F0-BBAC-44DF-85B3-15A86E2ED416}" name="閩拼方案" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{972A94F9-A940-4172-AB75-0BE33372A5A6}" name="白話字" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{88460F28-F486-4EB3-974F-039F84D0E83A}" name="方音符號" dataDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{EF2755BF-6678-4CD8-B300-0D0325E9E0D0}" name="台語注音" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{8C99734F-A142-4FBD-96DD-463C060588A5}" name="漢字例" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{80F0C42C-C2BD-4707-8BE9-49A90C7647AB}" name="十五音" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{77E72489-4845-4BE7-807E-50EDB35447E7}" name="十五音序" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{4D0E40DE-9C66-4BA2-B18D-2F564923928D}" name="舒促聲" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{1E5A033C-A3E4-47B2-8D3D-334C23BE852B}" name="十五音識別碼" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CFF90B7A-D09E-43B2-979B-7CD1EE35DCEF}" name="韻母對照表3" displayName="韻母對照表3" ref="A1:M85" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CFF90B7A-D09E-43B2-979B-7CD1EE35DCEF}" name="韻母對照表3" displayName="韻母對照表3" ref="A1:M85" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="A1:M85" xr:uid="{771C3941-9899-48C4-8E14-367017F7B2F5}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{C10E80BA-9FEE-411B-A2E1-0B8D75C43A73}" name="識別號" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{BDE2F94E-9AD0-4497-B0A4-0887F343995C}" name="十五音" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{1BB80AC9-0E65-4250-97F0-4C9BF936F6F4}" name="漢字例" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{FF3D3154-85AC-43FE-9B6E-613CB6837684}" name="方音符號" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{76F226E4-4708-40A7-849D-3CC6919D3693}" name="台語音標" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{B2037F3B-8888-4074-8870-6B45341F0C3A}" name="國際音標" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{C10E80BA-9FEE-411B-A2E1-0B8D75C43A73}" name="識別號" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{BDE2F94E-9AD0-4497-B0A4-0887F343995C}" name="十五音" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{1BB80AC9-0E65-4250-97F0-4C9BF936F6F4}" name="漢字例" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{FF3D3154-85AC-43FE-9B6E-613CB6837684}" name="方音符號" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{76F226E4-4708-40A7-849D-3CC6919D3693}" name="台語音標" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{B2037F3B-8888-4074-8870-6B45341F0C3A}" name="國際音標" dataDxfId="8">
       <calculatedColumnFormula array="1" xml:space="preserve"> IF(韻母對照表3[[#This Row],[舒促聲]]="舒聲", INDEX(十五音韻母!$G$3:$G$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)), INDEX(十五音韻母!$H$3:$H$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8FF1DC7C-D8AD-4071-B26D-6830788BB67A}" name="閩拼方案" dataDxfId="10">
+    <tableColumn id="10" xr3:uid="{8FF1DC7C-D8AD-4071-B26D-6830788BB67A}" name="閩拼方案" dataDxfId="7">
       <calculatedColumnFormula array="1" xml:space="preserve"> IF(韻母對照表3[[#This Row],[舒促聲]]="舒聲", INDEX(十五音韻母!$I$3:$I$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)), INDEX(十五音韻母!$J$3:$J$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{76F2259B-CA5E-44D6-86F0-A1217D200D54}" name="台羅拼音" dataDxfId="9">
+    <tableColumn id="7" xr3:uid="{76F2259B-CA5E-44D6-86F0-A1217D200D54}" name="台羅拼音" dataDxfId="6">
       <calculatedColumnFormula array="1" xml:space="preserve"> IF(韻母對照表3[[#This Row],[舒促聲]]="舒聲", INDEX(十五音韻母!$K$3:$K$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)), INDEX(十五音韻母!$L$3:$L$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DF4BA570-1408-41DB-8328-90FB8913B1DF}" name="注音二式" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{42E33940-E4F1-4C86-AD57-6236C50EBE40}" name="白話字" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{BE8C4436-8D84-475B-A5C6-C392918893AA}" name="十五音序" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{4D04DB9F-1246-4494-8D81-B2950125EC5B}" name="舒促聲" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{EB7195BB-541B-463D-BA37-EBE312BD24A4}" name="十五音識別碼" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{DF4BA570-1408-41DB-8328-90FB8913B1DF}" name="注音二式" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{42E33940-E4F1-4C86-AD57-6236C50EBE40}" name="白話字" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{BE8C4436-8D84-475B-A5C6-C392918893AA}" name="十五音序" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{4D04DB9F-1246-4494-8D81-B2950125EC5B}" name="舒促聲" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{EB7195BB-541B-463D-BA37-EBE312BD24A4}" name="十五音識別碼" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10491,14 +10693,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{619E8012-85E3-4410-BF6F-8322F40DAF24}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="25.5"/>
   <cols>
     <col min="1" max="1" width="6.4140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10524,16 +10726,19 @@
         <v>4</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>2260</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="29.25">
+    <row r="2" spans="1:12" ht="29.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -10558,15 +10763,18 @@
       <c r="H2" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" ht="29.25">
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" ht="29.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -10591,15 +10799,18 @@
       <c r="H3" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="29.25">
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="29.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -10624,15 +10835,18 @@
       <c r="H4" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" ht="29.25">
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="29.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -10657,15 +10871,18 @@
       <c r="H5" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" ht="29.25">
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" ht="29.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -10690,15 +10907,18 @@
       <c r="H6" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" ht="29.25">
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="29.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -10723,15 +10943,18 @@
       <c r="H7" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" ht="29.25">
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" ht="29.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -10756,15 +10979,18 @@
       <c r="H8" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" ht="29.25">
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" ht="29.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -10789,15 +11015,18 @@
       <c r="H9" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" ht="29.25">
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" ht="29.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -10822,15 +11051,18 @@
       <c r="H10" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="1" t="s">
+        <v>2261</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>557</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="K10" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" ht="29.25">
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" ht="29.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -10855,15 +11087,18 @@
       <c r="H11" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="1" t="s">
+        <v>2262</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" ht="29.25">
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="1:12" ht="29.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -10888,15 +11123,18 @@
       <c r="H12" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="J12" s="15" t="s">
         <v>566</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" ht="29.25">
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" ht="29.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -10921,15 +11159,18 @@
       <c r="H13" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="1" t="s">
+        <v>2263</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" ht="29.25">
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" ht="29.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -10954,15 +11195,18 @@
       <c r="H14" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" ht="29.25">
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" ht="29.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -10987,15 +11231,18 @@
       <c r="H15" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="1" t="s">
+        <v>2264</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" ht="29.25">
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:12" ht="29.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -11020,15 +11267,18 @@
       <c r="H16" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>583</v>
+      <c r="I16" s="1" t="s">
+        <v>585</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" ht="29.25">
+      <c r="K16" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="1:12" ht="29.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -11053,17 +11303,20 @@
       <c r="H17" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>586</v>
+      <c r="I17" s="1" t="s">
+        <v>587</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="K17" s="16" t="s">
+      <c r="K17" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="L17" s="16" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="29.25">
+    <row r="18" spans="1:12" ht="29.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -11088,17 +11341,20 @@
       <c r="H18" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>590</v>
+      <c r="I18" s="1" t="s">
+        <v>592</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="K18" s="19" t="s">
+      <c r="K18" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="L18" s="19" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="29.25">
+    <row r="19" spans="1:12" ht="29.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -11123,17 +11379,20 @@
       <c r="H19" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>595</v>
+      <c r="I19" s="1" t="s">
+        <v>2265</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="K19" s="19" t="s">
+      <c r="K19" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="L19" s="19" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="29.25">
+    <row r="20" spans="1:12" ht="29.25">
       <c r="A20" s="17">
         <v>19</v>
       </c>
@@ -11158,17 +11417,20 @@
       <c r="H20" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="I20" s="18" t="s">
+      <c r="I20" s="16" t="s">
+        <v>2261</v>
+      </c>
+      <c r="J20" s="18" t="s">
         <v>557</v>
       </c>
-      <c r="J20" s="18" t="s">
+      <c r="K20" s="18" t="s">
         <v>555</v>
       </c>
-      <c r="K20" s="19" t="s">
+      <c r="L20" s="19" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="29.25">
+    <row r="21" spans="1:12" ht="29.25">
       <c r="A21" s="17">
         <v>20</v>
       </c>
@@ -11193,17 +11455,20 @@
       <c r="H21" s="19" t="s">
         <v>607</v>
       </c>
-      <c r="I21" s="18" t="s">
+      <c r="I21" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="J21" s="18" t="s">
         <v>550</v>
       </c>
-      <c r="J21" s="18" t="s">
+      <c r="K21" s="18" t="s">
         <v>605</v>
       </c>
-      <c r="K21" s="19" t="s">
+      <c r="L21" s="19" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="29.25">
+    <row r="22" spans="1:12" ht="29.25">
       <c r="A22" s="17">
         <v>21</v>
       </c>
@@ -11228,17 +11493,20 @@
       <c r="H22" s="19" t="s">
         <v>613</v>
       </c>
-      <c r="I22" s="18" t="s">
+      <c r="I22" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="J22" s="18" t="s">
         <v>579</v>
       </c>
-      <c r="J22" s="18" t="s">
+      <c r="K22" s="18" t="s">
         <v>611</v>
       </c>
-      <c r="K22" s="19" t="s">
+      <c r="L22" s="19" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="29.25">
+    <row r="23" spans="1:12" ht="29.25">
       <c r="A23" s="17">
         <v>22</v>
       </c>
@@ -11263,13 +11531,16 @@
       <c r="H23" s="19" t="s">
         <v>619</v>
       </c>
-      <c r="I23" s="18" t="s">
+      <c r="I23" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="J23" s="18" t="s">
         <v>563</v>
       </c>
-      <c r="J23" s="18" t="s">
+      <c r="K23" s="18" t="s">
         <v>617</v>
       </c>
-      <c r="K23" s="19" t="s">
+      <c r="L23" s="19" t="s">
         <v>625</v>
       </c>
     </row>
@@ -31582,19 +31853,19 @@
   <sheetFormatPr defaultRowHeight="25.5"/>
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" thickBot="1">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="160" t="s">
         <v>936</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
-      <c r="J1" s="159"/>
-      <c r="K1" s="159"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
     </row>
     <row r="2" spans="1:11" ht="26.25" thickBot="1">
       <c r="A2" s="77" t="s">
@@ -32482,21 +32753,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42442B6C-5679-4370-9927-A55154F8A277}">
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr defaultRowHeight="26.25"/>
   <cols>
     <col min="1" max="1" width="7.33203125" customWidth="1"/>
     <col min="3" max="4" width="9.1640625" customWidth="1"/>
-    <col min="16" max="16" width="9.1640625" style="95" customWidth="1"/>
-    <col min="18" max="18" width="12.4140625" customWidth="1"/>
-    <col min="21" max="21" width="9.1640625" customWidth="1"/>
-    <col min="23" max="23" width="9.1640625" customWidth="1"/>
-    <col min="27" max="28" width="9.1640625" customWidth="1"/>
-    <col min="29" max="29" width="7.33203125" customWidth="1"/>
-    <col min="30" max="30" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="9.1640625" style="95" customWidth="1"/>
+    <col min="19" max="19" width="12.4140625" customWidth="1"/>
+    <col min="22" max="22" width="9.1640625" customWidth="1"/>
+    <col min="24" max="24" width="9.1640625" customWidth="1"/>
+    <col min="28" max="29" width="9.1640625" customWidth="1"/>
+    <col min="30" max="30" width="7.33203125" customWidth="1"/>
+    <col min="31" max="31" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="25.5">
+    <row r="1" spans="1:17" ht="25.5">
       <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
@@ -32522,23 +32793,26 @@
         <v>4</v>
       </c>
       <c r="I1" s="71" t="s">
+        <v>2260</v>
+      </c>
+      <c r="J1" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="71" t="s">
+      <c r="K1" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="71" t="s">
+      <c r="L1" s="71" t="s">
         <v>511</v>
       </c>
-      <c r="L1" s="71" t="s">
+      <c r="M1" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="72" t="s">
+      <c r="N1" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="P1"/>
-    </row>
-    <row r="2" spans="1:16" ht="29.25">
+      <c r="Q1"/>
+    </row>
+    <row r="2" spans="1:17" ht="29.25">
       <c r="A2" s="63">
         <v>1</v>
       </c>
@@ -32563,24 +32837,27 @@
       <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="64" t="s">
+      <c r="N2" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="P2"/>
-    </row>
-    <row r="3" spans="1:16" ht="29.25">
+      <c r="Q2"/>
+    </row>
+    <row r="3" spans="1:17" ht="29.25">
       <c r="A3" s="63">
         <v>2</v>
       </c>
@@ -32605,24 +32882,27 @@
       <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>2266</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="64" t="s">
+      <c r="N3" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="P3"/>
-    </row>
-    <row r="4" spans="1:16" ht="30">
+      <c r="Q3"/>
+    </row>
+    <row r="4" spans="1:17" ht="30">
       <c r="A4" s="63">
         <v>3</v>
       </c>
@@ -32647,24 +32927,27 @@
       <c r="H4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="64" t="s">
+      <c r="N4" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="P4"/>
-    </row>
-    <row r="5" spans="1:16" ht="30">
+      <c r="Q4"/>
+    </row>
+    <row r="5" spans="1:17" ht="30">
       <c r="A5" s="63">
         <v>4</v>
       </c>
@@ -32689,24 +32972,27 @@
       <c r="H5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="1" t="s">
+        <v>2267</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="64" t="s">
+      <c r="N5" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="P5"/>
-    </row>
-    <row r="6" spans="1:16" ht="29.25">
+      <c r="Q5"/>
+    </row>
+    <row r="6" spans="1:17" ht="29.25">
       <c r="A6" s="63">
         <v>5</v>
       </c>
@@ -32731,24 +33017,27 @@
       <c r="H6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="1" t="s">
+        <v>2268</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="64" t="s">
+      <c r="N6" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="P6"/>
-    </row>
-    <row r="7" spans="1:16" ht="29.25">
+      <c r="Q6"/>
+    </row>
+    <row r="7" spans="1:17" ht="29.25">
       <c r="A7" s="63">
         <v>6</v>
       </c>
@@ -32773,24 +33062,27 @@
       <c r="H7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="1" t="s">
+        <v>2269</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M7" s="64" t="s">
+      <c r="N7" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="P7"/>
-    </row>
-    <row r="8" spans="1:16" ht="29.25">
+      <c r="Q7"/>
+    </row>
+    <row r="8" spans="1:17" ht="29.25">
       <c r="A8" s="63">
         <v>7</v>
       </c>
@@ -32815,24 +33107,27 @@
       <c r="H8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="64" t="s">
+      <c r="N8" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="P8"/>
-    </row>
-    <row r="9" spans="1:16" ht="30">
+      <c r="Q8"/>
+    </row>
+    <row r="9" spans="1:17" ht="30">
       <c r="A9" s="63">
         <v>9</v>
       </c>
@@ -32855,24 +33150,27 @@
       <c r="H9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="K9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="64" t="s">
+      <c r="N9" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="P9"/>
-    </row>
-    <row r="10" spans="1:16" ht="29.25">
+      <c r="Q9"/>
+    </row>
+    <row r="10" spans="1:17" ht="29.25">
       <c r="A10" s="63">
         <v>10</v>
       </c>
@@ -32895,24 +33193,27 @@
       <c r="H10" s="1" t="s">
         <v>911</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="1" t="s">
+        <v>2270</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="64" t="s">
+      <c r="N10" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="P10"/>
-    </row>
-    <row r="11" spans="1:16" ht="29.25">
+      <c r="Q10"/>
+    </row>
+    <row r="11" spans="1:17" ht="29.25">
       <c r="A11" s="63">
         <v>11</v>
       </c>
@@ -32937,24 +33238,27 @@
       <c r="H11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="64" t="s">
+      <c r="N11" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="P11"/>
-    </row>
-    <row r="12" spans="1:16" ht="29.25">
+      <c r="Q11"/>
+    </row>
+    <row r="12" spans="1:17" ht="29.25">
       <c r="A12" s="63">
         <v>12</v>
       </c>
@@ -32979,24 +33283,27 @@
       <c r="H12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="1" t="s">
+        <v>2271</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M12" s="64" t="s">
+      <c r="N12" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="P12"/>
-    </row>
-    <row r="13" spans="1:16" ht="29.25">
+      <c r="Q12"/>
+    </row>
+    <row r="13" spans="1:17" ht="29.25">
       <c r="A13" s="63">
         <v>13</v>
       </c>
@@ -33021,24 +33328,27 @@
       <c r="H13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="64" t="s">
+      <c r="N13" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="P13"/>
-    </row>
-    <row r="14" spans="1:16" ht="29.25">
+      <c r="Q13"/>
+    </row>
+    <row r="14" spans="1:17" ht="29.25">
       <c r="A14" s="63">
         <v>14</v>
       </c>
@@ -33063,24 +33373,27 @@
       <c r="H14" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="1" t="s">
+        <v>2273</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M14" s="64" t="s">
+      <c r="N14" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="P14"/>
-    </row>
-    <row r="15" spans="1:16" ht="29.25">
+      <c r="Q14"/>
+    </row>
+    <row r="15" spans="1:17" ht="29.25">
       <c r="A15" s="63">
         <v>15</v>
       </c>
@@ -33105,24 +33418,27 @@
       <c r="H15" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M15" s="64" t="s">
+      <c r="N15" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="P15"/>
-    </row>
-    <row r="16" spans="1:16" ht="39">
+      <c r="Q15"/>
+    </row>
+    <row r="16" spans="1:17" ht="39">
       <c r="A16" s="63">
         <v>16</v>
       </c>
@@ -33147,24 +33463,27 @@
       <c r="H16" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="1" t="s">
+        <v>2274</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="K16" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M16" s="64" t="s">
+      <c r="N16" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="P16"/>
-    </row>
-    <row r="17" spans="1:16" ht="30">
+      <c r="Q16"/>
+    </row>
+    <row r="17" spans="1:17" ht="30">
       <c r="A17" s="63">
         <v>17</v>
       </c>
@@ -33189,24 +33508,27 @@
       <c r="H17" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="K17" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M17" s="64" t="s">
+      <c r="N17" s="64" t="s">
         <v>111</v>
       </c>
-      <c r="P17"/>
-    </row>
-    <row r="18" spans="1:16" ht="30">
+      <c r="Q17"/>
+    </row>
+    <row r="18" spans="1:17" ht="30">
       <c r="A18" s="63">
         <v>18</v>
       </c>
@@ -33231,24 +33553,27 @@
       <c r="H18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="1" t="s">
+        <v>2275</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M18" s="64" t="s">
+      <c r="N18" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="P18"/>
-    </row>
-    <row r="19" spans="1:16" ht="29.25">
+      <c r="Q18"/>
+    </row>
+    <row r="19" spans="1:17" ht="29.25">
       <c r="A19" s="63">
         <v>19</v>
       </c>
@@ -33273,24 +33598,27 @@
       <c r="H19" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="M19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M19" s="64" t="s">
+      <c r="N19" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="P19"/>
-    </row>
-    <row r="20" spans="1:16" ht="29.25">
+      <c r="Q19"/>
+    </row>
+    <row r="20" spans="1:17" ht="29.25">
       <c r="A20" s="63">
         <v>20</v>
       </c>
@@ -33315,24 +33643,27 @@
       <c r="H20" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="1" t="s">
+        <v>2276</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="M20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M20" s="64" t="s">
+      <c r="N20" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="P20"/>
-    </row>
-    <row r="21" spans="1:16" ht="29.25">
+      <c r="Q20"/>
+    </row>
+    <row r="21" spans="1:17" ht="29.25">
       <c r="A21" s="63">
         <v>21</v>
       </c>
@@ -33358,24 +33689,27 @@
       <c r="H21" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="1" t="s">
+        <v>2277</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="M21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M21" s="64" t="s">
+      <c r="N21" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="P21"/>
-    </row>
-    <row r="22" spans="1:16" ht="30">
+      <c r="Q21"/>
+    </row>
+    <row r="22" spans="1:17" ht="30">
       <c r="A22" s="63">
         <v>23</v>
       </c>
@@ -33400,24 +33734,27 @@
       <c r="H22" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M22" s="64" t="s">
+      <c r="N22" s="64" t="s">
         <v>145</v>
       </c>
-      <c r="P22"/>
-    </row>
-    <row r="23" spans="1:16" ht="30">
+      <c r="Q22"/>
+    </row>
+    <row r="23" spans="1:17" ht="30">
       <c r="A23" s="63">
         <v>24</v>
       </c>
@@ -33442,24 +33779,27 @@
       <c r="H23" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" s="1" t="s">
+        <v>2278</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M23" s="64" t="s">
+      <c r="N23" s="64" t="s">
         <v>150</v>
       </c>
-      <c r="P23"/>
-    </row>
-    <row r="24" spans="1:16" ht="29.25">
+      <c r="Q23"/>
+    </row>
+    <row r="24" spans="1:17" ht="29.25">
       <c r="A24" s="63">
         <v>25</v>
       </c>
@@ -33482,24 +33822,27 @@
       <c r="H24" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="M24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M24" s="64" t="s">
+      <c r="N24" s="64" t="s">
         <v>156</v>
       </c>
-      <c r="P24"/>
-    </row>
-    <row r="25" spans="1:16" ht="29.25">
+      <c r="Q24"/>
+    </row>
+    <row r="25" spans="1:17" ht="29.25">
       <c r="A25" s="63">
         <v>27</v>
       </c>
@@ -33524,24 +33867,27 @@
       <c r="H25" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="1" t="s">
+        <v>2279</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="K25" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="M25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M25" s="64" t="s">
+      <c r="N25" s="64" t="s">
         <v>163</v>
       </c>
-      <c r="P25"/>
-    </row>
-    <row r="26" spans="1:16" ht="29.25">
+      <c r="Q25"/>
+    </row>
+    <row r="26" spans="1:17" ht="29.25">
       <c r="A26" s="63">
         <v>28</v>
       </c>
@@ -33566,24 +33912,27 @@
       <c r="H26" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="1" t="s">
+        <v>2280</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="K26" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="M26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M26" s="64" t="s">
+      <c r="N26" s="64" t="s">
         <v>168</v>
       </c>
-      <c r="P26"/>
-    </row>
-    <row r="27" spans="1:16" ht="29.25">
+      <c r="Q26"/>
+    </row>
+    <row r="27" spans="1:17" ht="29.25">
       <c r="A27" s="63">
         <v>29</v>
       </c>
@@ -33608,24 +33957,27 @@
       <c r="H27" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="M27" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M27" s="64" t="s">
+      <c r="N27" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="P27"/>
-    </row>
-    <row r="28" spans="1:16" ht="29.25">
+      <c r="Q27"/>
+    </row>
+    <row r="28" spans="1:17" ht="29.25">
       <c r="A28" s="63">
         <v>30</v>
       </c>
@@ -33650,24 +34002,27 @@
       <c r="H28" s="1" t="s">
         <v>915</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="1" t="s">
+        <v>2281</v>
+      </c>
+      <c r="J28" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="K28" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M28" s="64" t="s">
+      <c r="N28" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="P28"/>
-    </row>
-    <row r="29" spans="1:16" ht="30">
+      <c r="Q28"/>
+    </row>
+    <row r="29" spans="1:17" ht="30">
       <c r="A29" s="63">
         <v>31</v>
       </c>
@@ -33692,24 +34047,27 @@
       <c r="H29" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="K29" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="M29" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M29" s="64" t="s">
+      <c r="N29" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="P29"/>
-    </row>
-    <row r="30" spans="1:16" ht="29.25">
+      <c r="Q29"/>
+    </row>
+    <row r="30" spans="1:17" ht="29.25">
       <c r="A30" s="63">
         <v>33</v>
       </c>
@@ -33734,24 +34092,27 @@
       <c r="H30" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="I30" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="K30" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="M30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M30" s="64" t="s">
+      <c r="N30" s="64" t="s">
         <v>192</v>
       </c>
-      <c r="P30"/>
-    </row>
-    <row r="31" spans="1:16" ht="29.25">
+      <c r="Q30"/>
+    </row>
+    <row r="31" spans="1:17" ht="29.25">
       <c r="A31" s="63">
         <v>34</v>
       </c>
@@ -33776,24 +34137,27 @@
       <c r="H31" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="1" t="s">
+        <v>2282</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="K31" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="L31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L31" s="1" t="s">
+      <c r="M31" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M31" s="64" t="s">
+      <c r="N31" s="64" t="s">
         <v>198</v>
       </c>
-      <c r="P31"/>
-    </row>
-    <row r="32" spans="1:16" ht="30">
+      <c r="Q31"/>
+    </row>
+    <row r="32" spans="1:17" ht="30">
       <c r="A32" s="63">
         <v>35</v>
       </c>
@@ -33818,24 +34182,27 @@
       <c r="H32" s="1" t="s">
         <v>916</v>
       </c>
-      <c r="I32" s="5" t="s">
+      <c r="I32" s="1" t="s">
+        <v>2226</v>
+      </c>
+      <c r="J32" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="K32" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="L32" s="1" t="s">
+      <c r="M32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M32" s="64" t="s">
+      <c r="N32" s="64" t="s">
         <v>204</v>
       </c>
-      <c r="P32"/>
-    </row>
-    <row r="33" spans="1:16" ht="30">
+      <c r="Q32"/>
+    </row>
+    <row r="33" spans="1:17" ht="30">
       <c r="A33" s="63">
         <v>36</v>
       </c>
@@ -33860,24 +34227,27 @@
       <c r="H33" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" s="1" t="s">
+        <v>2283</v>
+      </c>
+      <c r="J33" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="K33" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="L33" s="1" t="s">
+      <c r="M33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M33" s="64" t="s">
+      <c r="N33" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="P33"/>
-    </row>
-    <row r="34" spans="1:16" ht="29.25">
+      <c r="Q33"/>
+    </row>
+    <row r="34" spans="1:17" ht="29.25">
       <c r="A34" s="63">
         <v>37</v>
       </c>
@@ -33902,24 +34272,27 @@
       <c r="H34" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="1" t="s">
+        <v>2284</v>
+      </c>
+      <c r="J34" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="K34" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="M34" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M34" s="64" t="s">
+      <c r="N34" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="P34"/>
-    </row>
-    <row r="35" spans="1:16" ht="29.25">
+      <c r="Q34"/>
+    </row>
+    <row r="35" spans="1:17" ht="29.25">
       <c r="A35" s="63">
         <v>38</v>
       </c>
@@ -33944,24 +34317,27 @@
       <c r="H35" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="1" t="s">
+        <v>2285</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="K35" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="L35" s="1" t="s">
+      <c r="M35" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M35" s="64" t="s">
+      <c r="N35" s="64" t="s">
         <v>220</v>
       </c>
-      <c r="P35"/>
-    </row>
-    <row r="36" spans="1:16" ht="29.25">
+      <c r="Q35"/>
+    </row>
+    <row r="36" spans="1:17" ht="29.25">
       <c r="A36" s="63">
         <v>39</v>
       </c>
@@ -33986,24 +34362,27 @@
       <c r="H36" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="K36" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="M36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M36" s="64" t="s">
+      <c r="N36" s="64" t="s">
         <v>227</v>
       </c>
-      <c r="P36"/>
-    </row>
-    <row r="37" spans="1:16" ht="29.25">
+      <c r="Q36"/>
+    </row>
+    <row r="37" spans="1:17" ht="29.25">
       <c r="A37" s="63">
         <v>40</v>
       </c>
@@ -34028,24 +34407,27 @@
       <c r="H37" s="1" t="s">
         <v>918</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="1" t="s">
+        <v>2286</v>
+      </c>
+      <c r="J37" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="K37" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="L37" s="1" t="s">
+      <c r="M37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M37" s="64" t="s">
+      <c r="N37" s="64" t="s">
         <v>232</v>
       </c>
-      <c r="P37"/>
-    </row>
-    <row r="38" spans="1:16" ht="30">
+      <c r="Q37"/>
+    </row>
+    <row r="38" spans="1:17" ht="30">
       <c r="A38" s="63">
         <v>41</v>
       </c>
@@ -34070,24 +34452,27 @@
       <c r="H38" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I38" s="1" t="s">
+        <v>2219</v>
+      </c>
+      <c r="J38" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="K38" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="L38" s="1" t="s">
+      <c r="M38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="64" t="s">
+      <c r="N38" s="64" t="s">
         <v>238</v>
       </c>
-      <c r="P38"/>
-    </row>
-    <row r="39" spans="1:16" ht="29.25">
+      <c r="Q38"/>
+    </row>
+    <row r="39" spans="1:17" ht="29.25">
       <c r="A39" s="63">
         <v>42</v>
       </c>
@@ -34112,24 +34497,27 @@
       <c r="H39" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" s="1" t="s">
+        <v>2287</v>
+      </c>
+      <c r="J39" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="K39" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="L39" s="1" t="s">
+      <c r="M39" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M39" s="64" t="s">
+      <c r="N39" s="64" t="s">
         <v>244</v>
       </c>
-      <c r="P39"/>
-    </row>
-    <row r="40" spans="1:16" ht="29.25">
+      <c r="Q39"/>
+    </row>
+    <row r="40" spans="1:17" ht="29.25">
       <c r="A40" s="63">
         <v>43</v>
       </c>
@@ -34154,24 +34542,27 @@
       <c r="H40" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="1" t="s">
+        <v>2288</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="K40" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="L40" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="M40" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M40" s="64" t="s">
+      <c r="N40" s="64" t="s">
         <v>250</v>
       </c>
-      <c r="P40"/>
-    </row>
-    <row r="41" spans="1:16" ht="29.25">
+      <c r="Q40"/>
+    </row>
+    <row r="41" spans="1:17" ht="29.25">
       <c r="A41" s="63">
         <v>44</v>
       </c>
@@ -34196,24 +34587,27 @@
       <c r="H41" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="1" t="s">
+        <v>2289</v>
+      </c>
+      <c r="J41" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="K41" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="M41" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M41" s="64" t="s">
+      <c r="N41" s="64" t="s">
         <v>257</v>
       </c>
-      <c r="P41"/>
-    </row>
-    <row r="42" spans="1:16" ht="30">
+      <c r="Q41"/>
+    </row>
+    <row r="42" spans="1:17" ht="30">
       <c r="A42" s="63">
         <v>45</v>
       </c>
@@ -34238,24 +34632,27 @@
       <c r="H42" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I42" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J42" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="K42" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="L42" s="1" t="s">
+      <c r="M42" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M42" s="64" t="s">
+      <c r="N42" s="64" t="s">
         <v>264</v>
       </c>
-      <c r="P42"/>
-    </row>
-    <row r="43" spans="1:16" ht="30">
+      <c r="Q42"/>
+    </row>
+    <row r="43" spans="1:17" ht="30">
       <c r="A43" s="63">
         <v>46</v>
       </c>
@@ -34280,24 +34677,27 @@
       <c r="H43" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="I43" s="1" t="s">
+        <v>2290</v>
+      </c>
+      <c r="J43" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="K43" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="L43" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="L43" s="1" t="s">
+      <c r="M43" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M43" s="64" t="s">
+      <c r="N43" s="64" t="s">
         <v>269</v>
       </c>
-      <c r="P43"/>
-    </row>
-    <row r="44" spans="1:16" ht="30">
+      <c r="Q43"/>
+    </row>
+    <row r="44" spans="1:17" ht="30">
       <c r="A44" s="63">
         <v>47</v>
       </c>
@@ -34322,24 +34722,27 @@
       <c r="H44" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="J44" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="J44" s="4" t="s">
+      <c r="K44" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="L44" s="1" t="s">
+      <c r="M44" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M44" s="64" t="s">
+      <c r="N44" s="64" t="s">
         <v>275</v>
       </c>
-      <c r="P44"/>
-    </row>
-    <row r="45" spans="1:16" ht="30">
+      <c r="Q44"/>
+    </row>
+    <row r="45" spans="1:17" ht="30">
       <c r="A45" s="63">
         <v>48</v>
       </c>
@@ -34364,24 +34767,27 @@
       <c r="H45" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I45" s="1" t="s">
+        <v>2291</v>
+      </c>
+      <c r="J45" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="J45" s="4" t="s">
+      <c r="K45" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="L45" s="1" t="s">
+      <c r="M45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M45" s="64" t="s">
+      <c r="N45" s="64" t="s">
         <v>279</v>
       </c>
-      <c r="P45"/>
-    </row>
-    <row r="46" spans="1:16" ht="29.25">
+      <c r="Q45"/>
+    </row>
+    <row r="46" spans="1:17" ht="29.25">
       <c r="A46" s="63">
         <v>49</v>
       </c>
@@ -34406,24 +34812,27 @@
       <c r="H46" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="I46" s="1" t="s">
+        <v>2292</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="K46" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="L46" s="1" t="s">
+      <c r="M46" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M46" s="64" t="s">
+      <c r="N46" s="64" t="s">
         <v>287</v>
       </c>
-      <c r="P46"/>
-    </row>
-    <row r="47" spans="1:16" ht="29.25">
+      <c r="Q46"/>
+    </row>
+    <row r="47" spans="1:17" ht="29.25">
       <c r="A47" s="63">
         <v>50</v>
       </c>
@@ -34448,24 +34857,27 @@
       <c r="H47" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="I47" s="1" t="s">
+        <v>2293</v>
+      </c>
+      <c r="J47" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="K47" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="M47" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M47" s="64" t="s">
+      <c r="N47" s="64" t="s">
         <v>292</v>
       </c>
-      <c r="P47"/>
-    </row>
-    <row r="48" spans="1:16" ht="29.25">
+      <c r="Q47"/>
+    </row>
+    <row r="48" spans="1:17" ht="29.25">
       <c r="A48" s="63">
         <v>51</v>
       </c>
@@ -34490,24 +34902,27 @@
       <c r="H48" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="I48" s="1" t="s">
+        <v>2294</v>
+      </c>
+      <c r="J48" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="K48" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="L48" s="1" t="s">
+      <c r="M48" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="64" t="s">
+      <c r="N48" s="64" t="s">
         <v>300</v>
       </c>
-      <c r="P48"/>
-    </row>
-    <row r="49" spans="1:16" ht="29.25">
+      <c r="Q48"/>
+    </row>
+    <row r="49" spans="1:17" ht="29.25">
       <c r="A49" s="63">
         <v>52</v>
       </c>
@@ -34532,24 +34947,27 @@
       <c r="H49" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="I49" s="9" t="s">
+      <c r="I49" s="1" t="s">
+        <v>2295</v>
+      </c>
+      <c r="J49" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="K49" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="L49" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="L49" s="1" t="s">
+      <c r="M49" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M49" s="64" t="s">
+      <c r="N49" s="64" t="s">
         <v>306</v>
       </c>
-      <c r="P49"/>
-    </row>
-    <row r="50" spans="1:16" ht="29.25">
+      <c r="Q49"/>
+    </row>
+    <row r="50" spans="1:17" ht="29.25">
       <c r="A50" s="63">
         <v>53</v>
       </c>
@@ -34574,24 +34992,27 @@
       <c r="H50" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="I50" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="J50" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="K50" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="L50" s="1" t="s">
+      <c r="M50" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M50" s="64" t="s">
+      <c r="N50" s="64" t="s">
         <v>311</v>
       </c>
-      <c r="P50"/>
-    </row>
-    <row r="51" spans="1:16" ht="29.25">
+      <c r="Q50"/>
+    </row>
+    <row r="51" spans="1:17" ht="29.25">
       <c r="A51" s="63">
         <v>54</v>
       </c>
@@ -34616,24 +35037,27 @@
       <c r="H51" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="I51" s="4" t="s">
+      <c r="I51" s="1" t="s">
+        <v>2296</v>
+      </c>
+      <c r="J51" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="K51" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="L51" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="L51" s="1" t="s">
+      <c r="M51" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M51" s="64" t="s">
+      <c r="N51" s="64" t="s">
         <v>314</v>
       </c>
-      <c r="P51"/>
-    </row>
-    <row r="52" spans="1:16" ht="29.25">
+      <c r="Q51"/>
+    </row>
+    <row r="52" spans="1:17" ht="29.25">
       <c r="A52" s="63">
         <v>55</v>
       </c>
@@ -34658,24 +35082,27 @@
       <c r="H52" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="I52" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="K52" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="L52" s="1" t="s">
+      <c r="M52" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M52" s="64" t="s">
+      <c r="N52" s="64" t="s">
         <v>319</v>
       </c>
-      <c r="P52"/>
-    </row>
-    <row r="53" spans="1:16" ht="29.25">
+      <c r="Q52"/>
+    </row>
+    <row r="53" spans="1:17" ht="29.25">
       <c r="A53" s="63">
         <v>56</v>
       </c>
@@ -34700,24 +35127,27 @@
       <c r="H53" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="I53" s="1" t="s">
+        <v>2297</v>
+      </c>
+      <c r="J53" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="K53" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="L53" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="L53" s="1" t="s">
+      <c r="M53" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M53" s="64" t="s">
+      <c r="N53" s="64" t="s">
         <v>322</v>
       </c>
-      <c r="P53"/>
-    </row>
-    <row r="54" spans="1:16" ht="29.25">
+      <c r="Q53"/>
+    </row>
+    <row r="54" spans="1:17" ht="29.25">
       <c r="A54" s="63">
         <v>57</v>
       </c>
@@ -34742,24 +35172,27 @@
       <c r="H54" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="I54" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="J54" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="K54" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="L54" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="L54" s="1" t="s">
+      <c r="M54" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M54" s="64" t="s">
+      <c r="N54" s="64" t="s">
         <v>327</v>
       </c>
-      <c r="P54"/>
-    </row>
-    <row r="55" spans="1:16" ht="29.25">
+      <c r="Q54"/>
+    </row>
+    <row r="55" spans="1:17" ht="29.25">
       <c r="A55" s="63">
         <v>58</v>
       </c>
@@ -34784,24 +35217,27 @@
       <c r="H55" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="I55" s="5" t="s">
+      <c r="I55" s="1" t="s">
+        <v>2298</v>
+      </c>
+      <c r="J55" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="K55" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="L55" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="L55" s="1" t="s">
+      <c r="M55" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M55" s="64" t="s">
+      <c r="N55" s="64" t="s">
         <v>330</v>
       </c>
-      <c r="P55"/>
-    </row>
-    <row r="56" spans="1:16" ht="29.25">
+      <c r="Q55"/>
+    </row>
+    <row r="56" spans="1:17" ht="29.25">
       <c r="A56" s="63">
         <v>59</v>
       </c>
@@ -34826,24 +35262,27 @@
       <c r="H56" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="I56" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="J56" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="K56" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="L56" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="L56" s="1" t="s">
+      <c r="M56" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M56" s="64" t="s">
+      <c r="N56" s="64" t="s">
         <v>335</v>
       </c>
-      <c r="P56"/>
-    </row>
-    <row r="57" spans="1:16" ht="29.25">
+      <c r="Q56"/>
+    </row>
+    <row r="57" spans="1:17" ht="29.25">
       <c r="A57" s="63">
         <v>61</v>
       </c>
@@ -34868,24 +35307,27 @@
       <c r="H57" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="I57" s="3" t="s">
+      <c r="I57" s="1" t="s">
+        <v>2299</v>
+      </c>
+      <c r="J57" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="J57" s="8" t="s">
+      <c r="K57" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="L57" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="L57" s="1" t="s">
+      <c r="M57" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M57" s="64" t="s">
+      <c r="N57" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="P57"/>
-    </row>
-    <row r="58" spans="1:16" ht="29.25">
+      <c r="Q57"/>
+    </row>
+    <row r="58" spans="1:17" ht="29.25">
       <c r="A58" s="63">
         <v>62</v>
       </c>
@@ -34910,24 +35352,27 @@
       <c r="H58" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="I58" s="10" t="s">
+      <c r="I58" s="1" t="s">
+        <v>2300</v>
+      </c>
+      <c r="J58" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="J58" s="8" t="s">
+      <c r="K58" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="L58" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="L58" s="1" t="s">
+      <c r="M58" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M58" s="64" t="s">
+      <c r="N58" s="64" t="s">
         <v>347</v>
       </c>
-      <c r="P58"/>
-    </row>
-    <row r="59" spans="1:16" ht="29.25">
+      <c r="Q58"/>
+    </row>
+    <row r="59" spans="1:17" ht="29.25">
       <c r="A59" s="63">
         <v>63</v>
       </c>
@@ -34952,24 +35397,27 @@
       <c r="H59" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="I59" s="5" t="s">
+      <c r="I59" s="1" t="s">
+        <v>2301</v>
+      </c>
+      <c r="J59" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="J59" s="4" t="s">
+      <c r="K59" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="L59" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="L59" s="1" t="s">
+      <c r="M59" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M59" s="64" t="s">
+      <c r="N59" s="64" t="s">
         <v>354</v>
       </c>
-      <c r="P59"/>
-    </row>
-    <row r="60" spans="1:16" ht="29.25">
+      <c r="Q59"/>
+    </row>
+    <row r="60" spans="1:17" ht="29.25">
       <c r="A60" s="63">
         <v>65</v>
       </c>
@@ -34994,24 +35442,27 @@
       <c r="H60" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="I60" s="3" t="s">
+      <c r="I60" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J60" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="J60" s="5" t="s">
+      <c r="K60" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="K60" s="1" t="s">
+      <c r="L60" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="L60" s="1" t="s">
+      <c r="M60" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M60" s="64" t="s">
+      <c r="N60" s="64" t="s">
         <v>361</v>
       </c>
-      <c r="P60"/>
-    </row>
-    <row r="61" spans="1:16" ht="29.25">
+      <c r="Q60"/>
+    </row>
+    <row r="61" spans="1:17" ht="29.25">
       <c r="A61" s="63">
         <v>66</v>
       </c>
@@ -35036,24 +35487,27 @@
       <c r="H61" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="I61" s="4" t="s">
+      <c r="I61" s="1" t="s">
+        <v>2302</v>
+      </c>
+      <c r="J61" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="J61" s="3" t="s">
+      <c r="K61" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="L61" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="L61" s="1" t="s">
+      <c r="M61" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M61" s="64" t="s">
+      <c r="N61" s="64" t="s">
         <v>365</v>
       </c>
-      <c r="P61"/>
-    </row>
-    <row r="62" spans="1:16" ht="29.25">
+      <c r="Q61"/>
+    </row>
+    <row r="62" spans="1:17" ht="29.25">
       <c r="A62" s="63">
         <v>67</v>
       </c>
@@ -35079,24 +35533,27 @@
       <c r="H62" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="I62" s="3" t="s">
+      <c r="I62" s="1" t="s">
+        <v>2303</v>
+      </c>
+      <c r="J62" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="K62" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="L62" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="L62" s="1" t="s">
+      <c r="M62" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M62" s="64" t="s">
+      <c r="N62" s="64" t="s">
         <v>373</v>
       </c>
-      <c r="P62"/>
-    </row>
-    <row r="63" spans="1:16" ht="29.25">
+      <c r="Q62"/>
+    </row>
+    <row r="63" spans="1:17" ht="29.25">
       <c r="A63" s="63">
         <v>68</v>
       </c>
@@ -35122,24 +35579,27 @@
       <c r="H63" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="I63" s="4" t="s">
+      <c r="I63" s="1" t="s">
+        <v>2304</v>
+      </c>
+      <c r="J63" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="J63" s="3" t="s">
+      <c r="K63" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="L63" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="L63" s="1" t="s">
+      <c r="M63" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M63" s="64" t="s">
+      <c r="N63" s="64" t="s">
         <v>378</v>
       </c>
-      <c r="P63"/>
-    </row>
-    <row r="64" spans="1:16" ht="29.25">
+      <c r="Q63"/>
+    </row>
+    <row r="64" spans="1:17" ht="29.25">
       <c r="A64" s="63">
         <v>69</v>
       </c>
@@ -35165,24 +35625,27 @@
       <c r="H64" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="I64" s="7" t="s">
+      <c r="I64" s="1" t="s">
+        <v>2305</v>
+      </c>
+      <c r="J64" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="J64" s="6" t="s">
+      <c r="K64" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="L64" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="L64" s="1" t="s">
+      <c r="M64" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M64" s="64" t="s">
+      <c r="N64" s="64" t="s">
         <v>387</v>
       </c>
-      <c r="P64"/>
-    </row>
-    <row r="65" spans="1:16" ht="29.25">
+      <c r="Q64"/>
+    </row>
+    <row r="65" spans="1:17" ht="29.25">
       <c r="A65" s="63">
         <v>71</v>
       </c>
@@ -35208,24 +35671,27 @@
       <c r="H65" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="I65" s="3" t="s">
+      <c r="I65" s="1" t="s">
+        <v>2306</v>
+      </c>
+      <c r="J65" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="K65" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="L65" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="L65" s="1" t="s">
+      <c r="M65" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M65" s="64" t="s">
+      <c r="N65" s="64" t="s">
         <v>395</v>
       </c>
-      <c r="P65"/>
-    </row>
-    <row r="66" spans="1:16" ht="29.25">
+      <c r="Q65"/>
+    </row>
+    <row r="66" spans="1:17" ht="29.25">
       <c r="A66" s="63">
         <v>73</v>
       </c>
@@ -35251,24 +35717,27 @@
       <c r="H66" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="I66" s="3" t="s">
+      <c r="I66" s="1" t="s">
+        <v>2307</v>
+      </c>
+      <c r="J66" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="K66" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="K66" s="1" t="s">
+      <c r="L66" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L66" s="1" t="s">
+      <c r="M66" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M66" s="64" t="s">
+      <c r="N66" s="64" t="s">
         <v>402</v>
       </c>
-      <c r="P66"/>
-    </row>
-    <row r="67" spans="1:16" ht="30">
+      <c r="Q66"/>
+    </row>
+    <row r="67" spans="1:17" ht="30">
       <c r="A67" s="63">
         <v>75</v>
       </c>
@@ -35293,24 +35762,27 @@
       <c r="H67" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="I67" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="J67" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="K67" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="K67" s="1" t="s">
+      <c r="L67" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="L67" s="1" t="s">
+      <c r="M67" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M67" s="64" t="s">
+      <c r="N67" s="64" t="s">
         <v>408</v>
       </c>
-      <c r="P67"/>
-    </row>
-    <row r="68" spans="1:16" ht="29.25">
+      <c r="Q67"/>
+    </row>
+    <row r="68" spans="1:17" ht="29.25">
       <c r="A68" s="63">
         <v>77</v>
       </c>
@@ -35335,24 +35807,27 @@
       <c r="H68" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I68" s="3" t="s">
+      <c r="I68" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J68" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="J68" s="3" t="s">
+      <c r="K68" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="L68" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="M68" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M68" s="64" t="s">
+      <c r="N68" s="64" t="s">
         <v>411</v>
       </c>
-      <c r="P68"/>
-    </row>
-    <row r="69" spans="1:16" ht="29.25">
+      <c r="Q68"/>
+    </row>
+    <row r="69" spans="1:17" ht="29.25">
       <c r="A69" s="63">
         <v>78</v>
       </c>
@@ -35377,24 +35852,27 @@
       <c r="H69" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="I69" s="3" t="s">
+      <c r="I69" s="1" t="s">
+        <v>2270</v>
+      </c>
+      <c r="J69" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="J69" s="3" t="s">
+      <c r="K69" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="L69" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="L69" s="1" t="s">
+      <c r="M69" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M69" s="64" t="s">
+      <c r="N69" s="64" t="s">
         <v>413</v>
       </c>
-      <c r="P69"/>
-    </row>
-    <row r="70" spans="1:16" ht="29.25">
+      <c r="Q69"/>
+    </row>
+    <row r="70" spans="1:17" ht="29.25">
       <c r="A70" s="63">
         <v>79</v>
       </c>
@@ -35420,24 +35898,27 @@
       <c r="H70" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="I70" s="6" t="s">
+      <c r="I70" s="1" t="s">
+        <v>2308</v>
+      </c>
+      <c r="J70" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="J70" s="6" t="s">
+      <c r="K70" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="L70" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="L70" s="1" t="s">
+      <c r="M70" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M70" s="64" t="s">
+      <c r="N70" s="64" t="s">
         <v>420</v>
       </c>
-      <c r="P70"/>
-    </row>
-    <row r="71" spans="1:16" ht="29.25">
+      <c r="Q70"/>
+    </row>
+    <row r="71" spans="1:17" ht="29.25">
       <c r="A71" s="63">
         <v>81</v>
       </c>
@@ -35463,24 +35944,27 @@
       <c r="H71" s="1" t="s">
         <v>931</v>
       </c>
-      <c r="I71" s="6" t="s">
+      <c r="I71" s="1" t="s">
+        <v>2309</v>
+      </c>
+      <c r="J71" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="J71" s="11" t="s">
+      <c r="K71" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="L71" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="L71" s="1" t="s">
+      <c r="M71" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M71" s="64" t="s">
+      <c r="N71" s="64" t="s">
         <v>428</v>
       </c>
-      <c r="P71"/>
-    </row>
-    <row r="72" spans="1:16" ht="29.25">
+      <c r="Q71"/>
+    </row>
+    <row r="72" spans="1:17" ht="29.25">
       <c r="A72" s="63">
         <v>83</v>
       </c>
@@ -35505,24 +35989,27 @@
       <c r="H72" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>429</v>
+      <c r="I72" s="1" t="s">
+        <v>587</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="K72" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="L72" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="L72" s="1" t="s">
+      <c r="M72" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M72" s="64" t="s">
+      <c r="N72" s="64" t="s">
         <v>433</v>
       </c>
-      <c r="P72"/>
-    </row>
-    <row r="73" spans="1:16" ht="30">
+      <c r="Q72"/>
+    </row>
+    <row r="73" spans="1:17" ht="30">
       <c r="A73" s="63">
         <v>85</v>
       </c>
@@ -35547,24 +36034,27 @@
       <c r="H73" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="I73" s="6" t="s">
+      <c r="I73" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="J73" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="J73" s="5" t="s">
+      <c r="K73" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="K73" s="1" t="s">
+      <c r="L73" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="L73" s="1" t="s">
+      <c r="M73" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M73" s="64" t="s">
+      <c r="N73" s="64" t="s">
         <v>439</v>
       </c>
-      <c r="P73"/>
-    </row>
-    <row r="74" spans="1:16" ht="29.25">
+      <c r="Q73"/>
+    </row>
+    <row r="74" spans="1:17" ht="29.25">
       <c r="A74" s="63">
         <v>86</v>
       </c>
@@ -35589,24 +36079,27 @@
       <c r="H74" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="I74" s="6" t="s">
+      <c r="I74" s="1" t="s">
+        <v>2310</v>
+      </c>
+      <c r="J74" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="J74" s="5" t="s">
+      <c r="K74" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="L74" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="L74" s="1" t="s">
+      <c r="M74" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M74" s="64" t="s">
+      <c r="N74" s="64" t="s">
         <v>445</v>
       </c>
-      <c r="P74"/>
-    </row>
-    <row r="75" spans="1:16" ht="29.25">
+      <c r="Q74"/>
+    </row>
+    <row r="75" spans="1:17" ht="29.25">
       <c r="A75" s="63">
         <v>87</v>
       </c>
@@ -35632,24 +36125,27 @@
       <c r="H75" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="I75" s="3" t="s">
+      <c r="I75" s="1" t="s">
+        <v>2311</v>
+      </c>
+      <c r="J75" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="J75" s="7" t="s">
+      <c r="K75" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="K75" s="1" t="s">
+      <c r="L75" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="L75" s="1" t="s">
+      <c r="M75" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M75" s="64" t="s">
+      <c r="N75" s="64" t="s">
         <v>452</v>
       </c>
-      <c r="P75"/>
-    </row>
-    <row r="76" spans="1:16" ht="29.25">
+      <c r="Q75"/>
+    </row>
+    <row r="76" spans="1:17" ht="29.25">
       <c r="A76" s="63">
         <v>88</v>
       </c>
@@ -35675,24 +36171,27 @@
       <c r="H76" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="I76" s="9" t="s">
+      <c r="I76" s="1" t="s">
+        <v>2312</v>
+      </c>
+      <c r="J76" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="J76" s="7" t="s">
+      <c r="K76" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="L76" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="L76" s="1" t="s">
+      <c r="M76" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M76" s="64" t="s">
+      <c r="N76" s="64" t="s">
         <v>457</v>
       </c>
-      <c r="P76"/>
-    </row>
-    <row r="77" spans="1:16" ht="39">
+      <c r="Q76"/>
+    </row>
+    <row r="77" spans="1:17" ht="39">
       <c r="A77" s="63">
         <v>89</v>
       </c>
@@ -35718,24 +36217,27 @@
       <c r="H77" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="I77" s="3" t="s">
+      <c r="I77" s="1" t="s">
+        <v>2313</v>
+      </c>
+      <c r="J77" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="J77" s="12" t="s">
+      <c r="K77" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="L77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="L77" s="1" t="s">
+      <c r="M77" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M77" s="64" t="s">
+      <c r="N77" s="64" t="s">
         <v>463</v>
       </c>
-      <c r="P77"/>
-    </row>
-    <row r="78" spans="1:16" ht="29.25">
+      <c r="Q77"/>
+    </row>
+    <row r="78" spans="1:17" ht="29.25">
       <c r="A78" s="63">
         <v>91</v>
       </c>
@@ -35761,28 +36263,31 @@
       <c r="H78" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="I78" s="5" t="s">
+      <c r="I78" s="1" t="s">
+        <v>2314</v>
+      </c>
+      <c r="J78" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="J78" s="11" t="s">
+      <c r="K78" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="L78" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="L78" s="1" t="s">
+      <c r="M78" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M78" s="64" t="s">
+      <c r="N78" s="64" t="s">
         <v>470</v>
       </c>
-      <c r="O78" t="str">
+      <c r="P78" t="str">
         <f xml:space="preserve"> _xlfn.UNICHAR( HEX2DEC(129))</f>
         <v>ĩ</v>
       </c>
-      <c r="P78"/>
-    </row>
-    <row r="79" spans="1:16" ht="39">
+      <c r="Q78"/>
+    </row>
+    <row r="79" spans="1:17" ht="39">
       <c r="A79" s="63">
         <v>92</v>
       </c>
@@ -35808,28 +36313,31 @@
       <c r="H79" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="I79" s="3" t="s">
+      <c r="I79" s="1" t="s">
+        <v>2315</v>
+      </c>
+      <c r="J79" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="J79" s="3" t="s">
+      <c r="K79" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="L79" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="L79" s="1" t="s">
+      <c r="M79" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M79" s="64" t="s">
+      <c r="N79" s="64" t="s">
         <v>474</v>
       </c>
-      <c r="O79" t="str">
+      <c r="P79" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("i", _xlfn.UNICHAR( HEX2DEC(303)))</f>
         <v>ĩ</v>
       </c>
-      <c r="P79"/>
-    </row>
-    <row r="80" spans="1:16" ht="29.25">
+      <c r="Q79"/>
+    </row>
+    <row r="80" spans="1:17" ht="29.25">
       <c r="A80" s="63">
         <v>93</v>
       </c>
@@ -35854,24 +36362,27 @@
       <c r="H80" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="I80" s="5" t="s">
+      <c r="I80" s="1" t="s">
+        <v>2316</v>
+      </c>
+      <c r="J80" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="J80" s="13" t="s">
+      <c r="K80" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="L80" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="L80" s="1" t="s">
+      <c r="M80" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M80" s="64" t="s">
+      <c r="N80" s="64" t="s">
         <v>481</v>
       </c>
-      <c r="P80"/>
-    </row>
-    <row r="81" spans="1:16" ht="29.25">
+      <c r="Q80"/>
+    </row>
+    <row r="81" spans="1:17" ht="29.25">
       <c r="A81" s="63">
         <v>94</v>
       </c>
@@ -35896,24 +36407,27 @@
       <c r="H81" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="I81" s="1" t="s">
+        <v>2317</v>
+      </c>
+      <c r="J81" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="J81" s="13" t="s">
+      <c r="K81" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="K81" s="1" t="s">
+      <c r="L81" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="L81" s="1" t="s">
+      <c r="M81" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M81" s="64" t="s">
+      <c r="N81" s="64" t="s">
         <v>487</v>
       </c>
-      <c r="P81"/>
-    </row>
-    <row r="82" spans="1:16" ht="29.25">
+      <c r="Q81"/>
+    </row>
+    <row r="82" spans="1:17" ht="29.25">
       <c r="A82" s="63">
         <v>95</v>
       </c>
@@ -35939,24 +36453,27 @@
       <c r="H82" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="I82" s="9" t="s">
+      <c r="I82" s="1" t="s">
+        <v>2318</v>
+      </c>
+      <c r="J82" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="J82" s="13" t="s">
+      <c r="K82" s="13" t="s">
         <v>489</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="L82" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="L82" s="1" t="s">
+      <c r="M82" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M82" s="64" t="s">
+      <c r="N82" s="64" t="s">
         <v>494</v>
       </c>
-      <c r="P82"/>
-    </row>
-    <row r="83" spans="1:16" ht="29.25">
+      <c r="Q82"/>
+    </row>
+    <row r="83" spans="1:17" ht="29.25">
       <c r="A83" s="63">
         <v>97</v>
       </c>
@@ -35982,24 +36499,27 @@
       <c r="H83" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="I83" s="1" t="s">
+        <v>2309</v>
+      </c>
+      <c r="J83" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="J83" s="12" t="s">
+      <c r="K83" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="L83" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L83" s="1" t="s">
+      <c r="M83" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M83" s="64" t="s">
+      <c r="N83" s="64" t="s">
         <v>499</v>
       </c>
-      <c r="P83"/>
-    </row>
-    <row r="84" spans="1:16" ht="39">
+      <c r="Q83"/>
+    </row>
+    <row r="84" spans="1:17" ht="39">
       <c r="A84" s="63">
         <v>98</v>
       </c>
@@ -36025,24 +36545,27 @@
       <c r="H84" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="I84" s="3" t="s">
+      <c r="I84" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="J84" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="J84" s="12" t="s">
+      <c r="K84" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="K84" s="1" t="s">
+      <c r="L84" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L84" s="1" t="s">
+      <c r="M84" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M84" s="64" t="s">
+      <c r="N84" s="64" t="s">
         <v>503</v>
       </c>
-      <c r="P84"/>
-    </row>
-    <row r="85" spans="1:16" ht="29.25">
+      <c r="Q84"/>
+    </row>
+    <row r="85" spans="1:17" ht="29.25">
       <c r="A85" s="65">
         <v>99</v>
       </c>
@@ -36067,22 +36590,25 @@
       <c r="H85" s="68" t="s">
         <v>506</v>
       </c>
-      <c r="I85" s="67" t="s">
+      <c r="I85" s="68" t="s">
+        <v>2320</v>
+      </c>
+      <c r="J85" s="67" t="s">
         <v>504</v>
       </c>
-      <c r="J85" s="66" t="s">
+      <c r="K85" s="66" t="s">
         <v>505</v>
       </c>
-      <c r="K85" s="68" t="s">
+      <c r="L85" s="68" t="s">
         <v>288</v>
       </c>
-      <c r="L85" s="68" t="s">
+      <c r="M85" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="M85" s="69" t="s">
+      <c r="N85" s="69" t="s">
         <v>510</v>
       </c>
-      <c r="P85"/>
+      <c r="Q85"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -36286,16 +36812,16 @@
         <v>319</v>
       </c>
       <c r="K4" s="55">
-        <f xml:space="preserve"> LEN(D4)</f>
+        <f t="shared" ref="K4:K35" si="0" xml:space="preserve"> LEN(D4)</f>
         <v>1</v>
       </c>
       <c r="L4" s="74"/>
       <c r="M4" s="58" t="str">
-        <f>C4</f>
+        <f t="shared" ref="M4:M35" si="1">C4</f>
         <v>a</v>
       </c>
       <c r="N4" s="58" t="str">
-        <f>D4</f>
+        <f t="shared" ref="N4:N35" si="2">D4</f>
         <v>a</v>
       </c>
       <c r="P4" s="123" t="str">
@@ -36326,39 +36852,39 @@
         <v>a</v>
       </c>
       <c r="Y4" s="134" t="str">
-        <f t="shared" ref="Y4:AG4" si="0" xml:space="preserve"> _xlfn.CONCAT($W4, IF(Y$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(Y$3,4)))))</f>
+        <f t="shared" ref="Y4:AG4" si="3" xml:space="preserve"> _xlfn.CONCAT($W4, IF(Y$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(Y$3,4)))))</f>
         <v>á</v>
       </c>
       <c r="Z4" s="134" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>à</v>
       </c>
       <c r="AA4" s="134" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>a</v>
       </c>
       <c r="AB4" s="134" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>ǎ</v>
       </c>
       <c r="AC4" s="134" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>á</v>
       </c>
       <c r="AD4" s="134" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>ā</v>
       </c>
       <c r="AE4" s="134" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>a̍</v>
       </c>
       <c r="AF4" s="134" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>a̋</v>
       </c>
       <c r="AG4" s="134" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>å</v>
       </c>
       <c r="AI4" s="136" t="str">
@@ -36370,23 +36896,23 @@
         <v xml:space="preserve">    - xform/》a2/á/</v>
       </c>
       <c r="AK4" s="136" t="str">
-        <f t="shared" ref="AK4:AP10" si="1" xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $W4, Z$2, "/", Z4, "/")</f>
+        <f t="shared" ref="AK4:AP10" si="4" xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $W4, Z$2, "/", Z4, "/")</f>
         <v xml:space="preserve">    - xform/》a3/à/</v>
       </c>
       <c r="AL4" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a4/a/</v>
       </c>
       <c r="AM4" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a5/ǎ/</v>
       </c>
       <c r="AN4" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a6/á/</v>
       </c>
       <c r="AO4" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a7/ā/</v>
       </c>
       <c r="AP4" s="136" t="str">
@@ -36394,11 +36920,11 @@
         <v xml:space="preserve">    - xform/》a8/a̍/</v>
       </c>
       <c r="AQ4" s="136" t="str">
-        <f t="shared" ref="AQ4:AR10" si="2" xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $W4, AF$2, "/", AF4, "/")</f>
+        <f t="shared" ref="AQ4:AR10" si="5" xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $W4, AF$2, "/", AF4, "/")</f>
         <v xml:space="preserve">    - xform/》a9/a̋/</v>
       </c>
       <c r="AR4" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》a9/å/</v>
       </c>
       <c r="AS4" s="134"/>
@@ -36407,7 +36933,7 @@
     </row>
     <row r="5" spans="1:47" ht="27.75" thickBot="1">
       <c r="A5" s="58">
-        <f t="shared" ref="A5:A68" si="3" xml:space="preserve"> ROW() - 3</f>
+        <f t="shared" ref="A5:A68" si="6" xml:space="preserve"> ROW() - 3</f>
         <v>2</v>
       </c>
       <c r="B5" s="141" t="s">
@@ -36438,27 +36964,27 @@
         <v>1341</v>
       </c>
       <c r="K5" s="55">
-        <f xml:space="preserve"> LEN(D5)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="L5" s="74"/>
       <c r="M5" s="58" t="str">
-        <f>C5</f>
+        <f t="shared" si="1"/>
         <v>ann</v>
       </c>
       <c r="N5" s="58" t="str">
-        <f>D5</f>
+        <f t="shared" si="2"/>
         <v>ann</v>
       </c>
       <c r="P5" s="123" t="str">
-        <f t="shared" ref="P5:P68" si="4" xml:space="preserve"> _xlfn.CONCAT(M5, "(\d)")</f>
+        <f t="shared" ref="P5:P68" si="7" xml:space="preserve"> _xlfn.CONCAT(M5, "(\d)")</f>
         <v>ann(\d)</v>
       </c>
       <c r="Q5" s="128" t="s">
         <v>1230</v>
       </c>
       <c r="R5" s="126">
-        <f t="shared" ref="R5:R68" si="5" xml:space="preserve"> IFERROR( IF(Q5="", "", SEARCH(Q5, $M5)), "")</f>
+        <f t="shared" ref="R5:R68" si="8" xml:space="preserve"> IFERROR( IF(Q5="", "", SEARCH(Q5, $M5)), "")</f>
         <v>1</v>
       </c>
       <c r="S5" s="123" t="str">
@@ -36467,90 +36993,90 @@
       </c>
       <c r="T5" s="56"/>
       <c r="U5" s="57" t="str">
-        <f t="shared" ref="U5:U68" si="6" xml:space="preserve"> IF(AND(N5&lt;&gt;"", M5&lt;&gt;""), "    - xform/》" &amp; P5 &amp;  "/"  &amp; S5 &amp;  "/", "")</f>
+        <f t="shared" ref="U5:U68" si="9" xml:space="preserve"> IF(AND(N5&lt;&gt;"", M5&lt;&gt;""), "    - xform/》" &amp; P5 &amp;  "/"  &amp; S5 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》ann(\d)/》a${1}nn/</v>
       </c>
       <c r="W5" s="131" t="s">
         <v>1231</v>
       </c>
       <c r="X5" s="134" t="str">
-        <f t="shared" ref="X5:AG10" si="7" xml:space="preserve"> _xlfn.CONCAT($W5, IF(X$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(X$3,4)))))</f>
+        <f t="shared" ref="X5:AG10" si="10" xml:space="preserve"> _xlfn.CONCAT($W5, IF(X$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(X$3,4)))))</f>
         <v>i</v>
       </c>
       <c r="Y5" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>í</v>
       </c>
       <c r="Z5" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ì</v>
       </c>
       <c r="AA5" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>i</v>
       </c>
       <c r="AB5" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ǐ</v>
       </c>
       <c r="AC5" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>í</v>
       </c>
       <c r="AD5" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ī</v>
       </c>
       <c r="AE5" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>i̍</v>
       </c>
       <c r="AF5" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>i̋</v>
       </c>
       <c r="AG5" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>i̊</v>
       </c>
       <c r="AI5" s="136" t="str">
-        <f t="shared" ref="AI5:AJ10" si="8" xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $W5, X$2, "/", X5, "/")</f>
+        <f t="shared" ref="AI5:AJ10" si="11" xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $W5, X$2, "/", X5, "/")</f>
         <v xml:space="preserve">    - xform/》i1/i/</v>
       </c>
       <c r="AJ5" s="136" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">    - xform/》i2/í/</v>
       </c>
       <c r="AK5" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i3/ì/</v>
       </c>
       <c r="AL5" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i4/i/</v>
       </c>
       <c r="AM5" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i5/ǐ/</v>
       </c>
       <c r="AN5" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i6/í/</v>
       </c>
       <c r="AO5" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i7/ī/</v>
       </c>
       <c r="AP5" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i8/i̍/</v>
       </c>
       <c r="AQ5" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》i9/i̋/</v>
       </c>
       <c r="AR5" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》i9/i̊/</v>
       </c>
       <c r="AS5" s="134"/>
@@ -36559,7 +37085,7 @@
     </row>
     <row r="6" spans="1:47" ht="27.75" thickBot="1">
       <c r="A6" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="B6" s="141" t="s">
@@ -36588,119 +37114,119 @@
       </c>
       <c r="J6" s="58"/>
       <c r="K6" s="55">
-        <f xml:space="preserve"> LEN(D6)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L6" s="74"/>
       <c r="M6" s="58" t="str">
-        <f>C6</f>
+        <f t="shared" si="1"/>
         <v>ah</v>
       </c>
       <c r="N6" s="58" t="str">
-        <f>D6</f>
+        <f t="shared" si="2"/>
         <v>ah</v>
       </c>
       <c r="P6" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ah(\d)</v>
       </c>
       <c r="Q6" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R6" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S6" s="123" t="str">
-        <f t="shared" ref="S6:S69" si="9" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(M6,R6-1), "》", MID(M6,R6,1), "${1}", RIGHT(M6, LEN(M6)-R6)), "" )</f>
+        <f t="shared" ref="S6:S69" si="12" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(M6,R6-1), "》", MID(M6,R6,1), "${1}", RIGHT(M6, LEN(M6)-R6)), "" )</f>
         <v>》a${1}h</v>
       </c>
       <c r="T6" s="56"/>
       <c r="U6" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ah(\d)/》a${1}h/</v>
       </c>
       <c r="W6" s="131" t="s">
         <v>1229</v>
       </c>
       <c r="X6" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>u</v>
       </c>
       <c r="Y6" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ú</v>
       </c>
       <c r="Z6" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ù</v>
       </c>
       <c r="AA6" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>u</v>
       </c>
       <c r="AB6" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ǔ</v>
       </c>
       <c r="AC6" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ú</v>
       </c>
       <c r="AD6" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ū</v>
       </c>
       <c r="AE6" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>u̍</v>
       </c>
       <c r="AF6" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ű</v>
       </c>
       <c r="AG6" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ů</v>
       </c>
       <c r="AI6" s="136" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">    - xform/》u1/u/</v>
       </c>
       <c r="AJ6" s="136" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">    - xform/》u2/ú/</v>
       </c>
       <c r="AK6" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u3/ù/</v>
       </c>
       <c r="AL6" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u4/u/</v>
       </c>
       <c r="AM6" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u5/ǔ/</v>
       </c>
       <c r="AN6" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u6/ú/</v>
       </c>
       <c r="AO6" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u7/ū/</v>
       </c>
       <c r="AP6" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u8/u̍/</v>
       </c>
       <c r="AQ6" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》u9/ű/</v>
       </c>
       <c r="AR6" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》u9/ů/</v>
       </c>
       <c r="AS6" s="134"/>
@@ -36709,7 +37235,7 @@
     </row>
     <row r="7" spans="1:47" ht="27.75" thickBot="1">
       <c r="A7" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="B7" s="141" t="s">
@@ -36740,119 +37266,119 @@
         <v>1341</v>
       </c>
       <c r="K7" s="55">
-        <f xml:space="preserve"> LEN(D7)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="L7" s="74"/>
       <c r="M7" s="58" t="str">
-        <f>C7</f>
+        <f t="shared" si="1"/>
         <v>annh</v>
       </c>
       <c r="N7" s="58" t="str">
-        <f>D7</f>
+        <f t="shared" si="2"/>
         <v>ahnn</v>
       </c>
       <c r="P7" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>annh(\d)</v>
       </c>
       <c r="Q7" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R7" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S7" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》a${1}nnh</v>
       </c>
       <c r="T7" s="56"/>
       <c r="U7" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》annh(\d)/》a${1}nnh/</v>
       </c>
       <c r="W7" s="131" t="s">
         <v>1183</v>
       </c>
       <c r="X7" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>e</v>
       </c>
       <c r="Y7" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>é</v>
       </c>
       <c r="Z7" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>è</v>
       </c>
       <c r="AA7" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>e</v>
       </c>
       <c r="AB7" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ě</v>
       </c>
       <c r="AC7" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>é</v>
       </c>
       <c r="AD7" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ē</v>
       </c>
       <c r="AE7" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>e̍</v>
       </c>
       <c r="AF7" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>e̋</v>
       </c>
       <c r="AG7" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>e̊</v>
       </c>
       <c r="AI7" s="136" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">    - xform/》e1/e/</v>
       </c>
       <c r="AJ7" s="136" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">    - xform/》e2/é/</v>
       </c>
       <c r="AK7" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e3/è/</v>
       </c>
       <c r="AL7" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e4/e/</v>
       </c>
       <c r="AM7" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e5/ě/</v>
       </c>
       <c r="AN7" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e6/é/</v>
       </c>
       <c r="AO7" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e7/ē/</v>
       </c>
       <c r="AP7" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e8/e̍/</v>
       </c>
       <c r="AQ7" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》e9/e̋/</v>
       </c>
       <c r="AR7" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》e9/e̊/</v>
       </c>
       <c r="AS7" s="134"/>
@@ -36861,7 +37387,7 @@
     </row>
     <row r="8" spans="1:47" ht="27.75" thickBot="1">
       <c r="A8" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="B8" s="141" t="s">
@@ -36890,119 +37416,119 @@
       </c>
       <c r="J8" s="58"/>
       <c r="K8" s="55">
-        <f xml:space="preserve"> LEN(D8)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L8" s="74"/>
       <c r="M8" s="58" t="str">
-        <f>C8</f>
+        <f t="shared" si="1"/>
         <v>am</v>
       </c>
       <c r="N8" s="58" t="str">
-        <f>D8</f>
+        <f t="shared" si="2"/>
         <v>am</v>
       </c>
       <c r="P8" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>am(\d)</v>
       </c>
       <c r="Q8" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R8" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S8" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》a${1}m</v>
       </c>
       <c r="T8" s="56"/>
       <c r="U8" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》am(\d)/》a${1}m/</v>
       </c>
       <c r="W8" s="131" t="s">
         <v>1218</v>
       </c>
       <c r="X8" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>o</v>
       </c>
       <c r="Y8" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ó</v>
       </c>
       <c r="Z8" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ò</v>
       </c>
       <c r="AA8" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>o</v>
       </c>
       <c r="AB8" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ǒ</v>
       </c>
       <c r="AC8" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ó</v>
       </c>
       <c r="AD8" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ō</v>
       </c>
       <c r="AE8" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>o̍</v>
       </c>
       <c r="AF8" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ő</v>
       </c>
       <c r="AG8" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>o̊</v>
       </c>
       <c r="AI8" s="136" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">    - xform/》o1/o/</v>
       </c>
       <c r="AJ8" s="136" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">    - xform/》o2/ó/</v>
       </c>
       <c r="AK8" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o3/ò/</v>
       </c>
       <c r="AL8" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o4/o/</v>
       </c>
       <c r="AM8" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o5/ǒ/</v>
       </c>
       <c r="AN8" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o6/ó/</v>
       </c>
       <c r="AO8" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o7/ō/</v>
       </c>
       <c r="AP8" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o8/o̍/</v>
       </c>
       <c r="AQ8" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》o9/ő/</v>
       </c>
       <c r="AR8" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》o9/o̊/</v>
       </c>
       <c r="AS8" s="134"/>
@@ -37011,7 +37537,7 @@
     </row>
     <row r="9" spans="1:47" ht="27.75" thickBot="1">
       <c r="A9" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="B9" s="141" t="s">
@@ -37040,119 +37566,119 @@
       </c>
       <c r="J9" s="58"/>
       <c r="K9" s="55">
-        <f xml:space="preserve"> LEN(D9)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L9" s="74"/>
       <c r="M9" s="58" t="str">
-        <f>C9</f>
+        <f t="shared" si="1"/>
         <v>an</v>
       </c>
       <c r="N9" s="58" t="str">
-        <f>D9</f>
+        <f t="shared" si="2"/>
         <v>an</v>
       </c>
       <c r="P9" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>an(\d)</v>
       </c>
       <c r="Q9" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R9" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S9" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》a${1}n</v>
       </c>
       <c r="T9" s="56"/>
       <c r="U9" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》an(\d)/》a${1}n/</v>
       </c>
       <c r="W9" s="131" t="s">
         <v>1335</v>
       </c>
       <c r="X9" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>m</v>
       </c>
       <c r="Y9" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ḿ</v>
       </c>
       <c r="Z9" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>m̀</v>
       </c>
       <c r="AA9" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>m</v>
       </c>
       <c r="AB9" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>m̌</v>
       </c>
       <c r="AC9" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ḿ</v>
       </c>
       <c r="AD9" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>m̄</v>
       </c>
       <c r="AE9" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>m̍</v>
       </c>
       <c r="AF9" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>m̋</v>
       </c>
       <c r="AG9" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>m̊</v>
       </c>
       <c r="AI9" s="136" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">    - xform/》m1/m/</v>
       </c>
       <c r="AJ9" s="136" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">    - xform/》m2/ḿ/</v>
       </c>
       <c r="AK9" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m3/m̀/</v>
       </c>
       <c r="AL9" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m4/m/</v>
       </c>
       <c r="AM9" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m5/m̌/</v>
       </c>
       <c r="AN9" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m6/ḿ/</v>
       </c>
       <c r="AO9" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m7/m̄/</v>
       </c>
       <c r="AP9" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m8/m̍/</v>
       </c>
       <c r="AQ9" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》m9/m̋/</v>
       </c>
       <c r="AR9" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》m9/m̊/</v>
       </c>
       <c r="AS9" s="134"/>
@@ -37161,7 +37687,7 @@
     </row>
     <row r="10" spans="1:47" ht="27.75" thickBot="1">
       <c r="A10" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="B10" s="141" t="s">
@@ -37190,119 +37716,119 @@
       </c>
       <c r="J10" s="58"/>
       <c r="K10" s="55">
-        <f xml:space="preserve"> LEN(D10)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="L10" s="74"/>
       <c r="M10" s="58" t="str">
-        <f>C10</f>
+        <f t="shared" si="1"/>
         <v>ang</v>
       </c>
       <c r="N10" s="58" t="str">
-        <f>D10</f>
+        <f t="shared" si="2"/>
         <v>ang</v>
       </c>
       <c r="P10" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ang(\d)</v>
       </c>
       <c r="Q10" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R10" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S10" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》a${1}ng</v>
       </c>
       <c r="T10" s="56"/>
       <c r="U10" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ang(\d)/》a${1}ng/</v>
       </c>
       <c r="W10" s="131" t="s">
         <v>1334</v>
       </c>
       <c r="X10" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>n</v>
       </c>
       <c r="Y10" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ń</v>
       </c>
       <c r="Z10" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ǹ</v>
       </c>
       <c r="AA10" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>n</v>
       </c>
       <c r="AB10" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ň</v>
       </c>
       <c r="AC10" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>ń</v>
       </c>
       <c r="AD10" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>n̄</v>
       </c>
       <c r="AE10" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>n̍</v>
       </c>
       <c r="AF10" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>n̋</v>
       </c>
       <c r="AG10" s="134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>n̊</v>
       </c>
       <c r="AI10" s="136" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">    - xform/》n1/n/</v>
       </c>
       <c r="AJ10" s="136" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">    - xform/》n2/ń/</v>
       </c>
       <c r="AK10" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n3/ǹ/</v>
       </c>
       <c r="AL10" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n4/n/</v>
       </c>
       <c r="AM10" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n5/ň/</v>
       </c>
       <c r="AN10" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n6/ń/</v>
       </c>
       <c r="AO10" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n7/n̄/</v>
       </c>
       <c r="AP10" s="136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n8/n̍/</v>
       </c>
       <c r="AQ10" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》n9/n̋/</v>
       </c>
       <c r="AR10" s="136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    - xform/》n9/n̊/</v>
       </c>
       <c r="AS10" s="134"/>
@@ -37311,7 +37837,7 @@
     </row>
     <row r="11" spans="1:47" ht="27.75" thickBot="1">
       <c r="A11" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="B11" s="141" t="s">
@@ -37340,42 +37866,42 @@
       </c>
       <c r="J11" s="58"/>
       <c r="K11" s="55">
-        <f xml:space="preserve"> LEN(D11)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L11" s="74"/>
       <c r="M11" s="58" t="str">
-        <f>C11</f>
+        <f t="shared" si="1"/>
         <v>ap</v>
       </c>
       <c r="N11" s="58" t="str">
-        <f>D11</f>
+        <f t="shared" si="2"/>
         <v>ap</v>
       </c>
       <c r="P11" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ap(\d)</v>
       </c>
       <c r="Q11" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R11" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S11" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》a${1}p</v>
       </c>
       <c r="T11" s="56"/>
       <c r="U11" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ap(\d)/》a${1}p/</v>
       </c>
     </row>
     <row r="12" spans="1:47" ht="27.75" thickBot="1">
       <c r="A12" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="B12" s="141" t="s">
@@ -37404,42 +37930,42 @@
       </c>
       <c r="J12" s="58"/>
       <c r="K12" s="55">
-        <f xml:space="preserve"> LEN(D12)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L12" s="74"/>
       <c r="M12" s="58" t="str">
-        <f>C12</f>
+        <f t="shared" si="1"/>
         <v>at</v>
       </c>
       <c r="N12" s="58" t="str">
-        <f>D12</f>
+        <f t="shared" si="2"/>
         <v>at</v>
       </c>
       <c r="P12" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>at(\d)</v>
       </c>
       <c r="Q12" s="126" t="s">
         <v>1218</v>
       </c>
       <c r="R12" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S12" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T12" s="56"/>
       <c r="U12" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》at(\d)//</v>
       </c>
     </row>
     <row r="13" spans="1:47" ht="27.75" thickBot="1">
       <c r="A13" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="B13" s="141" t="s">
@@ -37468,42 +37994,42 @@
       </c>
       <c r="J13" s="58"/>
       <c r="K13" s="55">
-        <f xml:space="preserve"> LEN(D13)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L13" s="74"/>
       <c r="M13" s="58" t="str">
-        <f>C13</f>
+        <f t="shared" si="1"/>
         <v>ak</v>
       </c>
       <c r="N13" s="58" t="str">
-        <f>D13</f>
+        <f t="shared" si="2"/>
         <v>ak</v>
       </c>
       <c r="P13" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ak(\d)</v>
       </c>
       <c r="Q13" s="126" t="s">
         <v>1183</v>
       </c>
       <c r="R13" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S13" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T13" s="56"/>
       <c r="U13" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ak(\d)//</v>
       </c>
     </row>
     <row r="14" spans="1:47" ht="27.75" thickBot="1">
       <c r="A14" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="B14" s="141" t="s">
@@ -37532,42 +38058,42 @@
       </c>
       <c r="J14" s="58"/>
       <c r="K14" s="55">
-        <f xml:space="preserve"> LEN(D14)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L14" s="74"/>
       <c r="M14" s="58" t="str">
-        <f>C14</f>
+        <f t="shared" si="1"/>
         <v>ai</v>
       </c>
       <c r="N14" s="58" t="str">
-        <f>D14</f>
+        <f t="shared" si="2"/>
         <v>ai</v>
       </c>
       <c r="P14" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ai(\d)</v>
       </c>
       <c r="Q14" s="126" t="s">
         <v>1218</v>
       </c>
       <c r="R14" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S14" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T14" s="56"/>
       <c r="U14" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ai(\d)//</v>
       </c>
     </row>
     <row r="15" spans="1:47" ht="27.75" thickBot="1">
       <c r="A15" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="B15" s="141" t="s">
@@ -37598,42 +38124,42 @@
         <v>1341</v>
       </c>
       <c r="K15" s="55">
-        <f xml:space="preserve"> LEN(D15)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="L15" s="74"/>
       <c r="M15" s="58" t="str">
-        <f>C15</f>
+        <f t="shared" si="1"/>
         <v>ainn</v>
       </c>
       <c r="N15" s="58" t="str">
-        <f>D15</f>
+        <f t="shared" si="2"/>
         <v>ainn</v>
       </c>
       <c r="P15" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ainn(\d)</v>
       </c>
       <c r="Q15" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R15" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S15" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》a${1}inn</v>
       </c>
       <c r="T15" s="56"/>
       <c r="U15" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ainn(\d)/》a${1}inn/</v>
       </c>
     </row>
     <row r="16" spans="1:47" ht="30.75" thickBot="1">
       <c r="A16" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="B16" s="141" t="s">
@@ -37662,42 +38188,42 @@
       </c>
       <c r="J16" s="58"/>
       <c r="K16" s="55">
-        <f xml:space="preserve"> LEN(D16)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="L16" s="74"/>
       <c r="M16" s="58" t="str">
-        <f>C16</f>
+        <f t="shared" si="1"/>
         <v>aih</v>
       </c>
       <c r="N16" s="58" t="str">
-        <f>D16</f>
+        <f t="shared" si="2"/>
         <v>aih</v>
       </c>
       <c r="P16" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>aih(\d)</v>
       </c>
       <c r="Q16" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R16" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S16" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》a${1}ih</v>
       </c>
       <c r="T16" s="56"/>
       <c r="U16" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》aih(\d)/》a${1}ih/</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="27.75" thickBot="1">
       <c r="A17" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="B17" s="141" t="s">
@@ -37726,42 +38252,42 @@
       </c>
       <c r="J17" s="58"/>
       <c r="K17" s="55">
-        <f xml:space="preserve"> LEN(D17)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L17" s="74"/>
       <c r="M17" s="58" t="str">
-        <f>C17</f>
+        <f t="shared" si="1"/>
         <v>au</v>
       </c>
       <c r="N17" s="58" t="str">
-        <f>D17</f>
+        <f t="shared" si="2"/>
         <v>au</v>
       </c>
       <c r="P17" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>au(\d)</v>
       </c>
       <c r="Q17" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R17" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S17" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》a${1}u</v>
       </c>
       <c r="T17" s="56"/>
       <c r="U17" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》au(\d)/》a${1}u/</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="27.75" thickBot="1">
       <c r="A18" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="B18" s="141" t="s">
@@ -37790,42 +38316,42 @@
       </c>
       <c r="J18" s="58"/>
       <c r="K18" s="55">
-        <f xml:space="preserve"> LEN(D18)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="L18" s="74"/>
       <c r="M18" s="58" t="str">
-        <f>C18</f>
+        <f t="shared" si="1"/>
         <v>auh</v>
       </c>
       <c r="N18" s="58" t="str">
-        <f>D18</f>
+        <f t="shared" si="2"/>
         <v>auh</v>
       </c>
       <c r="P18" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>auh(\d)</v>
       </c>
       <c r="Q18" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R18" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S18" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》a${1}uh</v>
       </c>
       <c r="T18" s="56"/>
       <c r="U18" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》auh(\d)/》a${1}uh/</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="27.75" thickBot="1">
       <c r="A19" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="B19" s="141" t="s">
@@ -37854,42 +38380,42 @@
       </c>
       <c r="J19" s="58"/>
       <c r="K19" s="55">
-        <f xml:space="preserve"> LEN(D19)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L19" s="74"/>
       <c r="M19" s="58" t="str">
-        <f>C19</f>
+        <f t="shared" si="1"/>
         <v>e</v>
       </c>
       <c r="N19" s="58" t="str">
-        <f>D19</f>
+        <f t="shared" si="2"/>
         <v>ei</v>
       </c>
       <c r="P19" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>e(\d)</v>
       </c>
       <c r="Q19" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R19" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S19" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T19" s="56"/>
       <c r="U19" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》e(\d)//</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="27.75" thickBot="1">
       <c r="A20" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="B20" s="141" t="s">
@@ -37920,42 +38446,42 @@
         <v>1341</v>
       </c>
       <c r="K20" s="55">
-        <f xml:space="preserve"> LEN(D20)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="L20" s="74"/>
       <c r="M20" s="58" t="str">
-        <f>C20</f>
+        <f t="shared" si="1"/>
         <v>enn</v>
       </c>
       <c r="N20" s="58" t="str">
-        <f>D20</f>
+        <f t="shared" si="2"/>
         <v>enn</v>
       </c>
       <c r="P20" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>enn(\d)</v>
       </c>
       <c r="Q20" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R20" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S20" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T20" s="56"/>
       <c r="U20" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》enn(\d)//</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="27.75" thickBot="1">
       <c r="A21" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="B21" s="141" t="s">
@@ -37984,42 +38510,42 @@
       </c>
       <c r="J21" s="58"/>
       <c r="K21" s="55">
-        <f xml:space="preserve"> LEN(D21)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L21" s="74"/>
       <c r="M21" s="58" t="str">
-        <f>C21</f>
+        <f t="shared" si="1"/>
         <v>eh</v>
       </c>
       <c r="N21" s="58" t="str">
-        <f>D21</f>
+        <f t="shared" si="2"/>
         <v>eh</v>
       </c>
       <c r="P21" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>eh(\d)</v>
       </c>
       <c r="Q21" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R21" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S21" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T21" s="56"/>
       <c r="U21" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》eh(\d)//</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="30.75" thickBot="1">
       <c r="A22" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="B22" s="141" t="s">
@@ -38050,42 +38576,42 @@
         <v>1341</v>
       </c>
       <c r="K22" s="55">
-        <f xml:space="preserve"> LEN(D22)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="L22" s="74"/>
       <c r="M22" s="58" t="str">
-        <f>C22</f>
+        <f t="shared" si="1"/>
         <v>ennh</v>
       </c>
       <c r="N22" s="58" t="str">
-        <f>D22</f>
+        <f t="shared" si="2"/>
         <v>ennh</v>
       </c>
       <c r="P22" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ennh(\d)</v>
       </c>
       <c r="Q22" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R22" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S22" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T22" s="56"/>
       <c r="U22" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ennh(\d)//</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="27.75" thickBot="1">
       <c r="A23" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="B23" s="141" t="s">
@@ -38114,42 +38640,42 @@
       </c>
       <c r="J23" s="58"/>
       <c r="K23" s="55">
-        <f xml:space="preserve"> LEN(D23)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L23" s="74"/>
       <c r="M23" s="58" t="str">
-        <f>C23</f>
+        <f t="shared" si="1"/>
         <v>i</v>
       </c>
       <c r="N23" s="58" t="str">
-        <f>D23</f>
+        <f t="shared" si="2"/>
         <v>i</v>
       </c>
       <c r="P23" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>i(\d)</v>
       </c>
       <c r="Q23" s="126" t="s">
         <v>1218</v>
       </c>
       <c r="R23" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S23" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T23" s="56"/>
       <c r="U23" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》i(\d)//</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="27.75" thickBot="1">
       <c r="A24" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="B24" s="141" t="s">
@@ -38180,42 +38706,42 @@
         <v>1341</v>
       </c>
       <c r="K24" s="55">
-        <f xml:space="preserve"> LEN(D24)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="L24" s="74"/>
       <c r="M24" s="58" t="str">
-        <f>C24</f>
+        <f t="shared" si="1"/>
         <v>inn</v>
       </c>
       <c r="N24" s="58" t="str">
-        <f>D24</f>
+        <f t="shared" si="2"/>
         <v>inn</v>
       </c>
       <c r="P24" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>inn(\d)</v>
       </c>
       <c r="Q24" s="126" t="s">
         <v>1218</v>
       </c>
       <c r="R24" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S24" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T24" s="56"/>
       <c r="U24" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》inn(\d)//</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="27.75" thickBot="1">
       <c r="A25" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="B25" s="141" t="s">
@@ -38244,42 +38770,42 @@
       </c>
       <c r="J25" s="58"/>
       <c r="K25" s="55">
-        <f xml:space="preserve"> LEN(D25)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L25" s="74"/>
       <c r="M25" s="58" t="str">
-        <f>C25</f>
+        <f t="shared" si="1"/>
         <v>ih</v>
       </c>
       <c r="N25" s="58" t="str">
-        <f>D25</f>
+        <f t="shared" si="2"/>
         <v>ih</v>
       </c>
       <c r="P25" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ih(\d)</v>
       </c>
       <c r="Q25" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R25" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S25" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T25" s="56"/>
       <c r="U25" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ih(\d)//</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="27.75" thickBot="1">
       <c r="A26" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="B26" s="141" t="s">
@@ -38308,42 +38834,42 @@
       </c>
       <c r="J26" s="58"/>
       <c r="K26" s="55">
-        <f xml:space="preserve"> LEN(D26)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L26" s="74"/>
       <c r="M26" s="58" t="str">
-        <f>C26</f>
+        <f t="shared" si="1"/>
         <v>im</v>
       </c>
       <c r="N26" s="58" t="str">
-        <f>D26</f>
+        <f t="shared" si="2"/>
         <v>im</v>
       </c>
       <c r="P26" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>im(\d)</v>
       </c>
       <c r="Q26" s="126" t="s">
         <v>1183</v>
       </c>
       <c r="R26" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S26" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T26" s="56"/>
       <c r="U26" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》im(\d)//</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="27.75" thickBot="1">
       <c r="A27" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="B27" s="141" t="s">
@@ -38372,42 +38898,42 @@
       </c>
       <c r="J27" s="58"/>
       <c r="K27" s="55">
-        <f xml:space="preserve"> LEN(D27)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L27" s="74"/>
       <c r="M27" s="58" t="str">
-        <f>C27</f>
+        <f t="shared" si="1"/>
         <v>in</v>
       </c>
       <c r="N27" s="58" t="str">
-        <f>D27</f>
+        <f t="shared" si="2"/>
         <v>in</v>
       </c>
       <c r="P27" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>in(\d)</v>
       </c>
       <c r="Q27" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R27" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S27" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T27" s="56"/>
       <c r="U27" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》in(\d)//</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="27.75" thickBot="1">
       <c r="A28" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>25</v>
       </c>
       <c r="B28" s="141" t="s">
@@ -38436,42 +38962,42 @@
       </c>
       <c r="J28" s="58"/>
       <c r="K28" s="55">
-        <f xml:space="preserve"> LEN(D28)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="L28" s="74"/>
       <c r="M28" s="58" t="str">
-        <f>C28</f>
+        <f t="shared" si="1"/>
         <v>ing</v>
       </c>
       <c r="N28" s="58" t="str">
-        <f>D28</f>
+        <f t="shared" si="2"/>
         <v>ing</v>
       </c>
       <c r="P28" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ing(\d)</v>
       </c>
       <c r="Q28" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R28" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S28" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T28" s="56"/>
       <c r="U28" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ing(\d)//</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="27.75" thickBot="1">
       <c r="A29" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="B29" s="141" t="s">
@@ -38500,42 +39026,42 @@
       </c>
       <c r="J29" s="58"/>
       <c r="K29" s="55">
-        <f xml:space="preserve"> LEN(D29)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L29" s="74"/>
       <c r="M29" s="58" t="str">
-        <f>C29</f>
+        <f t="shared" si="1"/>
         <v>ip</v>
       </c>
       <c r="N29" s="58" t="str">
-        <f>D29</f>
+        <f t="shared" si="2"/>
         <v>ip</v>
       </c>
       <c r="P29" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ip(\d)</v>
       </c>
       <c r="Q29" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R29" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S29" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T29" s="56"/>
       <c r="U29" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ip(\d)//</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.75" thickBot="1">
       <c r="A30" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="B30" s="141" t="s">
@@ -38564,42 +39090,42 @@
       </c>
       <c r="J30" s="58"/>
       <c r="K30" s="55">
-        <f xml:space="preserve"> LEN(D30)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L30" s="74"/>
       <c r="M30" s="58" t="str">
-        <f>C30</f>
+        <f t="shared" si="1"/>
         <v>it</v>
       </c>
       <c r="N30" s="58" t="str">
-        <f>D30</f>
+        <f t="shared" si="2"/>
         <v>it</v>
       </c>
       <c r="P30" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>it(\d)</v>
       </c>
       <c r="Q30" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R30" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S30" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T30" s="56"/>
       <c r="U30" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》it(\d)//</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="27.75" thickBot="1">
       <c r="A31" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="B31" s="141" t="s">
@@ -38628,42 +39154,42 @@
       </c>
       <c r="J31" s="58"/>
       <c r="K31" s="55">
-        <f xml:space="preserve"> LEN(D31)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L31" s="74"/>
       <c r="M31" s="58" t="str">
-        <f>C31</f>
+        <f t="shared" si="1"/>
         <v>ik</v>
       </c>
       <c r="N31" s="58" t="str">
-        <f>D31</f>
+        <f t="shared" si="2"/>
         <v>ik</v>
       </c>
       <c r="P31" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ik(\d)</v>
       </c>
       <c r="Q31" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R31" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S31" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T31" s="56"/>
       <c r="U31" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ik(\d)//</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="27.75" thickBot="1">
       <c r="A32" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="B32" s="141" t="s">
@@ -38692,42 +39218,42 @@
       </c>
       <c r="J32" s="58"/>
       <c r="K32" s="55">
-        <f xml:space="preserve"> LEN(D32)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L32" s="74"/>
       <c r="M32" s="58" t="str">
-        <f>C32</f>
+        <f t="shared" si="1"/>
         <v>ia</v>
       </c>
       <c r="N32" s="58" t="str">
-        <f>D32</f>
+        <f t="shared" si="2"/>
         <v>ia</v>
       </c>
       <c r="P32" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ia(\d)</v>
       </c>
       <c r="Q32" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R32" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="S32" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>i》a${1}</v>
       </c>
       <c r="T32" s="56"/>
       <c r="U32" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ia(\d)/i》a${1}/</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="27.75" thickBot="1">
       <c r="A33" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="B33" s="141" t="s">
@@ -38758,42 +39284,42 @@
         <v>1341</v>
       </c>
       <c r="K33" s="55">
-        <f xml:space="preserve"> LEN(D33)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="L33" s="74"/>
       <c r="M33" s="58" t="str">
-        <f>C33</f>
+        <f t="shared" si="1"/>
         <v>iann</v>
       </c>
       <c r="N33" s="58" t="str">
-        <f>D33</f>
+        <f t="shared" si="2"/>
         <v>iann</v>
       </c>
       <c r="P33" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iann(\d)</v>
       </c>
       <c r="Q33" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R33" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="S33" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>i》a${1}nn</v>
       </c>
       <c r="T33" s="56"/>
       <c r="U33" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iann(\d)/i》a${1}nn/</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="27.75" thickBot="1">
       <c r="A34" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>31</v>
       </c>
       <c r="B34" s="141" t="s">
@@ -38822,42 +39348,42 @@
       </c>
       <c r="J34" s="58"/>
       <c r="K34" s="55">
-        <f xml:space="preserve"> LEN(D34)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="L34" s="74"/>
       <c r="M34" s="58" t="str">
-        <f>C34</f>
+        <f t="shared" si="1"/>
         <v>iah</v>
       </c>
       <c r="N34" s="58" t="str">
-        <f>D34</f>
+        <f t="shared" si="2"/>
         <v>iah</v>
       </c>
       <c r="P34" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iah(\d)</v>
       </c>
       <c r="Q34" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R34" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="S34" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>i》a${1}h</v>
       </c>
       <c r="T34" s="56"/>
       <c r="U34" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iah(\d)/i》a${1}h/</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="30.75" thickBot="1">
       <c r="A35" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="B35" s="141" t="s">
@@ -38888,42 +39414,42 @@
         <v>1341</v>
       </c>
       <c r="K35" s="55">
-        <f xml:space="preserve"> LEN(D35)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="L35" s="74"/>
       <c r="M35" s="58" t="str">
-        <f>C35</f>
+        <f t="shared" si="1"/>
         <v>iannh</v>
       </c>
       <c r="N35" s="58" t="str">
-        <f>D35</f>
+        <f t="shared" si="2"/>
         <v>iannh</v>
       </c>
       <c r="P35" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iannh(\d)</v>
       </c>
       <c r="Q35" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R35" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="S35" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>i》a${1}nnh</v>
       </c>
       <c r="T35" s="56"/>
       <c r="U35" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iannh(\d)/i》a${1}nnh/</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="27.75" thickBot="1">
       <c r="A36" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>33</v>
       </c>
       <c r="B36" s="141" t="s">
@@ -38952,42 +39478,42 @@
       </c>
       <c r="J36" s="58"/>
       <c r="K36" s="55">
-        <f xml:space="preserve"> LEN(D36)</f>
+        <f t="shared" ref="K36:K67" si="13" xml:space="preserve"> LEN(D36)</f>
         <v>3</v>
       </c>
       <c r="L36" s="74"/>
       <c r="M36" s="58" t="str">
-        <f>C36</f>
+        <f t="shared" ref="M36:M67" si="14">C36</f>
         <v>iam</v>
       </c>
       <c r="N36" s="58" t="str">
-        <f>D36</f>
+        <f t="shared" ref="N36:N67" si="15">D36</f>
         <v>iam</v>
       </c>
       <c r="P36" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iam(\d)</v>
       </c>
       <c r="Q36" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R36" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S36" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》i${1}am</v>
       </c>
       <c r="T36" s="56"/>
       <c r="U36" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iam(\d)/》i${1}am/</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="27.75" thickBot="1">
       <c r="A37" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>34</v>
       </c>
       <c r="B37" s="141" t="s">
@@ -39016,42 +39542,42 @@
       </c>
       <c r="J37" s="58"/>
       <c r="K37" s="55">
-        <f xml:space="preserve"> LEN(D37)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="L37" s="74"/>
       <c r="M37" s="58" t="str">
-        <f>C37</f>
+        <f t="shared" si="14"/>
         <v>ian</v>
       </c>
       <c r="N37" s="58" t="str">
-        <f>D37</f>
+        <f t="shared" si="15"/>
         <v>ian</v>
       </c>
       <c r="P37" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ian(\d)</v>
       </c>
       <c r="Q37" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R37" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S37" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》i${1}an</v>
       </c>
       <c r="T37" s="56"/>
       <c r="U37" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ian(\d)/》i${1}an/</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="27.75" thickBot="1">
       <c r="A38" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
       <c r="B38" s="141" t="s">
@@ -39080,42 +39606,42 @@
       </c>
       <c r="J38" s="58"/>
       <c r="K38" s="55">
-        <f xml:space="preserve"> LEN(D38)</f>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="L38" s="74"/>
       <c r="M38" s="58" t="str">
-        <f>C38</f>
+        <f t="shared" si="14"/>
         <v>iang</v>
       </c>
       <c r="N38" s="58" t="str">
-        <f>D38</f>
+        <f t="shared" si="15"/>
         <v>iang</v>
       </c>
       <c r="P38" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iang(\d)</v>
       </c>
       <c r="Q38" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R38" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S38" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》i${1}ang</v>
       </c>
       <c r="T38" s="56"/>
       <c r="U38" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iang(\d)/》i${1}ang/</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="27.75" thickBot="1">
       <c r="A39" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>36</v>
       </c>
       <c r="B39" s="141" t="s">
@@ -39144,42 +39670,42 @@
       </c>
       <c r="J39" s="58"/>
       <c r="K39" s="55">
-        <f xml:space="preserve"> LEN(D39)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="L39" s="74"/>
       <c r="M39" s="58" t="str">
-        <f>C39</f>
+        <f t="shared" si="14"/>
         <v>iap</v>
       </c>
       <c r="N39" s="58" t="str">
-        <f>D39</f>
+        <f t="shared" si="15"/>
         <v>iap</v>
       </c>
       <c r="P39" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iap(\d)</v>
       </c>
       <c r="Q39" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R39" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S39" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》i${1}ap</v>
       </c>
       <c r="T39" s="56"/>
       <c r="U39" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iap(\d)/》i${1}ap/</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="27.75" thickBot="1">
       <c r="A40" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>37</v>
       </c>
       <c r="B40" s="141" t="s">
@@ -39208,42 +39734,42 @@
       </c>
       <c r="J40" s="58"/>
       <c r="K40" s="55">
-        <f xml:space="preserve"> LEN(D40)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="L40" s="74"/>
       <c r="M40" s="58" t="str">
-        <f>C40</f>
+        <f t="shared" si="14"/>
         <v>iat</v>
       </c>
       <c r="N40" s="58" t="str">
-        <f>D40</f>
+        <f t="shared" si="15"/>
         <v>iat</v>
       </c>
       <c r="P40" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iat(\d)</v>
       </c>
       <c r="Q40" s="126" t="s">
         <v>1183</v>
       </c>
       <c r="R40" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S40" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T40" s="56"/>
       <c r="U40" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iat(\d)//</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="27.75" thickBot="1">
       <c r="A41" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
       <c r="B41" s="141" t="s">
@@ -39272,42 +39798,42 @@
       </c>
       <c r="J41" s="58"/>
       <c r="K41" s="55">
-        <f xml:space="preserve"> LEN(D41)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="L41" s="74"/>
       <c r="M41" s="58" t="str">
-        <f>C41</f>
+        <f t="shared" si="14"/>
         <v>iak</v>
       </c>
       <c r="N41" s="58" t="str">
-        <f>D41</f>
+        <f t="shared" si="15"/>
         <v>iak</v>
       </c>
       <c r="P41" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iak(\d)</v>
       </c>
       <c r="Q41" s="126" t="s">
         <v>1334</v>
       </c>
       <c r="R41" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S41" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T41" s="56"/>
       <c r="U41" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iak(\d)//</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="27.75" thickBot="1">
       <c r="A42" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>39</v>
       </c>
       <c r="B42" s="141" t="s">
@@ -39336,42 +39862,42 @@
       </c>
       <c r="J42" s="58"/>
       <c r="K42" s="55">
-        <f xml:space="preserve"> LEN(D42)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="L42" s="74"/>
       <c r="M42" s="58" t="str">
-        <f>C42</f>
+        <f t="shared" si="14"/>
         <v>iau</v>
       </c>
       <c r="N42" s="58" t="str">
-        <f>D42</f>
+        <f t="shared" si="15"/>
         <v>iau</v>
       </c>
       <c r="P42" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iau(\d)</v>
       </c>
       <c r="Q42" s="126" t="s">
         <v>1218</v>
       </c>
       <c r="R42" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S42" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T42" s="56"/>
       <c r="U42" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iau(\d)//</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="27.75" thickBot="1">
       <c r="A43" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="B43" s="141" t="s">
@@ -39402,42 +39928,42 @@
         <v>1341</v>
       </c>
       <c r="K43" s="55">
-        <f xml:space="preserve"> LEN(D43)</f>
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
       <c r="L43" s="74"/>
       <c r="M43" s="58" t="str">
-        <f>C43</f>
+        <f t="shared" si="14"/>
         <v>iaunn</v>
       </c>
       <c r="N43" s="58" t="str">
-        <f>D43</f>
+        <f t="shared" si="15"/>
         <v>iaunn</v>
       </c>
       <c r="P43" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iaunn(\d)</v>
       </c>
       <c r="Q43" s="126" t="s">
         <v>1218</v>
       </c>
       <c r="R43" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S43" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T43" s="56"/>
       <c r="U43" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iaunn(\d)//</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="27.75" thickBot="1">
       <c r="A44" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>41</v>
       </c>
       <c r="B44" s="141" t="s">
@@ -39466,42 +39992,42 @@
       </c>
       <c r="J44" s="58"/>
       <c r="K44" s="55">
-        <f xml:space="preserve"> LEN(D44)</f>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="L44" s="74"/>
       <c r="M44" s="58" t="str">
-        <f>C44</f>
+        <f t="shared" si="14"/>
         <v>iauh</v>
       </c>
       <c r="N44" s="58" t="str">
-        <f>D44</f>
+        <f t="shared" si="15"/>
         <v>iauh</v>
       </c>
       <c r="P44" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iauh(\d)</v>
       </c>
       <c r="Q44" s="126" t="s">
         <v>1218</v>
       </c>
       <c r="R44" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S44" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T44" s="56"/>
       <c r="U44" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iauh(\d)//</v>
       </c>
     </row>
     <row r="45" spans="1:21" ht="27.75" thickBot="1">
       <c r="A45" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>42</v>
       </c>
       <c r="B45" s="141" t="s">
@@ -39530,42 +40056,42 @@
       </c>
       <c r="J45" s="58"/>
       <c r="K45" s="55">
-        <f xml:space="preserve"> LEN(D45)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="L45" s="74"/>
       <c r="M45" s="58" t="str">
-        <f>C45</f>
+        <f t="shared" si="14"/>
         <v>io</v>
       </c>
       <c r="N45" s="58" t="str">
-        <f>D45</f>
+        <f t="shared" si="15"/>
         <v>io</v>
       </c>
       <c r="P45" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>io(\d)</v>
       </c>
       <c r="Q45" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R45" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S45" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T45" s="56"/>
       <c r="U45" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》io(\d)//</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="27.75" thickBot="1">
       <c r="A46" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>43</v>
       </c>
       <c r="B46" s="141" t="s">
@@ -39596,42 +40122,42 @@
         <v>1341</v>
       </c>
       <c r="K46" s="55">
-        <f xml:space="preserve"> LEN(D46)</f>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="L46" s="74"/>
       <c r="M46" s="58" t="str">
-        <f>C46</f>
+        <f t="shared" si="14"/>
         <v>ionn</v>
       </c>
       <c r="N46" s="58" t="str">
-        <f>D46</f>
+        <f t="shared" si="15"/>
         <v>ionn</v>
       </c>
       <c r="P46" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ionn(\d)</v>
       </c>
       <c r="Q46" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R46" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S46" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T46" s="56"/>
       <c r="U46" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ionn(\d)//</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="27.75" thickBot="1">
       <c r="A47" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>44</v>
       </c>
       <c r="B47" s="141" t="s">
@@ -39660,42 +40186,42 @@
       </c>
       <c r="J47" s="58"/>
       <c r="K47" s="55">
-        <f xml:space="preserve"> LEN(D47)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="L47" s="74"/>
       <c r="M47" s="58" t="str">
-        <f>C47</f>
+        <f t="shared" si="14"/>
         <v>ioh</v>
       </c>
       <c r="N47" s="58" t="str">
-        <f>D47</f>
+        <f t="shared" si="15"/>
         <v>ioh</v>
       </c>
       <c r="P47" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ioh(\d)</v>
       </c>
       <c r="Q47" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R47" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S47" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T47" s="56"/>
       <c r="U47" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ioh(\d)//</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="27.75" thickBot="1">
       <c r="A48" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>45</v>
       </c>
       <c r="B48" s="141" t="s">
@@ -39724,42 +40250,42 @@
       </c>
       <c r="J48" s="58"/>
       <c r="K48" s="55">
-        <f xml:space="preserve"> LEN(D48)</f>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="L48" s="74"/>
       <c r="M48" s="58" t="str">
-        <f>C48</f>
+        <f t="shared" si="14"/>
         <v>iong</v>
       </c>
       <c r="N48" s="58" t="str">
-        <f>D48</f>
+        <f t="shared" si="15"/>
         <v>iong</v>
       </c>
       <c r="P48" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iong(\d)</v>
       </c>
       <c r="Q48" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R48" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S48" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T48" s="56"/>
       <c r="U48" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iong(\d)//</v>
       </c>
     </row>
     <row r="49" spans="1:21" ht="27.75" thickBot="1">
       <c r="A49" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>46</v>
       </c>
       <c r="B49" s="141" t="s">
@@ -39788,42 +40314,42 @@
       </c>
       <c r="J49" s="58"/>
       <c r="K49" s="55">
-        <f xml:space="preserve"> LEN(D49)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="L49" s="74"/>
       <c r="M49" s="58" t="str">
-        <f>C49</f>
+        <f t="shared" si="14"/>
         <v>iok</v>
       </c>
       <c r="N49" s="58" t="str">
-        <f>D49</f>
+        <f t="shared" si="15"/>
         <v>iok</v>
       </c>
       <c r="P49" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iok(\d)</v>
       </c>
       <c r="Q49" s="126" t="s">
         <v>1183</v>
       </c>
       <c r="R49" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S49" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T49" s="56"/>
       <c r="U49" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iok(\d)//</v>
       </c>
     </row>
     <row r="50" spans="1:21" ht="27.75" thickBot="1">
       <c r="A50" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>47</v>
       </c>
       <c r="B50" s="141" t="s">
@@ -39852,42 +40378,42 @@
       </c>
       <c r="J50" s="58"/>
       <c r="K50" s="55">
-        <f xml:space="preserve"> LEN(D50)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="L50" s="74"/>
       <c r="M50" s="58" t="str">
-        <f>C50</f>
+        <f t="shared" si="14"/>
         <v>iu</v>
       </c>
       <c r="N50" s="58" t="str">
-        <f>D50</f>
+        <f t="shared" si="15"/>
         <v>iu</v>
       </c>
       <c r="P50" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iu(\d)</v>
       </c>
       <c r="Q50" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R50" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S50" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T50" s="56"/>
       <c r="U50" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iu(\d)//</v>
       </c>
     </row>
     <row r="51" spans="1:21" ht="27.75" thickBot="1">
       <c r="A51" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>48</v>
       </c>
       <c r="B51" s="141" t="s">
@@ -39918,42 +40444,42 @@
         <v>1341</v>
       </c>
       <c r="K51" s="55">
-        <f xml:space="preserve"> LEN(D51)</f>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="L51" s="74"/>
       <c r="M51" s="58" t="str">
-        <f>C51</f>
+        <f t="shared" si="14"/>
         <v>iunn</v>
       </c>
       <c r="N51" s="58" t="str">
-        <f>D51</f>
+        <f t="shared" si="15"/>
         <v>iunn</v>
       </c>
       <c r="P51" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iunn(\d)</v>
       </c>
       <c r="Q51" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R51" s="126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S51" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>》i${1}unn</v>
       </c>
       <c r="T51" s="56"/>
       <c r="U51" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iunn(\d)/》i${1}unn/</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="30.75" thickBot="1">
       <c r="A52" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>49</v>
       </c>
       <c r="B52" s="141" t="s">
@@ -39984,42 +40510,42 @@
         <v>1341</v>
       </c>
       <c r="K52" s="55">
-        <f xml:space="preserve"> LEN(D52)</f>
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
       <c r="L52" s="74"/>
       <c r="M52" s="58" t="str">
-        <f>C52</f>
+        <f t="shared" si="14"/>
         <v>iunnh</v>
       </c>
       <c r="N52" s="58" t="str">
-        <f>D52</f>
+        <f t="shared" si="15"/>
         <v>iunnh</v>
       </c>
       <c r="P52" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>iunnh(\d)</v>
       </c>
       <c r="Q52" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R52" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S52" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T52" s="56"/>
       <c r="U52" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》iunnh(\d)//</v>
       </c>
     </row>
     <row r="53" spans="1:21" ht="27.75" thickBot="1">
       <c r="A53" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>50</v>
       </c>
       <c r="B53" s="141" t="s">
@@ -40048,42 +40574,42 @@
       </c>
       <c r="J53" s="58"/>
       <c r="K53" s="55">
-        <f xml:space="preserve"> LEN(D53)</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="L53" s="74"/>
       <c r="M53" s="58" t="str">
-        <f>C53</f>
+        <f t="shared" si="14"/>
         <v>o</v>
       </c>
       <c r="N53" s="58" t="str">
-        <f>D53</f>
+        <f t="shared" si="15"/>
         <v>o</v>
       </c>
       <c r="P53" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>o(\d)</v>
       </c>
       <c r="Q53" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R53" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S53" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T53" s="56"/>
       <c r="U53" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》o(\d)//</v>
       </c>
     </row>
     <row r="54" spans="1:21" ht="27.75" thickBot="1">
       <c r="A54" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>51</v>
       </c>
       <c r="B54" s="141" t="s">
@@ -40112,42 +40638,42 @@
       </c>
       <c r="J54" s="58"/>
       <c r="K54" s="55">
-        <f xml:space="preserve"> LEN(D54)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="L54" s="74"/>
       <c r="M54" s="58" t="str">
-        <f>C54</f>
+        <f t="shared" si="14"/>
         <v>oo</v>
       </c>
       <c r="N54" s="58" t="str">
-        <f>D54</f>
+        <f t="shared" si="15"/>
         <v>oo</v>
       </c>
       <c r="P54" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>oo(\d)</v>
       </c>
       <c r="Q54" s="126" t="s">
         <v>1183</v>
       </c>
       <c r="R54" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S54" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T54" s="56"/>
       <c r="U54" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》oo(\d)//</v>
       </c>
     </row>
     <row r="55" spans="1:21" ht="27.75" thickBot="1">
       <c r="A55" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>52</v>
       </c>
       <c r="B55" s="141" t="s">
@@ -40176,42 +40702,42 @@
       </c>
       <c r="J55" s="58"/>
       <c r="K55" s="55">
-        <f xml:space="preserve"> LEN(D55)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="L55" s="74"/>
       <c r="M55" s="58" t="str">
-        <f>C55</f>
+        <f t="shared" si="14"/>
         <v>onn</v>
       </c>
       <c r="N55" s="58" t="str">
-        <f>D55</f>
+        <f t="shared" si="15"/>
         <v>onn</v>
       </c>
       <c r="P55" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>onn(\d)</v>
       </c>
       <c r="Q55" s="126" t="s">
         <v>1183</v>
       </c>
       <c r="R55" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S55" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T55" s="56"/>
       <c r="U55" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》onn(\d)//</v>
       </c>
     </row>
     <row r="56" spans="1:21" ht="27.75" thickBot="1">
       <c r="A56" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>53</v>
       </c>
       <c r="B56" s="141" t="s">
@@ -40240,42 +40766,42 @@
       </c>
       <c r="J56" s="58"/>
       <c r="K56" s="55">
-        <f xml:space="preserve"> LEN(D56)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="L56" s="74"/>
       <c r="M56" s="58" t="str">
-        <f>C56</f>
+        <f t="shared" si="14"/>
         <v>oh</v>
       </c>
       <c r="N56" s="58" t="str">
-        <f>D56</f>
+        <f t="shared" si="15"/>
         <v>oh</v>
       </c>
       <c r="P56" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>oh(\d)</v>
       </c>
       <c r="Q56" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R56" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S56" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T56" s="56"/>
       <c r="U56" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》oh(\d)//</v>
       </c>
     </row>
     <row r="57" spans="1:21" ht="30.75" thickBot="1">
       <c r="A57" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>54</v>
       </c>
       <c r="B57" s="141" t="s">
@@ -40304,42 +40830,42 @@
       </c>
       <c r="J57" s="58"/>
       <c r="K57" s="55">
-        <f xml:space="preserve"> LEN(D57)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="L57" s="74"/>
       <c r="M57" s="58" t="str">
-        <f>C57</f>
+        <f t="shared" si="14"/>
         <v>ooh</v>
       </c>
       <c r="N57" s="58" t="str">
-        <f>D57</f>
+        <f t="shared" si="15"/>
         <v>ooh</v>
       </c>
       <c r="P57" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ooh(\d)</v>
       </c>
       <c r="Q57" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R57" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S57" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T57" s="56"/>
       <c r="U57" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ooh(\d)//</v>
       </c>
     </row>
     <row r="58" spans="1:21" ht="27.75" thickBot="1">
       <c r="A58" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="B58" s="141" t="s">
@@ -40370,42 +40896,42 @@
         <v>1341</v>
       </c>
       <c r="K58" s="55">
-        <f xml:space="preserve"> LEN(D58)</f>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="L58" s="74"/>
       <c r="M58" s="58" t="str">
-        <f>C58</f>
+        <f t="shared" si="14"/>
         <v>onnh</v>
       </c>
       <c r="N58" s="58" t="str">
-        <f>D58</f>
+        <f t="shared" si="15"/>
         <v>ohnn</v>
       </c>
       <c r="P58" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>onnh(\d)</v>
       </c>
       <c r="Q58" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R58" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S58" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T58" s="56"/>
       <c r="U58" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》onnh(\d)//</v>
       </c>
     </row>
     <row r="59" spans="1:21" ht="27.75" thickBot="1">
       <c r="A59" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>56</v>
       </c>
       <c r="B59" s="141" t="s">
@@ -40434,42 +40960,42 @@
       </c>
       <c r="J59" s="58"/>
       <c r="K59" s="55">
-        <f xml:space="preserve"> LEN(D59)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="L59" s="74"/>
       <c r="M59" s="58" t="str">
-        <f>C59</f>
+        <f t="shared" si="14"/>
         <v>om</v>
       </c>
       <c r="N59" s="58" t="str">
-        <f>D59</f>
+        <f t="shared" si="15"/>
         <v>om</v>
       </c>
       <c r="P59" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>om(\d)</v>
       </c>
       <c r="Q59" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R59" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S59" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T59" s="56"/>
       <c r="U59" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》om(\d)//</v>
       </c>
     </row>
     <row r="60" spans="1:21" ht="27.75" thickBot="1">
       <c r="A60" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>57</v>
       </c>
       <c r="B60" s="141" t="s">
@@ -40498,42 +41024,42 @@
       </c>
       <c r="J60" s="58"/>
       <c r="K60" s="55">
-        <f xml:space="preserve"> LEN(D60)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="L60" s="74"/>
       <c r="M60" s="58" t="str">
-        <f>C60</f>
+        <f t="shared" si="14"/>
         <v>ong</v>
       </c>
       <c r="N60" s="58" t="str">
-        <f>D60</f>
+        <f t="shared" si="15"/>
         <v>ong</v>
       </c>
       <c r="P60" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ong(\d)</v>
       </c>
       <c r="Q60" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R60" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S60" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T60" s="56"/>
       <c r="U60" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ong(\d)//</v>
       </c>
     </row>
     <row r="61" spans="1:21" ht="27.75" thickBot="1">
       <c r="A61" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>58</v>
       </c>
       <c r="B61" s="141" t="s">
@@ -40562,42 +41088,42 @@
       </c>
       <c r="J61" s="58"/>
       <c r="K61" s="55">
-        <f xml:space="preserve"> LEN(D61)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="L61" s="74"/>
       <c r="M61" s="58" t="str">
-        <f>C61</f>
+        <f t="shared" si="14"/>
         <v>op</v>
       </c>
       <c r="N61" s="58" t="str">
-        <f>D61</f>
+        <f t="shared" si="15"/>
         <v>op</v>
       </c>
       <c r="P61" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>op(\d)</v>
       </c>
       <c r="Q61" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R61" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S61" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T61" s="56"/>
       <c r="U61" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》op(\d)//</v>
       </c>
     </row>
     <row r="62" spans="1:21" ht="27.75" thickBot="1">
       <c r="A62" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>59</v>
       </c>
       <c r="B62" s="141" t="s">
@@ -40626,42 +41152,42 @@
       </c>
       <c r="J62" s="58"/>
       <c r="K62" s="55">
-        <f xml:space="preserve"> LEN(D62)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="L62" s="74"/>
       <c r="M62" s="58" t="str">
-        <f>C62</f>
+        <f t="shared" si="14"/>
         <v>ok</v>
       </c>
       <c r="N62" s="58" t="str">
-        <f>D62</f>
+        <f t="shared" si="15"/>
         <v>ok</v>
       </c>
       <c r="P62" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ok(\d)</v>
       </c>
       <c r="Q62" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R62" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S62" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T62" s="56"/>
       <c r="U62" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ok(\d)//</v>
       </c>
     </row>
     <row r="63" spans="1:21" ht="27.75" thickBot="1">
       <c r="A63" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="B63" s="141" t="s">
@@ -40690,42 +41216,42 @@
       </c>
       <c r="J63" s="58"/>
       <c r="K63" s="55">
-        <f xml:space="preserve"> LEN(D63)</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="L63" s="74"/>
       <c r="M63" s="58" t="str">
-        <f>C63</f>
+        <f t="shared" si="14"/>
         <v>u</v>
       </c>
       <c r="N63" s="58" t="str">
-        <f>D63</f>
+        <f t="shared" si="15"/>
         <v>u</v>
       </c>
       <c r="P63" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>u(\d)</v>
       </c>
       <c r="Q63" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R63" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S63" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T63" s="56"/>
       <c r="U63" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》u(\d)//</v>
       </c>
     </row>
     <row r="64" spans="1:21" ht="27.75" thickBot="1">
       <c r="A64" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>61</v>
       </c>
       <c r="B64" s="141" t="s">
@@ -40754,42 +41280,42 @@
       </c>
       <c r="J64" s="58"/>
       <c r="K64" s="55">
-        <f xml:space="preserve"> LEN(D64)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="L64" s="74"/>
       <c r="M64" s="58" t="str">
-        <f>C64</f>
+        <f t="shared" si="14"/>
         <v>uh</v>
       </c>
       <c r="N64" s="58" t="str">
-        <f>D64</f>
+        <f t="shared" si="15"/>
         <v>uh</v>
       </c>
       <c r="P64" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>uh(\d)</v>
       </c>
       <c r="Q64" s="126" t="s">
         <v>1183</v>
       </c>
       <c r="R64" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S64" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T64" s="56"/>
       <c r="U64" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》uh(\d)//</v>
       </c>
     </row>
     <row r="65" spans="1:21" ht="27.75" thickBot="1">
       <c r="A65" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>62</v>
       </c>
       <c r="B65" s="141" t="s">
@@ -40818,42 +41344,42 @@
       </c>
       <c r="J65" s="58"/>
       <c r="K65" s="55">
-        <f xml:space="preserve"> LEN(D65)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="L65" s="74"/>
       <c r="M65" s="58" t="str">
-        <f>C65</f>
+        <f t="shared" si="14"/>
         <v>un</v>
       </c>
       <c r="N65" s="58" t="str">
-        <f>D65</f>
+        <f t="shared" si="15"/>
         <v>un</v>
       </c>
       <c r="P65" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>un(\d)</v>
       </c>
       <c r="Q65" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R65" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S65" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T65" s="56"/>
       <c r="U65" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》un(\d)//</v>
       </c>
     </row>
     <row r="66" spans="1:21" ht="27.75" thickBot="1">
       <c r="A66" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>63</v>
       </c>
       <c r="B66" s="141" t="s">
@@ -40882,42 +41408,42 @@
       </c>
       <c r="J66" s="58"/>
       <c r="K66" s="55">
-        <f xml:space="preserve"> LEN(D66)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="L66" s="74"/>
       <c r="M66" s="58" t="str">
-        <f>C66</f>
+        <f t="shared" si="14"/>
         <v>ut</v>
       </c>
       <c r="N66" s="58" t="str">
-        <f>D66</f>
+        <f t="shared" si="15"/>
         <v>ut</v>
       </c>
       <c r="P66" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ut(\d)</v>
       </c>
       <c r="Q66" s="126" t="s">
         <v>1230</v>
       </c>
       <c r="R66" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S66" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T66" s="56"/>
       <c r="U66" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ut(\d)//</v>
       </c>
     </row>
     <row r="67" spans="1:21" ht="27.75" thickBot="1">
       <c r="A67" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>64</v>
       </c>
       <c r="B67" s="141" t="s">
@@ -40946,42 +41472,42 @@
       </c>
       <c r="J67" s="58"/>
       <c r="K67" s="55">
-        <f xml:space="preserve"> LEN(D67)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="L67" s="74"/>
       <c r="M67" s="58" t="str">
-        <f>C67</f>
+        <f t="shared" si="14"/>
         <v>ua</v>
       </c>
       <c r="N67" s="58" t="str">
-        <f>D67</f>
+        <f t="shared" si="15"/>
         <v>ua</v>
       </c>
       <c r="P67" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>ua(\d)</v>
       </c>
       <c r="Q67" s="126" t="s">
         <v>1183</v>
       </c>
       <c r="R67" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S67" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T67" s="56"/>
       <c r="U67" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》ua(\d)//</v>
       </c>
     </row>
     <row r="68" spans="1:21" ht="27.75" thickBot="1">
       <c r="A68" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>65</v>
       </c>
       <c r="B68" s="141" t="s">
@@ -41010,42 +41536,42 @@
       </c>
       <c r="J68" s="58"/>
       <c r="K68" s="55">
-        <f xml:space="preserve"> LEN(D68)</f>
+        <f t="shared" ref="K68:K85" si="16" xml:space="preserve"> LEN(D68)</f>
         <v>4</v>
       </c>
       <c r="L68" s="74"/>
       <c r="M68" s="58" t="str">
-        <f>C68</f>
+        <f t="shared" ref="M68:M85" si="17">C68</f>
         <v>uann</v>
       </c>
       <c r="N68" s="58" t="str">
-        <f>D68</f>
+        <f t="shared" ref="N68:N85" si="18">D68</f>
         <v>uann</v>
       </c>
       <c r="P68" s="123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>uann(\d)</v>
       </c>
       <c r="Q68" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R68" s="126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S68" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T68" s="56"/>
       <c r="U68" s="57" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/》uann(\d)//</v>
       </c>
     </row>
     <row r="69" spans="1:21" ht="27.75" thickBot="1">
       <c r="A69" s="58">
-        <f t="shared" ref="A69:A85" si="10" xml:space="preserve"> ROW() - 3</f>
+        <f t="shared" ref="A69:A85" si="19" xml:space="preserve"> ROW() - 3</f>
         <v>66</v>
       </c>
       <c r="B69" s="141" t="s">
@@ -41074,42 +41600,42 @@
       </c>
       <c r="J69" s="58"/>
       <c r="K69" s="55">
-        <f xml:space="preserve"> LEN(D69)</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="L69" s="74"/>
       <c r="M69" s="58" t="str">
-        <f>C69</f>
+        <f t="shared" si="17"/>
         <v>uah</v>
       </c>
       <c r="N69" s="58" t="str">
-        <f>D69</f>
+        <f t="shared" si="18"/>
         <v>uah</v>
       </c>
       <c r="P69" s="123" t="str">
-        <f t="shared" ref="P69:P85" si="11" xml:space="preserve"> _xlfn.CONCAT(M69, "(\d)")</f>
+        <f t="shared" ref="P69:P85" si="20" xml:space="preserve"> _xlfn.CONCAT(M69, "(\d)")</f>
         <v>uah(\d)</v>
       </c>
       <c r="Q69" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R69" s="126" t="str">
-        <f t="shared" ref="R69:R85" si="12" xml:space="preserve"> IFERROR( IF(Q69="", "", SEARCH(Q69, $M69)), "")</f>
+        <f t="shared" ref="R69:R85" si="21" xml:space="preserve"> IFERROR( IF(Q69="", "", SEARCH(Q69, $M69)), "")</f>
         <v/>
       </c>
       <c r="S69" s="123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T69" s="56"/>
       <c r="U69" s="57" t="str">
-        <f t="shared" ref="U69:U85" si="13" xml:space="preserve"> IF(AND(N69&lt;&gt;"", M69&lt;&gt;""), "    - xform/》" &amp; P69 &amp;  "/"  &amp; S69 &amp;  "/", "")</f>
+        <f t="shared" ref="U69:U85" si="22" xml:space="preserve"> IF(AND(N69&lt;&gt;"", M69&lt;&gt;""), "    - xform/》" &amp; P69 &amp;  "/"  &amp; S69 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》uah(\d)//</v>
       </c>
     </row>
     <row r="70" spans="1:21" ht="27.75" thickBot="1">
       <c r="A70" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>67</v>
       </c>
       <c r="B70" s="141" t="s">
@@ -41138,42 +41664,42 @@
       </c>
       <c r="J70" s="58"/>
       <c r="K70" s="55">
-        <f xml:space="preserve"> LEN(D70)</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="L70" s="74"/>
       <c r="M70" s="58" t="str">
-        <f>C70</f>
+        <f t="shared" si="17"/>
         <v>uan</v>
       </c>
       <c r="N70" s="58" t="str">
-        <f>D70</f>
+        <f t="shared" si="18"/>
         <v>uan</v>
       </c>
       <c r="P70" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>uan(\d)</v>
       </c>
       <c r="Q70" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R70" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S70" s="123" t="str">
-        <f t="shared" ref="S70:S85" si="14" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(M70,R70-1), "》", MID(M70,R70,1), "${1}", RIGHT(M70, LEN(M70)-R70)), "" )</f>
+        <f t="shared" ref="S70:S85" si="23" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(M70,R70-1), "》", MID(M70,R70,1), "${1}", RIGHT(M70, LEN(M70)-R70)), "" )</f>
         <v/>
       </c>
       <c r="T70" s="56"/>
       <c r="U70" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uan(\d)//</v>
       </c>
     </row>
     <row r="71" spans="1:21" ht="27.75" thickBot="1">
       <c r="A71" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>68</v>
       </c>
       <c r="B71" s="141" t="s">
@@ -41202,42 +41728,42 @@
       </c>
       <c r="J71" s="58"/>
       <c r="K71" s="55">
-        <f xml:space="preserve"> LEN(D71)</f>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="L71" s="74"/>
       <c r="M71" s="58" t="str">
-        <f>C71</f>
+        <f t="shared" si="17"/>
         <v>uang</v>
       </c>
       <c r="N71" s="58" t="str">
-        <f>D71</f>
+        <f t="shared" si="18"/>
         <v>uang</v>
       </c>
       <c r="P71" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>uang(\d)</v>
       </c>
       <c r="Q71" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R71" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S71" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T71" s="56"/>
       <c r="U71" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uang(\d)//</v>
       </c>
     </row>
     <row r="72" spans="1:21" ht="27.75" thickBot="1">
       <c r="A72" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>69</v>
       </c>
       <c r="B72" s="141" t="s">
@@ -41266,42 +41792,42 @@
       </c>
       <c r="J72" s="58"/>
       <c r="K72" s="55">
-        <f xml:space="preserve"> LEN(D72)</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="L72" s="74"/>
       <c r="M72" s="58" t="str">
-        <f>C72</f>
+        <f t="shared" si="17"/>
         <v>uat</v>
       </c>
       <c r="N72" s="58" t="str">
-        <f>D72</f>
+        <f t="shared" si="18"/>
         <v>uat</v>
       </c>
       <c r="P72" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>uat(\d)</v>
       </c>
       <c r="Q72" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R72" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S72" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T72" s="56"/>
       <c r="U72" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uat(\d)//</v>
       </c>
     </row>
     <row r="73" spans="1:21" ht="27.75" thickBot="1">
       <c r="A73" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>70</v>
       </c>
       <c r="B73" s="141" t="s">
@@ -41330,42 +41856,42 @@
       </c>
       <c r="J73" s="58"/>
       <c r="K73" s="55">
-        <f xml:space="preserve"> LEN(D73)</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="L73" s="74"/>
       <c r="M73" s="58" t="str">
-        <f>C73</f>
+        <f t="shared" si="17"/>
         <v>uai</v>
       </c>
       <c r="N73" s="58" t="str">
-        <f>D73</f>
+        <f t="shared" si="18"/>
         <v>uai</v>
       </c>
       <c r="P73" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>uai(\d)</v>
       </c>
       <c r="Q73" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R73" s="126">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="S73" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v>ua》i${1}</v>
       </c>
       <c r="T73" s="56"/>
       <c r="U73" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uai(\d)/ua》i${1}/</v>
       </c>
     </row>
     <row r="74" spans="1:21" ht="27.75" thickBot="1">
       <c r="A74" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>71</v>
       </c>
       <c r="B74" s="141" t="s">
@@ -41396,42 +41922,42 @@
         <v>1341</v>
       </c>
       <c r="K74" s="55">
-        <f xml:space="preserve"> LEN(D74)</f>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="L74" s="74"/>
       <c r="M74" s="58" t="str">
-        <f>C74</f>
+        <f t="shared" si="17"/>
         <v>uainn</v>
       </c>
       <c r="N74" s="58" t="str">
-        <f>D74</f>
+        <f t="shared" si="18"/>
         <v>uainn</v>
       </c>
       <c r="P74" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>uainn(\d)</v>
       </c>
       <c r="Q74" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R74" s="126">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="S74" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v>ua》i${1}nn</v>
       </c>
       <c r="T74" s="56"/>
       <c r="U74" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uainn(\d)/ua》i${1}nn/</v>
       </c>
     </row>
     <row r="75" spans="1:21" ht="27.75" thickBot="1">
       <c r="A75" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>72</v>
       </c>
       <c r="B75" s="141" t="s">
@@ -41460,42 +41986,42 @@
       </c>
       <c r="J75" s="58"/>
       <c r="K75" s="55">
-        <f xml:space="preserve"> LEN(D75)</f>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="L75" s="74"/>
       <c r="M75" s="58" t="str">
-        <f>C75</f>
+        <f t="shared" si="17"/>
         <v>uaih</v>
       </c>
       <c r="N75" s="58" t="str">
-        <f>D75</f>
+        <f t="shared" si="18"/>
         <v>uaih</v>
       </c>
       <c r="P75" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>uaih(\d)</v>
       </c>
       <c r="Q75" s="126" t="s">
         <v>1231</v>
       </c>
       <c r="R75" s="126">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="S75" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v>ua》i${1}h</v>
       </c>
       <c r="T75" s="56"/>
       <c r="U75" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uaih(\d)/ua》i${1}h/</v>
       </c>
     </row>
     <row r="76" spans="1:21" ht="27.75" thickBot="1">
       <c r="A76" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>73</v>
       </c>
       <c r="B76" s="141" t="s">
@@ -41526,42 +42052,42 @@
         <v>1341</v>
       </c>
       <c r="K76" s="55">
-        <f xml:space="preserve"> LEN(D76)</f>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="L76" s="74"/>
       <c r="M76" s="58" t="str">
-        <f>C76</f>
+        <f t="shared" si="17"/>
         <v>uainnh</v>
       </c>
       <c r="N76" s="58" t="str">
-        <f>D76</f>
+        <f t="shared" si="18"/>
         <v>uaihnn</v>
       </c>
       <c r="P76" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>uainnh(\d)</v>
       </c>
       <c r="Q76" s="126" t="s">
         <v>1335</v>
       </c>
       <c r="R76" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S76" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T76" s="56"/>
       <c r="U76" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uainnh(\d)//</v>
       </c>
     </row>
     <row r="77" spans="1:21" ht="27.75" thickBot="1">
       <c r="A77" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>74</v>
       </c>
       <c r="B77" s="141" t="s">
@@ -41590,42 +42116,42 @@
       </c>
       <c r="J77" s="58"/>
       <c r="K77" s="55">
-        <f xml:space="preserve"> LEN(D77)</f>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="L77" s="74"/>
       <c r="M77" s="58" t="str">
-        <f>C77</f>
+        <f t="shared" si="17"/>
         <v>ue</v>
       </c>
       <c r="N77" s="58" t="str">
-        <f>D77</f>
+        <f t="shared" si="18"/>
         <v>ue</v>
       </c>
       <c r="P77" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>ue(\d)</v>
       </c>
       <c r="Q77" s="126" t="s">
         <v>1334</v>
       </c>
       <c r="R77" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S77" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T77" s="56"/>
       <c r="U77" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》ue(\d)//</v>
       </c>
     </row>
     <row r="78" spans="1:21" ht="27.75" thickBot="1">
       <c r="A78" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>75</v>
       </c>
       <c r="B78" s="141" t="s">
@@ -41654,42 +42180,42 @@
       </c>
       <c r="J78" s="58"/>
       <c r="K78" s="55">
-        <f xml:space="preserve"> LEN(D78)</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="L78" s="74"/>
       <c r="M78" s="58" t="str">
-        <f>C78</f>
+        <f t="shared" si="17"/>
         <v>ueh</v>
       </c>
       <c r="N78" s="58" t="str">
-        <f>D78</f>
+        <f t="shared" si="18"/>
         <v>ueh</v>
       </c>
       <c r="P78" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>ueh(\d)</v>
       </c>
       <c r="Q78" s="126" t="s">
         <v>1218</v>
       </c>
       <c r="R78" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S78" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T78" s="56"/>
       <c r="U78" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》ueh(\d)//</v>
       </c>
     </row>
     <row r="79" spans="1:21" ht="27.75" thickBot="1">
       <c r="A79" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>76</v>
       </c>
       <c r="B79" s="141" t="s">
@@ -41718,42 +42244,42 @@
       </c>
       <c r="J79" s="58"/>
       <c r="K79" s="55">
-        <f xml:space="preserve"> LEN(D79)</f>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="L79" s="74"/>
       <c r="M79" s="58" t="str">
-        <f>C79</f>
+        <f t="shared" si="17"/>
         <v>ui</v>
       </c>
       <c r="N79" s="58" t="str">
-        <f>D79</f>
+        <f t="shared" si="18"/>
         <v>ui</v>
       </c>
       <c r="P79" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>ui(\d)</v>
       </c>
       <c r="Q79" s="126" t="s">
         <v>1218</v>
       </c>
       <c r="R79" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S79" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T79" s="56"/>
       <c r="U79" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》ui(\d)//</v>
       </c>
     </row>
     <row r="80" spans="1:21" ht="27.75" thickBot="1">
       <c r="A80" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>77</v>
       </c>
       <c r="B80" s="141" t="s">
@@ -41782,42 +42308,42 @@
       </c>
       <c r="J80" s="58"/>
       <c r="K80" s="55">
-        <f xml:space="preserve"> LEN(D80)</f>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="L80" s="74"/>
       <c r="M80" s="58" t="str">
-        <f>C80</f>
+        <f t="shared" si="17"/>
         <v>uinn</v>
       </c>
       <c r="N80" s="58" t="str">
-        <f>D80</f>
+        <f t="shared" si="18"/>
         <v>uinn</v>
       </c>
       <c r="P80" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>uinn(\d)</v>
       </c>
       <c r="Q80" s="126" t="s">
         <v>1218</v>
       </c>
       <c r="R80" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S80" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T80" s="56"/>
       <c r="U80" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uinn(\d)//</v>
       </c>
     </row>
     <row r="81" spans="1:21" ht="27.75" thickBot="1">
       <c r="A81" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>78</v>
       </c>
       <c r="B81" s="141" t="s">
@@ -41848,42 +42374,42 @@
         <v>1341</v>
       </c>
       <c r="K81" s="55">
-        <f xml:space="preserve"> LEN(D81)</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="L81" s="74"/>
       <c r="M81" s="58" t="str">
-        <f>C81</f>
+        <f t="shared" si="17"/>
         <v>uih</v>
       </c>
       <c r="N81" s="58" t="str">
-        <f>D81</f>
+        <f t="shared" si="18"/>
         <v>uih</v>
       </c>
       <c r="P81" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>uih(\d)</v>
       </c>
       <c r="Q81" s="126" t="s">
         <v>1218</v>
       </c>
       <c r="R81" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S81" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T81" s="56"/>
       <c r="U81" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uih(\d)//</v>
       </c>
     </row>
     <row r="82" spans="1:21" ht="27.75" thickBot="1">
       <c r="A82" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>79</v>
       </c>
       <c r="B82" s="141" t="s">
@@ -41912,42 +42438,42 @@
       </c>
       <c r="J82" s="58"/>
       <c r="K82" s="55">
-        <f xml:space="preserve"> LEN(D82)</f>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="L82" s="74"/>
       <c r="M82" s="58" t="str">
-        <f>C82</f>
+        <f t="shared" si="17"/>
         <v>m</v>
       </c>
       <c r="N82" s="58" t="str">
-        <f>D82</f>
+        <f t="shared" si="18"/>
         <v>m</v>
       </c>
       <c r="P82" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>m(\d)</v>
       </c>
       <c r="Q82" s="126" t="s">
         <v>1229</v>
       </c>
       <c r="R82" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S82" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T82" s="56"/>
       <c r="U82" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》m(\d)//</v>
       </c>
     </row>
     <row r="83" spans="1:21" ht="27.75" thickBot="1">
       <c r="A83" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>80</v>
       </c>
       <c r="B83" s="141" t="s">
@@ -41976,42 +42502,42 @@
       </c>
       <c r="J83" s="58"/>
       <c r="K83" s="55">
-        <f xml:space="preserve"> LEN(D83)</f>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="L83" s="74"/>
       <c r="M83" s="58" t="str">
-        <f>C83</f>
+        <f t="shared" si="17"/>
         <v>mh</v>
       </c>
       <c r="N83" s="58" t="str">
-        <f>D83</f>
+        <f t="shared" si="18"/>
         <v>mh</v>
       </c>
       <c r="P83" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>mh(\d)</v>
       </c>
       <c r="Q83" s="126" t="s">
         <v>1229</v>
       </c>
       <c r="R83" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S83" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T83" s="56"/>
       <c r="U83" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》mh(\d)//</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="27.75" thickBot="1">
       <c r="A84" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>81</v>
       </c>
       <c r="B84" s="141" t="s">
@@ -42040,42 +42566,42 @@
       </c>
       <c r="J84" s="58"/>
       <c r="K84" s="55">
-        <f xml:space="preserve"> LEN(D84)</f>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="L84" s="74"/>
       <c r="M84" s="58" t="str">
-        <f>C84</f>
+        <f t="shared" si="17"/>
         <v>ng</v>
       </c>
       <c r="N84" s="58" t="str">
-        <f>D84</f>
+        <f t="shared" si="18"/>
         <v>ng</v>
       </c>
       <c r="P84" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>ng(\d)</v>
       </c>
       <c r="Q84" s="126" t="s">
         <v>1229</v>
       </c>
       <c r="R84" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S84" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T84" s="56"/>
       <c r="U84" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》ng(\d)//</v>
       </c>
     </row>
     <row r="85" spans="1:21" ht="27.75" thickBot="1">
       <c r="A85" s="58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>82</v>
       </c>
       <c r="B85" s="141" t="s">
@@ -42104,36 +42630,36 @@
       </c>
       <c r="J85" s="58"/>
       <c r="K85" s="55">
-        <f xml:space="preserve"> LEN(D85)</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="L85" s="74"/>
       <c r="M85" s="58" t="str">
-        <f>C85</f>
+        <f t="shared" si="17"/>
         <v>ngh</v>
       </c>
       <c r="N85" s="58" t="str">
-        <f>D85</f>
+        <f t="shared" si="18"/>
         <v>ngh</v>
       </c>
       <c r="P85" s="123" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>ngh(\d)</v>
       </c>
       <c r="Q85" s="126" t="s">
         <v>1229</v>
       </c>
       <c r="R85" s="126" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="S85" s="123" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T85" s="56"/>
       <c r="U85" s="57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》ngh(\d)//</v>
       </c>
     </row>
@@ -48366,14 +48892,14 @@
         <v>1</v>
       </c>
       <c r="F2" s="107"/>
-      <c r="G2" s="161" t="str">
+      <c r="G2" s="159" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("a", IF($F2="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($F2,4)))))</f>
         <v>a</v>
       </c>
       <c r="H2" s="106" t="s">
         <v>635</v>
       </c>
-      <c r="I2" s="160" t="str">
+      <c r="I2" s="158" t="str">
         <f>IFERROR( _xlfn.CONCAT("t", "o", IF($F2="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($F2,4)))), IF(RIGHT($C2,1)&lt;&gt;"入", "ng", "k")), "")</f>
         <v>tong</v>
       </c>
@@ -48384,7 +48910,7 @@
         <f xml:space="preserve"> _xlfn.CONCAT("ㄚ", IF($J2="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($J2,4)))))</f>
         <v>ㄚ</v>
       </c>
-      <c r="L2" s="160" t="str">
+      <c r="L2" s="158" t="str">
         <f>IFERROR( _xlfn.CONCAT("ㄉ", IF(RIGHT($C2,1)&lt;&gt;"入", "ㆲ", "ㆦㆻ"),  IF($J2="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($J2,4)))),), "")</f>
         <v>ㄉㆲ</v>
       </c>
@@ -48414,14 +48940,14 @@
       <c r="F3" s="107" t="s">
         <v>669</v>
       </c>
-      <c r="G3" s="161" t="str">
+      <c r="G3" s="159" t="str">
         <f t="shared" ref="G3:G6" si="0" xml:space="preserve"> _xlfn.CONCAT("a", IF($F3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($F3,4)))))</f>
         <v>ā</v>
       </c>
       <c r="H3" s="106" t="s">
         <v>639</v>
       </c>
-      <c r="I3" s="160" t="str">
+      <c r="I3" s="158" t="str">
         <f t="shared" ref="I3:I8" si="1">IFERROR( _xlfn.CONCAT("t", "o", IF($F3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($F3,4)))), IF(RIGHT($C3,1)&lt;&gt;"入", "ng", "k")), "")</f>
         <v>tōng</v>
       </c>
@@ -48432,7 +48958,7 @@
         <f t="shared" ref="K3:K6" si="2" xml:space="preserve"> _xlfn.CONCAT("ㄚ", IF($J3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($J3,4)))))</f>
         <v>ㄚ˫</v>
       </c>
-      <c r="L3" s="160" t="str">
+      <c r="L3" s="158" t="str">
         <f t="shared" ref="L3:L8" si="3">IFERROR( _xlfn.CONCAT("ㄉ", IF(RIGHT($C3,1)&lt;&gt;"入", "ㆲ", "ㆦㆻ"),  IF($J3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($J3,4)))),), "")</f>
         <v>ㄉㆲ˫</v>
       </c>
@@ -48462,14 +48988,14 @@
       <c r="F4" s="107" t="s">
         <v>755</v>
       </c>
-      <c r="G4" s="161" t="str">
+      <c r="G4" s="159" t="str">
         <f t="shared" si="0"/>
         <v>à</v>
       </c>
       <c r="H4" s="106" t="s">
         <v>644</v>
       </c>
-      <c r="I4" s="160" t="str">
+      <c r="I4" s="158" t="str">
         <f t="shared" si="1"/>
         <v>tòng</v>
       </c>
@@ -48480,7 +49006,7 @@
         <f t="shared" si="2"/>
         <v>ㄚ˪</v>
       </c>
-      <c r="L4" s="160" t="str">
+      <c r="L4" s="158" t="str">
         <f t="shared" si="3"/>
         <v>ㄉㆲ˪</v>
       </c>
@@ -48510,14 +49036,14 @@
       <c r="F5" s="107" t="s">
         <v>757</v>
       </c>
-      <c r="G5" s="161" t="str">
+      <c r="G5" s="159" t="str">
         <f t="shared" si="0"/>
         <v>á</v>
       </c>
       <c r="H5" s="106" t="s">
         <v>648</v>
       </c>
-      <c r="I5" s="160" t="str">
+      <c r="I5" s="158" t="str">
         <f t="shared" si="1"/>
         <v>tóng</v>
       </c>
@@ -48528,7 +49054,7 @@
         <f t="shared" si="2"/>
         <v>ㄚ̀</v>
       </c>
-      <c r="L5" s="160" t="str">
+      <c r="L5" s="158" t="str">
         <f t="shared" si="3"/>
         <v>ㄉㆲ̀</v>
       </c>
@@ -48558,14 +49084,14 @@
       <c r="F6" s="107" t="s">
         <v>763</v>
       </c>
-      <c r="G6" s="161" t="str">
+      <c r="G6" s="159" t="str">
         <f t="shared" si="0"/>
         <v>ǎ</v>
       </c>
       <c r="H6" s="106" t="s">
         <v>652</v>
       </c>
-      <c r="I6" s="160" t="str">
+      <c r="I6" s="158" t="str">
         <f t="shared" si="1"/>
         <v>tǒng</v>
       </c>
@@ -48576,7 +49102,7 @@
         <f t="shared" si="2"/>
         <v>ㄚ́</v>
       </c>
-      <c r="L6" s="160" t="str">
+      <c r="L6" s="158" t="str">
         <f t="shared" si="3"/>
         <v>ㄉㆲ́</v>
       </c>
@@ -48604,14 +49130,14 @@
         <v>4</v>
       </c>
       <c r="F7" s="107"/>
-      <c r="G7" s="161" t="str">
+      <c r="G7" s="159" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("a", IF($F7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($F7,4)))), "h")</f>
         <v>ah</v>
       </c>
       <c r="H7" s="106" t="s">
         <v>656</v>
       </c>
-      <c r="I7" s="160" t="str">
+      <c r="I7" s="158" t="str">
         <f t="shared" si="1"/>
         <v>tok</v>
       </c>
@@ -48622,7 +49148,7 @@
         <f xml:space="preserve"> _xlfn.CONCAT("ㄚ", "ㆷ", IF($J7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($J7,4)))))</f>
         <v>ㄚㆷ</v>
       </c>
-      <c r="L7" s="160" t="str">
+      <c r="L7" s="158" t="str">
         <f t="shared" si="3"/>
         <v>ㄉㆦㆻ</v>
       </c>
@@ -48652,14 +49178,14 @@
       <c r="F8" s="107" t="s">
         <v>778</v>
       </c>
-      <c r="G8" s="161" t="str">
+      <c r="G8" s="159" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("a", IF($F8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($F8,4)))), "h")</f>
         <v>a̍h</v>
       </c>
       <c r="H8" s="106" t="s">
         <v>660</v>
       </c>
-      <c r="I8" s="160" t="str">
+      <c r="I8" s="158" t="str">
         <f t="shared" si="1"/>
         <v>to̍k</v>
       </c>
@@ -48670,7 +49196,7 @@
         <f xml:space="preserve"> _xlfn.CONCAT("ㄚ", "ㆷ", IF($J8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($J8,4)))))</f>
         <v>ㄚㆷ˙</v>
       </c>
-      <c r="L8" s="160" t="str">
+      <c r="L8" s="158" t="str">
         <f t="shared" si="3"/>
         <v>ㄉㆦㆻ˙</v>
       </c>
@@ -49033,11 +49559,11 @@
         <v>a</v>
       </c>
       <c r="S24" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT($K24,4))), "n"), "")</f>
+        <f t="shared" ref="S24:S31" si="5" xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT($K24,4))), "n"), "")</f>
         <v>lūn</v>
       </c>
       <c r="T24" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT($K24,4))), "o"), "")</f>
+        <f t="shared" ref="T24:T31" si="6" xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT($K24,4))), "o"), "")</f>
         <v>ngōo</v>
       </c>
       <c r="U24">
@@ -49098,11 +49624,11 @@
         <v>á</v>
       </c>
       <c r="S25" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT($K25,4))), "n"), "")</f>
+        <f t="shared" si="5"/>
         <v>lǔn</v>
       </c>
       <c r="T25" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT($K25,4))), "o"), "")</f>
+        <f t="shared" si="6"/>
         <v>ngǒo</v>
       </c>
       <c r="U25">
@@ -49113,7 +49639,7 @@
         <v>ó͘</v>
       </c>
       <c r="W25" s="150" t="str">
-        <f t="shared" ref="W25:W33" si="5" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $U$23, U25, "/", V25, "/")</f>
+        <f t="shared" ref="W25:W33" si="7" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $U$23, U25, "/", V25, "/")</f>
         <v xml:space="preserve">    - xform/o͘2/ó͘/</v>
       </c>
     </row>
@@ -49138,7 +49664,7 @@
         <v>755</v>
       </c>
       <c r="J26" s="99" t="str">
-        <f t="shared" ref="J26:J33" si="6" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT($I26,4)))), "")</f>
+        <f t="shared" ref="J26:J33" si="8" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT($I26,4)))), "")</f>
         <v>à</v>
       </c>
       <c r="K26" s="112" t="s">
@@ -49159,15 +49685,15 @@
         <v>ㄚ˪</v>
       </c>
       <c r="Q26" s="50" t="str">
-        <f t="shared" ref="Q26:Q33" si="7" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT($I26,4)))), "")</f>
+        <f t="shared" ref="Q26:Q33" si="9" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT($I26,4)))), "")</f>
         <v>à</v>
       </c>
       <c r="S26" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT($K26,4))), "n"), "")</f>
+        <f t="shared" si="5"/>
         <v>lùn</v>
       </c>
       <c r="T26" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT($K26,4))), "o"), "")</f>
+        <f t="shared" si="6"/>
         <v>ngòo</v>
       </c>
       <c r="U26">
@@ -49178,7 +49704,7 @@
         <v>ò͘</v>
       </c>
       <c r="W26" s="150" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/o͘3/ò͘/</v>
       </c>
     </row>
@@ -49201,7 +49727,7 @@
       </c>
       <c r="I27" s="114"/>
       <c r="J27" s="99" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K27" s="112" t="s">
@@ -49220,15 +49746,15 @@
         <v>ㄚㆷ</v>
       </c>
       <c r="Q27" s="50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="S27" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT($K27,4))), "n"), "")</f>
+        <f t="shared" si="5"/>
         <v>lūn</v>
       </c>
       <c r="T27" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT($K27,4))), "o"), "")</f>
+        <f t="shared" si="6"/>
         <v>ngōo</v>
       </c>
       <c r="U27">
@@ -49239,7 +49765,7 @@
         <v>o͘</v>
       </c>
       <c r="W27" s="150" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/o͘4/o͘/</v>
       </c>
     </row>
@@ -49264,14 +49790,14 @@
         <v>763</v>
       </c>
       <c r="J28" s="99" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>ǎ</v>
       </c>
       <c r="K28" s="112" t="s">
         <v>757</v>
       </c>
       <c r="L28" s="118" t="str">
-        <f t="shared" ref="L28:L29" si="8" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(K28,4)))), "")</f>
+        <f t="shared" ref="L28:L29" si="10" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(K28,4)))), "")</f>
         <v>á</v>
       </c>
       <c r="M28" s="105">
@@ -49285,26 +49811,26 @@
         <v>ㄚ́</v>
       </c>
       <c r="Q28" s="50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>ǎ</v>
       </c>
       <c r="S28" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT($K28,4))), "n"), "")</f>
+        <f t="shared" si="5"/>
         <v>lún</v>
       </c>
       <c r="T28" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT($K28,4))), "o"), "")</f>
+        <f t="shared" si="6"/>
         <v>ngóo</v>
       </c>
       <c r="U28">
         <v>5</v>
       </c>
       <c r="V28" s="149" t="str">
-        <f t="shared" ref="V28:V33" si="9">IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(I28,4)))), "")</f>
+        <f t="shared" ref="V28:V33" si="11">IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(I28,4)))), "")</f>
         <v>ǒ͘</v>
       </c>
       <c r="W28" s="150" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/o͘5/ǒ͘/</v>
       </c>
     </row>
@@ -49327,14 +49853,14 @@
         <v>757</v>
       </c>
       <c r="J29" s="99" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>á</v>
       </c>
       <c r="K29" s="113" t="s">
         <v>763</v>
       </c>
       <c r="L29" s="119" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ǎ</v>
       </c>
       <c r="M29" s="105"/>
@@ -49346,26 +49872,26 @@
         <v>ㄚ̀</v>
       </c>
       <c r="Q29" s="50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>á</v>
       </c>
       <c r="S29" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT($K29,4))), "n"), "")</f>
+        <f t="shared" si="5"/>
         <v>lǔn</v>
       </c>
       <c r="T29" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT($K29,4))), "o"), "")</f>
+        <f t="shared" si="6"/>
         <v>ngǒo</v>
       </c>
       <c r="U29">
         <v>6</v>
       </c>
       <c r="V29" s="149" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>ó͘</v>
       </c>
       <c r="W29" s="150" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/o͘6/ó͘/</v>
       </c>
     </row>
@@ -49390,14 +49916,14 @@
         <v>669</v>
       </c>
       <c r="J30" s="99" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>ā</v>
       </c>
       <c r="K30" s="112" t="s">
         <v>762</v>
       </c>
       <c r="L30" s="118" t="str">
-        <f t="shared" ref="L30" si="10" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(K30,4)))), "")</f>
+        <f t="shared" ref="L30" si="12" xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(K30,4)))), "")</f>
         <v>â</v>
       </c>
       <c r="M30" s="104">
@@ -49411,26 +49937,26 @@
         <v>ㄚ˫</v>
       </c>
       <c r="Q30" s="50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>ā</v>
       </c>
       <c r="S30" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT($K30,4))), "n"), "")</f>
+        <f t="shared" si="5"/>
         <v>lûn</v>
       </c>
       <c r="T30" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT($K30,4))), "o"), "")</f>
+        <f t="shared" si="6"/>
         <v>ngôo</v>
       </c>
       <c r="U30">
         <v>7</v>
       </c>
       <c r="V30" s="149" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>ō͘</v>
       </c>
       <c r="W30" s="150" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/o͘7/ō͘/</v>
       </c>
     </row>
@@ -49455,7 +49981,7 @@
         <v>778</v>
       </c>
       <c r="J31" s="99" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>a̍</v>
       </c>
       <c r="K31" s="112" t="s">
@@ -49476,26 +50002,26 @@
         <v>ㄚㆷ˙</v>
       </c>
       <c r="Q31" s="50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>a̍</v>
       </c>
       <c r="S31" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT($K31,4))), "n"), "")</f>
+        <f t="shared" si="5"/>
         <v>lún</v>
       </c>
       <c r="T31" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT($K31,4))), "o"), "")</f>
+        <f t="shared" si="6"/>
         <v>ngóo</v>
       </c>
       <c r="U31">
         <v>8</v>
       </c>
       <c r="V31" s="149" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>o̍͘</v>
       </c>
       <c r="W31" s="150" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/o͘8/o̍͘/</v>
       </c>
     </row>
@@ -49518,7 +50044,7 @@
         <v>673</v>
       </c>
       <c r="J32" s="99" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>a̋</v>
       </c>
       <c r="K32" s="112"/>
@@ -49527,7 +50053,7 @@
       <c r="N32" s="116"/>
       <c r="O32" s="120"/>
       <c r="Q32" s="50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>a̋</v>
       </c>
       <c r="S32" t="str">
@@ -49538,11 +50064,11 @@
         <v>9</v>
       </c>
       <c r="V32" s="149" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>ő͘</v>
       </c>
       <c r="W32" s="150" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/o͘9/ő͘/</v>
       </c>
     </row>
@@ -49565,7 +50091,7 @@
         <v>672</v>
       </c>
       <c r="J33" s="99" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>å</v>
       </c>
       <c r="K33" s="112"/>
@@ -49581,7 +50107,7 @@
         <v>ㄚ̊</v>
       </c>
       <c r="Q33" s="50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>å</v>
       </c>
       <c r="S33" t="str">
@@ -49592,11 +50118,11 @@
         <v>0</v>
       </c>
       <c r="V33" s="149" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>o̊͘</v>
       </c>
       <c r="W33" s="150" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/o͘0/o̊͘/</v>
       </c>
     </row>

--- a/docs/101_聲韻調對照表.xlsx
+++ b/docs/101_聲韻調對照表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51485D1-52C3-4438-871B-9F6CA02D7349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B01F07-29DF-4718-A57E-45FD1FA0CB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="811" activeTab="1" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="811" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
   </bookViews>
   <sheets>
     <sheet name="【聲】聲母對照表" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7532" uniqueCount="2321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7601" uniqueCount="2370">
   <si>
     <t>識別號</t>
   </si>
@@ -8159,6 +8159,185 @@
   </si>
   <si>
     <t>⁰ㄧㆫ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/o͘1/o͘/</t>
+  </si>
+  <si>
+    <t>ó͘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/o͘2/ó͘/</t>
+  </si>
+  <si>
+    <t>ò͘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/o͘3/ò͘/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/o͘4/o͘/</t>
+  </si>
+  <si>
+    <t>ǒ͘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/o͘5/ǒ͘/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/o͘6/ó͘/</t>
+  </si>
+  <si>
+    <t>ō͘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/o͘7/ō͘/</t>
+  </si>
+  <si>
+    <t>o̍͘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/o͘8/o̍͘/</t>
+  </si>
+  <si>
+    <t>ő͘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/o͘9/ő͘/</t>
+  </si>
+  <si>
+    <t>o̊͘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/o͘0/o̊͘/</t>
+  </si>
+  <si>
+    <t>b</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>p</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>bb</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>d</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ln</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>l</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>g</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>k</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>gg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>h</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>z</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>zz</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>jji</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ji</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>chi</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>shi</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ng</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>s1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>s2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄑ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>s3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>bbn</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ggn</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>zzi</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ci</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>si</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8801,7 +8980,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8886,8 +9065,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -9045,6 +9230,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -9061,7 +9257,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9548,6 +9744,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -9557,24 +9771,6 @@
     <cellStyle name="一般 5" xfId="2" xr:uid="{8C9CBB70-72B8-491C-A1A5-535BA1FE1D69}"/>
   </cellStyles>
   <dxfs count="35">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -10044,6 +10240,24 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <sz val="24"/>
         <name val="Segoe UI"/>
@@ -10317,40 +10531,40 @@
     <tableColumn id="10" xr3:uid="{BDA4D6F0-BBAC-44DF-85B3-15A86E2ED416}" name="閩拼方案" dataDxfId="25"/>
     <tableColumn id="9" xr3:uid="{972A94F9-A940-4172-AB75-0BE33372A5A6}" name="白話字" dataDxfId="24"/>
     <tableColumn id="5" xr3:uid="{88460F28-F486-4EB3-974F-039F84D0E83A}" name="方音符號" dataDxfId="23"/>
-    <tableColumn id="14" xr3:uid="{EF2755BF-6678-4CD8-B300-0D0325E9E0D0}" name="台語注音" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{8C99734F-A142-4FBD-96DD-463C060588A5}" name="漢字例" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{80F0C42C-C2BD-4707-8BE9-49A90C7647AB}" name="十五音" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{77E72489-4845-4BE7-807E-50EDB35447E7}" name="十五音序" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{4D0E40DE-9C66-4BA2-B18D-2F564923928D}" name="舒促聲" dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{1E5A033C-A3E4-47B2-8D3D-334C23BE852B}" name="十五音識別碼" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{EF2755BF-6678-4CD8-B300-0D0325E9E0D0}" name="台語注音" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{8C99734F-A142-4FBD-96DD-463C060588A5}" name="漢字例" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{80F0C42C-C2BD-4707-8BE9-49A90C7647AB}" name="十五音" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{77E72489-4845-4BE7-807E-50EDB35447E7}" name="十五音序" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{4D0E40DE-9C66-4BA2-B18D-2F564923928D}" name="舒促聲" dataDxfId="18"/>
+    <tableColumn id="13" xr3:uid="{1E5A033C-A3E4-47B2-8D3D-334C23BE852B}" name="十五音識別碼" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CFF90B7A-D09E-43B2-979B-7CD1EE35DCEF}" name="韻母對照表3" displayName="韻母對照表3" ref="A1:M85" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CFF90B7A-D09E-43B2-979B-7CD1EE35DCEF}" name="韻母對照表3" displayName="韻母對照表3" ref="A1:M85" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
   <autoFilter ref="A1:M85" xr:uid="{771C3941-9899-48C4-8E14-367017F7B2F5}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{C10E80BA-9FEE-411B-A2E1-0B8D75C43A73}" name="識別號" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{BDE2F94E-9AD0-4497-B0A4-0887F343995C}" name="十五音" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{1BB80AC9-0E65-4250-97F0-4C9BF936F6F4}" name="漢字例" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{FF3D3154-85AC-43FE-9B6E-613CB6837684}" name="方音符號" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{76F226E4-4708-40A7-849D-3CC6919D3693}" name="台語音標" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{B2037F3B-8888-4074-8870-6B45341F0C3A}" name="國際音標" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{C10E80BA-9FEE-411B-A2E1-0B8D75C43A73}" name="識別號" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{BDE2F94E-9AD0-4497-B0A4-0887F343995C}" name="十五音" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{1BB80AC9-0E65-4250-97F0-4C9BF936F6F4}" name="漢字例" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{FF3D3154-85AC-43FE-9B6E-613CB6837684}" name="方音符號" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{76F226E4-4708-40A7-849D-3CC6919D3693}" name="台語音標" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{B2037F3B-8888-4074-8870-6B45341F0C3A}" name="國際音標" dataDxfId="7">
       <calculatedColumnFormula array="1" xml:space="preserve"> IF(韻母對照表3[[#This Row],[舒促聲]]="舒聲", INDEX(十五音韻母!$G$3:$G$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)), INDEX(十五音韻母!$H$3:$H$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8FF1DC7C-D8AD-4071-B26D-6830788BB67A}" name="閩拼方案" dataDxfId="7">
+    <tableColumn id="10" xr3:uid="{8FF1DC7C-D8AD-4071-B26D-6830788BB67A}" name="閩拼方案" dataDxfId="6">
       <calculatedColumnFormula array="1" xml:space="preserve"> IF(韻母對照表3[[#This Row],[舒促聲]]="舒聲", INDEX(十五音韻母!$I$3:$I$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)), INDEX(十五音韻母!$J$3:$J$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{76F2259B-CA5E-44D6-86F0-A1217D200D54}" name="台羅拼音" dataDxfId="6">
+    <tableColumn id="7" xr3:uid="{76F2259B-CA5E-44D6-86F0-A1217D200D54}" name="台羅拼音" dataDxfId="5">
       <calculatedColumnFormula array="1" xml:space="preserve"> IF(韻母對照表3[[#This Row],[舒促聲]]="舒聲", INDEX(十五音韻母!$K$3:$K$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)), INDEX(十五音韻母!$L$3:$L$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DF4BA570-1408-41DB-8328-90FB8913B1DF}" name="注音二式" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{42E33940-E4F1-4C86-AD57-6236C50EBE40}" name="白話字" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{BE8C4436-8D84-475B-A5C6-C392918893AA}" name="十五音序" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{4D04DB9F-1246-4494-8D81-B2950125EC5B}" name="舒促聲" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{EB7195BB-541B-463D-BA37-EBE312BD24A4}" name="十五音識別碼" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{DF4BA570-1408-41DB-8328-90FB8913B1DF}" name="注音二式" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{42E33940-E4F1-4C86-AD57-6236C50EBE40}" name="白話字" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{BE8C4436-8D84-475B-A5C6-C392918893AA}" name="十五音序" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{4D04DB9F-1246-4494-8D81-B2950125EC5B}" name="舒促聲" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{EB7195BB-541B-463D-BA37-EBE312BD24A4}" name="十五音識別碼" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10693,14 +10907,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{619E8012-85E3-4410-BF6F-8322F40DAF24}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr defaultRowHeight="25.5"/>
   <cols>
     <col min="1" max="1" width="6.4140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.08203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.83203125" customWidth="1"/>
+    <col min="14" max="15" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10737,814 +10953,1024 @@
       <c r="L1" s="2" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="29.25">
+      <c r="M1" s="163" t="s">
+        <v>2358</v>
+      </c>
+      <c r="N1" s="163" t="s">
+        <v>2359</v>
+      </c>
+      <c r="O1" s="163" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="29.25">
       <c r="A2" s="1">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="E2" s="151" t="s">
+        <v>567</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="164">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="N2" s="164" t="s">
+        <v>567</v>
+      </c>
+      <c r="O2" s="164" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="29.25">
+      <c r="A3" s="1">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E3" s="151" t="s">
+        <v>432</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="M3" s="165">
+        <v>2</v>
+      </c>
+      <c r="N3" s="165" t="s">
+        <v>1335</v>
+      </c>
+      <c r="O3" s="165" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="29.25">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E4" s="151" t="s">
+        <v>571</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>2263</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="166">
+        <v>3</v>
+      </c>
+      <c r="N4" s="166" t="s">
+        <v>2340</v>
+      </c>
+      <c r="O4" s="166" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="29.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E5" s="151" t="s">
+        <v>522</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="166">
+        <v>4</v>
+      </c>
+      <c r="N5" s="166" t="s">
+        <v>2338</v>
+      </c>
+      <c r="O5" s="166" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="29.25">
+      <c r="A6" s="1">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E6" s="151" t="s">
+        <v>519</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="167">
+        <v>5</v>
+      </c>
+      <c r="N6" s="167" t="s">
+        <v>2339</v>
+      </c>
+      <c r="O6" s="167" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="29.25">
+      <c r="A7" s="1">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E7" s="151" t="s">
+        <v>591</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>594</v>
+      </c>
+      <c r="M7" s="165">
+        <v>6</v>
+      </c>
+      <c r="N7" s="165" t="s">
+        <v>1334</v>
+      </c>
+      <c r="O7" s="165" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="29.25">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E8" s="151" t="s">
         <v>515</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="L2" s="1"/>
-    </row>
-    <row r="3" spans="1:12" ht="29.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" ht="29.25">
-      <c r="A4" s="1">
+      <c r="L8" s="1"/>
+      <c r="M8" s="166">
+        <v>7</v>
+      </c>
+      <c r="N8" s="166" t="s">
+        <v>2344</v>
+      </c>
+      <c r="O8" s="166" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="29.25">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E9" s="151" t="s">
+        <v>537</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="166">
+        <v>8</v>
+      </c>
+      <c r="N9" s="166" t="s">
+        <v>2341</v>
+      </c>
+      <c r="O9" s="166" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="29.25">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="E10" s="151" t="s">
+        <v>534</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="167">
+        <v>9</v>
+      </c>
+      <c r="N10" s="167" t="s">
+        <v>2342</v>
+      </c>
+      <c r="O10" s="167" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="29.25">
+      <c r="A11" s="1">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="E11" s="151" t="s">
+        <v>407</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>2265</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="M11" s="165">
+        <v>10</v>
+      </c>
+      <c r="N11" s="165" t="s">
+        <v>2357</v>
+      </c>
+      <c r="O11" s="165" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="29.25">
+      <c r="A12" s="1">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E12" s="151" t="s">
+        <v>576</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="166">
+        <v>11</v>
+      </c>
+      <c r="N12" s="166" t="s">
+        <v>2347</v>
+      </c>
+      <c r="O12" s="166" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="29.25">
+      <c r="A13" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E13" s="151" t="s">
         <v>527</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="L4" s="1"/>
-    </row>
-    <row r="5" spans="1:12" ht="29.25">
-      <c r="A5" s="1">
+      <c r="L13" s="1"/>
+      <c r="M13" s="166">
+        <v>12</v>
+      </c>
+      <c r="N13" s="166" t="s">
+        <v>2345</v>
+      </c>
+      <c r="O13" s="166" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="29.25">
+      <c r="A14" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E14" s="151" t="s">
         <v>524</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="L5" s="1"/>
-    </row>
-    <row r="6" spans="1:12" ht="29.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="L6" s="1"/>
-    </row>
-    <row r="7" spans="1:12" ht="29.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="L7" s="1"/>
-    </row>
-    <row r="8" spans="1:12" ht="29.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="L8" s="1"/>
-    </row>
-    <row r="9" spans="1:12" ht="29.25">
-      <c r="A9" s="1">
+      <c r="L14" s="1"/>
+      <c r="M14" s="167">
+        <v>13</v>
+      </c>
+      <c r="N14" s="167" t="s">
+        <v>2346</v>
+      </c>
+      <c r="O14" s="167" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="29.25">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="E15" s="151" t="s">
+        <v>560</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>2261</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="165">
+        <v>14</v>
+      </c>
+      <c r="N15" s="165" t="s">
+        <v>2352</v>
+      </c>
+      <c r="O15" s="165" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="29.25">
+      <c r="A16" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E16" s="151" t="s">
         <v>552</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K16" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:12" ht="29.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="I10" s="1" t="s">
+      <c r="L16" s="1"/>
+      <c r="M16" s="166">
+        <v>15</v>
+      </c>
+      <c r="N16" s="166" t="s">
+        <v>2349</v>
+      </c>
+      <c r="O16" s="166" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="29.25">
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E17" s="151" t="s">
+        <v>580</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>2264</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="166">
+        <v>16</v>
+      </c>
+      <c r="N17" s="166" t="s">
+        <v>2350</v>
+      </c>
+      <c r="O17" s="166" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="29.25">
+      <c r="A18" s="1">
+        <v>10</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E18" s="151" t="s">
+        <v>562</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>2262</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="167">
+        <v>17</v>
+      </c>
+      <c r="N18" s="167" t="s">
+        <v>2351</v>
+      </c>
+      <c r="O18" s="167" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="29.25">
+      <c r="A19" s="17">
+        <v>19</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="E19" s="162" t="s">
+        <v>604</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>603</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="I19" s="16" t="s">
         <v>2261</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J19" s="18" t="s">
         <v>557</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K19" s="18" t="s">
         <v>555</v>
       </c>
-      <c r="L10" s="1"/>
-    </row>
-    <row r="11" spans="1:12" ht="29.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>2262</v>
-      </c>
-      <c r="J11" s="11" t="s">
+      <c r="L19" s="19" t="s">
+        <v>622</v>
+      </c>
+      <c r="M19" s="165">
+        <v>18</v>
+      </c>
+      <c r="N19" s="165" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O19" s="165" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="29.25">
+      <c r="A20" s="17">
+        <v>20</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>606</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>609</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>608</v>
+      </c>
+      <c r="E20" s="162" t="s">
+        <v>602</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>608</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>610</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>2360</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>550</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>605</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>623</v>
+      </c>
+      <c r="M20" s="166">
+        <v>19</v>
+      </c>
+      <c r="N20" s="166" t="s">
+        <v>2354</v>
+      </c>
+      <c r="O20" s="166" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="29.25">
+      <c r="A21" s="17">
+        <v>21</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>615</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>614</v>
+      </c>
+      <c r="E21" s="162" t="s">
+        <v>610</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>614</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>616</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>2361</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>579</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>611</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>627</v>
+      </c>
+      <c r="M21" s="166">
+        <v>20</v>
+      </c>
+      <c r="N21" s="166" t="s">
+        <v>2355</v>
+      </c>
+      <c r="O21" s="166" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="29.25">
+      <c r="A22" s="17">
+        <v>22</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>618</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="E22" s="162" t="s">
+        <v>621</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>2362</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="J22" s="18" t="s">
         <v>563</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="L11" s="1"/>
-    </row>
-    <row r="12" spans="1:12" ht="29.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>566</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="L12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" ht="29.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>2263</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="L13" s="1"/>
-    </row>
-    <row r="14" spans="1:12" ht="29.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:12" ht="29.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>2264</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="1:12" ht="29.25">
-      <c r="A16" s="1">
+      <c r="K22" s="18" t="s">
+        <v>617</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>625</v>
+      </c>
+      <c r="M22" s="167">
+        <v>21</v>
+      </c>
+      <c r="N22" s="167" t="s">
+        <v>2356</v>
+      </c>
+      <c r="O22" s="167" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="29.25">
+      <c r="A23" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E23" s="151" t="s">
         <v>584</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="1:12" ht="29.25">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="29.25">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="29.25">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>2265</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="L19" s="19" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="29.25">
-      <c r="A20" s="17">
-        <v>19</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>600</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>602</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>602</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>604</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>603</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>602</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>601</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>2261</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>557</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>555</v>
-      </c>
-      <c r="L20" s="19" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="29.25">
-      <c r="A21" s="17">
-        <v>20</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>606</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>609</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>608</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>602</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>608</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>610</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>607</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>607</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>550</v>
-      </c>
-      <c r="K21" s="18" t="s">
-        <v>605</v>
-      </c>
-      <c r="L21" s="19" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="29.25">
-      <c r="A22" s="17">
-        <v>21</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>612</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>615</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>614</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>610</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>614</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>616</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>613</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>613</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>579</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>611</v>
-      </c>
-      <c r="L22" s="19" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="29.25">
-      <c r="A23" s="17">
+      <c r="L23" s="1"/>
+      <c r="M23" s="167">
         <v>22</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>618</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>620</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>620</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>621</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>620</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>620</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>619</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>619</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>563</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>617</v>
-      </c>
-      <c r="L23" s="19" t="s">
-        <v>625</v>
+      <c r="N23" s="167" t="s">
+        <v>2348</v>
+      </c>
+      <c r="O23" s="167" t="s">
+        <v>2348</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N23">
+    <sortCondition ref="M2:M23"/>
+  </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -50126,6 +50552,124 @@
         <v xml:space="preserve">    - xform/o͘0/o̊͘/</v>
       </c>
     </row>
+    <row r="36" spans="1:23" ht="30">
+      <c r="U36" s="149" t="s">
+        <v>137</v>
+      </c>
+      <c r="V36" s="49" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="30">
+      <c r="U37">
+        <v>1</v>
+      </c>
+      <c r="V37" s="149" t="s">
+        <v>137</v>
+      </c>
+      <c r="W37" s="150" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" ht="30">
+      <c r="U38">
+        <v>2</v>
+      </c>
+      <c r="V38" s="149" t="s">
+        <v>2322</v>
+      </c>
+      <c r="W38" s="150" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" ht="30">
+      <c r="U39">
+        <v>3</v>
+      </c>
+      <c r="V39" s="149" t="s">
+        <v>2324</v>
+      </c>
+      <c r="W39" s="150" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="30">
+      <c r="U40">
+        <v>4</v>
+      </c>
+      <c r="V40" s="149" t="s">
+        <v>137</v>
+      </c>
+      <c r="W40" s="150" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="30">
+      <c r="U41">
+        <v>5</v>
+      </c>
+      <c r="V41" s="149" t="s">
+        <v>2327</v>
+      </c>
+      <c r="W41" s="150" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" ht="30">
+      <c r="U42">
+        <v>6</v>
+      </c>
+      <c r="V42" s="149" t="s">
+        <v>2322</v>
+      </c>
+      <c r="W42" s="150" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" ht="30">
+      <c r="U43">
+        <v>7</v>
+      </c>
+      <c r="V43" s="149" t="s">
+        <v>2330</v>
+      </c>
+      <c r="W43" s="150" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" ht="30">
+      <c r="U44">
+        <v>8</v>
+      </c>
+      <c r="V44" s="149" t="s">
+        <v>2332</v>
+      </c>
+      <c r="W44" s="150" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" ht="30">
+      <c r="U45">
+        <v>9</v>
+      </c>
+      <c r="V45" s="149" t="s">
+        <v>2334</v>
+      </c>
+      <c r="W45" s="150" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" ht="30">
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46" s="149" t="s">
+        <v>2336</v>
+      </c>
+      <c r="W46" s="150" t="s">
+        <v>2337</v>
+      </c>
+    </row>
     <row r="51" spans="10:15">
       <c r="J51" s="49" t="s">
         <v>1324</v>

--- a/docs/101_聲韻調對照表.xlsx
+++ b/docs/101_聲韻調對照表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B01F07-29DF-4718-A57E-45FD1FA0CB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD72754-31C1-406F-B798-19DA68A74E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="811" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
+    <workbookView xWindow="11115" yWindow="-3225" windowWidth="16410" windowHeight="22800" tabRatio="811" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
   </bookViews>
   <sheets>
     <sheet name="【聲】聲母對照表" sheetId="1" r:id="rId1"/>
@@ -9738,12 +9738,6 @@
     <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -9760,6 +9754,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -10953,1023 +10953,1023 @@
       <c r="L1" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="M1" s="163" t="s">
+      <c r="M1" s="161" t="s">
         <v>2358</v>
       </c>
-      <c r="N1" s="163" t="s">
+      <c r="N1" s="161" t="s">
         <v>2359</v>
       </c>
-      <c r="O1" s="163" t="s">
+      <c r="O1" s="161" t="s">
         <v>2363</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="29.25">
       <c r="A2" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>565</v>
+        <v>515</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>567</v>
+        <v>515</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>567</v>
+        <v>515</v>
       </c>
       <c r="E2" s="151" t="s">
-        <v>567</v>
+        <v>515</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>567</v>
+        <v>515</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>567</v>
+        <v>515</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>567</v>
+        <v>517</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>566</v>
+        <v>517</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>516</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>564</v>
+        <v>514</v>
       </c>
       <c r="L2" s="1"/>
-      <c r="M2" s="164">
-        <v>1</v>
-      </c>
-      <c r="N2" s="164" t="s">
-        <v>567</v>
-      </c>
-      <c r="O2" s="164" t="s">
-        <v>567</v>
+      <c r="M2" s="162">
+        <v>7</v>
+      </c>
+      <c r="N2" s="162" t="s">
+        <v>2344</v>
+      </c>
+      <c r="O2" s="162" t="s">
+        <v>2344</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="29.25">
       <c r="A3" s="1">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>432</v>
+        <v>519</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>432</v>
+        <v>519</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>432</v>
+        <v>519</v>
       </c>
       <c r="E3" s="151" t="s">
-        <v>432</v>
+        <v>522</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>588</v>
+        <v>522</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>432</v>
+        <v>519</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>587</v>
+        <v>521</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>587</v>
+        <v>521</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>586</v>
+        <v>520</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>589</v>
-      </c>
-      <c r="M3" s="165">
-        <v>2</v>
-      </c>
-      <c r="N3" s="165" t="s">
-        <v>1335</v>
-      </c>
-      <c r="O3" s="165" t="s">
-        <v>2364</v>
+        <v>518</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="163">
+        <v>4</v>
+      </c>
+      <c r="N3" s="163" t="s">
+        <v>2338</v>
+      </c>
+      <c r="O3" s="163" t="s">
+        <v>2338</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="29.25">
       <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E4" s="151" t="s">
+        <v>527</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="164">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="E4" s="151" t="s">
-        <v>571</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>2263</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="166">
-        <v>3</v>
-      </c>
-      <c r="N4" s="166" t="s">
-        <v>2340</v>
-      </c>
-      <c r="O4" s="166" t="s">
-        <v>2340</v>
+      <c r="N4" s="164" t="s">
+        <v>2345</v>
+      </c>
+      <c r="O4" s="164" t="s">
+        <v>2345</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="29.25">
       <c r="A5" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="E5" s="151" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="L5" s="1"/>
-      <c r="M5" s="166">
-        <v>4</v>
-      </c>
-      <c r="N5" s="166" t="s">
-        <v>2338</v>
-      </c>
-      <c r="O5" s="166" t="s">
-        <v>2338</v>
+      <c r="M5" s="164">
+        <v>13</v>
+      </c>
+      <c r="N5" s="164" t="s">
+        <v>2346</v>
+      </c>
+      <c r="O5" s="164" t="s">
+        <v>2346</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="29.25">
       <c r="A6" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="E6" s="151" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="L6" s="1"/>
-      <c r="M6" s="167">
-        <v>5</v>
-      </c>
-      <c r="N6" s="167" t="s">
-        <v>2339</v>
-      </c>
-      <c r="O6" s="167" t="s">
-        <v>2339</v>
+      <c r="M6" s="165">
+        <v>8</v>
+      </c>
+      <c r="N6" s="165" t="s">
+        <v>2341</v>
+      </c>
+      <c r="O6" s="165" t="s">
+        <v>2341</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="29.25">
       <c r="A7" s="1">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>591</v>
+        <v>539</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>591</v>
+        <v>542</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>591</v>
+        <v>542</v>
       </c>
       <c r="E7" s="151" t="s">
-        <v>591</v>
+        <v>519</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>593</v>
+        <v>519</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>591</v>
+        <v>542</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>592</v>
+        <v>541</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>592</v>
+        <v>541</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>590</v>
+        <v>540</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>594</v>
-      </c>
-      <c r="M7" s="165">
-        <v>6</v>
-      </c>
-      <c r="N7" s="165" t="s">
-        <v>1334</v>
-      </c>
-      <c r="O7" s="165" t="s">
-        <v>2343</v>
+        <v>538</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="163">
+        <v>5</v>
+      </c>
+      <c r="N7" s="163" t="s">
+        <v>2339</v>
+      </c>
+      <c r="O7" s="163" t="s">
+        <v>2339</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="29.25">
       <c r="A8" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>515</v>
+        <v>544</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="E8" s="151" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>517</v>
+        <v>546</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>517</v>
+        <v>546</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>516</v>
+        <v>545</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>514</v>
+        <v>543</v>
       </c>
       <c r="L8" s="1"/>
-      <c r="M8" s="166">
-        <v>7</v>
-      </c>
-      <c r="N8" s="166" t="s">
-        <v>2344</v>
-      </c>
-      <c r="O8" s="166" t="s">
-        <v>2344</v>
+      <c r="M8" s="164">
+        <v>9</v>
+      </c>
+      <c r="N8" s="164" t="s">
+        <v>2342</v>
+      </c>
+      <c r="O8" s="164" t="s">
+        <v>2342</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="29.25">
       <c r="A9" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="E9" s="151" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>533</v>
+        <v>548</v>
       </c>
       <c r="L9" s="1"/>
-      <c r="M9" s="166">
-        <v>8</v>
-      </c>
-      <c r="N9" s="166" t="s">
-        <v>2341</v>
-      </c>
-      <c r="O9" s="166" t="s">
-        <v>2341</v>
+      <c r="M9" s="164">
+        <v>15</v>
+      </c>
+      <c r="N9" s="164" t="s">
+        <v>2349</v>
+      </c>
+      <c r="O9" s="164" t="s">
+        <v>2349</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="29.25">
       <c r="A10" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="E10" s="151" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>543</v>
+        <v>2261</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>555</v>
       </c>
       <c r="L10" s="1"/>
-      <c r="M10" s="167">
-        <v>9</v>
-      </c>
-      <c r="N10" s="167" t="s">
-        <v>2342</v>
-      </c>
-      <c r="O10" s="167" t="s">
-        <v>2342</v>
+      <c r="M10" s="165">
+        <v>14</v>
+      </c>
+      <c r="N10" s="165" t="s">
+        <v>2352</v>
+      </c>
+      <c r="O10" s="165" t="s">
+        <v>2352</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="29.25">
       <c r="A11" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>596</v>
+        <v>562</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>407</v>
+        <v>562</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>407</v>
+        <v>562</v>
       </c>
       <c r="E11" s="151" t="s">
-        <v>407</v>
+        <v>562</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>598</v>
+        <v>562</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>407</v>
+        <v>562</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>597</v>
+        <v>624</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>2265</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>595</v>
+        <v>2262</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>563</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="L11" s="19" t="s">
-        <v>599</v>
-      </c>
-      <c r="M11" s="165">
-        <v>10</v>
-      </c>
-      <c r="N11" s="165" t="s">
-        <v>2357</v>
-      </c>
-      <c r="O11" s="165" t="s">
-        <v>2365</v>
+        <v>561</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="163">
+        <v>17</v>
+      </c>
+      <c r="N11" s="163" t="s">
+        <v>2351</v>
+      </c>
+      <c r="O11" s="163" t="s">
+        <v>2351</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="29.25">
       <c r="A12" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>527</v>
+        <v>567</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>527</v>
+        <v>567</v>
       </c>
       <c r="E12" s="151" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>527</v>
+        <v>567</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>574</v>
+        <v>567</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>566</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="L12" s="1"/>
-      <c r="M12" s="166">
-        <v>11</v>
-      </c>
-      <c r="N12" s="166" t="s">
-        <v>2347</v>
-      </c>
-      <c r="O12" s="166" t="s">
-        <v>2347</v>
+      <c r="M12" s="164">
+        <v>1</v>
+      </c>
+      <c r="N12" s="164" t="s">
+        <v>567</v>
+      </c>
+      <c r="O12" s="164" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="29.25">
       <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E13" s="151" t="s">
+        <v>571</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>2263</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="164">
         <v>3</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="E13" s="151" t="s">
-        <v>527</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="L13" s="1"/>
-      <c r="M13" s="166">
-        <v>12</v>
-      </c>
-      <c r="N13" s="166" t="s">
-        <v>2345</v>
-      </c>
-      <c r="O13" s="166" t="s">
-        <v>2345</v>
+      <c r="N13" s="164" t="s">
+        <v>2340</v>
+      </c>
+      <c r="O13" s="164" t="s">
+        <v>2340</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="29.25">
       <c r="A14" s="1">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>529</v>
+        <v>573</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="E14" s="151" t="s">
-        <v>524</v>
+        <v>576</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>524</v>
+        <v>576</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>531</v>
+        <v>597</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>530</v>
+        <v>574</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>528</v>
+        <v>572</v>
       </c>
       <c r="L14" s="1"/>
-      <c r="M14" s="167">
-        <v>13</v>
-      </c>
-      <c r="N14" s="167" t="s">
-        <v>2346</v>
-      </c>
-      <c r="O14" s="167" t="s">
-        <v>2346</v>
+      <c r="M14" s="165">
+        <v>11</v>
+      </c>
+      <c r="N14" s="165" t="s">
+        <v>2347</v>
+      </c>
+      <c r="O14" s="165" t="s">
+        <v>2347</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="29.25">
       <c r="A15" s="1">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>556</v>
+        <v>578</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>559</v>
+        <v>581</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="E15" s="151" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>558</v>
+        <v>626</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>2261</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>557</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>555</v>
+        <v>2264</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>577</v>
       </c>
       <c r="L15" s="1"/>
-      <c r="M15" s="165">
-        <v>14</v>
-      </c>
-      <c r="N15" s="165" t="s">
-        <v>2352</v>
-      </c>
-      <c r="O15" s="165" t="s">
-        <v>2352</v>
+      <c r="M15" s="163">
+        <v>16</v>
+      </c>
+      <c r="N15" s="163" t="s">
+        <v>2350</v>
+      </c>
+      <c r="O15" s="163" t="s">
+        <v>2350</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="29.25">
       <c r="A16" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>549</v>
+        <v>584</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="E16" s="151" t="s">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>551</v>
+        <v>585</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>551</v>
+        <v>585</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>550</v>
+        <v>583</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>548</v>
+        <v>583</v>
       </c>
       <c r="L16" s="1"/>
-      <c r="M16" s="166">
-        <v>15</v>
-      </c>
-      <c r="N16" s="166" t="s">
-        <v>2349</v>
-      </c>
-      <c r="O16" s="166" t="s">
-        <v>2349</v>
+      <c r="M16" s="164">
+        <v>22</v>
+      </c>
+      <c r="N16" s="164" t="s">
+        <v>2348</v>
+      </c>
+      <c r="O16" s="164" t="s">
+        <v>2348</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="29.25">
       <c r="A17" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>578</v>
+        <v>432</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>581</v>
+        <v>432</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>580</v>
+        <v>432</v>
       </c>
       <c r="E17" s="151" t="s">
-        <v>580</v>
+        <v>432</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>582</v>
+        <v>432</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>626</v>
+        <v>587</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>2264</v>
+        <v>587</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="L17" s="1"/>
-      <c r="M17" s="166">
-        <v>16</v>
-      </c>
-      <c r="N17" s="166" t="s">
-        <v>2350</v>
-      </c>
-      <c r="O17" s="166" t="s">
-        <v>2350</v>
+        <v>586</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="M17" s="164">
+        <v>2</v>
+      </c>
+      <c r="N17" s="164" t="s">
+        <v>1335</v>
+      </c>
+      <c r="O17" s="164" t="s">
+        <v>2364</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="29.25">
       <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E18" s="151" t="s">
+        <v>591</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>594</v>
+      </c>
+      <c r="M18" s="165">
+        <v>6</v>
+      </c>
+      <c r="N18" s="165" t="s">
+        <v>1334</v>
+      </c>
+      <c r="O18" s="165" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="29.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="E19" s="151" t="s">
+        <v>407</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>2265</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="M19" s="163">
         <v>10</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="E18" s="151" t="s">
-        <v>562</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>2262</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>563</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="L18" s="1"/>
-      <c r="M18" s="167">
-        <v>17</v>
-      </c>
-      <c r="N18" s="167" t="s">
-        <v>2351</v>
-      </c>
-      <c r="O18" s="167" t="s">
-        <v>2351</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="29.25">
-      <c r="A19" s="17">
-        <v>19</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>600</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>602</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>602</v>
-      </c>
-      <c r="E19" s="162" t="s">
-        <v>604</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>603</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>602</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>601</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>2261</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>557</v>
-      </c>
-      <c r="K19" s="18" t="s">
-        <v>555</v>
-      </c>
-      <c r="L19" s="19" t="s">
-        <v>622</v>
-      </c>
-      <c r="M19" s="165">
-        <v>18</v>
-      </c>
-      <c r="N19" s="165" t="s">
-        <v>2353</v>
-      </c>
-      <c r="O19" s="165" t="s">
-        <v>2366</v>
+      <c r="N19" s="163" t="s">
+        <v>2357</v>
+      </c>
+      <c r="O19" s="163" t="s">
+        <v>2365</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="29.25">
       <c r="A20" s="17">
-        <v>20</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>606</v>
+        <v>19</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>600</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>608</v>
-      </c>
-      <c r="E20" s="162" t="s">
         <v>602</v>
       </c>
+      <c r="E20" s="160" t="s">
+        <v>604</v>
+      </c>
       <c r="F20" s="17" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>610</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>2360</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>607</v>
+        <v>602</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>2261</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>605</v>
+        <v>555</v>
       </c>
       <c r="L20" s="19" t="s">
-        <v>623</v>
-      </c>
-      <c r="M20" s="166">
-        <v>19</v>
-      </c>
-      <c r="N20" s="166" t="s">
-        <v>2354</v>
-      </c>
-      <c r="O20" s="166" t="s">
-        <v>2367</v>
+        <v>622</v>
+      </c>
+      <c r="M20" s="164">
+        <v>18</v>
+      </c>
+      <c r="N20" s="164" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O20" s="164" t="s">
+        <v>2366</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="29.25">
       <c r="A21" s="17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>614</v>
-      </c>
-      <c r="E21" s="162" t="s">
+        <v>608</v>
+      </c>
+      <c r="E21" s="160" t="s">
+        <v>602</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>608</v>
+      </c>
+      <c r="G21" s="17" t="s">
         <v>610</v>
       </c>
-      <c r="F21" s="17" t="s">
-        <v>614</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>616</v>
-      </c>
       <c r="H21" s="19" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>579</v>
+        <v>550</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="L21" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="M21" s="166">
-        <v>20</v>
-      </c>
-      <c r="N21" s="166" t="s">
-        <v>2355</v>
-      </c>
-      <c r="O21" s="166" t="s">
-        <v>2368</v>
+        <v>623</v>
+      </c>
+      <c r="M21" s="164">
+        <v>19</v>
+      </c>
+      <c r="N21" s="164" t="s">
+        <v>2354</v>
+      </c>
+      <c r="O21" s="164" t="s">
+        <v>2367</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="29.25">
       <c r="A22" s="17">
+        <v>21</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>615</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>614</v>
+      </c>
+      <c r="E22" s="160" t="s">
+        <v>610</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>614</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>616</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>2361</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>579</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>611</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>627</v>
+      </c>
+      <c r="M22" s="165">
+        <v>20</v>
+      </c>
+      <c r="N22" s="165" t="s">
+        <v>2355</v>
+      </c>
+      <c r="O22" s="165" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="29.25">
+      <c r="A23" s="17">
         <v>22</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B23" s="19" t="s">
         <v>618</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C23" s="17" t="s">
         <v>620</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D23" s="17" t="s">
         <v>620</v>
       </c>
-      <c r="E22" s="162" t="s">
+      <c r="E23" s="160" t="s">
         <v>621</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F23" s="17" t="s">
         <v>620</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="G23" s="17" t="s">
         <v>620</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="H23" s="19" t="s">
         <v>2362</v>
       </c>
-      <c r="I22" s="19" t="s">
+      <c r="I23" s="19" t="s">
         <v>619</v>
       </c>
-      <c r="J22" s="18" t="s">
+      <c r="J23" s="18" t="s">
         <v>563</v>
       </c>
-      <c r="K22" s="18" t="s">
+      <c r="K23" s="18" t="s">
         <v>617</v>
       </c>
-      <c r="L22" s="19" t="s">
+      <c r="L23" s="19" t="s">
         <v>625</v>
       </c>
-      <c r="M22" s="167">
+      <c r="M23" s="165">
         <v>21</v>
       </c>
-      <c r="N22" s="167" t="s">
+      <c r="N23" s="165" t="s">
         <v>2356</v>
       </c>
-      <c r="O22" s="167" t="s">
+      <c r="O23" s="165" t="s">
         <v>2369</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="29.25">
-      <c r="A23" s="1">
-        <v>15</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="E23" s="151" t="s">
-        <v>584</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="L23" s="1"/>
-      <c r="M23" s="167">
-        <v>22</v>
-      </c>
-      <c r="N23" s="167" t="s">
-        <v>2348</v>
-      </c>
-      <c r="O23" s="167" t="s">
-        <v>2348</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N23">
-    <sortCondition ref="M2:M23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O23">
+    <sortCondition ref="A8:A23"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -32279,19 +32279,19 @@
   <sheetFormatPr defaultRowHeight="25.5"/>
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" thickBot="1">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="166" t="s">
         <v>936</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="J1" s="161"/>
-      <c r="K1" s="161"/>
+      <c r="B1" s="167"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="167"/>
+      <c r="G1" s="167"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="167"/>
+      <c r="J1" s="167"/>
+      <c r="K1" s="167"/>
     </row>
     <row r="2" spans="1:11" ht="26.25" thickBot="1">
       <c r="A2" s="77" t="s">

--- a/docs/101_聲韻調對照表.xlsx
+++ b/docs/101_聲韻調對照表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40971D8-CBE7-49E1-9E67-C9F8DEF73D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36341416-4B08-41E2-B2AC-05CD8E4F1550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="811" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="811" activeTab="1" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
   </bookViews>
   <sheets>
     <sheet name="輸入工具" sheetId="20" r:id="rId1"/>
@@ -314,7 +314,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -9741,7 +9741,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -10288,12 +10288,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="48" fillId="5" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -10318,29 +10312,14 @@
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="11" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="11" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="16" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="7" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="7" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="7" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10364,464 +10343,6 @@
         <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <name val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFDEE2E6"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE2E6"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <name val="Noto Sans"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE2E6"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE2E6"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE2E6"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE2E6"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <name val="Noto Sans"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE2E6"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE2E6"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE2E6"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE2E6"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE2E6"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE2E6"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE2E6"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE2E6"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Noto Sans"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE2E6"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE2E6"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE2E6"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE2E6"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Noto Sans"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE2E6"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE2E6"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE2E6"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE2E6"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Noto Sans"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE2E6"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE2E6"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE2E6"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE2E6"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Noto Sans"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE2E6"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE2E6"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE2E6"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE2E6"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="8"/>
-        <name val="Noto Sans"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE2E6"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE2E6"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE2E6"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE2E6"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFC00000"/>
-        <name val="Noto Sans"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE2E6"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE2E6"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE2E6"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE2E6"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <name val="Noto Sans"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFDEE2E6"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE2E6"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE2E6"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFDEE2E6"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE2E6"/>
-        </right>
-      </border>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -11553,6 +11074,464 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <name val="Noto Sans"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE2E6"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE2E6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE2E6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <name val="Noto Sans"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE2E6"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE2E6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE2E6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE2E6"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE2E6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE2E6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Noto Sans"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE2E6"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE2E6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE2E6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Noto Sans"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE2E6"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE2E6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE2E6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Noto Sans"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE2E6"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE2E6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE2E6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Noto Sans"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE2E6"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE2E6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE2E6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="8"/>
+        <name val="Noto Sans"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE2E6"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE2E6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE2E6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFC00000"/>
+        <name val="Noto Sans"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE2E6"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE2E6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE2E6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <name val="Noto Sans"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE2E6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE2E6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFDEE2E6"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFDEE2E6"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -11572,23 +11551,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C40E26AF-4D3B-4E1A-8080-AAAFDBD9F514}" name="台羅韻母表" displayName="台羅韻母表" ref="A3:L89" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="14" headerRowCellStyle="一般 4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C40E26AF-4D3B-4E1A-8080-AAAFDBD9F514}" name="台羅韻母表" displayName="台羅韻母表" ref="A3:L89" totalsRowShown="0" headerRowDxfId="49" tableBorderDxfId="48" headerRowCellStyle="一般 4">
   <autoFilter ref="A3:L89" xr:uid="{C40E26AF-4D3B-4E1A-8080-AAAFDBD9F514}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{67434336-EDB9-486F-A543-044F4F8ED438}" name="序號" dataDxfId="13" dataCellStyle="一般 4">
+    <tableColumn id="1" xr3:uid="{67434336-EDB9-486F-A543-044F4F8ED438}" name="序號" dataDxfId="47" dataCellStyle="一般 4">
       <calculatedColumnFormula xml:space="preserve"> ROW() - 3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3F9C0D5C-037D-401B-9E57-7E99A8351BB7}" name="國際音標" dataDxfId="12" dataCellStyle="一般 4"/>
-    <tableColumn id="3" xr3:uid="{B8205AD7-58F1-43A8-824B-C0E88B7F29C9}" name="台羅拼音" dataDxfId="11" dataCellStyle="一般 4"/>
-    <tableColumn id="4" xr3:uid="{1D977D40-0654-4AD5-9198-DBDACA80FC0C}" name="台語音標" dataDxfId="10" dataCellStyle="一般 4"/>
-    <tableColumn id="5" xr3:uid="{62D369BE-67AE-46A8-A874-749CA8F4D5FA}" name="台語注音二式" dataDxfId="9" dataCellStyle="一般 4"/>
-    <tableColumn id="6" xr3:uid="{6ACFDCD0-A05A-4E77-B6C3-F4F9693A1A87}" name="閩拼方案" dataDxfId="8" dataCellStyle="一般 4"/>
-    <tableColumn id="7" xr3:uid="{EA72CB27-56D4-45DE-A159-5ECE3355E261}" name="白話字" dataDxfId="7" dataCellStyle="一般 4"/>
+    <tableColumn id="2" xr3:uid="{3F9C0D5C-037D-401B-9E57-7E99A8351BB7}" name="國際音標" dataDxfId="46" dataCellStyle="一般 4"/>
+    <tableColumn id="3" xr3:uid="{B8205AD7-58F1-43A8-824B-C0E88B7F29C9}" name="台羅拼音" dataDxfId="45" dataCellStyle="一般 4"/>
+    <tableColumn id="4" xr3:uid="{1D977D40-0654-4AD5-9198-DBDACA80FC0C}" name="台語音標" dataDxfId="44" dataCellStyle="一般 4"/>
+    <tableColumn id="5" xr3:uid="{62D369BE-67AE-46A8-A874-749CA8F4D5FA}" name="台語注音二式" dataDxfId="43" dataCellStyle="一般 4"/>
+    <tableColumn id="6" xr3:uid="{6ACFDCD0-A05A-4E77-B6C3-F4F9693A1A87}" name="閩拼方案" dataDxfId="42" dataCellStyle="一般 4"/>
+    <tableColumn id="7" xr3:uid="{EA72CB27-56D4-45DE-A159-5ECE3355E261}" name="白話字" dataDxfId="41" dataCellStyle="一般 4"/>
     <tableColumn id="8" xr3:uid="{86276E07-00D8-414F-A14A-89CA8E4736C0}" name="方音符號"/>
-    <tableColumn id="13" xr3:uid="{4AC7395E-4D7D-4B49-A8A4-FDDE23D368B8}" name="台語注音" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{32F912D0-78F9-4541-95B9-4330F53FB63D}" name="十五音" dataDxfId="6" dataCellStyle="一般 4"/>
-    <tableColumn id="10" xr3:uid="{B3319D84-8B1E-4C1D-99D4-7DD8250E72D0}" name="聲韻調類" dataDxfId="5" dataCellStyle="一般 4"/>
-    <tableColumn id="11" xr3:uid="{0232C7F0-707C-4291-B834-2A92B01DFDF9}" name="字長" dataDxfId="4" dataCellStyle="一般 4">
+    <tableColumn id="13" xr3:uid="{4AC7395E-4D7D-4B49-A8A4-FDDE23D368B8}" name="台語注音" dataDxfId="40"/>
+    <tableColumn id="9" xr3:uid="{32F912D0-78F9-4541-95B9-4330F53FB63D}" name="十五音" dataDxfId="39" dataCellStyle="一般 4"/>
+    <tableColumn id="10" xr3:uid="{B3319D84-8B1E-4C1D-99D4-7DD8250E72D0}" name="聲韻調類" dataDxfId="38" dataCellStyle="一般 4"/>
+    <tableColumn id="11" xr3:uid="{0232C7F0-707C-4291-B834-2A92B01DFDF9}" name="字長" dataDxfId="37" dataCellStyle="一般 4">
       <calculatedColumnFormula xml:space="preserve"> LEN(D4)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11597,51 +11576,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{771C3941-9899-48C4-8E14-367017F7B2F5}" name="韻母對照表" displayName="韻母對照表" ref="A1:N85" totalsRowShown="0" headerRowDxfId="49" headerRowBorderDxfId="48" tableBorderDxfId="47" totalsRowBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{771C3941-9899-48C4-8E14-367017F7B2F5}" name="韻母對照表" displayName="韻母對照表" ref="A1:N85" totalsRowShown="0" headerRowDxfId="36" headerRowBorderDxfId="35" tableBorderDxfId="34" totalsRowBorderDxfId="33">
   <autoFilter ref="A1:N85" xr:uid="{771C3941-9899-48C4-8E14-367017F7B2F5}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{93BCA6A2-508B-467B-95D1-473C97CCD52B}" name="識別號" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{C4E57A92-27A9-46F6-A864-9668B62AB3D8}" name="國際音標" dataDxfId="44"/>
-    <tableColumn id="7" xr3:uid="{D04A8FC9-DCA4-4643-AE3B-824F465B8E3A}" name="台羅拼音" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{DA98A1A1-49CA-4EC1-91D5-BF45045A4B18}" name="台語音標" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{E8D82139-523B-47F7-B0CC-47FDC35BBF0B}" name="注音二式" dataDxfId="41"/>
-    <tableColumn id="10" xr3:uid="{BDA4D6F0-BBAC-44DF-85B3-15A86E2ED416}" name="閩拼方案" dataDxfId="40"/>
-    <tableColumn id="9" xr3:uid="{972A94F9-A940-4172-AB75-0BE33372A5A6}" name="白話字" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{88460F28-F486-4EB3-974F-039F84D0E83A}" name="方音符號" dataDxfId="38"/>
-    <tableColumn id="14" xr3:uid="{EF2755BF-6678-4CD8-B300-0D0325E9E0D0}" name="台語注音" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{8C99734F-A142-4FBD-96DD-463C060588A5}" name="漢字例" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{80F0C42C-C2BD-4707-8BE9-49A90C7647AB}" name="十五音" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{77E72489-4845-4BE7-807E-50EDB35447E7}" name="十五音序" dataDxfId="34"/>
-    <tableColumn id="12" xr3:uid="{4D0E40DE-9C66-4BA2-B18D-2F564923928D}" name="舒促聲" dataDxfId="33"/>
-    <tableColumn id="13" xr3:uid="{1E5A033C-A3E4-47B2-8D3D-334C23BE852B}" name="十五音識別碼" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{93BCA6A2-508B-467B-95D1-473C97CCD52B}" name="識別號" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{C4E57A92-27A9-46F6-A864-9668B62AB3D8}" name="國際音標" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{D04A8FC9-DCA4-4643-AE3B-824F465B8E3A}" name="台羅拼音" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{DA98A1A1-49CA-4EC1-91D5-BF45045A4B18}" name="台語音標" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{E8D82139-523B-47F7-B0CC-47FDC35BBF0B}" name="注音二式" dataDxfId="28"/>
+    <tableColumn id="10" xr3:uid="{BDA4D6F0-BBAC-44DF-85B3-15A86E2ED416}" name="閩拼方案" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{972A94F9-A940-4172-AB75-0BE33372A5A6}" name="白話字" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{88460F28-F486-4EB3-974F-039F84D0E83A}" name="方音符號" dataDxfId="25"/>
+    <tableColumn id="14" xr3:uid="{EF2755BF-6678-4CD8-B300-0D0325E9E0D0}" name="台語注音" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{8C99734F-A142-4FBD-96DD-463C060588A5}" name="漢字例" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{80F0C42C-C2BD-4707-8BE9-49A90C7647AB}" name="十五音" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{77E72489-4845-4BE7-807E-50EDB35447E7}" name="十五音序" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{4D0E40DE-9C66-4BA2-B18D-2F564923928D}" name="舒促聲" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{1E5A033C-A3E4-47B2-8D3D-334C23BE852B}" name="十五音識別碼" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CFF90B7A-D09E-43B2-979B-7CD1EE35DCEF}" name="韻母對照表3" displayName="韻母對照表3" ref="A1:M85" totalsRowShown="0" headerRowDxfId="31" headerRowBorderDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CFF90B7A-D09E-43B2-979B-7CD1EE35DCEF}" name="韻母對照表3" displayName="韻母對照表3" ref="A1:M85" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A1:M85" xr:uid="{771C3941-9899-48C4-8E14-367017F7B2F5}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{C10E80BA-9FEE-411B-A2E1-0B8D75C43A73}" name="識別號" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{BDE2F94E-9AD0-4497-B0A4-0887F343995C}" name="十五音" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{1BB80AC9-0E65-4250-97F0-4C9BF936F6F4}" name="漢字例" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{FF3D3154-85AC-43FE-9B6E-613CB6837684}" name="方音符號" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{76F226E4-4708-40A7-849D-3CC6919D3693}" name="台語音標" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{B2037F3B-8888-4074-8870-6B45341F0C3A}" name="國際音標" dataDxfId="22">
+    <tableColumn id="1" xr3:uid="{C10E80BA-9FEE-411B-A2E1-0B8D75C43A73}" name="識別號" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{BDE2F94E-9AD0-4497-B0A4-0887F343995C}" name="十五音" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{1BB80AC9-0E65-4250-97F0-4C9BF936F6F4}" name="漢字例" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{FF3D3154-85AC-43FE-9B6E-613CB6837684}" name="方音符號" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{76F226E4-4708-40A7-849D-3CC6919D3693}" name="台語音標" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{B2037F3B-8888-4074-8870-6B45341F0C3A}" name="國際音標" dataDxfId="9">
       <calculatedColumnFormula array="1" xml:space="preserve"> IF(韻母對照表3[[#This Row],[舒促聲]]="舒聲", INDEX(十五音韻母!$G$3:$G$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)), INDEX(十五音韻母!$H$3:$H$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8FF1DC7C-D8AD-4071-B26D-6830788BB67A}" name="閩拼方案" dataDxfId="21">
+    <tableColumn id="10" xr3:uid="{8FF1DC7C-D8AD-4071-B26D-6830788BB67A}" name="閩拼方案" dataDxfId="8">
       <calculatedColumnFormula array="1" xml:space="preserve"> IF(韻母對照表3[[#This Row],[舒促聲]]="舒聲", INDEX(十五音韻母!$I$3:$I$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)), INDEX(十五音韻母!$J$3:$J$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{76F2259B-CA5E-44D6-86F0-A1217D200D54}" name="台羅拼音" dataDxfId="20">
+    <tableColumn id="7" xr3:uid="{76F2259B-CA5E-44D6-86F0-A1217D200D54}" name="台羅拼音" dataDxfId="7">
       <calculatedColumnFormula array="1" xml:space="preserve"> IF(韻母對照表3[[#This Row],[舒促聲]]="舒聲", INDEX(十五音韻母!$K$3:$K$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)), INDEX(十五音韻母!$L$3:$L$52, MATCH(TRUE, EXACT(韻母對照表3[[#This Row],[十五音]], 十五音韻母!$B$3:$B$52), 0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DF4BA570-1408-41DB-8328-90FB8913B1DF}" name="注音二式" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{42E33940-E4F1-4C86-AD57-6236C50EBE40}" name="白話字" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{BE8C4436-8D84-475B-A5C6-C392918893AA}" name="十五音序" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{4D04DB9F-1246-4494-8D81-B2950125EC5B}" name="舒促聲" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{EB7195BB-541B-463D-BA37-EBE312BD24A4}" name="十五音識別碼" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{DF4BA570-1408-41DB-8328-90FB8913B1DF}" name="注音二式" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{42E33940-E4F1-4C86-AD57-6236C50EBE40}" name="白話字" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{BE8C4436-8D84-475B-A5C6-C392918893AA}" name="十五音序" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{4D04DB9F-1246-4494-8D81-B2950125EC5B}" name="舒促聲" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{EB7195BB-541B-463D-BA37-EBE312BD24A4}" name="十五音識別碼" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12012,16 +11991,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="190" t="s">
         <v>2358</v>
       </c>
-      <c r="D2" s="199" t="s">
+      <c r="D2" s="190" t="s">
         <v>2359</v>
       </c>
-      <c r="E2" s="199" t="s">
+      <c r="E2" s="190" t="s">
         <v>2360</v>
       </c>
-      <c r="F2" s="199" t="s">
+      <c r="F2" s="190" t="s">
         <v>878</v>
       </c>
       <c r="H2" t="s">
@@ -39109,19 +39088,19 @@
   <sheetFormatPr defaultRowHeight="25.5"/>
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" thickBot="1">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="191" t="s">
         <v>936</v>
       </c>
-      <c r="B1" s="183"/>
-      <c r="C1" s="183"/>
-      <c r="D1" s="183"/>
-      <c r="E1" s="183"/>
-      <c r="F1" s="183"/>
-      <c r="G1" s="183"/>
-      <c r="H1" s="183"/>
-      <c r="I1" s="183"/>
-      <c r="J1" s="183"/>
-      <c r="K1" s="183"/>
+      <c r="B1" s="192"/>
+      <c r="C1" s="192"/>
+      <c r="D1" s="192"/>
+      <c r="E1" s="192"/>
+      <c r="F1" s="192"/>
+      <c r="G1" s="192"/>
+      <c r="H1" s="192"/>
+      <c r="I1" s="192"/>
+      <c r="J1" s="192"/>
+      <c r="K1" s="192"/>
     </row>
     <row r="2" spans="1:11" ht="26.25" thickBot="1">
       <c r="A2" s="77" t="s">
@@ -40004,6 +39983,7 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -40067,1011 +40047,1011 @@
     </row>
     <row r="2" spans="1:15" ht="29.25">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>515</v>
+        <v>565</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>515</v>
+        <v>567</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>515</v>
+        <v>567</v>
       </c>
       <c r="E2" s="150" t="s">
-        <v>515</v>
+        <v>567</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>515</v>
+        <v>567</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>515</v>
+        <v>567</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>517</v>
+        <v>567</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>516</v>
+        <v>567</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>566</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>514</v>
+        <v>564</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="161">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N2" s="161" t="s">
-        <v>2315</v>
+        <v>567</v>
       </c>
       <c r="O2" s="161" t="s">
-        <v>2315</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="29.25">
       <c r="A3" s="1">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E3" s="150" t="s">
+        <v>432</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="M3" s="162">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E3" s="150" t="s">
-        <v>522</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="162">
-        <v>4</v>
-      </c>
       <c r="N3" s="162" t="s">
-        <v>2309</v>
+        <v>1306</v>
       </c>
       <c r="O3" s="162" t="s">
-        <v>2309</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="29.25">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E4" s="150" t="s">
-        <v>527</v>
+        <v>571</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>527</v>
+        <v>571</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>526</v>
+        <v>570</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>525</v>
+        <v>2234</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>569</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>523</v>
+        <v>568</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="163">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N4" s="163" t="s">
-        <v>2316</v>
+        <v>2311</v>
       </c>
       <c r="O4" s="163" t="s">
-        <v>2316</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="29.25">
       <c r="A5" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="E5" s="150" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="163">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N5" s="163" t="s">
-        <v>2317</v>
+        <v>2309</v>
       </c>
       <c r="O5" s="163" t="s">
-        <v>2317</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="29.25">
       <c r="A6" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="E6" s="150" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="164">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N6" s="164" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
       <c r="O6" s="164" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="29.25">
       <c r="A7" s="1">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E7" s="150" t="s">
+        <v>591</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>594</v>
+      </c>
+      <c r="M7" s="162">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="E7" s="150" t="s">
-        <v>519</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="162">
-        <v>5</v>
-      </c>
       <c r="N7" s="162" t="s">
-        <v>2310</v>
+        <v>1305</v>
       </c>
       <c r="O7" s="162" t="s">
-        <v>2310</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="29.25">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>547</v>
+        <v>515</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>547</v>
+        <v>515</v>
       </c>
       <c r="E8" s="150" t="s">
-        <v>534</v>
+        <v>515</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>534</v>
+        <v>515</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>547</v>
+        <v>515</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>546</v>
+        <v>517</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>546</v>
+        <v>517</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>545</v>
+        <v>516</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>543</v>
+        <v>514</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="163">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N8" s="163" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="O8" s="163" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="29.25">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>553</v>
+        <v>534</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="E9" s="150" t="s">
-        <v>552</v>
+        <v>537</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>552</v>
+        <v>537</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="163">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N9" s="163" t="s">
-        <v>2320</v>
+        <v>2312</v>
       </c>
       <c r="O9" s="163" t="s">
-        <v>2320</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="29.25">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="E10" s="150" t="s">
-        <v>560</v>
+        <v>534</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>560</v>
+        <v>534</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>2232</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>557</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>555</v>
+        <v>546</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>543</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="164">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N10" s="164" t="s">
-        <v>2323</v>
+        <v>2313</v>
       </c>
       <c r="O10" s="164" t="s">
-        <v>2323</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="29.25">
       <c r="A11" s="1">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="E11" s="150" t="s">
+        <v>407</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>2236</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="M11" s="162">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="E11" s="150" t="s">
-        <v>562</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>2233</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>563</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="162">
-        <v>17</v>
-      </c>
       <c r="N11" s="162" t="s">
-        <v>2322</v>
+        <v>2328</v>
       </c>
       <c r="O11" s="162" t="s">
-        <v>2322</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="29.25">
       <c r="A12" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>567</v>
+        <v>527</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>567</v>
+        <v>527</v>
       </c>
       <c r="E12" s="150" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>567</v>
+        <v>527</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>566</v>
+        <v>597</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="163">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N12" s="163" t="s">
-        <v>567</v>
+        <v>2318</v>
       </c>
       <c r="O12" s="163" t="s">
-        <v>567</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="29.25">
       <c r="A13" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E13" s="150" t="s">
-        <v>571</v>
+        <v>527</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>571</v>
+        <v>527</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>570</v>
+        <v>526</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>569</v>
+        <v>526</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>525</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>568</v>
+        <v>523</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="163">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N13" s="163" t="s">
-        <v>2311</v>
+        <v>2316</v>
       </c>
       <c r="O13" s="163" t="s">
-        <v>2311</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="29.25">
       <c r="A14" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>573</v>
+        <v>529</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="E14" s="150" t="s">
-        <v>576</v>
+        <v>524</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>576</v>
+        <v>524</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>575</v>
+        <v>531</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>597</v>
+        <v>531</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>574</v>
+        <v>530</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>572</v>
+        <v>528</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="164">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N14" s="164" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="O14" s="164" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="29.25">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>581</v>
+        <v>559</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="E15" s="150" t="s">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>626</v>
+        <v>558</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>2235</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>577</v>
+        <v>2232</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>555</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="162">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N15" s="162" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="O15" s="162" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="29.25">
       <c r="A16" s="1">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>584</v>
+        <v>549</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>584</v>
+        <v>553</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="E16" s="150" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>584</v>
+        <v>554</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>583</v>
+        <v>550</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>583</v>
+        <v>548</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="163">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="N16" s="163" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="O16" s="163" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="29.25">
       <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>580</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="163">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="E17" s="150" t="s">
-        <v>432</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>589</v>
-      </c>
-      <c r="M17" s="163">
-        <v>2</v>
-      </c>
       <c r="N17" s="163" t="s">
-        <v>1306</v>
+        <v>2321</v>
       </c>
       <c r="O17" s="163" t="s">
-        <v>2335</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="29.25">
       <c r="A18" s="1">
+        <v>10</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E18" s="150" t="s">
+        <v>562</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>2233</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="164">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="E18" s="150" t="s">
-        <v>591</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>594</v>
-      </c>
-      <c r="M18" s="164">
-        <v>6</v>
-      </c>
       <c r="N18" s="164" t="s">
-        <v>1305</v>
+        <v>2322</v>
       </c>
       <c r="O18" s="164" t="s">
-        <v>2314</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="29.25">
-      <c r="A19" s="1">
+      <c r="A19" s="17">
+        <v>19</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="E19" s="159" t="s">
+        <v>604</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>603</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>2232</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>557</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>555</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>622</v>
+      </c>
+      <c r="M19" s="162">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="E19" s="150" t="s">
-        <v>407</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>2236</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="L19" s="19" t="s">
-        <v>599</v>
-      </c>
-      <c r="M19" s="162">
-        <v>10</v>
-      </c>
       <c r="N19" s="162" t="s">
-        <v>2328</v>
+        <v>2324</v>
       </c>
       <c r="O19" s="162" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="29.25">
       <c r="A20" s="17">
+        <v>20</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>606</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>609</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>608</v>
+      </c>
+      <c r="E20" s="159" t="s">
+        <v>602</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>608</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>610</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>2331</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>550</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>605</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>623</v>
+      </c>
+      <c r="M20" s="163">
         <v>19</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>600</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>602</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>602</v>
-      </c>
-      <c r="E20" s="159" t="s">
-        <v>604</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>603</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>602</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>601</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>2232</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>557</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>555</v>
-      </c>
-      <c r="L20" s="19" t="s">
-        <v>622</v>
-      </c>
-      <c r="M20" s="163">
-        <v>18</v>
-      </c>
       <c r="N20" s="163" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="O20" s="163" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="29.25">
       <c r="A21" s="17">
+        <v>21</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>615</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>614</v>
+      </c>
+      <c r="E21" s="159" t="s">
+        <v>610</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>614</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>616</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>2332</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>579</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>611</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>627</v>
+      </c>
+      <c r="M21" s="163">
         <v>20</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>606</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>609</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>608</v>
-      </c>
-      <c r="E21" s="159" t="s">
-        <v>602</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>608</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>610</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>2331</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>607</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>550</v>
-      </c>
-      <c r="K21" s="18" t="s">
-        <v>605</v>
-      </c>
-      <c r="L21" s="19" t="s">
-        <v>623</v>
-      </c>
-      <c r="M21" s="163">
-        <v>19</v>
-      </c>
       <c r="N21" s="163" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="O21" s="163" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="29.25">
       <c r="A22" s="17">
+        <v>22</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>618</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="E22" s="159" t="s">
+        <v>621</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>2333</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>563</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>617</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>625</v>
+      </c>
+      <c r="M22" s="164">
         <v>21</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>612</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>615</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>614</v>
-      </c>
-      <c r="E22" s="159" t="s">
-        <v>610</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>614</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>616</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>2332</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>613</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>579</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>611</v>
-      </c>
-      <c r="L22" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="M22" s="164">
-        <v>20</v>
-      </c>
       <c r="N22" s="164" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="O22" s="164" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="29.25">
-      <c r="A23" s="17">
+      <c r="A23" s="1">
+        <v>15</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="E23" s="150" t="s">
+        <v>584</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="L23" s="1"/>
+      <c r="M23" s="164">
         <v>22</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>618</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>620</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>620</v>
-      </c>
-      <c r="E23" s="159" t="s">
-        <v>621</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>620</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>620</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>2333</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>619</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>563</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>617</v>
-      </c>
-      <c r="L23" s="19" t="s">
-        <v>625</v>
-      </c>
-      <c r="M23" s="164">
-        <v>21</v>
-      </c>
       <c r="N23" s="164" t="s">
-        <v>2327</v>
+        <v>2319</v>
       </c>
       <c r="O23" s="164" t="s">
-        <v>2340</v>
+        <v>2319</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O23">
-    <sortCondition ref="A8:A23"/>
+    <sortCondition ref="M12:M23"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -41118,7 +41098,7 @@
       <c r="I1" s="51" t="s">
         <v>2486</v>
       </c>
-      <c r="J1" s="191" t="s">
+      <c r="J1" s="189" t="s">
         <v>2487</v>
       </c>
       <c r="K1" s="51"/>
@@ -41157,7 +41137,7 @@
     </row>
     <row r="2" spans="1:48" ht="27" thickBot="1"/>
     <row r="3" spans="1:48" ht="54.75" thickBot="1">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="182" t="s">
         <v>898</v>
       </c>
       <c r="B3" s="141" t="s">
@@ -41242,7 +41222,7 @@
       <c r="AI3" s="131"/>
     </row>
     <row r="4" spans="1:48" ht="27.75" thickBot="1">
-      <c r="A4" s="185">
+      <c r="A4" s="183">
         <f xml:space="preserve"> ROW() - 3</f>
         <v>1</v>
       </c>
@@ -41350,43 +41330,43 @@
         <v>å</v>
       </c>
       <c r="AJ4" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, Y$1, "/", Y4, "/")</f>
+        <f t="shared" ref="AJ4:AS10" si="4" xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, Y$1, "/", Y4, "/")</f>
         <v xml:space="preserve">    - xform/》a1/a/</v>
       </c>
       <c r="AK4" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, Z$1, "/", Z4, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a2/á/</v>
       </c>
       <c r="AL4" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, AA$1, "/", AA4, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a3/à/</v>
       </c>
       <c r="AM4" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, AB$1, "/", AB4, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a4/a/</v>
       </c>
       <c r="AN4" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, AC$1, "/", AC4, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a5/ǎ/</v>
       </c>
       <c r="AO4" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, AD$1, "/", AD4, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a6/á/</v>
       </c>
       <c r="AP4" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, AE$1, "/", AE4, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a7/ā/</v>
       </c>
       <c r="AQ4" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, AF$1, "/", AF4, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a8/a̍/</v>
       </c>
       <c r="AR4" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, AG$1, "/", AG4, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a9/a̋/</v>
       </c>
       <c r="AS4" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, AH$1, "/", AH4, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》a9/å/</v>
       </c>
       <c r="AT4" s="133"/>
@@ -41394,8 +41374,8 @@
       <c r="AV4" s="130"/>
     </row>
     <row r="5" spans="1:48" ht="27.75" thickBot="1">
-      <c r="A5" s="185">
-        <f t="shared" ref="A5:A72" si="4" xml:space="preserve"> ROW() - 3</f>
+      <c r="A5" s="183">
+        <f t="shared" ref="A5:A72" si="5" xml:space="preserve"> ROW() - 3</f>
         <v>2</v>
       </c>
       <c r="B5" s="140" t="s">
@@ -41442,14 +41422,14 @@
         <v>ann</v>
       </c>
       <c r="Q5" s="122" t="str">
-        <f t="shared" ref="Q5:Q68" si="5" xml:space="preserve"> _xlfn.CONCAT(N5, "(\d)")</f>
+        <f t="shared" ref="Q5:Q68" si="6" xml:space="preserve"> _xlfn.CONCAT(N5, "(\d)")</f>
         <v>ann(\d)</v>
       </c>
       <c r="R5" s="127" t="s">
         <v>1228</v>
       </c>
       <c r="S5" s="125">
-        <f t="shared" ref="S5:S68" si="6" xml:space="preserve"> IFERROR( IF(R5="", "", SEARCH(R5, $N5)), "")</f>
+        <f t="shared" ref="S5:S68" si="7" xml:space="preserve"> IFERROR( IF(R5="", "", SEARCH(R5, $N5)), "")</f>
         <v>1</v>
       </c>
       <c r="T5" s="122" t="str">
@@ -41458,90 +41438,90 @@
       </c>
       <c r="U5" s="56"/>
       <c r="V5" s="57" t="str">
-        <f t="shared" ref="V5:V68" si="7" xml:space="preserve"> IF(AND(O5&lt;&gt;"", N5&lt;&gt;""), "    - xform/》" &amp; Q5 &amp;  "/"  &amp; T5 &amp;  "/", "")</f>
+        <f t="shared" ref="V5:V68" si="8" xml:space="preserve"> IF(AND(O5&lt;&gt;"", N5&lt;&gt;""), "    - xform/》" &amp; Q5 &amp;  "/"  &amp; T5 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》ann(\d)/》a${1}nn/</v>
       </c>
       <c r="X5" s="130" t="s">
         <v>1229</v>
       </c>
       <c r="Y5" s="133" t="str">
-        <f t="shared" ref="Y5:AH10" si="8" xml:space="preserve"> _xlfn.CONCAT($X5, IF(Y$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(Y$3,4)))))</f>
+        <f t="shared" ref="Y5:AH10" si="9" xml:space="preserve"> _xlfn.CONCAT($X5, IF(Y$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(Y$3,4)))))</f>
         <v>i</v>
       </c>
       <c r="Z5" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>í</v>
       </c>
       <c r="AA5" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ì</v>
       </c>
       <c r="AB5" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>i</v>
       </c>
       <c r="AC5" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ǐ</v>
       </c>
       <c r="AD5" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>í</v>
       </c>
       <c r="AE5" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ī</v>
       </c>
       <c r="AF5" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>i̍</v>
       </c>
       <c r="AG5" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>i̋</v>
       </c>
       <c r="AH5" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>i̊</v>
       </c>
       <c r="AJ5" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X5, Y$1, "/", Y5, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i1/i/</v>
       </c>
       <c r="AK5" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X5, Z$1, "/", Z5, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i2/í/</v>
       </c>
       <c r="AL5" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X5, AA$1, "/", AA5, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i3/ì/</v>
       </c>
       <c r="AM5" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X5, AB$1, "/", AB5, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i4/i/</v>
       </c>
       <c r="AN5" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X5, AC$1, "/", AC5, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i5/ǐ/</v>
       </c>
       <c r="AO5" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X5, AD$1, "/", AD5, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i6/í/</v>
       </c>
       <c r="AP5" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X5, AE$1, "/", AE5, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i7/ī/</v>
       </c>
       <c r="AQ5" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X5, AF$1, "/", AF5, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i8/i̍/</v>
       </c>
       <c r="AR5" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X5, AG$1, "/", AG5, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i9/i̋/</v>
       </c>
       <c r="AS5" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X5, AH$1, "/", AH5, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》i9/i̊/</v>
       </c>
       <c r="AT5" s="133"/>
@@ -41549,8 +41529,8 @@
       <c r="AV5" s="130"/>
     </row>
     <row r="6" spans="1:48" ht="27.75" thickBot="1">
-      <c r="A6" s="185">
-        <f t="shared" si="4"/>
+      <c r="A6" s="183">
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="B6" s="140" t="s">
@@ -41595,106 +41575,106 @@
         <v>ah</v>
       </c>
       <c r="Q6" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ah(\d)</v>
       </c>
       <c r="R6" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S6" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T6" s="122" t="str">
-        <f t="shared" ref="T6:T69" si="9" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(N6,S6-1), "》", MID(N6,S6,1), "${1}", RIGHT(N6, LEN(N6)-S6)), "" )</f>
+        <f t="shared" ref="T6:T69" si="10" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(N6,S6-1), "》", MID(N6,S6,1), "${1}", RIGHT(N6, LEN(N6)-S6)), "" )</f>
         <v>》a${1}h</v>
       </c>
       <c r="U6" s="56"/>
       <c r="V6" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ah(\d)/》a${1}h/</v>
       </c>
       <c r="X6" s="130" t="s">
         <v>1227</v>
       </c>
       <c r="Y6" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>u</v>
       </c>
       <c r="Z6" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ú</v>
       </c>
       <c r="AA6" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ù</v>
       </c>
       <c r="AB6" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>u</v>
       </c>
       <c r="AC6" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ǔ</v>
       </c>
       <c r="AD6" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ú</v>
       </c>
       <c r="AE6" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ū</v>
       </c>
       <c r="AF6" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>u̍</v>
       </c>
       <c r="AG6" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ű</v>
       </c>
       <c r="AH6" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ů</v>
       </c>
       <c r="AJ6" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X6, Y$1, "/", Y6, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u1/u/</v>
       </c>
       <c r="AK6" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X6, Z$1, "/", Z6, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u2/ú/</v>
       </c>
       <c r="AL6" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X6, AA$1, "/", AA6, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u3/ù/</v>
       </c>
       <c r="AM6" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X6, AB$1, "/", AB6, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u4/u/</v>
       </c>
       <c r="AN6" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X6, AC$1, "/", AC6, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u5/ǔ/</v>
       </c>
       <c r="AO6" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X6, AD$1, "/", AD6, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u6/ú/</v>
       </c>
       <c r="AP6" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X6, AE$1, "/", AE6, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u7/ū/</v>
       </c>
       <c r="AQ6" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X6, AF$1, "/", AF6, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u8/u̍/</v>
       </c>
       <c r="AR6" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X6, AG$1, "/", AG6, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u9/ű/</v>
       </c>
       <c r="AS6" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X6, AH$1, "/", AH6, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》u9/ů/</v>
       </c>
       <c r="AT6" s="133"/>
@@ -41702,8 +41682,8 @@
       <c r="AV6" s="130"/>
     </row>
     <row r="7" spans="1:48" ht="27.75" thickBot="1">
-      <c r="A7" s="185">
-        <f t="shared" si="4"/>
+      <c r="A7" s="183">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="B7" s="140" t="s">
@@ -41750,106 +41730,106 @@
         <v>ahnn</v>
       </c>
       <c r="Q7" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>annh(\d)</v>
       </c>
       <c r="R7" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S7" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T7" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》a${1}nnh</v>
       </c>
       <c r="U7" s="56"/>
       <c r="V7" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》annh(\d)/》a${1}nnh/</v>
       </c>
       <c r="X7" s="130" t="s">
         <v>1181</v>
       </c>
       <c r="Y7" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>e</v>
       </c>
       <c r="Z7" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>é</v>
       </c>
       <c r="AA7" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>è</v>
       </c>
       <c r="AB7" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>e</v>
       </c>
       <c r="AC7" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ě</v>
       </c>
       <c r="AD7" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>é</v>
       </c>
       <c r="AE7" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ē</v>
       </c>
       <c r="AF7" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>e̍</v>
       </c>
       <c r="AG7" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>e̋</v>
       </c>
       <c r="AH7" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>e̊</v>
       </c>
       <c r="AJ7" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X7, Y$1, "/", Y7, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e1/e/</v>
       </c>
       <c r="AK7" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X7, Z$1, "/", Z7, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e2/é/</v>
       </c>
       <c r="AL7" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X7, AA$1, "/", AA7, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e3/è/</v>
       </c>
       <c r="AM7" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X7, AB$1, "/", AB7, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e4/e/</v>
       </c>
       <c r="AN7" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X7, AC$1, "/", AC7, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e5/ě/</v>
       </c>
       <c r="AO7" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X7, AD$1, "/", AD7, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e6/é/</v>
       </c>
       <c r="AP7" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X7, AE$1, "/", AE7, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e7/ē/</v>
       </c>
       <c r="AQ7" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X7, AF$1, "/", AF7, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e8/e̍/</v>
       </c>
       <c r="AR7" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X7, AG$1, "/", AG7, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e9/e̋/</v>
       </c>
       <c r="AS7" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X7, AH$1, "/", AH7, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》e9/e̊/</v>
       </c>
       <c r="AT7" s="133"/>
@@ -41857,8 +41837,8 @@
       <c r="AV7" s="130"/>
     </row>
     <row r="8" spans="1:48" ht="27.75" thickBot="1">
-      <c r="A8" s="185">
-        <f t="shared" si="4"/>
+      <c r="A8" s="183">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="B8" s="140" t="s">
@@ -41903,106 +41883,106 @@
         <v>am</v>
       </c>
       <c r="Q8" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>am(\d)</v>
       </c>
       <c r="R8" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S8" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T8" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》a${1}m</v>
       </c>
       <c r="U8" s="56"/>
       <c r="V8" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》am(\d)/》a${1}m/</v>
       </c>
       <c r="X8" s="130" t="s">
         <v>1216</v>
       </c>
       <c r="Y8" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>o</v>
       </c>
       <c r="Z8" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ó</v>
       </c>
       <c r="AA8" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ò</v>
       </c>
       <c r="AB8" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>o</v>
       </c>
       <c r="AC8" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ǒ</v>
       </c>
       <c r="AD8" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ó</v>
       </c>
       <c r="AE8" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ō</v>
       </c>
       <c r="AF8" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>o̍</v>
       </c>
       <c r="AG8" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ő</v>
       </c>
       <c r="AH8" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>o̊</v>
       </c>
       <c r="AJ8" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X8, Y$1, "/", Y8, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o1/o/</v>
       </c>
       <c r="AK8" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X8, Z$1, "/", Z8, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o2/ó/</v>
       </c>
       <c r="AL8" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X8, AA$1, "/", AA8, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o3/ò/</v>
       </c>
       <c r="AM8" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X8, AB$1, "/", AB8, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o4/o/</v>
       </c>
       <c r="AN8" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X8, AC$1, "/", AC8, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o5/ǒ/</v>
       </c>
       <c r="AO8" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X8, AD$1, "/", AD8, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o6/ó/</v>
       </c>
       <c r="AP8" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X8, AE$1, "/", AE8, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o7/ō/</v>
       </c>
       <c r="AQ8" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X8, AF$1, "/", AF8, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o8/o̍/</v>
       </c>
       <c r="AR8" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X8, AG$1, "/", AG8, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o9/ő/</v>
       </c>
       <c r="AS8" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X8, AH$1, "/", AH8, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》o9/o̊/</v>
       </c>
       <c r="AT8" s="133"/>
@@ -42010,8 +41990,8 @@
       <c r="AV8" s="130"/>
     </row>
     <row r="9" spans="1:48" ht="27.75" thickBot="1">
-      <c r="A9" s="185">
-        <f t="shared" si="4"/>
+      <c r="A9" s="183">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="B9" s="140" t="s">
@@ -42056,106 +42036,106 @@
         <v>an</v>
       </c>
       <c r="Q9" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>an(\d)</v>
       </c>
       <c r="R9" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S9" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T9" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》a${1}n</v>
       </c>
       <c r="U9" s="56"/>
       <c r="V9" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》an(\d)/》a${1}n/</v>
       </c>
       <c r="X9" s="130" t="s">
         <v>1306</v>
       </c>
       <c r="Y9" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>m</v>
       </c>
       <c r="Z9" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ḿ</v>
       </c>
       <c r="AA9" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>m̀</v>
       </c>
       <c r="AB9" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>m</v>
       </c>
       <c r="AC9" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>m̌</v>
       </c>
       <c r="AD9" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ḿ</v>
       </c>
       <c r="AE9" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>m̄</v>
       </c>
       <c r="AF9" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>m̍</v>
       </c>
       <c r="AG9" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>m̋</v>
       </c>
       <c r="AH9" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>m̊</v>
       </c>
       <c r="AJ9" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X9, Y$1, "/", Y9, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m1/m/</v>
       </c>
       <c r="AK9" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X9, Z$1, "/", Z9, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m2/ḿ/</v>
       </c>
       <c r="AL9" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X9, AA$1, "/", AA9, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m3/m̀/</v>
       </c>
       <c r="AM9" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X9, AB$1, "/", AB9, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m4/m/</v>
       </c>
       <c r="AN9" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X9, AC$1, "/", AC9, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m5/m̌/</v>
       </c>
       <c r="AO9" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X9, AD$1, "/", AD9, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m6/ḿ/</v>
       </c>
       <c r="AP9" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X9, AE$1, "/", AE9, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m7/m̄/</v>
       </c>
       <c r="AQ9" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X9, AF$1, "/", AF9, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m8/m̍/</v>
       </c>
       <c r="AR9" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X9, AG$1, "/", AG9, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m9/m̋/</v>
       </c>
       <c r="AS9" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X9, AH$1, "/", AH9, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》m9/m̊/</v>
       </c>
       <c r="AT9" s="133"/>
@@ -42163,8 +42143,8 @@
       <c r="AV9" s="130"/>
     </row>
     <row r="10" spans="1:48" ht="27.75" thickBot="1">
-      <c r="A10" s="185">
-        <f t="shared" si="4"/>
+      <c r="A10" s="183">
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="B10" s="140" t="s">
@@ -42209,106 +42189,106 @@
         <v>ang</v>
       </c>
       <c r="Q10" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ang(\d)</v>
       </c>
       <c r="R10" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S10" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T10" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》a${1}ng</v>
       </c>
       <c r="U10" s="56"/>
       <c r="V10" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ang(\d)/》a${1}ng/</v>
       </c>
       <c r="X10" s="130" t="s">
         <v>1305</v>
       </c>
       <c r="Y10" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>n</v>
       </c>
       <c r="Z10" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ń</v>
       </c>
       <c r="AA10" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ǹ</v>
       </c>
       <c r="AB10" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>n</v>
       </c>
       <c r="AC10" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ň</v>
       </c>
       <c r="AD10" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>ń</v>
       </c>
       <c r="AE10" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>n̄</v>
       </c>
       <c r="AF10" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>n̍</v>
       </c>
       <c r="AG10" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>n̋</v>
       </c>
       <c r="AH10" s="133" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>n̊</v>
       </c>
       <c r="AJ10" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X10, Y$1, "/", Y10, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n1/n/</v>
       </c>
       <c r="AK10" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X10, Z$1, "/", Z10, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n2/ń/</v>
       </c>
       <c r="AL10" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X10, AA$1, "/", AA10, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n3/ǹ/</v>
       </c>
       <c r="AM10" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X10, AB$1, "/", AB10, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n4/n/</v>
       </c>
       <c r="AN10" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X10, AC$1, "/", AC10, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n5/ň/</v>
       </c>
       <c r="AO10" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X10, AD$1, "/", AD10, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n6/ń/</v>
       </c>
       <c r="AP10" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X10, AE$1, "/", AE10, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n7/n̄/</v>
       </c>
       <c r="AQ10" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X10, AF$1, "/", AF10, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n8/n̍/</v>
       </c>
       <c r="AR10" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X10, AG$1, "/", AG10, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n9/n̋/</v>
       </c>
       <c r="AS10" s="135" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X10, AH$1, "/", AH10, "/")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    - xform/》n9/n̊/</v>
       </c>
       <c r="AT10" s="133"/>
@@ -42316,8 +42296,8 @@
       <c r="AV10" s="130"/>
     </row>
     <row r="11" spans="1:48" ht="27.75" thickBot="1">
-      <c r="A11" s="185">
-        <f t="shared" si="4"/>
+      <c r="A11" s="183">
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="B11" s="140" t="str">
@@ -42363,29 +42343,29 @@
         <v>ap</v>
       </c>
       <c r="Q11" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ap(\d)</v>
       </c>
       <c r="R11" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S11" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T11" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》a${1}p</v>
       </c>
       <c r="U11" s="56"/>
       <c r="V11" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ap(\d)/》a${1}p/</v>
       </c>
     </row>
     <row r="12" spans="1:48" ht="27.75" thickBot="1">
-      <c r="A12" s="185">
-        <f t="shared" si="4"/>
+      <c r="A12" s="183">
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="B12" s="140" t="str">
@@ -42431,29 +42411,29 @@
         <v>at</v>
       </c>
       <c r="Q12" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>at(\d)</v>
       </c>
       <c r="R12" s="125" t="s">
         <v>1216</v>
       </c>
       <c r="S12" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T12" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U12" s="56"/>
       <c r="V12" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》at(\d)//</v>
       </c>
     </row>
     <row r="13" spans="1:48" ht="30.75" thickBot="1">
-      <c r="A13" s="185">
-        <f t="shared" si="4"/>
+      <c r="A13" s="183">
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="B13" s="140" t="str">
@@ -42475,10 +42455,10 @@
       <c r="G13" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="H13" s="188" t="s">
+      <c r="H13" s="186" t="s">
         <v>2480</v>
       </c>
-      <c r="I13" s="188" t="s">
+      <c r="I13" s="186" t="s">
         <v>2258</v>
       </c>
       <c r="J13" s="55" t="s">
@@ -42499,29 +42479,29 @@
         <v>ak</v>
       </c>
       <c r="Q13" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ak(\d)</v>
       </c>
       <c r="R13" s="125" t="s">
         <v>1181</v>
       </c>
       <c r="S13" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T13" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U13" s="56"/>
       <c r="V13" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ak(\d)//</v>
       </c>
     </row>
     <row r="14" spans="1:48" ht="27.75" thickBot="1">
-      <c r="A14" s="185">
-        <f t="shared" si="4"/>
+      <c r="A14" s="183">
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="B14" s="140" t="s">
@@ -42566,29 +42546,29 @@
         <v>ai</v>
       </c>
       <c r="Q14" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ai(\d)</v>
       </c>
       <c r="R14" s="125" t="s">
         <v>1216</v>
       </c>
       <c r="S14" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T14" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U14" s="56"/>
       <c r="V14" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ai(\d)//</v>
       </c>
     </row>
     <row r="15" spans="1:48" ht="27.75" thickBot="1">
-      <c r="A15" s="185">
-        <f t="shared" si="4"/>
+      <c r="A15" s="183">
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="B15" s="140" t="s">
@@ -42635,29 +42615,29 @@
         <v>ainn</v>
       </c>
       <c r="Q15" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ainn(\d)</v>
       </c>
       <c r="R15" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S15" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T15" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》a${1}inn</v>
       </c>
       <c r="U15" s="56"/>
       <c r="V15" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ainn(\d)/》a${1}inn/</v>
       </c>
     </row>
     <row r="16" spans="1:48" ht="30.75" thickBot="1">
-      <c r="A16" s="185">
-        <f t="shared" si="4"/>
+      <c r="A16" s="183">
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="B16" s="140" t="s">
@@ -42702,29 +42682,29 @@
         <v>aih</v>
       </c>
       <c r="Q16" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>aih(\d)</v>
       </c>
       <c r="R16" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S16" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T16" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》a${1}ih</v>
       </c>
       <c r="U16" s="56"/>
       <c r="V16" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》aih(\d)/》a${1}ih/</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A17" s="185">
-        <f t="shared" si="4"/>
+      <c r="A17" s="183">
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="B17" s="140" t="s">
@@ -42769,29 +42749,29 @@
         <v>au</v>
       </c>
       <c r="Q17" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>au(\d)</v>
       </c>
       <c r="R17" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S17" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T17" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》a${1}u</v>
       </c>
       <c r="U17" s="56"/>
       <c r="V17" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》au(\d)/》a${1}u/</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="30.75" thickBot="1">
-      <c r="A18" s="185">
-        <f t="shared" si="4"/>
+      <c r="A18" s="183">
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="B18" s="140" t="s">
@@ -42812,10 +42792,10 @@
       <c r="G18" s="61" t="s">
         <v>267</v>
       </c>
-      <c r="H18" s="188" t="s">
+      <c r="H18" s="186" t="s">
         <v>2477</v>
       </c>
-      <c r="I18" s="188" t="s">
+      <c r="I18" s="186" t="s">
         <v>2261</v>
       </c>
       <c r="J18" s="55" t="s">
@@ -42836,29 +42816,29 @@
         <v>auh</v>
       </c>
       <c r="Q18" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>auh(\d)</v>
       </c>
       <c r="R18" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S18" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T18" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》a${1}uh</v>
       </c>
       <c r="U18" s="56"/>
       <c r="V18" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》auh(\d)/》a${1}uh/</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A19" s="185">
-        <f t="shared" ref="A19:A20" si="10" xml:space="preserve"> ROW() - 3</f>
+      <c r="A19" s="183">
+        <f t="shared" ref="A19:A20" si="11" xml:space="preserve"> ROW() - 3</f>
         <v>16</v>
       </c>
       <c r="B19" s="140" t="s">
@@ -42870,13 +42850,13 @@
       <c r="D19" s="75" t="s">
         <v>2468</v>
       </c>
-      <c r="E19" s="189"/>
-      <c r="F19" s="189"/>
-      <c r="G19" s="189"/>
-      <c r="H19" s="186" t="s">
+      <c r="E19" s="187"/>
+      <c r="F19" s="187"/>
+      <c r="G19" s="187"/>
+      <c r="H19" s="184" t="s">
         <v>2476</v>
       </c>
-      <c r="I19" s="186" t="s">
+      <c r="I19" s="184" t="s">
         <v>58</v>
       </c>
       <c r="J19" s="146" t="s">
@@ -42884,42 +42864,42 @@
       </c>
       <c r="K19" s="58"/>
       <c r="L19" s="55">
-        <f t="shared" ref="L19:L20" si="11" xml:space="preserve"> LEN(D19)</f>
+        <f t="shared" ref="L19:L20" si="12" xml:space="preserve"> LEN(D19)</f>
         <v>2</v>
       </c>
       <c r="M19" s="74"/>
       <c r="N19" s="58" t="str">
-        <f>C23</f>
+        <f t="shared" ref="N19:N50" si="13">C23</f>
         <v>e</v>
       </c>
       <c r="O19" s="58" t="str">
-        <f>D23</f>
+        <f t="shared" ref="O19:O50" si="14">D23</f>
         <v>ei</v>
       </c>
       <c r="Q19" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>e(\d)</v>
       </c>
       <c r="R19" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S19" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T19" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U19" s="56"/>
       <c r="V19" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》e(\d)//</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A20" s="185">
-        <f t="shared" si="10"/>
+      <c r="A20" s="183">
+        <f t="shared" si="11"/>
         <v>17</v>
       </c>
       <c r="B20" s="140" t="str">
@@ -42932,13 +42912,13 @@
       <c r="D20" s="75" t="s">
         <v>2469</v>
       </c>
-      <c r="E20" s="189"/>
-      <c r="F20" s="189"/>
-      <c r="G20" s="189"/>
-      <c r="H20" s="186" t="s">
+      <c r="E20" s="187"/>
+      <c r="F20" s="187"/>
+      <c r="G20" s="187"/>
+      <c r="H20" s="184" t="s">
         <v>2478</v>
       </c>
-      <c r="I20" s="186" t="s">
+      <c r="I20" s="184" t="s">
         <v>2241</v>
       </c>
       <c r="J20" s="146" t="s">
@@ -42946,42 +42926,42 @@
       </c>
       <c r="K20" s="58"/>
       <c r="L20" s="55">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="M20" s="74"/>
       <c r="N20" s="58" t="str">
-        <f>C24</f>
+        <f t="shared" si="13"/>
         <v>enn</v>
       </c>
       <c r="O20" s="58" t="str">
-        <f>D24</f>
+        <f t="shared" si="14"/>
         <v>enn</v>
       </c>
       <c r="Q20" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>enn(\d)</v>
       </c>
       <c r="R20" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S20" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T20" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U20" s="56"/>
       <c r="V20" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》enn(\d)//</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A21" s="185">
-        <f t="shared" ref="A21:A22" si="12" xml:space="preserve"> ROW() - 3</f>
+      <c r="A21" s="183">
+        <f t="shared" ref="A21:A22" si="15" xml:space="preserve"> ROW() - 3</f>
         <v>18</v>
       </c>
       <c r="B21" s="140" t="str">
@@ -42994,13 +42974,13 @@
       <c r="D21" s="75" t="s">
         <v>2470</v>
       </c>
-      <c r="E21" s="189"/>
-      <c r="F21" s="189"/>
-      <c r="G21" s="189"/>
-      <c r="H21" s="187" t="s">
+      <c r="E21" s="187"/>
+      <c r="F21" s="187"/>
+      <c r="G21" s="187"/>
+      <c r="H21" s="185" t="s">
         <v>2479</v>
       </c>
-      <c r="I21" s="187" t="s">
+      <c r="I21" s="185" t="s">
         <v>2484</v>
       </c>
       <c r="J21" s="146" t="s">
@@ -43008,42 +42988,42 @@
       </c>
       <c r="K21" s="58"/>
       <c r="L21" s="55">
-        <f t="shared" ref="L21:L22" si="13" xml:space="preserve"> LEN(D21)</f>
+        <f t="shared" ref="L21:L22" si="16" xml:space="preserve"> LEN(D21)</f>
         <v>3</v>
       </c>
       <c r="M21" s="74"/>
       <c r="N21" s="58" t="str">
-        <f>C25</f>
+        <f t="shared" si="13"/>
         <v>eh</v>
       </c>
       <c r="O21" s="58" t="str">
-        <f>D25</f>
+        <f t="shared" si="14"/>
         <v>eh</v>
       </c>
       <c r="Q21" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>eh(\d)</v>
       </c>
       <c r="R21" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S21" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T21" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U21" s="56"/>
       <c r="V21" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》eh(\d)//</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A22" s="185">
-        <f t="shared" si="12"/>
+      <c r="A22" s="183">
+        <f t="shared" si="15"/>
         <v>19</v>
       </c>
       <c r="B22" s="140" t="str">
@@ -43056,13 +43036,13 @@
       <c r="D22" s="75" t="s">
         <v>2471</v>
       </c>
-      <c r="E22" s="189"/>
-      <c r="F22" s="189"/>
-      <c r="G22" s="189"/>
-      <c r="H22" s="187" t="s">
+      <c r="E22" s="187"/>
+      <c r="F22" s="187"/>
+      <c r="G22" s="187"/>
+      <c r="H22" s="185" t="s">
         <v>2481</v>
       </c>
-      <c r="I22" s="187" t="s">
+      <c r="I22" s="185" t="s">
         <v>2485</v>
       </c>
       <c r="J22" s="146" t="s">
@@ -43070,42 +43050,42 @@
       </c>
       <c r="K22" s="58"/>
       <c r="L22" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="M22" s="74"/>
       <c r="N22" s="58" t="str">
-        <f>C26</f>
+        <f t="shared" si="13"/>
         <v>ennh</v>
       </c>
       <c r="O22" s="58" t="str">
-        <f>D26</f>
+        <f t="shared" si="14"/>
         <v>ennh</v>
       </c>
       <c r="Q22" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ennh(\d)</v>
       </c>
       <c r="R22" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S22" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T22" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U22" s="56"/>
       <c r="V22" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ennh(\d)//</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A23" s="185">
-        <f t="shared" si="4"/>
+      <c r="A23" s="183">
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="B23" s="140" t="s">
@@ -43142,37 +43122,37 @@
       </c>
       <c r="M23" s="74"/>
       <c r="N23" s="58" t="str">
-        <f>C27</f>
+        <f t="shared" si="13"/>
         <v>i</v>
       </c>
       <c r="O23" s="58" t="str">
-        <f>D27</f>
+        <f t="shared" si="14"/>
         <v>i</v>
       </c>
       <c r="Q23" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>i(\d)</v>
       </c>
       <c r="R23" s="125" t="s">
         <v>1216</v>
       </c>
       <c r="S23" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T23" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U23" s="56"/>
       <c r="V23" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》i(\d)//</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A24" s="185">
-        <f t="shared" si="4"/>
+      <c r="A24" s="183">
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="B24" s="140" t="s">
@@ -43211,37 +43191,37 @@
       </c>
       <c r="M24" s="74"/>
       <c r="N24" s="58" t="str">
-        <f>C28</f>
+        <f t="shared" si="13"/>
         <v>inn</v>
       </c>
       <c r="O24" s="58" t="str">
-        <f>D28</f>
+        <f t="shared" si="14"/>
         <v>inn</v>
       </c>
       <c r="Q24" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>inn(\d)</v>
       </c>
       <c r="R24" s="125" t="s">
         <v>1216</v>
       </c>
       <c r="S24" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T24" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U24" s="56"/>
       <c r="V24" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》inn(\d)//</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A25" s="185">
-        <f t="shared" si="4"/>
+      <c r="A25" s="183">
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="B25" s="140" t="s">
@@ -43278,37 +43258,37 @@
       </c>
       <c r="M25" s="74"/>
       <c r="N25" s="58" t="str">
-        <f>C29</f>
+        <f t="shared" si="13"/>
         <v>ih</v>
       </c>
       <c r="O25" s="58" t="str">
-        <f>D29</f>
+        <f t="shared" si="14"/>
         <v>ih</v>
       </c>
       <c r="Q25" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ih(\d)</v>
       </c>
       <c r="R25" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S25" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T25" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U25" s="56"/>
       <c r="V25" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ih(\d)//</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="30.75" thickBot="1">
-      <c r="A26" s="185">
-        <f t="shared" si="4"/>
+      <c r="A26" s="183">
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="B26" s="140" t="s">
@@ -43332,7 +43312,7 @@
       <c r="H26" s="145" t="s">
         <v>927</v>
       </c>
-      <c r="I26" s="190" t="s">
+      <c r="I26" s="188" t="s">
         <v>2271</v>
       </c>
       <c r="J26" s="147" t="s">
@@ -43347,37 +43327,37 @@
       </c>
       <c r="M26" s="74"/>
       <c r="N26" s="58" t="str">
-        <f>C30</f>
+        <f t="shared" si="13"/>
         <v>im</v>
       </c>
       <c r="O26" s="58" t="str">
-        <f>D30</f>
+        <f t="shared" si="14"/>
         <v>im</v>
       </c>
       <c r="Q26" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>im(\d)</v>
       </c>
       <c r="R26" s="125" t="s">
         <v>1181</v>
       </c>
       <c r="S26" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T26" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U26" s="56"/>
       <c r="V26" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》im(\d)//</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A27" s="185">
-        <f t="shared" si="4"/>
+      <c r="A27" s="183">
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
       <c r="B27" s="140" t="s">
@@ -43414,37 +43394,37 @@
       </c>
       <c r="M27" s="74"/>
       <c r="N27" s="58" t="str">
-        <f>C31</f>
+        <f t="shared" si="13"/>
         <v>in</v>
       </c>
       <c r="O27" s="58" t="str">
-        <f>D31</f>
+        <f t="shared" si="14"/>
         <v>in</v>
       </c>
       <c r="Q27" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>in(\d)</v>
       </c>
       <c r="R27" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S27" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T27" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U27" s="56"/>
       <c r="V27" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》in(\d)//</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A28" s="185">
-        <f t="shared" si="4"/>
+      <c r="A28" s="183">
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="B28" s="140" t="s">
@@ -43483,37 +43463,37 @@
       </c>
       <c r="M28" s="74"/>
       <c r="N28" s="58" t="str">
-        <f>C32</f>
+        <f t="shared" si="13"/>
         <v>ing</v>
       </c>
       <c r="O28" s="58" t="str">
-        <f>D32</f>
+        <f t="shared" si="14"/>
         <v>ing</v>
       </c>
       <c r="Q28" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ing(\d)</v>
       </c>
       <c r="R28" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S28" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T28" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U28" s="56"/>
       <c r="V28" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ing(\d)//</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A29" s="185">
-        <f t="shared" si="4"/>
+      <c r="A29" s="183">
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="B29" s="140" t="s">
@@ -43550,37 +43530,37 @@
       </c>
       <c r="M29" s="74"/>
       <c r="N29" s="58" t="str">
-        <f>C33</f>
+        <f t="shared" si="13"/>
         <v>ip</v>
       </c>
       <c r="O29" s="58" t="str">
-        <f>D33</f>
+        <f t="shared" si="14"/>
         <v>ip</v>
       </c>
       <c r="Q29" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ip(\d)</v>
       </c>
       <c r="R29" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S29" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T29" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U29" s="56"/>
       <c r="V29" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ip(\d)//</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A30" s="185">
-        <f t="shared" si="4"/>
+      <c r="A30" s="183">
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="B30" s="140" t="s">
@@ -43617,37 +43597,37 @@
       </c>
       <c r="M30" s="74"/>
       <c r="N30" s="58" t="str">
-        <f>C34</f>
+        <f t="shared" si="13"/>
         <v>it</v>
       </c>
       <c r="O30" s="58" t="str">
-        <f>D34</f>
+        <f t="shared" si="14"/>
         <v>it</v>
       </c>
       <c r="Q30" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>it(\d)</v>
       </c>
       <c r="R30" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S30" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T30" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U30" s="56"/>
       <c r="V30" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》it(\d)//</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A31" s="185">
-        <f t="shared" si="4"/>
+      <c r="A31" s="183">
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="B31" s="140" t="s">
@@ -43684,37 +43664,37 @@
       </c>
       <c r="M31" s="74"/>
       <c r="N31" s="58" t="str">
-        <f>C35</f>
+        <f t="shared" si="13"/>
         <v>ik</v>
       </c>
       <c r="O31" s="58" t="str">
-        <f>D35</f>
+        <f t="shared" si="14"/>
         <v>ik</v>
       </c>
       <c r="Q31" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ik(\d)</v>
       </c>
       <c r="R31" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S31" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T31" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U31" s="56"/>
       <c r="V31" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ik(\d)//</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A32" s="185">
-        <f t="shared" si="4"/>
+      <c r="A32" s="183">
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="B32" s="140" t="s">
@@ -43751,37 +43731,37 @@
       </c>
       <c r="M32" s="74"/>
       <c r="N32" s="58" t="str">
-        <f>C36</f>
+        <f t="shared" si="13"/>
         <v>ia</v>
       </c>
       <c r="O32" s="58" t="str">
-        <f>D36</f>
+        <f t="shared" si="14"/>
         <v>ia</v>
       </c>
       <c r="Q32" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ia(\d)</v>
       </c>
       <c r="R32" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S32" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T32" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>i》a${1}</v>
       </c>
       <c r="U32" s="56"/>
       <c r="V32" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ia(\d)/i》a${1}/</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A33" s="185">
-        <f t="shared" si="4"/>
+      <c r="A33" s="183">
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="B33" s="140" t="s">
@@ -43818,37 +43798,37 @@
       </c>
       <c r="M33" s="74"/>
       <c r="N33" s="58" t="str">
-        <f>C37</f>
+        <f t="shared" si="13"/>
         <v>iann</v>
       </c>
       <c r="O33" s="58" t="str">
-        <f>D37</f>
+        <f t="shared" si="14"/>
         <v>iann</v>
       </c>
       <c r="Q33" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iann(\d)</v>
       </c>
       <c r="R33" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S33" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T33" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>i》a${1}nn</v>
       </c>
       <c r="U33" s="56"/>
       <c r="V33" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iann(\d)/i》a${1}nn/</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A34" s="185">
-        <f t="shared" si="4"/>
+      <c r="A34" s="183">
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
       <c r="B34" s="140" t="s">
@@ -43885,37 +43865,37 @@
       </c>
       <c r="M34" s="74"/>
       <c r="N34" s="58" t="str">
-        <f>C38</f>
+        <f t="shared" si="13"/>
         <v>iah</v>
       </c>
       <c r="O34" s="58" t="str">
-        <f>D38</f>
+        <f t="shared" si="14"/>
         <v>iah</v>
       </c>
       <c r="Q34" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iah(\d)</v>
       </c>
       <c r="R34" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S34" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T34" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>i》a${1}h</v>
       </c>
       <c r="U34" s="56"/>
       <c r="V34" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iah(\d)/i》a${1}h/</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A35" s="185">
-        <f t="shared" si="4"/>
+      <c r="A35" s="183">
+        <f t="shared" si="5"/>
         <v>32</v>
       </c>
       <c r="B35" s="140" t="s">
@@ -43952,37 +43932,37 @@
       </c>
       <c r="M35" s="74"/>
       <c r="N35" s="58" t="str">
-        <f>C39</f>
+        <f t="shared" si="13"/>
         <v>iannh</v>
       </c>
       <c r="O35" s="58" t="str">
-        <f>D39</f>
+        <f t="shared" si="14"/>
         <v>iannh</v>
       </c>
       <c r="Q35" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iannh(\d)</v>
       </c>
       <c r="R35" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S35" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T35" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>i》a${1}nnh</v>
       </c>
       <c r="U35" s="56"/>
       <c r="V35" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iannh(\d)/i》a${1}nnh/</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A36" s="185">
-        <f t="shared" si="4"/>
+      <c r="A36" s="183">
+        <f t="shared" si="5"/>
         <v>33</v>
       </c>
       <c r="B36" s="140" t="s">
@@ -44019,37 +43999,37 @@
       </c>
       <c r="M36" s="74"/>
       <c r="N36" s="58" t="str">
-        <f>C40</f>
+        <f t="shared" si="13"/>
         <v>iam</v>
       </c>
       <c r="O36" s="58" t="str">
-        <f>D40</f>
+        <f t="shared" si="14"/>
         <v>iam</v>
       </c>
       <c r="Q36" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iam(\d)</v>
       </c>
       <c r="R36" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S36" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T36" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》i${1}am</v>
       </c>
       <c r="U36" s="56"/>
       <c r="V36" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iam(\d)/》i${1}am/</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A37" s="185">
-        <f t="shared" si="4"/>
+      <c r="A37" s="183">
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="B37" s="140" t="str">
@@ -44089,37 +44069,37 @@
       </c>
       <c r="M37" s="74"/>
       <c r="N37" s="58" t="str">
-        <f>C41</f>
+        <f t="shared" si="13"/>
         <v>ian</v>
       </c>
       <c r="O37" s="58" t="str">
-        <f>D41</f>
+        <f t="shared" si="14"/>
         <v>ian</v>
       </c>
       <c r="Q37" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ian(\d)</v>
       </c>
       <c r="R37" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S37" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T37" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》i${1}an</v>
       </c>
       <c r="U37" s="56"/>
       <c r="V37" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ian(\d)/》i${1}an/</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A38" s="185">
-        <f t="shared" si="4"/>
+      <c r="A38" s="183">
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="B38" s="140" t="str">
@@ -44157,37 +44137,37 @@
       </c>
       <c r="M38" s="74"/>
       <c r="N38" s="58" t="str">
-        <f>C42</f>
+        <f t="shared" si="13"/>
         <v>iang</v>
       </c>
       <c r="O38" s="58" t="str">
-        <f>D42</f>
+        <f t="shared" si="14"/>
         <v>iang</v>
       </c>
       <c r="Q38" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iang(\d)</v>
       </c>
       <c r="R38" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S38" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T38" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》i${1}ang</v>
       </c>
       <c r="U38" s="56"/>
       <c r="V38" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iang(\d)/》i${1}ang/</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="30.75" thickBot="1">
-      <c r="A39" s="185">
-        <f t="shared" si="4"/>
+      <c r="A39" s="183">
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
       <c r="B39" s="140" t="str">
@@ -44227,37 +44207,37 @@
       </c>
       <c r="M39" s="74"/>
       <c r="N39" s="58" t="str">
-        <f>C43</f>
+        <f t="shared" si="13"/>
         <v>iap</v>
       </c>
       <c r="O39" s="58" t="str">
-        <f>D43</f>
+        <f t="shared" si="14"/>
         <v>iap</v>
       </c>
       <c r="Q39" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iap(\d)</v>
       </c>
       <c r="R39" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S39" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T39" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》i${1}ap</v>
       </c>
       <c r="U39" s="56"/>
       <c r="V39" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iap(\d)/》i${1}ap/</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A40" s="185">
-        <f t="shared" si="4"/>
+      <c r="A40" s="183">
+        <f t="shared" si="5"/>
         <v>37</v>
       </c>
       <c r="B40" s="140" t="s">
@@ -44289,42 +44269,42 @@
       </c>
       <c r="K40" s="58"/>
       <c r="L40" s="55">
-        <f t="shared" ref="L40:L71" si="14" xml:space="preserve"> LEN(D40)</f>
+        <f t="shared" ref="L40:L71" si="17" xml:space="preserve"> LEN(D40)</f>
         <v>3</v>
       </c>
       <c r="M40" s="74"/>
       <c r="N40" s="58" t="str">
-        <f>C44</f>
+        <f t="shared" si="13"/>
         <v>iat</v>
       </c>
       <c r="O40" s="58" t="str">
-        <f>D44</f>
+        <f t="shared" si="14"/>
         <v>iat</v>
       </c>
       <c r="Q40" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iat(\d)</v>
       </c>
       <c r="R40" s="125" t="s">
         <v>1181</v>
       </c>
       <c r="S40" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T40" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U40" s="56"/>
       <c r="V40" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iat(\d)//</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A41" s="185">
-        <f t="shared" si="4"/>
+      <c r="A41" s="183">
+        <f t="shared" si="5"/>
         <v>38</v>
       </c>
       <c r="B41" s="140" t="s">
@@ -44356,42 +44336,42 @@
       </c>
       <c r="K41" s="58"/>
       <c r="L41" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M41" s="74"/>
       <c r="N41" s="58" t="str">
-        <f>C45</f>
+        <f t="shared" si="13"/>
         <v>iak</v>
       </c>
       <c r="O41" s="58" t="str">
-        <f>D45</f>
+        <f t="shared" si="14"/>
         <v>iak</v>
       </c>
       <c r="Q41" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iak(\d)</v>
       </c>
       <c r="R41" s="125" t="s">
         <v>1305</v>
       </c>
       <c r="S41" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T41" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U41" s="56"/>
       <c r="V41" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iak(\d)//</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A42" s="185">
-        <f t="shared" si="4"/>
+      <c r="A42" s="183">
+        <f t="shared" si="5"/>
         <v>39</v>
       </c>
       <c r="B42" s="140" t="s">
@@ -44423,42 +44403,42 @@
       </c>
       <c r="K42" s="58"/>
       <c r="L42" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="M42" s="74"/>
       <c r="N42" s="58" t="str">
-        <f>C46</f>
+        <f t="shared" si="13"/>
         <v>iau</v>
       </c>
       <c r="O42" s="58" t="str">
-        <f>D46</f>
+        <f t="shared" si="14"/>
         <v>iau</v>
       </c>
       <c r="Q42" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iau(\d)</v>
       </c>
       <c r="R42" s="125" t="s">
         <v>1216</v>
       </c>
       <c r="S42" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T42" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U42" s="56"/>
       <c r="V42" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iau(\d)//</v>
       </c>
     </row>
     <row r="43" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A43" s="185">
-        <f t="shared" si="4"/>
+      <c r="A43" s="183">
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="B43" s="140" t="s">
@@ -44490,42 +44470,42 @@
       </c>
       <c r="K43" s="58"/>
       <c r="L43" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M43" s="74"/>
       <c r="N43" s="58" t="str">
-        <f>C47</f>
+        <f t="shared" si="13"/>
         <v>iaunn</v>
       </c>
       <c r="O43" s="58" t="str">
-        <f>D47</f>
+        <f t="shared" si="14"/>
         <v>iaunn</v>
       </c>
       <c r="Q43" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iaunn(\d)</v>
       </c>
       <c r="R43" s="125" t="s">
         <v>1216</v>
       </c>
       <c r="S43" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T43" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U43" s="56"/>
       <c r="V43" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iaunn(\d)//</v>
       </c>
     </row>
     <row r="44" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A44" s="185">
-        <f t="shared" si="4"/>
+      <c r="A44" s="183">
+        <f t="shared" si="5"/>
         <v>41</v>
       </c>
       <c r="B44" s="140" t="s">
@@ -44557,42 +44537,42 @@
       </c>
       <c r="K44" s="58"/>
       <c r="L44" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M44" s="74"/>
       <c r="N44" s="58" t="str">
-        <f>C48</f>
+        <f t="shared" si="13"/>
         <v>iauh</v>
       </c>
       <c r="O44" s="58" t="str">
-        <f>D48</f>
+        <f t="shared" si="14"/>
         <v>iauh</v>
       </c>
       <c r="Q44" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iauh(\d)</v>
       </c>
       <c r="R44" s="125" t="s">
         <v>1216</v>
       </c>
       <c r="S44" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T44" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U44" s="56"/>
       <c r="V44" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iauh(\d)//</v>
       </c>
     </row>
     <row r="45" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A45" s="185">
-        <f t="shared" si="4"/>
+      <c r="A45" s="183">
+        <f t="shared" si="5"/>
         <v>42</v>
       </c>
       <c r="B45" s="140" t="s">
@@ -44624,42 +44604,42 @@
       </c>
       <c r="K45" s="58"/>
       <c r="L45" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M45" s="74"/>
       <c r="N45" s="58" t="str">
-        <f>C49</f>
+        <f t="shared" si="13"/>
         <v>io</v>
       </c>
       <c r="O45" s="58" t="str">
-        <f>D49</f>
+        <f t="shared" si="14"/>
         <v>io</v>
       </c>
       <c r="Q45" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>io(\d)</v>
       </c>
       <c r="R45" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S45" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T45" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U45" s="56"/>
       <c r="V45" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》io(\d)//</v>
       </c>
     </row>
     <row r="46" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A46" s="185">
-        <f t="shared" si="4"/>
+      <c r="A46" s="183">
+        <f t="shared" si="5"/>
         <v>43</v>
       </c>
       <c r="B46" s="140" t="s">
@@ -44691,42 +44671,42 @@
       </c>
       <c r="K46" s="58"/>
       <c r="L46" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M46" s="74"/>
       <c r="N46" s="58" t="str">
-        <f>C50</f>
+        <f t="shared" si="13"/>
         <v>ionn</v>
       </c>
       <c r="O46" s="58" t="str">
-        <f>D50</f>
+        <f t="shared" si="14"/>
         <v>ionn</v>
       </c>
       <c r="Q46" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ionn(\d)</v>
       </c>
       <c r="R46" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S46" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T46" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U46" s="56"/>
       <c r="V46" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ionn(\d)//</v>
       </c>
     </row>
     <row r="47" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A47" s="185">
-        <f t="shared" si="4"/>
+      <c r="A47" s="183">
+        <f t="shared" si="5"/>
         <v>44</v>
       </c>
       <c r="B47" s="140" t="str">
@@ -44761,42 +44741,42 @@
         <v>1312</v>
       </c>
       <c r="L47" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>5</v>
       </c>
       <c r="M47" s="74"/>
       <c r="N47" s="58" t="str">
-        <f>C51</f>
+        <f t="shared" si="13"/>
         <v>ioh</v>
       </c>
       <c r="O47" s="58" t="str">
-        <f>D51</f>
+        <f t="shared" si="14"/>
         <v>ioh</v>
       </c>
       <c r="Q47" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ioh(\d)</v>
       </c>
       <c r="R47" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S47" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T47" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U47" s="56"/>
       <c r="V47" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ioh(\d)//</v>
       </c>
     </row>
     <row r="48" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A48" s="185">
-        <f t="shared" si="4"/>
+      <c r="A48" s="183">
+        <f t="shared" si="5"/>
         <v>45</v>
       </c>
       <c r="B48" s="140" t="str">
@@ -44829,42 +44809,42 @@
       </c>
       <c r="K48" s="58"/>
       <c r="L48" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="M48" s="74"/>
       <c r="N48" s="58" t="str">
-        <f>C52</f>
+        <f t="shared" si="13"/>
         <v>iong</v>
       </c>
       <c r="O48" s="58" t="str">
-        <f>D52</f>
+        <f t="shared" si="14"/>
         <v>iong</v>
       </c>
       <c r="Q48" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iong(\d)</v>
       </c>
       <c r="R48" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S48" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T48" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U48" s="56"/>
       <c r="V48" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iong(\d)//</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A49" s="185">
-        <f t="shared" si="4"/>
+      <c r="A49" s="183">
+        <f t="shared" si="5"/>
         <v>46</v>
       </c>
       <c r="B49" s="140" t="s">
@@ -44896,42 +44876,42 @@
       </c>
       <c r="K49" s="58"/>
       <c r="L49" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M49" s="74"/>
       <c r="N49" s="58" t="str">
-        <f>C53</f>
+        <f t="shared" si="13"/>
         <v>iok</v>
       </c>
       <c r="O49" s="58" t="str">
-        <f>D53</f>
+        <f t="shared" si="14"/>
         <v>iok</v>
       </c>
       <c r="Q49" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iok(\d)</v>
       </c>
       <c r="R49" s="125" t="s">
         <v>1181</v>
       </c>
       <c r="S49" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T49" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U49" s="56"/>
       <c r="V49" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iok(\d)//</v>
       </c>
     </row>
     <row r="50" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A50" s="185">
-        <f t="shared" si="4"/>
+      <c r="A50" s="183">
+        <f t="shared" si="5"/>
         <v>47</v>
       </c>
       <c r="B50" s="140" t="s">
@@ -44965,42 +44945,42 @@
         <v>1312</v>
       </c>
       <c r="L50" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="M50" s="74"/>
       <c r="N50" s="58" t="str">
-        <f>C54</f>
+        <f t="shared" si="13"/>
         <v>iu</v>
       </c>
       <c r="O50" s="58" t="str">
-        <f>D54</f>
+        <f t="shared" si="14"/>
         <v>iu</v>
       </c>
       <c r="Q50" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iu(\d)</v>
       </c>
       <c r="R50" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S50" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T50" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U50" s="56"/>
       <c r="V50" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iu(\d)//</v>
       </c>
     </row>
     <row r="51" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A51" s="185">
-        <f t="shared" si="4"/>
+      <c r="A51" s="183">
+        <f t="shared" si="5"/>
         <v>48</v>
       </c>
       <c r="B51" s="140" t="s">
@@ -45032,42 +45012,42 @@
       </c>
       <c r="K51" s="58"/>
       <c r="L51" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M51" s="74"/>
       <c r="N51" s="58" t="str">
-        <f>C55</f>
+        <f t="shared" ref="N51:N82" si="18">C55</f>
         <v>iunn</v>
       </c>
       <c r="O51" s="58" t="str">
-        <f>D55</f>
+        <f t="shared" ref="O51:O82" si="19">D55</f>
         <v>iunn</v>
       </c>
       <c r="Q51" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iunn(\d)</v>
       </c>
       <c r="R51" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S51" s="125">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T51" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>》i${1}unn</v>
       </c>
       <c r="U51" s="56"/>
       <c r="V51" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iunn(\d)/》i${1}unn/</v>
       </c>
     </row>
     <row r="52" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A52" s="185">
-        <f t="shared" si="4"/>
+      <c r="A52" s="183">
+        <f t="shared" si="5"/>
         <v>49</v>
       </c>
       <c r="B52" s="140" t="s">
@@ -45099,42 +45079,42 @@
       </c>
       <c r="K52" s="58"/>
       <c r="L52" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="M52" s="74"/>
       <c r="N52" s="58" t="str">
-        <f>C56</f>
+        <f t="shared" si="18"/>
         <v>iunnh</v>
       </c>
       <c r="O52" s="58" t="str">
-        <f>D56</f>
+        <f t="shared" si="19"/>
         <v>iunnh</v>
       </c>
       <c r="Q52" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>iunnh(\d)</v>
       </c>
       <c r="R52" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S52" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T52" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U52" s="56"/>
       <c r="V52" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》iunnh(\d)//</v>
       </c>
     </row>
     <row r="53" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A53" s="185">
-        <f t="shared" si="4"/>
+      <c r="A53" s="183">
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="B53" s="140" t="s">
@@ -45166,42 +45146,42 @@
       </c>
       <c r="K53" s="58"/>
       <c r="L53" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M53" s="74"/>
       <c r="N53" s="58" t="str">
-        <f>C57</f>
+        <f t="shared" si="18"/>
         <v>o</v>
       </c>
       <c r="O53" s="58" t="str">
-        <f>D57</f>
+        <f t="shared" si="19"/>
         <v>o</v>
       </c>
       <c r="Q53" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>o(\d)</v>
       </c>
       <c r="R53" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S53" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T53" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U53" s="56"/>
       <c r="V53" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》o(\d)//</v>
       </c>
     </row>
     <row r="54" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A54" s="185">
-        <f t="shared" si="4"/>
+      <c r="A54" s="183">
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="B54" s="140" t="str">
@@ -45234,42 +45214,42 @@
       </c>
       <c r="K54" s="58"/>
       <c r="L54" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M54" s="74"/>
       <c r="N54" s="58" t="str">
-        <f>C58</f>
+        <f t="shared" si="18"/>
         <v>oo</v>
       </c>
       <c r="O54" s="58" t="str">
-        <f>D58</f>
+        <f t="shared" si="19"/>
         <v>oo</v>
       </c>
       <c r="Q54" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>oo(\d)</v>
       </c>
       <c r="R54" s="125" t="s">
         <v>1181</v>
       </c>
       <c r="S54" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T54" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U54" s="56"/>
       <c r="V54" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》oo(\d)//</v>
       </c>
     </row>
     <row r="55" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A55" s="185">
-        <f t="shared" si="4"/>
+      <c r="A55" s="183">
+        <f t="shared" si="5"/>
         <v>52</v>
       </c>
       <c r="B55" s="140" t="str">
@@ -45304,42 +45284,42 @@
         <v>1312</v>
       </c>
       <c r="L55" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="M55" s="74"/>
       <c r="N55" s="58" t="str">
-        <f>C59</f>
+        <f t="shared" si="18"/>
         <v>onn</v>
       </c>
       <c r="O55" s="58" t="str">
-        <f>D59</f>
+        <f t="shared" si="19"/>
         <v>onn</v>
       </c>
       <c r="Q55" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>onn(\d)</v>
       </c>
       <c r="R55" s="125" t="s">
         <v>1181</v>
       </c>
       <c r="S55" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T55" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U55" s="56"/>
       <c r="V55" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》onn(\d)//</v>
       </c>
     </row>
     <row r="56" spans="1:22" ht="30.75" thickBot="1">
-      <c r="A56" s="185">
-        <f t="shared" si="4"/>
+      <c r="A56" s="183">
+        <f t="shared" si="5"/>
         <v>53</v>
       </c>
       <c r="B56" s="140" t="str">
@@ -45374,42 +45354,42 @@
         <v>1312</v>
       </c>
       <c r="L56" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>5</v>
       </c>
       <c r="M56" s="74"/>
       <c r="N56" s="58" t="str">
-        <f>C60</f>
+        <f t="shared" si="18"/>
         <v>oh</v>
       </c>
       <c r="O56" s="58" t="str">
-        <f>D60</f>
+        <f t="shared" si="19"/>
         <v>oh</v>
       </c>
       <c r="Q56" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>oh(\d)</v>
       </c>
       <c r="R56" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S56" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T56" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U56" s="56"/>
       <c r="V56" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》oh(\d)//</v>
       </c>
     </row>
     <row r="57" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A57" s="185">
-        <f t="shared" si="4"/>
+      <c r="A57" s="183">
+        <f t="shared" si="5"/>
         <v>54</v>
       </c>
       <c r="B57" s="140" t="s">
@@ -45441,42 +45421,42 @@
       </c>
       <c r="K57" s="58"/>
       <c r="L57" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M57" s="74"/>
       <c r="N57" s="58" t="str">
-        <f>C61</f>
+        <f t="shared" si="18"/>
         <v>ooh</v>
       </c>
       <c r="O57" s="58" t="str">
-        <f>D61</f>
+        <f t="shared" si="19"/>
         <v>ooh</v>
       </c>
       <c r="Q57" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ooh(\d)</v>
       </c>
       <c r="R57" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S57" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T57" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U57" s="56"/>
       <c r="V57" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ooh(\d)//</v>
       </c>
     </row>
     <row r="58" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A58" s="185">
-        <f t="shared" si="4"/>
+      <c r="A58" s="183">
+        <f t="shared" si="5"/>
         <v>55</v>
       </c>
       <c r="B58" s="140" t="s">
@@ -45508,42 +45488,42 @@
       </c>
       <c r="K58" s="58"/>
       <c r="L58" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M58" s="74"/>
       <c r="N58" s="58" t="str">
-        <f>C62</f>
+        <f t="shared" si="18"/>
         <v>onnh</v>
       </c>
       <c r="O58" s="58" t="str">
-        <f>D62</f>
+        <f t="shared" si="19"/>
         <v>ohnn</v>
       </c>
       <c r="Q58" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>onnh(\d)</v>
       </c>
       <c r="R58" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S58" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T58" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U58" s="56"/>
       <c r="V58" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》onnh(\d)//</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A59" s="185">
-        <f t="shared" si="4"/>
+      <c r="A59" s="183">
+        <f t="shared" si="5"/>
         <v>56</v>
       </c>
       <c r="B59" s="140" t="s">
@@ -45575,42 +45555,42 @@
       </c>
       <c r="K59" s="58"/>
       <c r="L59" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M59" s="74"/>
       <c r="N59" s="58" t="str">
-        <f>C63</f>
+        <f t="shared" si="18"/>
         <v>om</v>
       </c>
       <c r="O59" s="58" t="str">
-        <f>D63</f>
+        <f t="shared" si="19"/>
         <v>om</v>
       </c>
       <c r="Q59" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>om(\d)</v>
       </c>
       <c r="R59" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S59" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T59" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U59" s="56"/>
       <c r="V59" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》om(\d)//</v>
       </c>
     </row>
     <row r="60" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A60" s="185">
-        <f t="shared" si="4"/>
+      <c r="A60" s="183">
+        <f t="shared" si="5"/>
         <v>57</v>
       </c>
       <c r="B60" s="140" t="s">
@@ -45642,42 +45622,42 @@
       </c>
       <c r="K60" s="58"/>
       <c r="L60" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M60" s="74"/>
       <c r="N60" s="58" t="str">
-        <f>C64</f>
+        <f t="shared" si="18"/>
         <v>ong</v>
       </c>
       <c r="O60" s="58" t="str">
-        <f>D64</f>
+        <f t="shared" si="19"/>
         <v>ong</v>
       </c>
       <c r="Q60" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ong(\d)</v>
       </c>
       <c r="R60" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S60" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T60" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U60" s="56"/>
       <c r="V60" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ong(\d)//</v>
       </c>
     </row>
     <row r="61" spans="1:22" ht="30.75" thickBot="1">
-      <c r="A61" s="185">
-        <f t="shared" si="4"/>
+      <c r="A61" s="183">
+        <f t="shared" si="5"/>
         <v>58</v>
       </c>
       <c r="B61" s="140" t="s">
@@ -45709,42 +45689,42 @@
       </c>
       <c r="K61" s="58"/>
       <c r="L61" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M61" s="74"/>
       <c r="N61" s="58" t="str">
-        <f>C65</f>
+        <f t="shared" si="18"/>
         <v>op</v>
       </c>
       <c r="O61" s="58" t="str">
-        <f>D65</f>
+        <f t="shared" si="19"/>
         <v>op</v>
       </c>
       <c r="Q61" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>op(\d)</v>
       </c>
       <c r="R61" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S61" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T61" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U61" s="56"/>
       <c r="V61" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》op(\d)//</v>
       </c>
     </row>
     <row r="62" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A62" s="185">
-        <f t="shared" si="4"/>
+      <c r="A62" s="183">
+        <f t="shared" si="5"/>
         <v>59</v>
       </c>
       <c r="B62" s="140" t="s">
@@ -45778,42 +45758,42 @@
         <v>1312</v>
       </c>
       <c r="L62" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="M62" s="74"/>
       <c r="N62" s="58" t="str">
-        <f>C66</f>
+        <f t="shared" si="18"/>
         <v>ok</v>
       </c>
       <c r="O62" s="58" t="str">
-        <f>D66</f>
+        <f t="shared" si="19"/>
         <v>ok</v>
       </c>
       <c r="Q62" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ok(\d)</v>
       </c>
       <c r="R62" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S62" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T62" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U62" s="56"/>
       <c r="V62" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ok(\d)//</v>
       </c>
     </row>
     <row r="63" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A63" s="185">
-        <f t="shared" si="4"/>
+      <c r="A63" s="183">
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="B63" s="140" t="s">
@@ -45845,42 +45825,42 @@
       </c>
       <c r="K63" s="58"/>
       <c r="L63" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M63" s="74"/>
       <c r="N63" s="58" t="str">
-        <f>C67</f>
+        <f t="shared" si="18"/>
         <v>u</v>
       </c>
       <c r="O63" s="58" t="str">
-        <f>D67</f>
+        <f t="shared" si="19"/>
         <v>u</v>
       </c>
       <c r="Q63" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>u(\d)</v>
       </c>
       <c r="R63" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S63" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T63" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U63" s="56"/>
       <c r="V63" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》u(\d)//</v>
       </c>
     </row>
     <row r="64" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A64" s="185">
-        <f t="shared" si="4"/>
+      <c r="A64" s="183">
+        <f t="shared" si="5"/>
         <v>61</v>
       </c>
       <c r="B64" s="140" t="s">
@@ -45912,42 +45892,42 @@
       </c>
       <c r="K64" s="58"/>
       <c r="L64" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M64" s="74"/>
       <c r="N64" s="58" t="str">
-        <f>C68</f>
+        <f t="shared" si="18"/>
         <v>uh</v>
       </c>
       <c r="O64" s="58" t="str">
-        <f>D68</f>
+        <f t="shared" si="19"/>
         <v>uh</v>
       </c>
       <c r="Q64" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>uh(\d)</v>
       </c>
       <c r="R64" s="125" t="s">
         <v>1181</v>
       </c>
       <c r="S64" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T64" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U64" s="56"/>
       <c r="V64" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》uh(\d)//</v>
       </c>
     </row>
     <row r="65" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A65" s="185">
-        <f t="shared" si="4"/>
+      <c r="A65" s="183">
+        <f t="shared" si="5"/>
         <v>62</v>
       </c>
       <c r="B65" s="140" t="s">
@@ -45979,42 +45959,42 @@
       </c>
       <c r="K65" s="58"/>
       <c r="L65" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M65" s="74"/>
       <c r="N65" s="58" t="str">
-        <f>C69</f>
+        <f t="shared" si="18"/>
         <v>un</v>
       </c>
       <c r="O65" s="58" t="str">
-        <f>D69</f>
+        <f t="shared" si="19"/>
         <v>un</v>
       </c>
       <c r="Q65" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>un(\d)</v>
       </c>
       <c r="R65" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S65" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T65" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U65" s="56"/>
       <c r="V65" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》un(\d)//</v>
       </c>
     </row>
     <row r="66" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A66" s="185">
-        <f t="shared" si="4"/>
+      <c r="A66" s="183">
+        <f t="shared" si="5"/>
         <v>63</v>
       </c>
       <c r="B66" s="140" t="s">
@@ -46046,42 +46026,42 @@
       </c>
       <c r="K66" s="58"/>
       <c r="L66" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M66" s="74"/>
       <c r="N66" s="58" t="str">
-        <f>C70</f>
+        <f t="shared" si="18"/>
         <v>ut</v>
       </c>
       <c r="O66" s="58" t="str">
-        <f>D70</f>
+        <f t="shared" si="19"/>
         <v>ut</v>
       </c>
       <c r="Q66" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ut(\d)</v>
       </c>
       <c r="R66" s="125" t="s">
         <v>1228</v>
       </c>
       <c r="S66" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T66" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U66" s="56"/>
       <c r="V66" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ut(\d)//</v>
       </c>
     </row>
     <row r="67" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A67" s="185">
-        <f t="shared" si="4"/>
+      <c r="A67" s="183">
+        <f t="shared" si="5"/>
         <v>64</v>
       </c>
       <c r="B67" s="140" t="s">
@@ -46113,42 +46093,42 @@
       </c>
       <c r="K67" s="58"/>
       <c r="L67" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M67" s="74"/>
       <c r="N67" s="58" t="str">
-        <f>C71</f>
+        <f t="shared" si="18"/>
         <v>ua</v>
       </c>
       <c r="O67" s="58" t="str">
-        <f>D71</f>
+        <f t="shared" si="19"/>
         <v>ua</v>
       </c>
       <c r="Q67" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ua(\d)</v>
       </c>
       <c r="R67" s="125" t="s">
         <v>1181</v>
       </c>
       <c r="S67" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T67" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U67" s="56"/>
       <c r="V67" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》ua(\d)//</v>
       </c>
     </row>
     <row r="68" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A68" s="185">
-        <f t="shared" si="4"/>
+      <c r="A68" s="183">
+        <f t="shared" si="5"/>
         <v>65</v>
       </c>
       <c r="B68" s="140" t="s">
@@ -46180,42 +46160,42 @@
       </c>
       <c r="K68" s="58"/>
       <c r="L68" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M68" s="74"/>
       <c r="N68" s="58" t="str">
-        <f>C72</f>
+        <f t="shared" si="18"/>
         <v>uann</v>
       </c>
       <c r="O68" s="58" t="str">
-        <f>D72</f>
+        <f t="shared" si="19"/>
         <v>uann</v>
       </c>
       <c r="Q68" s="122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>uann(\d)</v>
       </c>
       <c r="R68" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S68" s="125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="T68" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U68" s="56"/>
       <c r="V68" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/》uann(\d)//</v>
       </c>
     </row>
     <row r="69" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A69" s="185">
-        <f t="shared" si="4"/>
+      <c r="A69" s="183">
+        <f t="shared" si="5"/>
         <v>66</v>
       </c>
       <c r="B69" s="140" t="s">
@@ -46247,42 +46227,42 @@
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M69" s="74"/>
       <c r="N69" s="58" t="str">
-        <f>C73</f>
+        <f t="shared" si="18"/>
         <v>uah</v>
       </c>
       <c r="O69" s="58" t="str">
-        <f>D73</f>
+        <f t="shared" si="19"/>
         <v>uah</v>
       </c>
       <c r="Q69" s="122" t="str">
-        <f t="shared" ref="Q69:Q85" si="15" xml:space="preserve"> _xlfn.CONCAT(N69, "(\d)")</f>
+        <f t="shared" ref="Q69:Q85" si="20" xml:space="preserve"> _xlfn.CONCAT(N69, "(\d)")</f>
         <v>uah(\d)</v>
       </c>
       <c r="R69" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S69" s="125" t="str">
-        <f t="shared" ref="S69:S85" si="16" xml:space="preserve"> IFERROR( IF(R69="", "", SEARCH(R69, $N69)), "")</f>
+        <f t="shared" ref="S69:S85" si="21" xml:space="preserve"> IFERROR( IF(R69="", "", SEARCH(R69, $N69)), "")</f>
         <v/>
       </c>
       <c r="T69" s="122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="U69" s="56"/>
       <c r="V69" s="57" t="str">
-        <f t="shared" ref="V69:V85" si="17" xml:space="preserve"> IF(AND(O69&lt;&gt;"", N69&lt;&gt;""), "    - xform/》" &amp; Q69 &amp;  "/"  &amp; T69 &amp;  "/", "")</f>
+        <f t="shared" ref="V69:V85" si="22" xml:space="preserve"> IF(AND(O69&lt;&gt;"", N69&lt;&gt;""), "    - xform/》" &amp; Q69 &amp;  "/"  &amp; T69 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》uah(\d)//</v>
       </c>
     </row>
     <row r="70" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A70" s="185">
-        <f t="shared" si="4"/>
+      <c r="A70" s="183">
+        <f t="shared" si="5"/>
         <v>67</v>
       </c>
       <c r="B70" s="140" t="s">
@@ -46314,42 +46294,42 @@
       </c>
       <c r="K70" s="58"/>
       <c r="L70" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M70" s="74"/>
       <c r="N70" s="58" t="str">
-        <f>C74</f>
+        <f t="shared" si="18"/>
         <v>uan</v>
       </c>
       <c r="O70" s="58" t="str">
-        <f>D74</f>
+        <f t="shared" si="19"/>
         <v>uan</v>
       </c>
       <c r="Q70" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>uan(\d)</v>
       </c>
       <c r="R70" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S70" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T70" s="122" t="str">
-        <f t="shared" ref="T70:T85" si="18" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(N70,S70-1), "》", MID(N70,S70,1), "${1}", RIGHT(N70, LEN(N70)-S70)), "" )</f>
+        <f t="shared" ref="T70:T85" si="23" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(N70,S70-1), "》", MID(N70,S70,1), "${1}", RIGHT(N70, LEN(N70)-S70)), "" )</f>
         <v/>
       </c>
       <c r="U70" s="56"/>
       <c r="V70" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uan(\d)//</v>
       </c>
     </row>
     <row r="71" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A71" s="185">
-        <f t="shared" si="4"/>
+      <c r="A71" s="183">
+        <f t="shared" si="5"/>
         <v>68</v>
       </c>
       <c r="B71" s="140" t="s">
@@ -46381,42 +46361,42 @@
       </c>
       <c r="K71" s="58"/>
       <c r="L71" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M71" s="74"/>
       <c r="N71" s="58" t="str">
-        <f>C75</f>
+        <f t="shared" si="18"/>
         <v>uang</v>
       </c>
       <c r="O71" s="58" t="str">
-        <f>D75</f>
+        <f t="shared" si="19"/>
         <v>uang</v>
       </c>
       <c r="Q71" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>uang(\d)</v>
       </c>
       <c r="R71" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S71" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T71" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U71" s="56"/>
       <c r="V71" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uang(\d)//</v>
       </c>
     </row>
     <row r="72" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A72" s="185">
-        <f t="shared" si="4"/>
+      <c r="A72" s="183">
+        <f t="shared" si="5"/>
         <v>69</v>
       </c>
       <c r="B72" s="140" t="s">
@@ -46448,42 +46428,42 @@
       </c>
       <c r="K72" s="58"/>
       <c r="L72" s="55">
-        <f t="shared" ref="L72:L89" si="19" xml:space="preserve"> LEN(D72)</f>
+        <f t="shared" ref="L72:L89" si="24" xml:space="preserve"> LEN(D72)</f>
         <v>4</v>
       </c>
       <c r="M72" s="74"/>
       <c r="N72" s="58" t="str">
-        <f>C76</f>
+        <f t="shared" si="18"/>
         <v>uat</v>
       </c>
       <c r="O72" s="58" t="str">
-        <f>D76</f>
+        <f t="shared" si="19"/>
         <v>uat</v>
       </c>
       <c r="Q72" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>uat(\d)</v>
       </c>
       <c r="R72" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S72" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T72" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U72" s="56"/>
       <c r="V72" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uat(\d)//</v>
       </c>
     </row>
     <row r="73" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A73" s="185">
-        <f t="shared" ref="A73:A89" si="20" xml:space="preserve"> ROW() - 3</f>
+      <c r="A73" s="183">
+        <f t="shared" ref="A73:A89" si="25" xml:space="preserve"> ROW() - 3</f>
         <v>70</v>
       </c>
       <c r="B73" s="140" t="s">
@@ -46515,42 +46495,42 @@
       </c>
       <c r="K73" s="58"/>
       <c r="L73" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
       <c r="M73" s="74"/>
       <c r="N73" s="58" t="str">
-        <f>C77</f>
+        <f t="shared" si="18"/>
         <v>uai</v>
       </c>
       <c r="O73" s="58" t="str">
-        <f>D77</f>
+        <f t="shared" si="19"/>
         <v>uai</v>
       </c>
       <c r="Q73" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>uai(\d)</v>
       </c>
       <c r="R73" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S73" s="125">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="T73" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>ua》i${1}</v>
       </c>
       <c r="U73" s="56"/>
       <c r="V73" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uai(\d)/ua》i${1}/</v>
       </c>
     </row>
     <row r="74" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A74" s="185">
-        <f t="shared" si="20"/>
+      <c r="A74" s="183">
+        <f t="shared" si="25"/>
         <v>71</v>
       </c>
       <c r="B74" s="140" t="s">
@@ -46582,42 +46562,42 @@
       </c>
       <c r="K74" s="58"/>
       <c r="L74" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
       <c r="M74" s="74"/>
       <c r="N74" s="58" t="str">
-        <f>C78</f>
+        <f t="shared" si="18"/>
         <v>uainn</v>
       </c>
       <c r="O74" s="58" t="str">
-        <f>D78</f>
+        <f t="shared" si="19"/>
         <v>uainn</v>
       </c>
       <c r="Q74" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>uainn(\d)</v>
       </c>
       <c r="R74" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S74" s="125">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="T74" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>ua》i${1}nn</v>
       </c>
       <c r="U74" s="56"/>
       <c r="V74" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uainn(\d)/ua》i${1}nn/</v>
       </c>
     </row>
     <row r="75" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A75" s="185">
-        <f t="shared" si="20"/>
+      <c r="A75" s="183">
+        <f t="shared" si="25"/>
         <v>72</v>
       </c>
       <c r="B75" s="140" t="s">
@@ -46649,42 +46629,42 @@
       </c>
       <c r="K75" s="58"/>
       <c r="L75" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>4</v>
       </c>
       <c r="M75" s="74"/>
       <c r="N75" s="58" t="str">
-        <f>C79</f>
+        <f t="shared" si="18"/>
         <v>uaih</v>
       </c>
       <c r="O75" s="58" t="str">
-        <f>D79</f>
+        <f t="shared" si="19"/>
         <v>uaih</v>
       </c>
       <c r="Q75" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>uaih(\d)</v>
       </c>
       <c r="R75" s="125" t="s">
         <v>1229</v>
       </c>
       <c r="S75" s="125">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="T75" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>ua》i${1}h</v>
       </c>
       <c r="U75" s="56"/>
       <c r="V75" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uaih(\d)/ua》i${1}h/</v>
       </c>
     </row>
     <row r="76" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A76" s="185">
-        <f t="shared" si="20"/>
+      <c r="A76" s="183">
+        <f t="shared" si="25"/>
         <v>73</v>
       </c>
       <c r="B76" s="140" t="s">
@@ -46716,42 +46696,42 @@
       </c>
       <c r="K76" s="58"/>
       <c r="L76" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
       <c r="M76" s="74"/>
       <c r="N76" s="58" t="str">
-        <f>C80</f>
+        <f t="shared" si="18"/>
         <v>uainnh</v>
       </c>
       <c r="O76" s="58" t="str">
-        <f>D80</f>
+        <f t="shared" si="19"/>
         <v>uaihnn</v>
       </c>
       <c r="Q76" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>uainnh(\d)</v>
       </c>
       <c r="R76" s="125" t="s">
         <v>1306</v>
       </c>
       <c r="S76" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T76" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U76" s="56"/>
       <c r="V76" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uainnh(\d)//</v>
       </c>
     </row>
     <row r="77" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A77" s="185">
-        <f t="shared" si="20"/>
+      <c r="A77" s="183">
+        <f t="shared" si="25"/>
         <v>74</v>
       </c>
       <c r="B77" s="140" t="s">
@@ -46783,42 +46763,42 @@
       </c>
       <c r="K77" s="58"/>
       <c r="L77" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
       <c r="M77" s="74"/>
       <c r="N77" s="58" t="str">
-        <f>C81</f>
+        <f t="shared" si="18"/>
         <v>ue</v>
       </c>
       <c r="O77" s="58" t="str">
-        <f>D81</f>
+        <f t="shared" si="19"/>
         <v>ue</v>
       </c>
       <c r="Q77" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>ue(\d)</v>
       </c>
       <c r="R77" s="125" t="s">
         <v>1305</v>
       </c>
       <c r="S77" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T77" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U77" s="56"/>
       <c r="V77" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》ue(\d)//</v>
       </c>
     </row>
     <row r="78" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A78" s="185">
-        <f t="shared" si="20"/>
+      <c r="A78" s="183">
+        <f t="shared" si="25"/>
         <v>75</v>
       </c>
       <c r="B78" s="140" t="s">
@@ -46852,42 +46832,42 @@
         <v>1312</v>
       </c>
       <c r="L78" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>5</v>
       </c>
       <c r="M78" s="74"/>
       <c r="N78" s="58" t="str">
-        <f>C82</f>
+        <f t="shared" si="18"/>
         <v>ueh</v>
       </c>
       <c r="O78" s="58" t="str">
-        <f>D82</f>
+        <f t="shared" si="19"/>
         <v>ueh</v>
       </c>
       <c r="Q78" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>ueh(\d)</v>
       </c>
       <c r="R78" s="125" t="s">
         <v>1216</v>
       </c>
       <c r="S78" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T78" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U78" s="56"/>
       <c r="V78" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》ueh(\d)//</v>
       </c>
     </row>
     <row r="79" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A79" s="185">
-        <f t="shared" si="20"/>
+      <c r="A79" s="183">
+        <f t="shared" si="25"/>
         <v>76</v>
       </c>
       <c r="B79" s="140" t="s">
@@ -46919,42 +46899,42 @@
       </c>
       <c r="K79" s="58"/>
       <c r="L79" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>4</v>
       </c>
       <c r="M79" s="74"/>
       <c r="N79" s="58" t="str">
-        <f>C83</f>
+        <f t="shared" si="18"/>
         <v>ui</v>
       </c>
       <c r="O79" s="58" t="str">
-        <f>D83</f>
+        <f t="shared" si="19"/>
         <v>ui</v>
       </c>
       <c r="Q79" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>ui(\d)</v>
       </c>
       <c r="R79" s="125" t="s">
         <v>1216</v>
       </c>
       <c r="S79" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T79" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U79" s="56"/>
       <c r="V79" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》ui(\d)//</v>
       </c>
     </row>
     <row r="80" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A80" s="185">
-        <f t="shared" si="20"/>
+      <c r="A80" s="183">
+        <f t="shared" si="25"/>
         <v>77</v>
       </c>
       <c r="B80" s="140" t="s">
@@ -46988,42 +46968,42 @@
         <v>1312</v>
       </c>
       <c r="L80" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>6</v>
       </c>
       <c r="M80" s="74"/>
       <c r="N80" s="58" t="str">
-        <f>C84</f>
+        <f t="shared" si="18"/>
         <v>uinn</v>
       </c>
       <c r="O80" s="58" t="str">
-        <f>D84</f>
+        <f t="shared" si="19"/>
         <v>uinn</v>
       </c>
       <c r="Q80" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>uinn(\d)</v>
       </c>
       <c r="R80" s="125" t="s">
         <v>1216</v>
       </c>
       <c r="S80" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T80" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U80" s="56"/>
       <c r="V80" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uinn(\d)//</v>
       </c>
     </row>
     <row r="81" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A81" s="185">
-        <f t="shared" si="20"/>
+      <c r="A81" s="183">
+        <f t="shared" si="25"/>
         <v>78</v>
       </c>
       <c r="B81" s="140" t="s">
@@ -47055,42 +47035,42 @@
       </c>
       <c r="K81" s="58"/>
       <c r="L81" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2</v>
       </c>
       <c r="M81" s="74"/>
       <c r="N81" s="58" t="str">
-        <f>C85</f>
+        <f t="shared" si="18"/>
         <v>uih</v>
       </c>
       <c r="O81" s="58" t="str">
-        <f>D85</f>
+        <f t="shared" si="19"/>
         <v>uih</v>
       </c>
       <c r="Q81" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>uih(\d)</v>
       </c>
       <c r="R81" s="125" t="s">
         <v>1216</v>
       </c>
       <c r="S81" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T81" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U81" s="56"/>
       <c r="V81" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》uih(\d)//</v>
       </c>
     </row>
     <row r="82" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A82" s="185">
-        <f t="shared" si="20"/>
+      <c r="A82" s="183">
+        <f t="shared" si="25"/>
         <v>79</v>
       </c>
       <c r="B82" s="140" t="s">
@@ -47122,42 +47102,42 @@
       </c>
       <c r="K82" s="58"/>
       <c r="L82" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
       <c r="M82" s="74"/>
       <c r="N82" s="58" t="str">
-        <f>C86</f>
+        <f t="shared" si="18"/>
         <v>m</v>
       </c>
       <c r="O82" s="58" t="str">
-        <f>D86</f>
+        <f t="shared" si="19"/>
         <v>m</v>
       </c>
       <c r="Q82" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>m(\d)</v>
       </c>
       <c r="R82" s="125" t="s">
         <v>1227</v>
       </c>
       <c r="S82" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T82" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U82" s="56"/>
       <c r="V82" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》m(\d)//</v>
       </c>
     </row>
     <row r="83" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A83" s="185">
-        <f t="shared" si="20"/>
+      <c r="A83" s="183">
+        <f t="shared" si="25"/>
         <v>80</v>
       </c>
       <c r="B83" s="140" t="s">
@@ -47189,42 +47169,42 @@
       </c>
       <c r="K83" s="58"/>
       <c r="L83" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2</v>
       </c>
       <c r="M83" s="74"/>
       <c r="N83" s="58" t="str">
-        <f>C87</f>
+        <f t="shared" ref="N83:N114" si="26">C87</f>
         <v>mh</v>
       </c>
       <c r="O83" s="58" t="str">
-        <f>D87</f>
+        <f t="shared" ref="O83:O114" si="27">D87</f>
         <v>mh</v>
       </c>
       <c r="Q83" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>mh(\d)</v>
       </c>
       <c r="R83" s="125" t="s">
         <v>1227</v>
       </c>
       <c r="S83" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T83" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U83" s="56"/>
       <c r="V83" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》mh(\d)//</v>
       </c>
     </row>
     <row r="84" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A84" s="185">
-        <f t="shared" si="20"/>
+      <c r="A84" s="183">
+        <f t="shared" si="25"/>
         <v>81</v>
       </c>
       <c r="B84" s="140" t="s">
@@ -47256,42 +47236,42 @@
       </c>
       <c r="K84" s="58"/>
       <c r="L84" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>4</v>
       </c>
       <c r="M84" s="74"/>
       <c r="N84" s="58" t="str">
-        <f>C88</f>
+        <f t="shared" si="26"/>
         <v>ng</v>
       </c>
       <c r="O84" s="58" t="str">
-        <f>D88</f>
+        <f t="shared" si="27"/>
         <v>ng</v>
       </c>
       <c r="Q84" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>ng(\d)</v>
       </c>
       <c r="R84" s="125" t="s">
         <v>1227</v>
       </c>
       <c r="S84" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T84" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U84" s="56"/>
       <c r="V84" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》ng(\d)//</v>
       </c>
     </row>
     <row r="85" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A85" s="185">
-        <f t="shared" si="20"/>
+      <c r="A85" s="183">
+        <f t="shared" si="25"/>
         <v>82</v>
       </c>
       <c r="B85" s="140" t="s">
@@ -47325,42 +47305,42 @@
         <v>1312</v>
       </c>
       <c r="L85" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
       <c r="M85" s="74"/>
       <c r="N85" s="58" t="str">
-        <f>C89</f>
+        <f t="shared" si="26"/>
         <v>ngh</v>
       </c>
       <c r="O85" s="58" t="str">
-        <f>D89</f>
+        <f t="shared" si="27"/>
         <v>ngh</v>
       </c>
       <c r="Q85" s="122" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>ngh(\d)</v>
       </c>
       <c r="R85" s="125" t="s">
         <v>1227</v>
       </c>
       <c r="S85" s="125" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="T85" s="122" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U85" s="56"/>
       <c r="V85" s="57" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve">    - xform/》ngh(\d)//</v>
       </c>
     </row>
     <row r="86" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A86" s="185">
-        <f t="shared" si="20"/>
+      <c r="A86" s="183">
+        <f t="shared" si="25"/>
         <v>83</v>
       </c>
       <c r="B86" s="140" t="s">
@@ -47392,13 +47372,13 @@
       </c>
       <c r="K86" s="58"/>
       <c r="L86" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A87" s="185">
-        <f t="shared" si="20"/>
+      <c r="A87" s="183">
+        <f t="shared" si="25"/>
         <v>84</v>
       </c>
       <c r="B87" s="140" t="s">
@@ -47430,13 +47410,13 @@
       </c>
       <c r="K87" s="58"/>
       <c r="L87" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A88" s="185">
-        <f t="shared" si="20"/>
+      <c r="A88" s="183">
+        <f t="shared" si="25"/>
         <v>85</v>
       </c>
       <c r="B88" s="140" t="s">
@@ -47468,13 +47448,13 @@
       </c>
       <c r="K88" s="58"/>
       <c r="L88" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:22" ht="27.75" thickBot="1">
-      <c r="A89" s="185">
-        <f t="shared" si="20"/>
+      <c r="A89" s="183">
+        <f t="shared" si="25"/>
         <v>86</v>
       </c>
       <c r="B89" s="140" t="s">
@@ -47506,7 +47486,7 @@
       </c>
       <c r="K89" s="58"/>
       <c r="L89" s="55">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
     </row>
@@ -56470,36 +56450,36 @@
       <c r="A19" s="58">
         <v>16</v>
       </c>
-      <c r="B19" s="192" t="s">
+      <c r="B19" s="140" t="s">
         <v>2467</v>
       </c>
-      <c r="C19" s="193" t="s">
+      <c r="C19" s="142" t="s">
         <v>2468</v>
       </c>
-      <c r="D19" s="194" t="s">
+      <c r="D19" s="75" t="s">
         <v>2468</v>
       </c>
-      <c r="E19" s="195"/>
-      <c r="F19" s="195"/>
-      <c r="G19" s="195"/>
-      <c r="H19" s="197" t="s">
+      <c r="E19" s="187"/>
+      <c r="F19" s="187"/>
+      <c r="G19" s="187"/>
+      <c r="H19" s="146" t="s">
         <v>2472</v>
       </c>
-      <c r="I19" s="196" t="s">
+      <c r="I19" s="184" t="s">
         <v>2476</v>
       </c>
-      <c r="J19" s="196"/>
+      <c r="J19" s="184"/>
       <c r="K19" s="74"/>
       <c r="L19" s="55">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M19" s="58" t="str">
-        <f>E23</f>
+        <f t="shared" ref="M19:M50" si="12">E23</f>
         <v>e</v>
       </c>
       <c r="N19" s="58" t="str">
-        <f>I23</f>
+        <f t="shared" ref="N19:N50" si="13">I23</f>
         <v>ㆤ</v>
       </c>
       <c r="P19" s="122" t="str">
@@ -56527,37 +56507,37 @@
       <c r="A20" s="58">
         <v>17</v>
       </c>
-      <c r="B20" s="192" t="str">
+      <c r="B20" s="140" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(B19, "ʔ")</f>
         <v>ɛʔ</v>
       </c>
-      <c r="C20" s="193" t="s">
+      <c r="C20" s="142" t="s">
         <v>2469</v>
       </c>
-      <c r="D20" s="194" t="s">
+      <c r="D20" s="75" t="s">
         <v>2469</v>
       </c>
-      <c r="E20" s="195"/>
-      <c r="F20" s="195"/>
-      <c r="G20" s="195"/>
-      <c r="H20" s="197" t="s">
+      <c r="E20" s="187"/>
+      <c r="F20" s="187"/>
+      <c r="G20" s="187"/>
+      <c r="H20" s="146" t="s">
         <v>2473</v>
       </c>
-      <c r="I20" s="196" t="s">
+      <c r="I20" s="184" t="s">
         <v>2478</v>
       </c>
-      <c r="J20" s="196"/>
+      <c r="J20" s="184"/>
       <c r="K20" s="74"/>
       <c r="L20" s="55">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="M20" s="58" t="str">
-        <f>E24</f>
+        <f t="shared" si="12"/>
         <v>enn</v>
       </c>
       <c r="N20" s="58" t="str">
-        <f>I24</f>
+        <f t="shared" si="13"/>
         <v>ㆥ</v>
       </c>
       <c r="P20" s="122" t="str">
@@ -56585,37 +56565,37 @@
       <c r="A21" s="58">
         <v>18</v>
       </c>
-      <c r="B21" s="192" t="str">
+      <c r="B21" s="140" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(B19, "ŋ")</f>
         <v>ɛŋ</v>
       </c>
-      <c r="C21" s="193" t="s">
+      <c r="C21" s="142" t="s">
         <v>2470</v>
       </c>
-      <c r="D21" s="194" t="s">
+      <c r="D21" s="75" t="s">
         <v>2470</v>
       </c>
-      <c r="E21" s="195"/>
-      <c r="F21" s="195"/>
-      <c r="G21" s="195"/>
-      <c r="H21" s="197" t="s">
+      <c r="E21" s="187"/>
+      <c r="F21" s="187"/>
+      <c r="G21" s="187"/>
+      <c r="H21" s="146" t="s">
         <v>2474</v>
       </c>
-      <c r="I21" s="198" t="s">
+      <c r="I21" s="185" t="s">
         <v>2479</v>
       </c>
-      <c r="J21" s="198"/>
+      <c r="J21" s="185"/>
       <c r="K21" s="74"/>
       <c r="L21" s="55">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="M21" s="58" t="str">
-        <f>E25</f>
+        <f t="shared" si="12"/>
         <v>eh</v>
       </c>
       <c r="N21" s="58" t="str">
-        <f>I25</f>
+        <f t="shared" si="13"/>
         <v>ㆤㆷ</v>
       </c>
       <c r="P21" s="122" t="str">
@@ -56643,37 +56623,37 @@
       <c r="A22" s="58">
         <v>19</v>
       </c>
-      <c r="B22" s="192" t="str">
+      <c r="B22" s="140" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(B19, "k")</f>
         <v>ɛk</v>
       </c>
-      <c r="C22" s="193" t="s">
+      <c r="C22" s="142" t="s">
         <v>2471</v>
       </c>
-      <c r="D22" s="194" t="s">
+      <c r="D22" s="75" t="s">
         <v>2471</v>
       </c>
-      <c r="E22" s="195"/>
-      <c r="F22" s="195"/>
-      <c r="G22" s="195"/>
-      <c r="H22" s="197" t="s">
+      <c r="E22" s="187"/>
+      <c r="F22" s="187"/>
+      <c r="G22" s="187"/>
+      <c r="H22" s="146" t="s">
         <v>2475</v>
       </c>
-      <c r="I22" s="198" t="s">
+      <c r="I22" s="185" t="s">
         <v>2481</v>
       </c>
-      <c r="J22" s="198"/>
+      <c r="J22" s="185"/>
       <c r="K22" s="74"/>
       <c r="L22" s="55">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="M22" s="58" t="str">
-        <f>E26</f>
+        <f t="shared" si="12"/>
         <v>ennh</v>
       </c>
       <c r="N22" s="58" t="str">
-        <f>I26</f>
+        <f t="shared" si="13"/>
         <v>ㆥㆷ</v>
       </c>
       <c r="P22" s="122" t="str">
@@ -56732,11 +56712,11 @@
         <v>1</v>
       </c>
       <c r="M23" s="58" t="str">
-        <f>E27</f>
+        <f t="shared" si="12"/>
         <v>i</v>
       </c>
       <c r="N23" s="58" t="str">
-        <f>I27</f>
+        <f t="shared" si="13"/>
         <v>ㄧ</v>
       </c>
       <c r="P23" s="122" t="str">
@@ -56797,11 +56777,11 @@
         <v>3</v>
       </c>
       <c r="M24" s="58" t="str">
-        <f>E28</f>
+        <f t="shared" si="12"/>
         <v>inn</v>
       </c>
       <c r="N24" s="58" t="str">
-        <f>I28</f>
+        <f t="shared" si="13"/>
         <v>ㆪ</v>
       </c>
       <c r="P24" s="122" t="str">
@@ -56860,11 +56840,11 @@
         <v>2</v>
       </c>
       <c r="M25" s="58" t="str">
-        <f>E29</f>
+        <f t="shared" si="12"/>
         <v>ih</v>
       </c>
       <c r="N25" s="58" t="str">
-        <f>I29</f>
+        <f t="shared" si="13"/>
         <v>ㄧㆷ</v>
       </c>
       <c r="P25" s="122" t="str">
@@ -56925,11 +56905,11 @@
         <v>2</v>
       </c>
       <c r="M26" s="58" t="str">
-        <f>E30</f>
+        <f t="shared" si="12"/>
         <v>im</v>
       </c>
       <c r="N26" s="58" t="str">
-        <f>I30</f>
+        <f t="shared" si="13"/>
         <v>ㄧㆬ</v>
       </c>
       <c r="P26" s="122" t="str">
@@ -56988,11 +56968,11 @@
         <v>2</v>
       </c>
       <c r="M27" s="58" t="str">
-        <f>E31</f>
+        <f t="shared" si="12"/>
         <v>in</v>
       </c>
       <c r="N27" s="58" t="str">
-        <f>I31</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄣ</v>
       </c>
       <c r="P27" s="122" t="str">
@@ -57053,11 +57033,11 @@
         <v>3</v>
       </c>
       <c r="M28" s="58" t="str">
-        <f>E32</f>
+        <f t="shared" si="12"/>
         <v>ing</v>
       </c>
       <c r="N28" s="58" t="str">
-        <f>I32</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄥ</v>
       </c>
       <c r="P28" s="122" t="str">
@@ -57116,11 +57096,11 @@
         <v>2</v>
       </c>
       <c r="M29" s="58" t="str">
-        <f>E33</f>
+        <f t="shared" si="12"/>
         <v>ip</v>
       </c>
       <c r="N29" s="58" t="str">
-        <f>I33</f>
+        <f t="shared" si="13"/>
         <v>一ㆴ</v>
       </c>
       <c r="P29" s="122" t="str">
@@ -57179,11 +57159,11 @@
         <v>2</v>
       </c>
       <c r="M30" s="58" t="str">
-        <f>E34</f>
+        <f t="shared" si="12"/>
         <v>it</v>
       </c>
       <c r="N30" s="58" t="str">
-        <f>I34</f>
+        <f t="shared" si="13"/>
         <v>ㄧㆵ</v>
       </c>
       <c r="P30" s="122" t="str">
@@ -57242,11 +57222,11 @@
         <v>2</v>
       </c>
       <c r="M31" s="58" t="str">
-        <f>E35</f>
+        <f t="shared" si="12"/>
         <v>ik</v>
       </c>
       <c r="N31" s="58" t="str">
-        <f>I35</f>
+        <f t="shared" si="13"/>
         <v>ㄧㆻ</v>
       </c>
       <c r="P31" s="122" t="str">
@@ -57305,11 +57285,11 @@
         <v>2</v>
       </c>
       <c r="M32" s="58" t="str">
-        <f>E36</f>
+        <f t="shared" si="12"/>
         <v>ia</v>
       </c>
       <c r="N32" s="58" t="str">
-        <f>I36</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄚ</v>
       </c>
       <c r="P32" s="122" t="str">
@@ -57368,11 +57348,11 @@
         <v>4</v>
       </c>
       <c r="M33" s="58" t="str">
-        <f>E37</f>
+        <f t="shared" si="12"/>
         <v>iann</v>
       </c>
       <c r="N33" s="58" t="str">
-        <f>I37</f>
+        <f t="shared" si="13"/>
         <v>ㄧㆩ</v>
       </c>
       <c r="P33" s="122" t="str">
@@ -57431,11 +57411,11 @@
         <v>3</v>
       </c>
       <c r="M34" s="58" t="str">
-        <f>E38</f>
+        <f t="shared" si="12"/>
         <v>iah</v>
       </c>
       <c r="N34" s="58" t="str">
-        <f>I38</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄚㆷ</v>
       </c>
       <c r="P34" s="122" t="str">
@@ -57494,11 +57474,11 @@
         <v>5</v>
       </c>
       <c r="M35" s="58" t="str">
-        <f>E39</f>
+        <f t="shared" si="12"/>
         <v>iannh</v>
       </c>
       <c r="N35" s="58" t="str">
-        <f>I39</f>
+        <f t="shared" si="13"/>
         <v>ㄧㆩㆷ</v>
       </c>
       <c r="P35" s="122" t="str">
@@ -57553,15 +57533,15 @@
       <c r="J36" s="58"/>
       <c r="K36" s="74"/>
       <c r="L36" s="55">
-        <f t="shared" ref="L36:L67" si="12" xml:space="preserve"> LEN(M36)</f>
+        <f t="shared" ref="L36:L67" si="14" xml:space="preserve"> LEN(M36)</f>
         <v>3</v>
       </c>
       <c r="M36" s="58" t="str">
-        <f>E40</f>
+        <f t="shared" si="12"/>
         <v>iam</v>
       </c>
       <c r="N36" s="58" t="str">
-        <f>I40</f>
+        <f t="shared" si="13"/>
         <v>ㄧㆰ</v>
       </c>
       <c r="P36" s="122" t="str">
@@ -57618,15 +57598,15 @@
       </c>
       <c r="K37" s="74"/>
       <c r="L37" s="55">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="M37" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>3</v>
-      </c>
-      <c r="M37" s="58" t="str">
-        <f>E41</f>
         <v>ian</v>
       </c>
       <c r="N37" s="58" t="str">
-        <f>I41</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄢ</v>
       </c>
       <c r="P37" s="122" t="str">
@@ -57681,15 +57661,15 @@
       <c r="J38" s="58"/>
       <c r="K38" s="74"/>
       <c r="L38" s="55">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="M38" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>4</v>
-      </c>
-      <c r="M38" s="58" t="str">
-        <f>E42</f>
         <v>iang</v>
       </c>
       <c r="N38" s="58" t="str">
-        <f>I42</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄤ</v>
       </c>
       <c r="P38" s="122" t="str">
@@ -57746,15 +57726,15 @@
       </c>
       <c r="K39" s="74"/>
       <c r="L39" s="55">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="M39" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>3</v>
-      </c>
-      <c r="M39" s="58" t="str">
-        <f>E43</f>
         <v>iap</v>
       </c>
       <c r="N39" s="58" t="str">
-        <f>I43</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄚㆴ</v>
       </c>
       <c r="P39" s="122" t="str">
@@ -57809,15 +57789,15 @@
       <c r="J40" s="58"/>
       <c r="K40" s="74"/>
       <c r="L40" s="55">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="M40" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>3</v>
-      </c>
-      <c r="M40" s="58" t="str">
-        <f>E44</f>
         <v>iat</v>
       </c>
       <c r="N40" s="58" t="str">
-        <f>I44</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄚㆵ</v>
       </c>
       <c r="P40" s="122" t="str">
@@ -57872,15 +57852,15 @@
       <c r="J41" s="58"/>
       <c r="K41" s="74"/>
       <c r="L41" s="55">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="M41" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>3</v>
-      </c>
-      <c r="M41" s="58" t="str">
-        <f>E45</f>
         <v>iak</v>
       </c>
       <c r="N41" s="58" t="str">
-        <f>I45</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄚㆻ</v>
       </c>
       <c r="P41" s="122" t="str">
@@ -57935,15 +57915,15 @@
       <c r="J42" s="58"/>
       <c r="K42" s="74"/>
       <c r="L42" s="55">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="M42" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>3</v>
-      </c>
-      <c r="M42" s="58" t="str">
-        <f>E46</f>
         <v>iau</v>
       </c>
       <c r="N42" s="58" t="str">
-        <f>I46</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄠ</v>
       </c>
       <c r="P42" s="122" t="str">
@@ -57998,15 +57978,15 @@
       <c r="J43" s="58"/>
       <c r="K43" s="74"/>
       <c r="L43" s="55">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="M43" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>5</v>
-      </c>
-      <c r="M43" s="58" t="str">
-        <f>E47</f>
         <v>iaunn</v>
       </c>
       <c r="N43" s="58" t="str">
-        <f>I47</f>
+        <f t="shared" si="13"/>
         <v>ㄧㆯ</v>
       </c>
       <c r="P43" s="122" t="str">
@@ -58061,15 +58041,15 @@
       <c r="J44" s="58"/>
       <c r="K44" s="74"/>
       <c r="L44" s="55">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="M44" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>4</v>
-      </c>
-      <c r="M44" s="58" t="str">
-        <f>E48</f>
         <v>iauh</v>
       </c>
       <c r="N44" s="58" t="str">
-        <f>I48</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄠㆷ</v>
       </c>
       <c r="P44" s="122" t="str">
@@ -58124,15 +58104,15 @@
       <c r="J45" s="58"/>
       <c r="K45" s="74"/>
       <c r="L45" s="55">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="M45" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>3</v>
-      </c>
-      <c r="M45" s="58" t="str">
-        <f>E49</f>
         <v>ior</v>
       </c>
       <c r="N45" s="58" t="str">
-        <f>I49</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄜ</v>
       </c>
       <c r="P45" s="122" t="str">
@@ -58187,15 +58167,15 @@
       <c r="J46" s="58"/>
       <c r="K46" s="74"/>
       <c r="L46" s="55">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="M46" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>5</v>
-      </c>
-      <c r="M46" s="58" t="str">
-        <f>E50</f>
         <v>ioonn</v>
       </c>
       <c r="N46" s="58" t="str">
-        <f>I50</f>
+        <f t="shared" si="13"/>
         <v>ㄧㆧ</v>
       </c>
       <c r="P46" s="122" t="str">
@@ -58252,15 +58232,15 @@
       </c>
       <c r="K47" s="74"/>
       <c r="L47" s="55">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="M47" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>4</v>
-      </c>
-      <c r="M47" s="58" t="str">
-        <f>E51</f>
         <v>iorh</v>
       </c>
       <c r="N47" s="58" t="str">
-        <f>I51</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄜㆷ</v>
       </c>
       <c r="P47" s="122" t="str">
@@ -58315,15 +58295,15 @@
       <c r="J48" s="58"/>
       <c r="K48" s="74"/>
       <c r="L48" s="55">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="M48" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>4</v>
-      </c>
-      <c r="M48" s="58" t="str">
-        <f>E52</f>
         <v>iong</v>
       </c>
       <c r="N48" s="58" t="str">
-        <f>I52</f>
+        <f t="shared" si="13"/>
         <v>ㄧㆲ</v>
       </c>
       <c r="P48" s="122" t="str">
@@ -58378,15 +58358,15 @@
       <c r="J49" s="58"/>
       <c r="K49" s="74"/>
       <c r="L49" s="55">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="M49" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>4</v>
-      </c>
-      <c r="M49" s="58" t="str">
-        <f>E53</f>
         <v>iook</v>
       </c>
       <c r="N49" s="58" t="str">
-        <f>I53</f>
+        <f t="shared" si="13"/>
         <v>ㄧㆦㆻ</v>
       </c>
       <c r="P49" s="122" t="str">
@@ -58443,15 +58423,15 @@
       </c>
       <c r="K50" s="74"/>
       <c r="L50" s="55">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="M50" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>2</v>
-      </c>
-      <c r="M50" s="58" t="str">
-        <f>E54</f>
         <v>iu</v>
       </c>
       <c r="N50" s="58" t="str">
-        <f>I54</f>
+        <f t="shared" si="13"/>
         <v>ㄧㄨ</v>
       </c>
       <c r="P50" s="122" t="str">
@@ -58506,15 +58486,15 @@
       <c r="J51" s="58"/>
       <c r="K51" s="74"/>
       <c r="L51" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="M51" s="58" t="str">
-        <f>E55</f>
+        <f t="shared" ref="M51:M82" si="15">E55</f>
         <v>iunn</v>
       </c>
       <c r="N51" s="58" t="str">
-        <f>I55</f>
+        <f t="shared" ref="N51:N82" si="16">I55</f>
         <v>ㄧㆫ</v>
       </c>
       <c r="P51" s="122" t="str">
@@ -58569,15 +58549,15 @@
       <c r="J52" s="58"/>
       <c r="K52" s="74"/>
       <c r="L52" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
       <c r="M52" s="58" t="str">
-        <f>E56</f>
+        <f t="shared" si="15"/>
         <v>iunnh</v>
       </c>
       <c r="N52" s="58" t="str">
-        <f>I56</f>
+        <f t="shared" si="16"/>
         <v>ㄧㆫㆷ</v>
       </c>
       <c r="P52" s="122" t="str">
@@ -58632,15 +58612,15 @@
       <c r="J53" s="58"/>
       <c r="K53" s="74"/>
       <c r="L53" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="M53" s="58" t="str">
-        <f>E57</f>
+        <f t="shared" si="15"/>
         <v>or</v>
       </c>
       <c r="N53" s="58" t="str">
-        <f>I57</f>
+        <f t="shared" si="16"/>
         <v>ㄜ</v>
       </c>
       <c r="P53" s="122" t="str">
@@ -58695,15 +58675,15 @@
       <c r="J54" s="58"/>
       <c r="K54" s="74"/>
       <c r="L54" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="M54" s="58" t="str">
-        <f>E58</f>
+        <f t="shared" si="15"/>
         <v>oo</v>
       </c>
       <c r="N54" s="58" t="str">
-        <f>I58</f>
+        <f t="shared" si="16"/>
         <v>ㆦ</v>
       </c>
       <c r="P54" s="122" t="str">
@@ -58760,15 +58740,15 @@
       </c>
       <c r="K55" s="74"/>
       <c r="L55" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="M55" s="58" t="str">
-        <f>E59</f>
+        <f t="shared" si="15"/>
         <v>oonn</v>
       </c>
       <c r="N55" s="58" t="str">
-        <f>I59</f>
+        <f t="shared" si="16"/>
         <v>ㆧ</v>
       </c>
       <c r="P55" s="122" t="str">
@@ -58825,15 +58805,15 @@
       </c>
       <c r="K56" s="74"/>
       <c r="L56" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="M56" s="58" t="str">
-        <f>E60</f>
+        <f t="shared" si="15"/>
         <v>orh</v>
       </c>
       <c r="N56" s="58" t="str">
-        <f>I60</f>
+        <f t="shared" si="16"/>
         <v>ㄜㆷ</v>
       </c>
       <c r="P56" s="122" t="str">
@@ -58888,15 +58868,15 @@
       <c r="J57" s="58"/>
       <c r="K57" s="74"/>
       <c r="L57" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="M57" s="58" t="str">
-        <f>E61</f>
+        <f t="shared" si="15"/>
         <v>ooh</v>
       </c>
       <c r="N57" s="58" t="str">
-        <f>I61</f>
+        <f t="shared" si="16"/>
         <v>ㆦㆷ</v>
       </c>
       <c r="P57" s="122" t="str">
@@ -58951,15 +58931,15 @@
       <c r="J58" s="58"/>
       <c r="K58" s="74"/>
       <c r="L58" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="M58" s="58" t="str">
-        <f>E62</f>
+        <f t="shared" si="15"/>
         <v>onnh</v>
       </c>
       <c r="N58" s="58" t="str">
-        <f>I62</f>
+        <f t="shared" si="16"/>
         <v>ㆧㆷ</v>
       </c>
       <c r="P58" s="122" t="str">
@@ -59014,15 +58994,15 @@
       <c r="J59" s="58"/>
       <c r="K59" s="74"/>
       <c r="L59" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="M59" s="58" t="str">
-        <f>E63</f>
+        <f t="shared" si="15"/>
         <v>oom</v>
       </c>
       <c r="N59" s="58" t="str">
-        <f>I63</f>
+        <f t="shared" si="16"/>
         <v>ㆱ</v>
       </c>
       <c r="P59" s="122" t="str">
@@ -59077,15 +59057,15 @@
       <c r="J60" s="58"/>
       <c r="K60" s="74"/>
       <c r="L60" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="M60" s="58" t="str">
-        <f>E64</f>
+        <f t="shared" si="15"/>
         <v>ong</v>
       </c>
       <c r="N60" s="58" t="str">
-        <f>I64</f>
+        <f t="shared" si="16"/>
         <v>ㆲ</v>
       </c>
       <c r="P60" s="122" t="str">
@@ -59140,15 +59120,15 @@
       <c r="J61" s="58"/>
       <c r="K61" s="74"/>
       <c r="L61" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="M61" s="58" t="str">
-        <f>E65</f>
+        <f t="shared" si="15"/>
         <v>oop</v>
       </c>
       <c r="N61" s="58" t="str">
-        <f>I65</f>
+        <f t="shared" si="16"/>
         <v>ㆦㆴ</v>
       </c>
       <c r="P61" s="122" t="str">
@@ -59205,15 +59185,15 @@
       </c>
       <c r="K62" s="74"/>
       <c r="L62" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="M62" s="58" t="str">
-        <f>E66</f>
+        <f t="shared" si="15"/>
         <v>ok</v>
       </c>
       <c r="N62" s="58" t="str">
-        <f>I66</f>
+        <f t="shared" si="16"/>
         <v>ㆦㆻ</v>
       </c>
       <c r="P62" s="122" t="str">
@@ -59268,15 +59248,15 @@
       <c r="J63" s="58"/>
       <c r="K63" s="74"/>
       <c r="L63" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M63" s="58" t="str">
-        <f>E67</f>
+        <f t="shared" si="15"/>
         <v>u</v>
       </c>
       <c r="N63" s="58" t="str">
-        <f>I67</f>
+        <f t="shared" si="16"/>
         <v>ㄨ</v>
       </c>
       <c r="P63" s="122" t="str">
@@ -59331,15 +59311,15 @@
       <c r="J64" s="58"/>
       <c r="K64" s="74"/>
       <c r="L64" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="M64" s="58" t="str">
-        <f>E68</f>
+        <f t="shared" si="15"/>
         <v>uh</v>
       </c>
       <c r="N64" s="58" t="str">
-        <f>I68</f>
+        <f t="shared" si="16"/>
         <v>ㄨㆷ</v>
       </c>
       <c r="P64" s="122" t="str">
@@ -59394,15 +59374,15 @@
       <c r="J65" s="58"/>
       <c r="K65" s="74"/>
       <c r="L65" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="M65" s="58" t="str">
-        <f>E69</f>
+        <f t="shared" si="15"/>
         <v>un</v>
       </c>
       <c r="N65" s="58" t="str">
-        <f>I69</f>
+        <f t="shared" si="16"/>
         <v>ㄨㄣ</v>
       </c>
       <c r="P65" s="122" t="str">
@@ -59457,15 +59437,15 @@
       <c r="J66" s="58"/>
       <c r="K66" s="74"/>
       <c r="L66" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="M66" s="58" t="str">
-        <f>E70</f>
+        <f t="shared" si="15"/>
         <v>ut</v>
       </c>
       <c r="N66" s="58" t="str">
-        <f>I70</f>
+        <f t="shared" si="16"/>
         <v>ㄨㆵ</v>
       </c>
       <c r="P66" s="122" t="str">
@@ -59520,15 +59500,15 @@
       <c r="J67" s="58"/>
       <c r="K67" s="74"/>
       <c r="L67" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="M67" s="58" t="str">
-        <f>E71</f>
+        <f t="shared" si="15"/>
         <v>ua</v>
       </c>
       <c r="N67" s="58" t="str">
-        <f>I71</f>
+        <f t="shared" si="16"/>
         <v>ㄨㄚ</v>
       </c>
       <c r="P67" s="122" t="str">
@@ -59583,15 +59563,15 @@
       <c r="J68" s="58"/>
       <c r="K68" s="74"/>
       <c r="L68" s="55">
-        <f t="shared" ref="L68:L85" si="13" xml:space="preserve"> LEN(M68)</f>
+        <f t="shared" ref="L68:L85" si="17" xml:space="preserve"> LEN(M68)</f>
         <v>4</v>
       </c>
       <c r="M68" s="58" t="str">
-        <f>E72</f>
+        <f t="shared" si="15"/>
         <v>uann</v>
       </c>
       <c r="N68" s="58" t="str">
-        <f>I72</f>
+        <f t="shared" si="16"/>
         <v>ㄨㆩ</v>
       </c>
       <c r="P68" s="122" t="str">
@@ -59646,26 +59626,26 @@
       <c r="J69" s="58"/>
       <c r="K69" s="74"/>
       <c r="L69" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M69" s="58" t="str">
-        <f>E73</f>
+        <f t="shared" si="15"/>
         <v>uah</v>
       </c>
       <c r="N69" s="58" t="str">
-        <f>I73</f>
+        <f t="shared" si="16"/>
         <v>ㄨㄚㆷ</v>
       </c>
       <c r="P69" s="122" t="str">
-        <f t="shared" ref="P69:P85" si="14" xml:space="preserve"> _xlfn.CONCAT(M69, "(\d)")</f>
+        <f t="shared" ref="P69:P85" si="18" xml:space="preserve"> _xlfn.CONCAT(M69, "(\d)")</f>
         <v>uah(\d)</v>
       </c>
       <c r="Q69" s="125" t="s">
         <v>316</v>
       </c>
       <c r="R69" s="125">
-        <f t="shared" ref="R69:R85" si="15" xml:space="preserve"> IFERROR( IF(Q69="", "", SEARCH(Q69, $M69)), "")</f>
+        <f t="shared" ref="R69:R85" si="19" xml:space="preserve"> IFERROR( IF(Q69="", "", SEARCH(Q69, $M69)), "")</f>
         <v>2</v>
       </c>
       <c r="S69" s="122" t="str">
@@ -59674,7 +59654,7 @@
       </c>
       <c r="T69" s="56"/>
       <c r="U69" s="57" t="str">
-        <f t="shared" ref="U69:U85" si="16" xml:space="preserve"> IF(AND(N69&lt;&gt;"", M69&lt;&gt;""), "    - xform/》" &amp; P69 &amp;  "/"  &amp; S69 &amp;  "/", "")</f>
+        <f t="shared" ref="U69:U85" si="20" xml:space="preserve"> IF(AND(N69&lt;&gt;"", M69&lt;&gt;""), "    - xform/》" &amp; P69 &amp;  "/"  &amp; S69 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》uah(\d)/u》a${1}h/</v>
       </c>
     </row>
@@ -59709,35 +59689,35 @@
       <c r="J70" s="58"/>
       <c r="K70" s="74"/>
       <c r="L70" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M70" s="58" t="str">
-        <f>E74</f>
+        <f t="shared" si="15"/>
         <v>uan</v>
       </c>
       <c r="N70" s="58" t="str">
-        <f>I74</f>
+        <f t="shared" si="16"/>
         <v>ㄨㄢ</v>
       </c>
       <c r="P70" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>uan(\d)</v>
       </c>
       <c r="Q70" s="125" t="s">
         <v>316</v>
       </c>
       <c r="R70" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="S70" s="122" t="str">
-        <f t="shared" ref="S70:S85" si="17" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(M70,R70-1), "》", MID(M70,R70,1), "${1}", RIGHT(M70, LEN(M70)-R70)), "" )</f>
+        <f t="shared" ref="S70:S85" si="21" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(M70,R70-1), "》", MID(M70,R70,1), "${1}", RIGHT(M70, LEN(M70)-R70)), "" )</f>
         <v>u》a${1}n</v>
       </c>
       <c r="T70" s="56"/>
       <c r="U70" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》uan(\d)/u》a${1}n/</v>
       </c>
     </row>
@@ -59772,35 +59752,35 @@
       <c r="J71" s="58"/>
       <c r="K71" s="74"/>
       <c r="L71" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="M71" s="58" t="str">
-        <f>E75</f>
+        <f t="shared" si="15"/>
         <v>uang</v>
       </c>
       <c r="N71" s="58" t="str">
-        <f>I75</f>
+        <f t="shared" si="16"/>
         <v>ㄨㄤ</v>
       </c>
       <c r="P71" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>uang(\d)</v>
       </c>
       <c r="Q71" s="125" t="s">
         <v>316</v>
       </c>
       <c r="R71" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="S71" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>u》a${1}ng</v>
       </c>
       <c r="T71" s="56"/>
       <c r="U71" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》uang(\d)/u》a${1}ng/</v>
       </c>
     </row>
@@ -59835,35 +59815,35 @@
       <c r="J72" s="58"/>
       <c r="K72" s="74"/>
       <c r="L72" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M72" s="58" t="str">
-        <f>E76</f>
+        <f t="shared" si="15"/>
         <v>uat</v>
       </c>
       <c r="N72" s="58" t="str">
-        <f>I76</f>
+        <f t="shared" si="16"/>
         <v>ㄨㄚㆵ</v>
       </c>
       <c r="P72" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>uat(\d)</v>
       </c>
       <c r="Q72" s="125" t="s">
         <v>316</v>
       </c>
       <c r="R72" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="S72" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>u》a${1}t</v>
       </c>
       <c r="T72" s="56"/>
       <c r="U72" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》uat(\d)/u》a${1}t/</v>
       </c>
     </row>
@@ -59898,35 +59878,35 @@
       <c r="J73" s="58"/>
       <c r="K73" s="74"/>
       <c r="L73" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M73" s="58" t="str">
-        <f>E77</f>
+        <f t="shared" si="15"/>
         <v>uai</v>
       </c>
       <c r="N73" s="58" t="str">
-        <f>I77</f>
+        <f t="shared" si="16"/>
         <v>ㄨㄞ</v>
       </c>
       <c r="P73" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>uai(\d)</v>
       </c>
       <c r="Q73" s="125" t="s">
         <v>316</v>
       </c>
       <c r="R73" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="S73" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>u》a${1}i</v>
       </c>
       <c r="T73" s="56"/>
       <c r="U73" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》uai(\d)/u》a${1}i/</v>
       </c>
     </row>
@@ -59961,35 +59941,35 @@
       <c r="J74" s="58"/>
       <c r="K74" s="74"/>
       <c r="L74" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>5</v>
       </c>
       <c r="M74" s="58" t="str">
-        <f>E78</f>
+        <f t="shared" si="15"/>
         <v>uainn</v>
       </c>
       <c r="N74" s="58" t="str">
-        <f>I78</f>
+        <f t="shared" si="16"/>
         <v>ㄨㆮ</v>
       </c>
       <c r="P74" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>uainn(\d)</v>
       </c>
       <c r="Q74" s="125" t="s">
         <v>316</v>
       </c>
       <c r="R74" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="S74" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>u》a${1}inn</v>
       </c>
       <c r="T74" s="56"/>
       <c r="U74" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》uainn(\d)/u》a${1}inn/</v>
       </c>
     </row>
@@ -60024,35 +60004,35 @@
       <c r="J75" s="58"/>
       <c r="K75" s="74"/>
       <c r="L75" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="M75" s="58" t="str">
-        <f>E79</f>
+        <f t="shared" si="15"/>
         <v>uaih</v>
       </c>
       <c r="N75" s="58" t="str">
-        <f>I79</f>
+        <f t="shared" si="16"/>
         <v>ㄨㄞㆷ</v>
       </c>
       <c r="P75" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>uaih(\d)</v>
       </c>
       <c r="Q75" s="125" t="s">
         <v>316</v>
       </c>
       <c r="R75" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="S75" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>u》a${1}ih</v>
       </c>
       <c r="T75" s="56"/>
       <c r="U75" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》uaih(\d)/u》a${1}ih/</v>
       </c>
     </row>
@@ -60087,35 +60067,35 @@
       <c r="J76" s="58"/>
       <c r="K76" s="74"/>
       <c r="L76" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>6</v>
       </c>
       <c r="M76" s="58" t="str">
-        <f>E80</f>
+        <f t="shared" si="15"/>
         <v>uainnh</v>
       </c>
       <c r="N76" s="58" t="str">
-        <f>I80</f>
+        <f t="shared" si="16"/>
         <v>ㄨㆮㆷ</v>
       </c>
       <c r="P76" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>uainnh(\d)</v>
       </c>
       <c r="Q76" s="125" t="s">
         <v>316</v>
       </c>
       <c r="R76" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
       <c r="S76" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>u》a${1}innh</v>
       </c>
       <c r="T76" s="56"/>
       <c r="U76" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》uainnh(\d)/u》a${1}innh/</v>
       </c>
     </row>
@@ -60150,35 +60130,35 @@
       <c r="J77" s="58"/>
       <c r="K77" s="74"/>
       <c r="L77" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M77" s="58" t="str">
-        <f>E81</f>
+        <f t="shared" si="15"/>
         <v>ue</v>
       </c>
       <c r="N77" s="58" t="str">
-        <f>I81</f>
+        <f t="shared" si="16"/>
         <v>ㄨㆤ</v>
       </c>
       <c r="P77" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>ue(\d)</v>
       </c>
       <c r="Q77" s="125" t="s">
         <v>308</v>
       </c>
       <c r="R77" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="S77" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>》u${1}e</v>
       </c>
       <c r="T77" s="56"/>
       <c r="U77" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》ue(\d)/》u${1}e/</v>
       </c>
     </row>
@@ -60215,35 +60195,35 @@
       </c>
       <c r="K78" s="74"/>
       <c r="L78" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M78" s="58" t="str">
-        <f>E82</f>
+        <f t="shared" si="15"/>
         <v>ueh</v>
       </c>
       <c r="N78" s="58" t="str">
-        <f>I82</f>
+        <f t="shared" si="16"/>
         <v>ㄨㆤㆷ</v>
       </c>
       <c r="P78" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>ueh(\d)</v>
       </c>
       <c r="Q78" s="125" t="s">
         <v>308</v>
       </c>
       <c r="R78" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="S78" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>》u${1}eh</v>
       </c>
       <c r="T78" s="56"/>
       <c r="U78" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》ueh(\d)/》u${1}eh/</v>
       </c>
     </row>
@@ -60278,35 +60258,35 @@
       <c r="J79" s="58"/>
       <c r="K79" s="74"/>
       <c r="L79" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M79" s="58" t="str">
-        <f>E83</f>
+        <f t="shared" si="15"/>
         <v>ui</v>
       </c>
       <c r="N79" s="58" t="str">
-        <f>I83</f>
+        <f t="shared" si="16"/>
         <v>ㄨㄧ</v>
       </c>
       <c r="P79" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>ui(\d)</v>
       </c>
       <c r="Q79" s="125" t="s">
         <v>308</v>
       </c>
       <c r="R79" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="S79" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>》u${1}i</v>
       </c>
       <c r="T79" s="56"/>
       <c r="U79" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》ui(\d)/》u${1}i/</v>
       </c>
     </row>
@@ -60343,35 +60323,35 @@
       </c>
       <c r="K80" s="74"/>
       <c r="L80" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="M80" s="58" t="str">
-        <f>E84</f>
+        <f t="shared" si="15"/>
         <v>uinn</v>
       </c>
       <c r="N80" s="58" t="str">
-        <f>I84</f>
+        <f t="shared" si="16"/>
         <v>ㄨㆪ</v>
       </c>
       <c r="P80" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>uinn(\d)</v>
       </c>
       <c r="Q80" s="125" t="s">
         <v>308</v>
       </c>
       <c r="R80" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="S80" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>》u${1}inn</v>
       </c>
       <c r="T80" s="56"/>
       <c r="U80" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》uinn(\d)/》u${1}inn/</v>
       </c>
     </row>
@@ -60406,35 +60386,35 @@
       <c r="J81" s="58"/>
       <c r="K81" s="74"/>
       <c r="L81" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M81" s="58" t="str">
-        <f>E85</f>
+        <f t="shared" si="15"/>
         <v>uih</v>
       </c>
       <c r="N81" s="58" t="str">
-        <f>I85</f>
+        <f t="shared" si="16"/>
         <v>ㄨㄧㆷ</v>
       </c>
       <c r="P81" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>uih(\d)</v>
       </c>
       <c r="Q81" s="125" t="s">
         <v>308</v>
       </c>
       <c r="R81" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="S81" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>》u${1}ih</v>
       </c>
       <c r="T81" s="56"/>
       <c r="U81" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》uih(\d)/》u${1}ih/</v>
       </c>
     </row>
@@ -60469,35 +60449,35 @@
       <c r="J82" s="58"/>
       <c r="K82" s="74"/>
       <c r="L82" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M82" s="58" t="str">
-        <f>E86</f>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="N82" s="58" t="str">
-        <f>I86</f>
+        <f t="shared" si="16"/>
         <v>ㆬ</v>
       </c>
       <c r="P82" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>m(\d)</v>
       </c>
       <c r="Q82" s="125" t="s">
         <v>432</v>
       </c>
       <c r="R82" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="S82" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>》m${1}</v>
       </c>
       <c r="T82" s="56"/>
       <c r="U82" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》m(\d)/》m${1}/</v>
       </c>
     </row>
@@ -60532,35 +60512,35 @@
       <c r="J83" s="58"/>
       <c r="K83" s="74"/>
       <c r="L83" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M83" s="58" t="str">
-        <f>E87</f>
+        <f t="shared" ref="M83:M114" si="22">E87</f>
         <v>mh</v>
       </c>
       <c r="N83" s="58" t="str">
-        <f>I87</f>
+        <f t="shared" ref="N83:N114" si="23">I87</f>
         <v>ㆬㆷ</v>
       </c>
       <c r="P83" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>mh(\d)</v>
       </c>
       <c r="Q83" s="125" t="s">
         <v>432</v>
       </c>
       <c r="R83" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="S83" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>》m${1}h</v>
       </c>
       <c r="T83" s="56"/>
       <c r="U83" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》mh(\d)/》m${1}h/</v>
       </c>
     </row>
@@ -60595,35 +60575,35 @@
       <c r="J84" s="58"/>
       <c r="K84" s="74"/>
       <c r="L84" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M84" s="58" t="str">
-        <f>E88</f>
+        <f t="shared" si="22"/>
         <v>ng</v>
       </c>
       <c r="N84" s="58" t="str">
-        <f>I88</f>
+        <f t="shared" si="23"/>
         <v>ㆭ</v>
       </c>
       <c r="P84" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>ng(\d)</v>
       </c>
       <c r="Q84" s="125" t="s">
         <v>591</v>
       </c>
       <c r="R84" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="S84" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>》n${1}g</v>
       </c>
       <c r="T84" s="56"/>
       <c r="U84" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》ng(\d)/》n${1}g/</v>
       </c>
     </row>
@@ -60660,35 +60640,35 @@
       </c>
       <c r="K85" s="74"/>
       <c r="L85" s="55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="M85" s="58" t="str">
-        <f>E89</f>
+        <f t="shared" si="22"/>
         <v>ngh</v>
       </c>
       <c r="N85" s="58" t="str">
-        <f>I89</f>
+        <f t="shared" si="23"/>
         <v>ㆭㆷ</v>
       </c>
       <c r="P85" s="122" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>ngh(\d)</v>
       </c>
       <c r="Q85" s="125" t="s">
         <v>591</v>
       </c>
       <c r="R85" s="125">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="S85" s="122" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>》n${1}gh</v>
       </c>
       <c r="T85" s="56"/>
       <c r="U85" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">    - xform/》ngh(\d)/》n${1}gh/</v>
       </c>
     </row>

--- a/docs/101_聲韻調對照表.xlsx
+++ b/docs/101_聲韻調對照表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCD150E-2881-4A14-9159-AF2BF547257C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96765B80-E391-4AA3-AFDD-EB83C564A519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="877" activeTab="8" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="877" activeTab="9" xr2:uid="{7E808FC4-FD7B-4D2F-8735-FF65DCE8E5C1}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="26" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <sheet name="馬重奇韻母50字" sheetId="8" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">【韻】韻母對照表!$B$3:$O$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">【韻】韻母對照表!$B$3:$P$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">台語注音二式轉方音符號!$B$3:$L$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6713" uniqueCount="2425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6714" uniqueCount="2426">
   <si>
     <t>識別號</t>
   </si>
@@ -8476,6 +8476,9 @@
   <si>
     <t>零聲母</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>十五音識別碼2</t>
   </si>
 </sst>
 </file>
@@ -9496,7 +9499,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -10094,12 +10097,6 @@
     <xf numFmtId="0" fontId="88" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -10160,6 +10157,15 @@
     <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -10168,7 +10174,48 @@
     <cellStyle name="一般 4" xfId="4" xr:uid="{E932D2E5-AF16-4FFA-AB0C-5F7E179E4D03}"/>
     <cellStyle name="一般 5" xfId="2" xr:uid="{8C9CBB70-72B8-491C-A1A5-535BA1FE1D69}"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="57">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <name val="Noto Sans"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE2E6"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE2E6"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE2E6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE2E6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -11702,55 +11749,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{50527B81-BE0C-4989-8113-79F20236AB33}" name="聲母對照表" displayName="聲母對照表" ref="A1:P23" totalsRowShown="0" headerRowDxfId="55" tableBorderDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{50527B81-BE0C-4989-8113-79F20236AB33}" name="聲母對照表" displayName="聲母對照表" ref="A1:P23" totalsRowShown="0" headerRowDxfId="56" tableBorderDxfId="55">
   <autoFilter ref="A1:P23" xr:uid="{50527B81-BE0C-4989-8113-79F20236AB33}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P23">
     <sortCondition ref="A8:A23"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{0496578E-8EFF-4E56-9F02-D6EFB72645B8}" name="識別號" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{78D5AE39-C891-435E-8D14-C962F474118F}" name="序號" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{1335DAED-BD1E-4CE0-98A0-285C07AE05B4}" name="國際音標" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{F9A38440-D11D-45B8-BE95-B6BB0AAAF1E3}" name="台羅拼音" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{AF657621-3918-4D23-BBFD-13EBF0B27858}" name="台語音標" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{C16CB252-C9A4-4CB2-8FDD-82813173CF4D}" name="注音二式" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{0D7F03C3-8C58-42B2-B097-C3B2A5C37034}" name="閩拼方案" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{9540CBC9-4FE3-4DE8-90B0-B77F1C52414A}" name="白話字" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{D9050C95-564C-4861-B1AE-AA03A7C3DE41}" name="方音符號" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{05251E82-C5E0-4833-BDD6-FE5DF5B1D381}" name="台語注音" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{315B1262-49A6-4891-8C01-10EC91043A3B}" name="十五音" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{DEEC4CA6-6FC2-4991-B54A-56DAB27197B0}" name="漢字例" dataDxfId="42"/>
-    <tableColumn id="13" xr3:uid="{C6123364-B523-47FE-9684-7560414EF39F}" name="備註" dataDxfId="41"/>
-    <tableColumn id="14" xr3:uid="{6018D2E9-8064-40AC-887E-308DB4B54742}" name="s1" dataDxfId="40"/>
-    <tableColumn id="15" xr3:uid="{C1ACEDB0-215C-486F-8C7A-D83ECFA591EB}" name="s2" dataDxfId="39"/>
-    <tableColumn id="16" xr3:uid="{E9B4DE26-B82C-4445-854F-C1B5EF3E2F79}" name="s3" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{0496578E-8EFF-4E56-9F02-D6EFB72645B8}" name="識別號" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{78D5AE39-C891-435E-8D14-C962F474118F}" name="序號" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{1335DAED-BD1E-4CE0-98A0-285C07AE05B4}" name="國際音標" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{F9A38440-D11D-45B8-BE95-B6BB0AAAF1E3}" name="台羅拼音" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{AF657621-3918-4D23-BBFD-13EBF0B27858}" name="台語音標" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{C16CB252-C9A4-4CB2-8FDD-82813173CF4D}" name="注音二式" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{0D7F03C3-8C58-42B2-B097-C3B2A5C37034}" name="閩拼方案" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{9540CBC9-4FE3-4DE8-90B0-B77F1C52414A}" name="白話字" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{D9050C95-564C-4861-B1AE-AA03A7C3DE41}" name="方音符號" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{05251E82-C5E0-4833-BDD6-FE5DF5B1D381}" name="台語注音" dataDxfId="45"/>
+    <tableColumn id="11" xr3:uid="{315B1262-49A6-4891-8C01-10EC91043A3B}" name="十五音" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{DEEC4CA6-6FC2-4991-B54A-56DAB27197B0}" name="漢字例" dataDxfId="43"/>
+    <tableColumn id="13" xr3:uid="{C6123364-B523-47FE-9684-7560414EF39F}" name="備註" dataDxfId="42"/>
+    <tableColumn id="14" xr3:uid="{6018D2E9-8064-40AC-887E-308DB4B54742}" name="s1" dataDxfId="41"/>
+    <tableColumn id="15" xr3:uid="{C1ACEDB0-215C-486F-8C7A-D83ECFA591EB}" name="s2" dataDxfId="40"/>
+    <tableColumn id="16" xr3:uid="{E9B4DE26-B82C-4445-854F-C1B5EF3E2F79}" name="s3" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C40E26AF-4D3B-4E1A-8080-AAAFDBD9F514}" name="韻母對照表" displayName="韻母對照表" ref="A3:N89" totalsRowShown="0" headerRowDxfId="37" tableBorderDxfId="36" headerRowCellStyle="一般 4">
-  <autoFilter ref="A3:N89" xr:uid="{C40E26AF-4D3B-4E1A-8080-AAAFDBD9F514}"/>
-  <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{67434336-EDB9-486F-A543-044F4F8ED438}" name="序號" dataDxfId="35" dataCellStyle="一般 4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C40E26AF-4D3B-4E1A-8080-AAAFDBD9F514}" name="韻母對照表" displayName="韻母對照表" ref="A3:O89" totalsRowShown="0" headerRowDxfId="38" tableBorderDxfId="37" headerRowCellStyle="一般 4">
+  <autoFilter ref="A3:O89" xr:uid="{C40E26AF-4D3B-4E1A-8080-AAAFDBD9F514}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{67434336-EDB9-486F-A543-044F4F8ED438}" name="序號" dataDxfId="36" dataCellStyle="一般 4">
       <calculatedColumnFormula xml:space="preserve"> ROW() - 3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3F9C0D5C-037D-401B-9E57-7E99A8351BB7}" name="國際音標" dataDxfId="34" dataCellStyle="一般 4"/>
-    <tableColumn id="3" xr3:uid="{B8205AD7-58F1-43A8-824B-C0E88B7F29C9}" name="台羅拼音" dataDxfId="33" dataCellStyle="一般 4"/>
-    <tableColumn id="4" xr3:uid="{1D977D40-0654-4AD5-9198-DBDACA80FC0C}" name="台語音標" dataDxfId="32" dataCellStyle="一般 4"/>
-    <tableColumn id="5" xr3:uid="{62D369BE-67AE-46A8-A874-749CA8F4D5FA}" name="台語注音二式" dataDxfId="31" dataCellStyle="一般 4"/>
-    <tableColumn id="6" xr3:uid="{6ACFDCD0-A05A-4E77-B6C3-F4F9693A1A87}" name="閩拼方案" dataDxfId="30" dataCellStyle="一般 4"/>
-    <tableColumn id="7" xr3:uid="{EA72CB27-56D4-45DE-A159-5ECE3355E261}" name="白話字" dataDxfId="29" dataCellStyle="一般 4"/>
+    <tableColumn id="2" xr3:uid="{3F9C0D5C-037D-401B-9E57-7E99A8351BB7}" name="國際音標" dataDxfId="35" dataCellStyle="一般 4"/>
+    <tableColumn id="3" xr3:uid="{B8205AD7-58F1-43A8-824B-C0E88B7F29C9}" name="台羅拼音" dataDxfId="34" dataCellStyle="一般 4"/>
+    <tableColumn id="4" xr3:uid="{1D977D40-0654-4AD5-9198-DBDACA80FC0C}" name="台語音標" dataDxfId="33" dataCellStyle="一般 4"/>
+    <tableColumn id="5" xr3:uid="{62D369BE-67AE-46A8-A874-749CA8F4D5FA}" name="台語注音二式" dataDxfId="32" dataCellStyle="一般 4"/>
+    <tableColumn id="6" xr3:uid="{6ACFDCD0-A05A-4E77-B6C3-F4F9693A1A87}" name="閩拼方案" dataDxfId="31" dataCellStyle="一般 4"/>
+    <tableColumn id="7" xr3:uid="{EA72CB27-56D4-45DE-A159-5ECE3355E261}" name="白話字" dataDxfId="30" dataCellStyle="一般 4"/>
     <tableColumn id="8" xr3:uid="{86276E07-00D8-414F-A14A-89CA8E4736C0}" name="方音符號"/>
-    <tableColumn id="13" xr3:uid="{4AC7395E-4D7D-4B49-A8A4-FDDE23D368B8}" name="台語注音" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{32F912D0-78F9-4541-95B9-4330F53FB63D}" name="十五音" dataDxfId="27" dataCellStyle="一般 4">
+    <tableColumn id="13" xr3:uid="{4AC7395E-4D7D-4B49-A8A4-FDDE23D368B8}" name="台語注音" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{32F912D0-78F9-4541-95B9-4330F53FB63D}" name="十五音" dataDxfId="28" dataCellStyle="一般 4">
       <calculatedColumnFormula xml:space="preserve"> LEFT(韻母對照表[[#This Row],[十五音識別碼]],1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{E48E1AF8-9745-43AE-BEAA-41D8235123F8}" name="漢字例" dataDxfId="26" dataCellStyle="一般 4"/>
-    <tableColumn id="12" xr3:uid="{B472CE12-1F6D-4207-8742-FA9AA5B789B0}" name="十五音識別碼" dataDxfId="25" dataCellStyle="一般 4"/>
-    <tableColumn id="10" xr3:uid="{B3319D84-8B1E-4C1D-99D4-7DD8250E72D0}" name="聲韻調類" dataDxfId="24" dataCellStyle="一般 4"/>
-    <tableColumn id="11" xr3:uid="{0232C7F0-707C-4291-B834-2A92B01DFDF9}" name="字長" dataDxfId="23" dataCellStyle="一般 4">
+    <tableColumn id="14" xr3:uid="{E48E1AF8-9745-43AE-BEAA-41D8235123F8}" name="漢字例" dataDxfId="27" dataCellStyle="一般 4"/>
+    <tableColumn id="12" xr3:uid="{B472CE12-1F6D-4207-8742-FA9AA5B789B0}" name="十五音識別碼" dataDxfId="26" dataCellStyle="一般 4">
+      <calculatedColumnFormula xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{F10BEE25-E2CE-41FF-8E1C-781E5B158AA1}" name="十五音識別碼2" dataDxfId="0" dataCellStyle="一般 4"/>
+    <tableColumn id="10" xr3:uid="{B3319D84-8B1E-4C1D-99D4-7DD8250E72D0}" name="聲韻調類" dataDxfId="25" dataCellStyle="一般 4"/>
+    <tableColumn id="11" xr3:uid="{0232C7F0-707C-4291-B834-2A92B01DFDF9}" name="字長" dataDxfId="24" dataCellStyle="一般 4">
       <calculatedColumnFormula xml:space="preserve"> LEN(D4)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11759,32 +11809,32 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C448E2C-CD3D-4ED2-BDC8-5AB53B6728E4}" name="音調對照表" displayName="音調對照表" ref="H3:Q11" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C448E2C-CD3D-4ED2-BDC8-5AB53B6728E4}" name="音調對照表" displayName="音調對照表" ref="H3:Q11" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <autoFilter ref="H3:Q11" xr:uid="{9C448E2C-CD3D-4ED2-BDC8-5AB53B6728E4}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B46EBE00-929F-433A-8CEB-034D0DC6906D}" name="傳統調號" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{0DCBA03B-CD89-497B-A3E4-4BC82EA25A2B}" name="調名" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{B46EBE00-929F-433A-8CEB-034D0DC6906D}" name="傳統調號" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{0DCBA03B-CD89-497B-A3E4-4BC82EA25A2B}" name="調名" dataDxfId="18"/>
     <tableColumn id="3" xr3:uid="{6CD4E8D7-7EEB-4B3B-8880-1CDF2A3935FB}" name="調值"/>
-    <tableColumn id="4" xr3:uid="{D8F89D5C-E6DC-463B-9685-6EF0D4474D7D}" name="調性" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{173864CA-2919-4644-BE09-D21E3DBCDBB6}" name="鍵盤按鍵" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{2ADB8177-FEA4-4F0B-A85D-19BFCA65A11C}" name="台羅調符編碼" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{86A0BE39-DEE8-4157-829F-97A8B9AE7B11}" name="台羅拼音" dataDxfId="13">
+    <tableColumn id="4" xr3:uid="{D8F89D5C-E6DC-463B-9685-6EF0D4474D7D}" name="調性" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{173864CA-2919-4644-BE09-D21E3DBCDBB6}" name="鍵盤按鍵" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{2ADB8177-FEA4-4F0B-A85D-19BFCA65A11C}" name="台羅調符編碼" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{86A0BE39-DEE8-4157-829F-97A8B9AE7B11}" name="台羅拼音" dataDxfId="14">
       <calculatedColumnFormula xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", IF($M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT($M4,4))))), "")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E6B4918A-DB73-4B67-94C1-81C2CD076534}" name="閩拼調符編碼" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{096D159D-6004-4E03-ABF1-3B8DF0B4C5E8}" name="閩拼方案" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{CD3469B2-531A-472E-830D-AD6482D31514}" name="閩拼調號" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{E6B4918A-DB73-4B67-94C1-81C2CD076534}" name="閩拼調符編碼" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{096D159D-6004-4E03-ABF1-3B8DF0B4C5E8}" name="閩拼方案" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{CD3469B2-531A-472E-830D-AD6482D31514}" name="閩拼調號" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{05BDFC42-94AA-4826-923D-BD9331E1250D}" name="上標對照表" displayName="上標對照表" ref="H13:I23" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{05BDFC42-94AA-4826-923D-BD9331E1250D}" name="上標對照表" displayName="上標對照表" ref="H13:I23" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="H13:I23" xr:uid="{05BDFC42-94AA-4826-923D-BD9331E1250D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3CC41888-DBE7-432A-92DC-605976F668C4}" name="調號" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{0B0EA5BF-5331-4F4D-9FAF-76DE29BBAABD}" name="上標值" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{3CC41888-DBE7-432A-92DC-605976F668C4}" name="調號" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{0B0EA5BF-5331-4F4D-9FAF-76DE29BBAABD}" name="上標值" dataDxfId="5">
       <calculatedColumnFormula>IFERROR(_xlfn.UNICHAR(CHOOSE($H14+1,8304,185,178,179,8308,8309,8310,8311,8312,8313)),"")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12602,7 +12652,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41FE6F7-1F1E-408C-ABA8-5C2E8953D0A0}">
-  <dimension ref="A2:AX101"/>
+  <dimension ref="A2:AY101"/>
   <sheetFormatPr defaultRowHeight="26.25" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="5.83203125" style="15" customWidth="1"/>
@@ -12610,28 +12660,28 @@
     <col min="5" max="5" width="13.83203125" style="15" customWidth="1" outlineLevel="1"/>
     <col min="6" max="7" width="10.25" style="15" customWidth="1" outlineLevel="1"/>
     <col min="8" max="11" width="10.25" style="15" customWidth="1"/>
-    <col min="12" max="12" width="10.25" style="15" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="10.25" style="15" customWidth="1"/>
-    <col min="14" max="14" width="5.83203125" style="15" customWidth="1"/>
-    <col min="15" max="15" width="4.9140625" style="15" customWidth="1"/>
-    <col min="16" max="17" width="10.08203125" style="15" customWidth="1"/>
-    <col min="18" max="18" width="1.9140625" style="15" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" style="47" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6" style="50" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="6.1640625" style="50" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="22" width="11.1640625" style="47" customWidth="1"/>
-    <col min="23" max="23" width="3" style="15" customWidth="1"/>
-    <col min="24" max="24" width="34.5" style="48" customWidth="1"/>
-    <col min="25" max="25" width="8.6640625" style="15"/>
-    <col min="26" max="37" width="5" style="55" customWidth="1"/>
-    <col min="38" max="43" width="12.9140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="44" max="46" width="13.25" style="59" customWidth="1"/>
-    <col min="47" max="47" width="13.25" style="15" customWidth="1"/>
-    <col min="48" max="16384" width="8.6640625" style="15"/>
+    <col min="12" max="13" width="10.25" style="15" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="10.25" style="15" customWidth="1"/>
+    <col min="15" max="15" width="5.83203125" style="15" customWidth="1"/>
+    <col min="16" max="16" width="4.9140625" style="15" customWidth="1"/>
+    <col min="17" max="18" width="10.08203125" style="15" customWidth="1"/>
+    <col min="19" max="19" width="1.9140625" style="15" customWidth="1"/>
+    <col min="20" max="20" width="9.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6" style="50" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="6.1640625" style="50" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="11.1640625" style="47" customWidth="1"/>
+    <col min="24" max="24" width="3" style="15" customWidth="1"/>
+    <col min="25" max="25" width="34.5" style="48" customWidth="1"/>
+    <col min="26" max="26" width="8.6640625" style="15"/>
+    <col min="27" max="38" width="5" style="55" customWidth="1"/>
+    <col min="39" max="44" width="12.9140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="13.25" style="59" customWidth="1"/>
+    <col min="48" max="48" width="13.25" style="15" customWidth="1"/>
+    <col min="49" max="16384" width="8.6640625" style="15"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:50" ht="27" thickBot="1"/>
-    <row r="3" spans="1:50" ht="54.75" thickBot="1">
+    <row r="2" spans="1:51" ht="27" thickBot="1"/>
+    <row r="3" spans="1:51" ht="54.75" thickBot="1">
       <c r="A3" s="100" t="s">
         <v>702</v>
       </c>
@@ -12669,60 +12719,63 @@
         <v>2227</v>
       </c>
       <c r="M3" s="22" t="s">
+        <v>2425</v>
+      </c>
+      <c r="N3" s="22" t="s">
         <v>1090</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="O3" s="22" t="s">
         <v>703</v>
       </c>
-      <c r="O3" s="17"/>
-      <c r="P3" s="22" t="s">
+      <c r="P3" s="17"/>
+      <c r="Q3" s="22" t="s">
         <v>637</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="R3" s="22" t="s">
         <v>629</v>
       </c>
-      <c r="S3" s="22" t="s">
+      <c r="T3" s="22" t="s">
         <v>637</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="U3" s="16" t="s">
         <v>1085</v>
       </c>
-      <c r="U3" s="53" t="s">
+      <c r="V3" s="53" t="s">
         <v>1083</v>
       </c>
-      <c r="V3" s="22" t="s">
+      <c r="W3" s="22" t="s">
         <v>629</v>
       </c>
-      <c r="X3" s="16"/>
-      <c r="Z3" s="54"/>
-      <c r="AB3" s="57" t="s">
+      <c r="Y3" s="16"/>
+      <c r="AA3" s="54"/>
+      <c r="AC3" s="57" t="s">
         <v>631</v>
       </c>
-      <c r="AC3" s="57" t="s">
+      <c r="AD3" s="57" t="s">
         <v>1088</v>
       </c>
-      <c r="AD3" s="57"/>
-      <c r="AE3" s="57" t="s">
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="57" t="s">
         <v>641</v>
       </c>
-      <c r="AF3" s="57" t="s">
+      <c r="AG3" s="57" t="s">
         <v>636</v>
       </c>
-      <c r="AG3" s="57" t="s">
+      <c r="AH3" s="57" t="s">
         <v>630</v>
       </c>
-      <c r="AH3" s="57" t="s">
+      <c r="AI3" s="57" t="s">
         <v>1089</v>
       </c>
-      <c r="AI3" s="57" t="s">
+      <c r="AJ3" s="57" t="s">
         <v>634</v>
       </c>
-      <c r="AJ3" s="57" t="s">
+      <c r="AK3" s="57" t="s">
         <v>633</v>
       </c>
-      <c r="AK3" s="56"/>
-    </row>
-    <row r="4" spans="1:50" ht="27.75" thickBot="1">
+      <c r="AL3" s="56"/>
+    </row>
+    <row r="4" spans="1:51" ht="27.75" thickBot="1">
       <c r="A4" s="101">
         <f xml:space="preserve"> ROW() - 3</f>
         <v>1</v>
@@ -12758,130 +12811,134 @@
       <c r="K4" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>膠（舒）</v>
+      </c>
+      <c r="M4" s="221" t="s">
         <v>319</v>
       </c>
-      <c r="N4" s="18">
-        <f t="shared" ref="N4:N52" si="0" xml:space="preserve"> LEN(D4)</f>
+      <c r="O4" s="18">
+        <f t="shared" ref="O4:O52" si="0" xml:space="preserve"> LEN(D4)</f>
         <v>1</v>
       </c>
-      <c r="O4" s="26"/>
-      <c r="P4" s="21" t="str">
-        <f t="shared" ref="P4:P14" si="1">C4</f>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="21" t="str">
+        <f t="shared" ref="Q4:Q14" si="1">C4</f>
         <v>a</v>
       </c>
-      <c r="Q4" s="21" t="str">
-        <f t="shared" ref="Q4:Q14" si="2">D4</f>
+      <c r="R4" s="21" t="str">
+        <f t="shared" ref="R4:R14" si="2">D4</f>
         <v>a</v>
       </c>
-      <c r="S4" s="47" t="str">
-        <f t="shared" ref="S4:S13" si="3" xml:space="preserve"> _xlfn.CONCAT(P4, "(\d)")</f>
+      <c r="T4" s="47" t="str">
+        <f t="shared" ref="T4:T13" si="3" xml:space="preserve"> _xlfn.CONCAT(Q4, "(\d)")</f>
         <v>a(\d)</v>
       </c>
-      <c r="T4" s="50" t="s">
+      <c r="U4" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U4" s="50">
-        <f t="shared" ref="U4:U13" si="4" xml:space="preserve"> IFERROR( IF(T4="", "", SEARCH(T4, $P4)), "")</f>
+      <c r="V4" s="50">
+        <f t="shared" ref="V4:V13" si="4" xml:space="preserve"> IFERROR( IF(U4="", "", SEARCH(U4, $Q4)), "")</f>
         <v>1</v>
       </c>
-      <c r="V4" s="47" t="str">
-        <f t="shared" ref="V4:V13" si="5" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P4,U4-1), "》", MID(P4,U4,1), "${1}", RIGHT(P4, LEN(P4)-U4)), "" )</f>
+      <c r="W4" s="47" t="str">
+        <f t="shared" ref="W4:W13" si="5" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q4,V4-1), "》", MID(Q4,V4,1), "${1}", RIGHT(Q4, LEN(Q4)-V4)), "" )</f>
         <v>》a${1}</v>
       </c>
-      <c r="W4" s="19"/>
-      <c r="X4" s="20" t="str">
-        <f t="shared" ref="X4:X13" si="6" xml:space="preserve"> IF(AND(Q4&lt;&gt;"", P4&lt;&gt;""), "    - xform/》" &amp; S4 &amp;  "/"  &amp; V4 &amp;  "/", "")</f>
+      <c r="X4" s="19"/>
+      <c r="Y4" s="20" t="str">
+        <f t="shared" ref="Y4:Y13" si="6" xml:space="preserve"> IF(AND(R4&lt;&gt;"", Q4&lt;&gt;""), "    - xform/》" &amp; T4 &amp;  "/"  &amp; W4 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》a(\d)/》a${1}/</v>
       </c>
-      <c r="Z4" s="55" t="s">
+      <c r="AA4" s="55" t="s">
         <v>1028</v>
       </c>
-      <c r="AA4" s="58" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT($Z4, IF(AA$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(AA$3,4)))))</f>
+      <c r="AB4" s="58" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($AA4, IF(AB$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(AB$3,4)))))</f>
         <v>a</v>
       </c>
-      <c r="AB4" s="58" t="str">
-        <f t="shared" ref="AB4:AJ4" si="7" xml:space="preserve"> _xlfn.CONCAT($Z4, IF(AB$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(AB$3,4)))))</f>
+      <c r="AC4" s="58" t="str">
+        <f t="shared" ref="AC4:AK4" si="7" xml:space="preserve"> _xlfn.CONCAT($AA4, IF(AC$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(AC$3,4)))))</f>
         <v>á</v>
       </c>
-      <c r="AC4" s="58" t="str">
+      <c r="AD4" s="58" t="str">
         <f t="shared" si="7"/>
         <v>à</v>
       </c>
-      <c r="AD4" s="58" t="str">
+      <c r="AE4" s="58" t="str">
         <f t="shared" si="7"/>
         <v>a</v>
       </c>
-      <c r="AE4" s="58" t="str">
+      <c r="AF4" s="58" t="str">
         <f t="shared" si="7"/>
         <v>ǎ</v>
       </c>
-      <c r="AF4" s="58" t="str">
+      <c r="AG4" s="58" t="str">
         <f t="shared" si="7"/>
         <v>á</v>
       </c>
-      <c r="AG4" s="58" t="str">
+      <c r="AH4" s="58" t="str">
         <f t="shared" si="7"/>
         <v>ā</v>
       </c>
-      <c r="AH4" s="58" t="str">
+      <c r="AI4" s="58" t="str">
         <f t="shared" si="7"/>
         <v>a̍</v>
       </c>
-      <c r="AI4" s="58" t="str">
+      <c r="AJ4" s="58" t="str">
         <f t="shared" si="7"/>
         <v>a̋</v>
       </c>
-      <c r="AJ4" s="58" t="str">
+      <c r="AK4" s="58" t="str">
         <f t="shared" si="7"/>
         <v>å</v>
       </c>
-      <c r="AL4" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z4, 【調】韻母標調!AJ$1, "/", AA4, "/")</f>
+      <c r="AM4" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA4, 【調】韻母標調!AJ$1, "/", AB4, "/")</f>
         <v xml:space="preserve">    - xform/》a1/a/</v>
       </c>
-      <c r="AM4" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z4, 【調】韻母標調!AK$1, "/", AB4, "/")</f>
+      <c r="AN4" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA4, 【調】韻母標調!AK$1, "/", AC4, "/")</f>
         <v xml:space="preserve">    - xform/》a2/á/</v>
       </c>
-      <c r="AN4" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z4, 【調】韻母標調!AL$1, "/", AC4, "/")</f>
+      <c r="AO4" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA4, 【調】韻母標調!AL$1, "/", AD4, "/")</f>
         <v xml:space="preserve">    - xform/》a3/à/</v>
       </c>
-      <c r="AO4" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z4, 【調】韻母標調!AM$1, "/", AD4, "/")</f>
+      <c r="AP4" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA4, 【調】韻母標調!AM$1, "/", AE4, "/")</f>
         <v xml:space="preserve">    - xform/》a4/a/</v>
       </c>
-      <c r="AP4" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z4, 【調】韻母標調!AN$1, "/", AE4, "/")</f>
+      <c r="AQ4" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA4, 【調】韻母標調!AN$1, "/", AF4, "/")</f>
         <v xml:space="preserve">    - xform/》a5/ǎ/</v>
       </c>
-      <c r="AQ4" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z4, 【調】韻母標調!AO$1, "/", AF4, "/")</f>
+      <c r="AR4" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA4, 【調】韻母標調!AO$1, "/", AG4, "/")</f>
         <v xml:space="preserve">    - xform/》a6/á/</v>
       </c>
-      <c r="AR4" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z4, 【調】韻母標調!AP$1, "/", AG4, "/")</f>
+      <c r="AS4" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA4, 【調】韻母標調!AP$1, "/", AH4, "/")</f>
         <v xml:space="preserve">    - xform/》a7/ā/</v>
       </c>
-      <c r="AS4" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z4, 【調】韻母標調!AQ$1, "/", AH4, "/")</f>
+      <c r="AT4" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA4, 【調】韻母標調!AQ$1, "/", AI4, "/")</f>
         <v xml:space="preserve">    - xform/》a8/a̍/</v>
       </c>
-      <c r="AT4" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z4, 【調】韻母標調!AR$1, "/", AI4, "/")</f>
+      <c r="AU4" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA4, 【調】韻母標調!AR$1, "/", AJ4, "/")</f>
         <v xml:space="preserve">    - xform/》a9/a̋/</v>
       </c>
-      <c r="AU4" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z4, 【調】韻母標調!AS$1, "/", AJ4, "/")</f>
+      <c r="AV4" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA4, 【調】韻母標調!AS$1, "/", AK4, "/")</f>
         <v xml:space="preserve">    - xform/》a9/å/</v>
       </c>
-      <c r="AV4" s="58"/>
       <c r="AW4" s="58"/>
-      <c r="AX4" s="55"/>
-    </row>
-    <row r="5" spans="1:50" ht="27.75" thickBot="1">
+      <c r="AX4" s="58"/>
+      <c r="AY4" s="55"/>
+    </row>
+    <row r="5" spans="1:51" ht="27.75" thickBot="1">
       <c r="A5" s="101">
         <f t="shared" ref="A5:A89" si="8" xml:space="preserve"> ROW() - 3</f>
         <v>2</v>
@@ -12917,131 +12974,135 @@
       <c r="K5" s="18" t="s">
         <v>320</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>膠（促）</v>
+      </c>
+      <c r="M5" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="M5" s="21"/>
-      <c r="N5" s="18">
-        <f t="shared" ref="N5:N13" si="9" xml:space="preserve"> LEN(D5)</f>
+      <c r="N5" s="21"/>
+      <c r="O5" s="18">
+        <f t="shared" ref="O5:O13" si="9" xml:space="preserve"> LEN(D5)</f>
         <v>2</v>
       </c>
-      <c r="O5" s="26"/>
-      <c r="P5" s="21" t="str">
-        <f t="shared" ref="P5:P13" si="10">C5</f>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="21" t="str">
+        <f t="shared" ref="Q5:Q13" si="10">C5</f>
         <v>ah</v>
       </c>
-      <c r="Q5" s="21" t="str">
+      <c r="R5" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ah</v>
       </c>
-      <c r="S5" s="47" t="str">
+      <c r="T5" s="47" t="str">
         <f t="shared" si="3"/>
         <v>ah(\d)</v>
       </c>
-      <c r="T5" s="50" t="s">
+      <c r="U5" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U5" s="50">
+      <c r="V5" s="50">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="V5" s="47" t="str">
+      <c r="W5" s="47" t="str">
         <f t="shared" si="5"/>
         <v>》a${1}h</v>
       </c>
-      <c r="W5" s="19"/>
-      <c r="X5" s="20" t="str">
+      <c r="X5" s="19"/>
+      <c r="Y5" s="20" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/》ah(\d)/》a${1}h/</v>
       </c>
-      <c r="Z5" s="55" t="s">
+      <c r="AA5" s="55" t="s">
         <v>1027</v>
       </c>
-      <c r="AA5" s="58" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT($Z5, IF(AA$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(AA$3,4)))))</f>
+      <c r="AB5" s="58" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($AA5, IF(AB$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(AB$3,4)))))</f>
         <v>u</v>
       </c>
-      <c r="AB5" s="58" t="str">
-        <f t="shared" ref="AB5:AJ5" si="11" xml:space="preserve"> _xlfn.CONCAT($Z5, IF(AB$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(AB$3,4)))))</f>
+      <c r="AC5" s="58" t="str">
+        <f t="shared" ref="AC5:AK5" si="11" xml:space="preserve"> _xlfn.CONCAT($AA5, IF(AC$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(AC$3,4)))))</f>
         <v>ú</v>
       </c>
-      <c r="AC5" s="58" t="str">
+      <c r="AD5" s="58" t="str">
         <f t="shared" si="11"/>
         <v>ù</v>
       </c>
-      <c r="AD5" s="58" t="str">
+      <c r="AE5" s="58" t="str">
         <f t="shared" si="11"/>
         <v>u</v>
       </c>
-      <c r="AE5" s="58" t="str">
+      <c r="AF5" s="58" t="str">
         <f t="shared" si="11"/>
         <v>ǔ</v>
       </c>
-      <c r="AF5" s="58" t="str">
+      <c r="AG5" s="58" t="str">
         <f t="shared" si="11"/>
         <v>ú</v>
       </c>
-      <c r="AG5" s="58" t="str">
+      <c r="AH5" s="58" t="str">
         <f t="shared" si="11"/>
         <v>ū</v>
       </c>
-      <c r="AH5" s="58" t="str">
+      <c r="AI5" s="58" t="str">
         <f t="shared" si="11"/>
         <v>u̍</v>
       </c>
-      <c r="AI5" s="58" t="str">
+      <c r="AJ5" s="58" t="str">
         <f t="shared" si="11"/>
         <v>ű</v>
       </c>
-      <c r="AJ5" s="58" t="str">
+      <c r="AK5" s="58" t="str">
         <f t="shared" si="11"/>
         <v>ů</v>
       </c>
-      <c r="AL5" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z5, 【調】韻母標調!AJ$1, "/", AA5, "/")</f>
+      <c r="AM5" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA5, 【調】韻母標調!AJ$1, "/", AB5, "/")</f>
         <v xml:space="preserve">    - xform/》u1/u/</v>
       </c>
-      <c r="AM5" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z5, 【調】韻母標調!AK$1, "/", AB5, "/")</f>
+      <c r="AN5" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA5, 【調】韻母標調!AK$1, "/", AC5, "/")</f>
         <v xml:space="preserve">    - xform/》u2/ú/</v>
       </c>
-      <c r="AN5" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z5, 【調】韻母標調!AL$1, "/", AC5, "/")</f>
+      <c r="AO5" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA5, 【調】韻母標調!AL$1, "/", AD5, "/")</f>
         <v xml:space="preserve">    - xform/》u3/ù/</v>
       </c>
-      <c r="AO5" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z5, 【調】韻母標調!AM$1, "/", AD5, "/")</f>
+      <c r="AP5" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA5, 【調】韻母標調!AM$1, "/", AE5, "/")</f>
         <v xml:space="preserve">    - xform/》u4/u/</v>
       </c>
-      <c r="AP5" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z5, 【調】韻母標調!AN$1, "/", AE5, "/")</f>
+      <c r="AQ5" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA5, 【調】韻母標調!AN$1, "/", AF5, "/")</f>
         <v xml:space="preserve">    - xform/》u5/ǔ/</v>
       </c>
-      <c r="AQ5" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z5, 【調】韻母標調!AO$1, "/", AF5, "/")</f>
+      <c r="AR5" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA5, 【調】韻母標調!AO$1, "/", AG5, "/")</f>
         <v xml:space="preserve">    - xform/》u6/ú/</v>
       </c>
-      <c r="AR5" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z5, 【調】韻母標調!AP$1, "/", AG5, "/")</f>
+      <c r="AS5" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA5, 【調】韻母標調!AP$1, "/", AH5, "/")</f>
         <v xml:space="preserve">    - xform/》u7/ū/</v>
       </c>
-      <c r="AS5" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z5, 【調】韻母標調!AQ$1, "/", AH5, "/")</f>
+      <c r="AT5" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA5, 【調】韻母標調!AQ$1, "/", AI5, "/")</f>
         <v xml:space="preserve">    - xform/》u8/u̍/</v>
       </c>
-      <c r="AT5" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z5, 【調】韻母標調!AR$1, "/", AI5, "/")</f>
+      <c r="AU5" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA5, 【調】韻母標調!AR$1, "/", AJ5, "/")</f>
         <v xml:space="preserve">    - xform/》u9/ű/</v>
       </c>
-      <c r="AU5" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z5, 【調】韻母標調!AS$1, "/", AJ5, "/")</f>
+      <c r="AV5" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA5, 【調】韻母標調!AS$1, "/", AK5, "/")</f>
         <v xml:space="preserve">    - xform/》u9/ů/</v>
       </c>
-      <c r="AV5" s="58"/>
       <c r="AW5" s="58"/>
-      <c r="AX5" s="55"/>
-    </row>
-    <row r="6" spans="1:50" ht="27.75" thickBot="1">
+      <c r="AX5" s="58"/>
+      <c r="AY5" s="55"/>
+    </row>
+    <row r="6" spans="1:51" ht="27.75" thickBot="1">
       <c r="A6" s="101">
         <f t="shared" si="8"/>
         <v>3</v>
@@ -13077,45 +13138,49 @@
       <c r="K6" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>皆（舒）</v>
+      </c>
+      <c r="M6" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="M6" s="21"/>
-      <c r="N6" s="18">
+      <c r="N6" s="21"/>
+      <c r="O6" s="18">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="O6" s="26"/>
-      <c r="P6" s="21" t="str">
+      <c r="P6" s="26"/>
+      <c r="Q6" s="21" t="str">
         <f t="shared" si="10"/>
         <v>ai</v>
       </c>
-      <c r="Q6" s="21" t="str">
+      <c r="R6" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ai</v>
       </c>
-      <c r="S6" s="47" t="str">
+      <c r="T6" s="47" t="str">
         <f t="shared" si="3"/>
         <v>ai(\d)</v>
       </c>
-      <c r="T6" s="50" t="s">
+      <c r="U6" s="50" t="s">
         <v>1016</v>
       </c>
-      <c r="U6" s="50" t="str">
+      <c r="V6" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="V6" s="47" t="str">
+      <c r="W6" s="47" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="W6" s="19"/>
-      <c r="X6" s="20" t="str">
+      <c r="X6" s="19"/>
+      <c r="Y6" s="20" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/》ai(\d)//</v>
       </c>
     </row>
-    <row r="7" spans="1:50" ht="30.75" thickBot="1">
+    <row r="7" spans="1:51" ht="30.75" thickBot="1">
       <c r="A7" s="101">
         <f t="shared" si="8"/>
         <v>4</v>
@@ -13151,45 +13216,49 @@
       <c r="K7" s="18" t="s">
         <v>2071</v>
       </c>
-      <c r="L7" s="70" t="s">
+      <c r="L7" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>皆（促）</v>
+      </c>
+      <c r="M7" s="70" t="s">
         <v>1948</v>
       </c>
-      <c r="M7" s="21"/>
-      <c r="N7" s="18">
+      <c r="N7" s="21"/>
+      <c r="O7" s="18">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="O7" s="26"/>
-      <c r="P7" s="21" t="str">
+      <c r="P7" s="26"/>
+      <c r="Q7" s="21" t="str">
         <f t="shared" si="10"/>
         <v>aih</v>
       </c>
-      <c r="Q7" s="21" t="str">
+      <c r="R7" s="21" t="str">
         <f t="shared" si="2"/>
         <v>aih</v>
       </c>
-      <c r="S7" s="47" t="str">
+      <c r="T7" s="47" t="str">
         <f t="shared" si="3"/>
         <v>aih(\d)</v>
       </c>
-      <c r="T7" s="50" t="s">
+      <c r="U7" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U7" s="50">
+      <c r="V7" s="50">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="V7" s="47" t="str">
+      <c r="W7" s="47" t="str">
         <f t="shared" si="5"/>
         <v>》a${1}ih</v>
       </c>
-      <c r="W7" s="19"/>
-      <c r="X7" s="20" t="str">
+      <c r="X7" s="19"/>
+      <c r="Y7" s="20" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/》aih(\d)/》a${1}ih/</v>
       </c>
     </row>
-    <row r="8" spans="1:50" ht="27.75" thickBot="1">
+    <row r="8" spans="1:51" ht="27.75" thickBot="1">
       <c r="A8" s="101">
         <f t="shared" si="8"/>
         <v>5</v>
@@ -13225,47 +13294,51 @@
       <c r="K8" s="18" t="s">
         <v>414</v>
       </c>
-      <c r="L8" s="18" t="s">
+      <c r="L8" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>閒（舒）</v>
+      </c>
+      <c r="M8" s="18" t="s">
         <v>420</v>
       </c>
-      <c r="M8" s="61" t="s">
+      <c r="N8" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N8" s="18">
+      <c r="O8" s="18">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="O8" s="26"/>
-      <c r="P8" s="21" t="str">
+      <c r="P8" s="26"/>
+      <c r="Q8" s="21" t="str">
         <f t="shared" si="10"/>
         <v>ainn</v>
       </c>
-      <c r="Q8" s="21" t="str">
+      <c r="R8" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ainn</v>
       </c>
-      <c r="S8" s="47" t="str">
+      <c r="T8" s="47" t="str">
         <f t="shared" si="3"/>
         <v>ainn(\d)</v>
       </c>
-      <c r="T8" s="50" t="s">
+      <c r="U8" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U8" s="50">
+      <c r="V8" s="50">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="V8" s="47" t="str">
+      <c r="W8" s="47" t="str">
         <f t="shared" si="5"/>
         <v>》a${1}inn</v>
       </c>
-      <c r="W8" s="19"/>
-      <c r="X8" s="20" t="str">
+      <c r="X8" s="19"/>
+      <c r="Y8" s="20" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/》ainn(\d)/》a${1}inn/</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="30.75" thickBot="1">
+    <row r="9" spans="1:51" ht="30.75" thickBot="1">
       <c r="A9" s="101">
         <f t="shared" si="8"/>
         <v>6</v>
@@ -13302,45 +13375,49 @@
       <c r="K9" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="L9" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>江（促）</v>
+      </c>
+      <c r="M9" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="M9" s="21"/>
-      <c r="N9" s="18">
+      <c r="N9" s="21"/>
+      <c r="O9" s="18">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="O9" s="26"/>
-      <c r="P9" s="21" t="str">
+      <c r="P9" s="26"/>
+      <c r="Q9" s="21" t="str">
         <f t="shared" si="10"/>
         <v>ak</v>
       </c>
-      <c r="Q9" s="21" t="str">
+      <c r="R9" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ak</v>
       </c>
-      <c r="S9" s="47" t="str">
+      <c r="T9" s="47" t="str">
         <f t="shared" si="3"/>
         <v>ak(\d)</v>
       </c>
-      <c r="T9" s="50" t="s">
+      <c r="U9" s="50" t="s">
         <v>981</v>
       </c>
-      <c r="U9" s="50" t="str">
+      <c r="V9" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="V9" s="47" t="str">
+      <c r="W9" s="47" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="W9" s="19"/>
-      <c r="X9" s="20" t="str">
+      <c r="X9" s="19"/>
+      <c r="Y9" s="20" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/》ak(\d)//</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="27.75" thickBot="1">
+    <row r="10" spans="1:51" ht="27.75" thickBot="1">
       <c r="A10" s="101">
         <f t="shared" si="8"/>
         <v>7</v>
@@ -13376,131 +13453,135 @@
       <c r="K10" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="L10" s="18" t="s">
+      <c r="L10" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>甘（舒）</v>
+      </c>
+      <c r="M10" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="M10" s="21"/>
-      <c r="N10" s="18">
+      <c r="N10" s="21"/>
+      <c r="O10" s="18">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="O10" s="26"/>
-      <c r="P10" s="21" t="str">
+      <c r="P10" s="26"/>
+      <c r="Q10" s="21" t="str">
         <f t="shared" si="10"/>
         <v>am</v>
       </c>
-      <c r="Q10" s="21" t="str">
+      <c r="R10" s="21" t="str">
         <f t="shared" si="2"/>
         <v>am</v>
       </c>
-      <c r="S10" s="47" t="str">
+      <c r="T10" s="47" t="str">
         <f t="shared" si="3"/>
         <v>am(\d)</v>
       </c>
-      <c r="T10" s="50" t="s">
+      <c r="U10" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U10" s="50">
+      <c r="V10" s="50">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="V10" s="47" t="str">
+      <c r="W10" s="47" t="str">
         <f t="shared" si="5"/>
         <v>》a${1}m</v>
       </c>
-      <c r="W10" s="19"/>
-      <c r="X10" s="20" t="str">
+      <c r="X10" s="19"/>
+      <c r="Y10" s="20" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/》am(\d)/》a${1}m/</v>
       </c>
-      <c r="Z10" s="55" t="s">
+      <c r="AA10" s="55" t="s">
         <v>1016</v>
       </c>
-      <c r="AA10" s="58" t="str">
-        <f t="shared" ref="AA10:AJ13" si="12" xml:space="preserve"> _xlfn.CONCAT($Z10, IF(AA$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(AA$3,4)))))</f>
+      <c r="AB10" s="58" t="str">
+        <f t="shared" ref="AB10:AK13" si="12" xml:space="preserve"> _xlfn.CONCAT($AA10, IF(AB$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(AB$3,4)))))</f>
         <v>o</v>
       </c>
-      <c r="AB10" s="58" t="str">
+      <c r="AC10" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ó</v>
       </c>
-      <c r="AC10" s="58" t="str">
+      <c r="AD10" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ò</v>
       </c>
-      <c r="AD10" s="58" t="str">
+      <c r="AE10" s="58" t="str">
         <f t="shared" si="12"/>
         <v>o</v>
       </c>
-      <c r="AE10" s="58" t="str">
+      <c r="AF10" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ǒ</v>
       </c>
-      <c r="AF10" s="58" t="str">
+      <c r="AG10" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ó</v>
       </c>
-      <c r="AG10" s="58" t="str">
+      <c r="AH10" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ō</v>
       </c>
-      <c r="AH10" s="58" t="str">
+      <c r="AI10" s="58" t="str">
         <f t="shared" si="12"/>
         <v>o̍</v>
       </c>
-      <c r="AI10" s="58" t="str">
+      <c r="AJ10" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ő</v>
       </c>
-      <c r="AJ10" s="58" t="str">
+      <c r="AK10" s="58" t="str">
         <f t="shared" si="12"/>
         <v>o̊</v>
       </c>
-      <c r="AL10" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z10, 【調】韻母標調!AJ$1, "/", AA10, "/")</f>
+      <c r="AM10" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA10, 【調】韻母標調!AJ$1, "/", AB10, "/")</f>
         <v xml:space="preserve">    - xform/》o1/o/</v>
       </c>
-      <c r="AM10" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z10, 【調】韻母標調!AK$1, "/", AB10, "/")</f>
+      <c r="AN10" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA10, 【調】韻母標調!AK$1, "/", AC10, "/")</f>
         <v xml:space="preserve">    - xform/》o2/ó/</v>
       </c>
-      <c r="AN10" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z10, 【調】韻母標調!AL$1, "/", AC10, "/")</f>
+      <c r="AO10" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA10, 【調】韻母標調!AL$1, "/", AD10, "/")</f>
         <v xml:space="preserve">    - xform/》o3/ò/</v>
       </c>
-      <c r="AO10" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z10, 【調】韻母標調!AM$1, "/", AD10, "/")</f>
+      <c r="AP10" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA10, 【調】韻母標調!AM$1, "/", AE10, "/")</f>
         <v xml:space="preserve">    - xform/》o4/o/</v>
       </c>
-      <c r="AP10" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z10, 【調】韻母標調!AN$1, "/", AE10, "/")</f>
+      <c r="AQ10" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA10, 【調】韻母標調!AN$1, "/", AF10, "/")</f>
         <v xml:space="preserve">    - xform/》o5/ǒ/</v>
       </c>
-      <c r="AQ10" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z10, 【調】韻母標調!AO$1, "/", AF10, "/")</f>
+      <c r="AR10" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA10, 【調】韻母標調!AO$1, "/", AG10, "/")</f>
         <v xml:space="preserve">    - xform/》o6/ó/</v>
       </c>
-      <c r="AR10" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z10, 【調】韻母標調!AP$1, "/", AG10, "/")</f>
+      <c r="AS10" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA10, 【調】韻母標調!AP$1, "/", AH10, "/")</f>
         <v xml:space="preserve">    - xform/》o7/ō/</v>
       </c>
-      <c r="AS10" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z10, 【調】韻母標調!AQ$1, "/", AH10, "/")</f>
+      <c r="AT10" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA10, 【調】韻母標調!AQ$1, "/", AI10, "/")</f>
         <v xml:space="preserve">    - xform/》o8/o̍/</v>
       </c>
-      <c r="AT10" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z10, 【調】韻母標調!AR$1, "/", AI10, "/")</f>
+      <c r="AU10" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA10, 【調】韻母標調!AR$1, "/", AJ10, "/")</f>
         <v xml:space="preserve">    - xform/》o9/ő/</v>
       </c>
-      <c r="AU10" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z10, 【調】韻母標調!AS$1, "/", AJ10, "/")</f>
+      <c r="AV10" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA10, 【調】韻母標調!AS$1, "/", AK10, "/")</f>
         <v xml:space="preserve">    - xform/》o9/o̊/</v>
       </c>
-      <c r="AV10" s="58"/>
       <c r="AW10" s="58"/>
-      <c r="AX10" s="55"/>
-    </row>
-    <row r="11" spans="1:50" ht="27.75" thickBot="1">
+      <c r="AX10" s="58"/>
+      <c r="AY10" s="55"/>
+    </row>
+    <row r="11" spans="1:51" ht="27.75" thickBot="1">
       <c r="A11" s="101">
         <f t="shared" si="8"/>
         <v>8</v>
@@ -13536,131 +13617,135 @@
       <c r="K11" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="L11" s="18" t="s">
+      <c r="L11" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>干（舒）</v>
+      </c>
+      <c r="M11" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="M11" s="21"/>
-      <c r="N11" s="18">
+      <c r="N11" s="21"/>
+      <c r="O11" s="18">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="O11" s="26"/>
-      <c r="P11" s="21" t="str">
+      <c r="P11" s="26"/>
+      <c r="Q11" s="21" t="str">
         <f t="shared" si="10"/>
         <v>an</v>
       </c>
-      <c r="Q11" s="21" t="str">
+      <c r="R11" s="21" t="str">
         <f t="shared" si="2"/>
         <v>an</v>
       </c>
-      <c r="S11" s="47" t="str">
+      <c r="T11" s="47" t="str">
         <f t="shared" si="3"/>
         <v>an(\d)</v>
       </c>
-      <c r="T11" s="50" t="s">
+      <c r="U11" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U11" s="50">
+      <c r="V11" s="50">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="V11" s="47" t="str">
+      <c r="W11" s="47" t="str">
         <f t="shared" si="5"/>
         <v>》a${1}n</v>
       </c>
-      <c r="W11" s="19"/>
-      <c r="X11" s="20" t="str">
+      <c r="X11" s="19"/>
+      <c r="Y11" s="20" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/》an(\d)/》a${1}n/</v>
       </c>
-      <c r="Z11" s="55" t="s">
+      <c r="AA11" s="55" t="s">
         <v>1087</v>
       </c>
-      <c r="AA11" s="58" t="str">
+      <c r="AB11" s="58" t="str">
         <f t="shared" si="12"/>
         <v>m</v>
       </c>
-      <c r="AB11" s="58" t="str">
+      <c r="AC11" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ḿ</v>
       </c>
-      <c r="AC11" s="58" t="str">
+      <c r="AD11" s="58" t="str">
         <f t="shared" si="12"/>
         <v>m̀</v>
       </c>
-      <c r="AD11" s="58" t="str">
+      <c r="AE11" s="58" t="str">
         <f t="shared" si="12"/>
         <v>m</v>
       </c>
-      <c r="AE11" s="58" t="str">
+      <c r="AF11" s="58" t="str">
         <f t="shared" si="12"/>
         <v>m̌</v>
       </c>
-      <c r="AF11" s="58" t="str">
+      <c r="AG11" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ḿ</v>
       </c>
-      <c r="AG11" s="58" t="str">
+      <c r="AH11" s="58" t="str">
         <f t="shared" si="12"/>
         <v>m̄</v>
       </c>
-      <c r="AH11" s="58" t="str">
+      <c r="AI11" s="58" t="str">
         <f t="shared" si="12"/>
         <v>m̍</v>
       </c>
-      <c r="AI11" s="58" t="str">
+      <c r="AJ11" s="58" t="str">
         <f t="shared" si="12"/>
         <v>m̋</v>
       </c>
-      <c r="AJ11" s="58" t="str">
+      <c r="AK11" s="58" t="str">
         <f t="shared" si="12"/>
         <v>m̊</v>
       </c>
-      <c r="AL11" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z11, 【調】韻母標調!AJ$1, "/", AA11, "/")</f>
+      <c r="AM11" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA11, 【調】韻母標調!AJ$1, "/", AB11, "/")</f>
         <v xml:space="preserve">    - xform/》m1/m/</v>
       </c>
-      <c r="AM11" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z11, 【調】韻母標調!AK$1, "/", AB11, "/")</f>
+      <c r="AN11" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA11, 【調】韻母標調!AK$1, "/", AC11, "/")</f>
         <v xml:space="preserve">    - xform/》m2/ḿ/</v>
       </c>
-      <c r="AN11" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z11, 【調】韻母標調!AL$1, "/", AC11, "/")</f>
+      <c r="AO11" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA11, 【調】韻母標調!AL$1, "/", AD11, "/")</f>
         <v xml:space="preserve">    - xform/》m3/m̀/</v>
       </c>
-      <c r="AO11" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z11, 【調】韻母標調!AM$1, "/", AD11, "/")</f>
+      <c r="AP11" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA11, 【調】韻母標調!AM$1, "/", AE11, "/")</f>
         <v xml:space="preserve">    - xform/》m4/m/</v>
       </c>
-      <c r="AP11" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z11, 【調】韻母標調!AN$1, "/", AE11, "/")</f>
+      <c r="AQ11" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA11, 【調】韻母標調!AN$1, "/", AF11, "/")</f>
         <v xml:space="preserve">    - xform/》m5/m̌/</v>
       </c>
-      <c r="AQ11" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z11, 【調】韻母標調!AO$1, "/", AF11, "/")</f>
+      <c r="AR11" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA11, 【調】韻母標調!AO$1, "/", AG11, "/")</f>
         <v xml:space="preserve">    - xform/》m6/ḿ/</v>
       </c>
-      <c r="AR11" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z11, 【調】韻母標調!AP$1, "/", AG11, "/")</f>
+      <c r="AS11" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA11, 【調】韻母標調!AP$1, "/", AH11, "/")</f>
         <v xml:space="preserve">    - xform/》m7/m̄/</v>
       </c>
-      <c r="AS11" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z11, 【調】韻母標調!AQ$1, "/", AH11, "/")</f>
+      <c r="AT11" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA11, 【調】韻母標調!AQ$1, "/", AI11, "/")</f>
         <v xml:space="preserve">    - xform/》m8/m̍/</v>
       </c>
-      <c r="AT11" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z11, 【調】韻母標調!AR$1, "/", AI11, "/")</f>
+      <c r="AU11" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA11, 【調】韻母標調!AR$1, "/", AJ11, "/")</f>
         <v xml:space="preserve">    - xform/》m9/m̋/</v>
       </c>
-      <c r="AU11" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z11, 【調】韻母標調!AS$1, "/", AJ11, "/")</f>
+      <c r="AV11" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA11, 【調】韻母標調!AS$1, "/", AK11, "/")</f>
         <v xml:space="preserve">    - xform/》m9/m̊/</v>
       </c>
-      <c r="AV11" s="58"/>
       <c r="AW11" s="58"/>
-      <c r="AX11" s="55"/>
-    </row>
-    <row r="12" spans="1:50" ht="27.75" thickBot="1">
+      <c r="AX11" s="58"/>
+      <c r="AY11" s="55"/>
+    </row>
+    <row r="12" spans="1:51" ht="27.75" thickBot="1">
       <c r="A12" s="101">
         <f t="shared" si="8"/>
         <v>9</v>
@@ -13696,131 +13781,135 @@
       <c r="K12" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="L12" s="18" t="s">
+      <c r="L12" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>江（舒）</v>
+      </c>
+      <c r="M12" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="M12" s="21"/>
-      <c r="N12" s="18">
+      <c r="N12" s="21"/>
+      <c r="O12" s="18">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="O12" s="26"/>
-      <c r="P12" s="21" t="str">
+      <c r="P12" s="26"/>
+      <c r="Q12" s="21" t="str">
         <f t="shared" si="10"/>
         <v>ang</v>
       </c>
-      <c r="Q12" s="21" t="str">
+      <c r="R12" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ang</v>
       </c>
-      <c r="S12" s="47" t="str">
+      <c r="T12" s="47" t="str">
         <f t="shared" si="3"/>
         <v>ang(\d)</v>
       </c>
-      <c r="T12" s="50" t="s">
+      <c r="U12" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U12" s="50">
+      <c r="V12" s="50">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="V12" s="47" t="str">
+      <c r="W12" s="47" t="str">
         <f t="shared" si="5"/>
         <v>》a${1}ng</v>
       </c>
-      <c r="W12" s="19"/>
-      <c r="X12" s="20" t="str">
+      <c r="X12" s="19"/>
+      <c r="Y12" s="20" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/》ang(\d)/》a${1}ng/</v>
       </c>
-      <c r="Z12" s="55" t="s">
+      <c r="AA12" s="55" t="s">
         <v>1086</v>
       </c>
-      <c r="AA12" s="58" t="str">
+      <c r="AB12" s="58" t="str">
         <f t="shared" si="12"/>
         <v>n</v>
       </c>
-      <c r="AB12" s="58" t="str">
+      <c r="AC12" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ń</v>
       </c>
-      <c r="AC12" s="58" t="str">
+      <c r="AD12" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ǹ</v>
       </c>
-      <c r="AD12" s="58" t="str">
+      <c r="AE12" s="58" t="str">
         <f t="shared" si="12"/>
         <v>n</v>
       </c>
-      <c r="AE12" s="58" t="str">
+      <c r="AF12" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ň</v>
       </c>
-      <c r="AF12" s="58" t="str">
+      <c r="AG12" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ń</v>
       </c>
-      <c r="AG12" s="58" t="str">
+      <c r="AH12" s="58" t="str">
         <f t="shared" si="12"/>
         <v>n̄</v>
       </c>
-      <c r="AH12" s="58" t="str">
+      <c r="AI12" s="58" t="str">
         <f t="shared" si="12"/>
         <v>n̍</v>
       </c>
-      <c r="AI12" s="58" t="str">
+      <c r="AJ12" s="58" t="str">
         <f t="shared" si="12"/>
         <v>n̋</v>
       </c>
-      <c r="AJ12" s="58" t="str">
+      <c r="AK12" s="58" t="str">
         <f t="shared" si="12"/>
         <v>n̊</v>
       </c>
-      <c r="AL12" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z12, 【調】韻母標調!AJ$1, "/", AA12, "/")</f>
+      <c r="AM12" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA12, 【調】韻母標調!AJ$1, "/", AB12, "/")</f>
         <v xml:space="preserve">    - xform/》n1/n/</v>
       </c>
-      <c r="AM12" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z12, 【調】韻母標調!AK$1, "/", AB12, "/")</f>
+      <c r="AN12" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA12, 【調】韻母標調!AK$1, "/", AC12, "/")</f>
         <v xml:space="preserve">    - xform/》n2/ń/</v>
       </c>
-      <c r="AN12" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z12, 【調】韻母標調!AL$1, "/", AC12, "/")</f>
+      <c r="AO12" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA12, 【調】韻母標調!AL$1, "/", AD12, "/")</f>
         <v xml:space="preserve">    - xform/》n3/ǹ/</v>
       </c>
-      <c r="AO12" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z12, 【調】韻母標調!AM$1, "/", AD12, "/")</f>
+      <c r="AP12" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA12, 【調】韻母標調!AM$1, "/", AE12, "/")</f>
         <v xml:space="preserve">    - xform/》n4/n/</v>
       </c>
-      <c r="AP12" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z12, 【調】韻母標調!AN$1, "/", AE12, "/")</f>
+      <c r="AQ12" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA12, 【調】韻母標調!AN$1, "/", AF12, "/")</f>
         <v xml:space="preserve">    - xform/》n5/ň/</v>
       </c>
-      <c r="AQ12" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z12, 【調】韻母標調!AO$1, "/", AF12, "/")</f>
+      <c r="AR12" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA12, 【調】韻母標調!AO$1, "/", AG12, "/")</f>
         <v xml:space="preserve">    - xform/》n6/ń/</v>
       </c>
-      <c r="AR12" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z12, 【調】韻母標調!AP$1, "/", AG12, "/")</f>
+      <c r="AS12" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA12, 【調】韻母標調!AP$1, "/", AH12, "/")</f>
         <v xml:space="preserve">    - xform/》n7/n̄/</v>
       </c>
-      <c r="AS12" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z12, 【調】韻母標調!AQ$1, "/", AH12, "/")</f>
+      <c r="AT12" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA12, 【調】韻母標調!AQ$1, "/", AI12, "/")</f>
         <v xml:space="preserve">    - xform/》n8/n̍/</v>
       </c>
-      <c r="AT12" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z12, 【調】韻母標調!AR$1, "/", AI12, "/")</f>
+      <c r="AU12" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA12, 【調】韻母標調!AR$1, "/", AJ12, "/")</f>
         <v xml:space="preserve">    - xform/》n9/n̋/</v>
       </c>
-      <c r="AU12" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z12, 【調】韻母標調!AS$1, "/", AJ12, "/")</f>
+      <c r="AV12" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA12, 【調】韻母標調!AS$1, "/", AK12, "/")</f>
         <v xml:space="preserve">    - xform/》n9/n̊/</v>
       </c>
-      <c r="AV12" s="58"/>
       <c r="AW12" s="58"/>
-      <c r="AX12" s="55"/>
-    </row>
-    <row r="13" spans="1:50" ht="27.75" thickBot="1">
+      <c r="AX12" s="58"/>
+      <c r="AY12" s="55"/>
+    </row>
+    <row r="13" spans="1:51" ht="27.75" thickBot="1">
       <c r="A13" s="101">
         <f t="shared" si="8"/>
         <v>10</v>
@@ -13856,133 +13945,137 @@
       <c r="K13" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="L13" s="18" t="s">
+      <c r="L13" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>監（舒）</v>
+      </c>
+      <c r="M13" s="18" t="s">
         <v>300</v>
       </c>
-      <c r="M13" s="61" t="s">
+      <c r="N13" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N13" s="18">
+      <c r="O13" s="18">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="O13" s="26"/>
-      <c r="P13" s="21" t="str">
+      <c r="P13" s="26"/>
+      <c r="Q13" s="21" t="str">
         <f t="shared" si="10"/>
         <v>ann</v>
       </c>
-      <c r="Q13" s="21" t="str">
+      <c r="R13" s="21" t="str">
         <f t="shared" si="2"/>
         <v>ann</v>
       </c>
-      <c r="S13" s="47" t="str">
+      <c r="T13" s="47" t="str">
         <f t="shared" si="3"/>
         <v>ann(\d)</v>
       </c>
-      <c r="T13" s="52" t="s">
+      <c r="U13" s="52" t="s">
         <v>1028</v>
       </c>
-      <c r="U13" s="50">
+      <c r="V13" s="50">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="V13" s="47" t="str">
+      <c r="W13" s="47" t="str">
         <f t="shared" si="5"/>
         <v>》a${1}nn</v>
       </c>
-      <c r="W13" s="19"/>
-      <c r="X13" s="20" t="str">
+      <c r="X13" s="19"/>
+      <c r="Y13" s="20" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/》ann(\d)/》a${1}nn/</v>
       </c>
-      <c r="Z13" s="55" t="s">
+      <c r="AA13" s="55" t="s">
         <v>1029</v>
       </c>
-      <c r="AA13" s="58" t="str">
+      <c r="AB13" s="58" t="str">
         <f t="shared" si="12"/>
         <v>i</v>
       </c>
-      <c r="AB13" s="58" t="str">
+      <c r="AC13" s="58" t="str">
         <f t="shared" si="12"/>
         <v>í</v>
       </c>
-      <c r="AC13" s="58" t="str">
+      <c r="AD13" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ì</v>
       </c>
-      <c r="AD13" s="58" t="str">
+      <c r="AE13" s="58" t="str">
         <f t="shared" si="12"/>
         <v>i</v>
       </c>
-      <c r="AE13" s="58" t="str">
+      <c r="AF13" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ǐ</v>
       </c>
-      <c r="AF13" s="58" t="str">
+      <c r="AG13" s="58" t="str">
         <f t="shared" si="12"/>
         <v>í</v>
       </c>
-      <c r="AG13" s="58" t="str">
+      <c r="AH13" s="58" t="str">
         <f t="shared" si="12"/>
         <v>ī</v>
       </c>
-      <c r="AH13" s="58" t="str">
+      <c r="AI13" s="58" t="str">
         <f t="shared" si="12"/>
         <v>i̍</v>
       </c>
-      <c r="AI13" s="58" t="str">
+      <c r="AJ13" s="58" t="str">
         <f t="shared" si="12"/>
         <v>i̋</v>
       </c>
-      <c r="AJ13" s="58" t="str">
+      <c r="AK13" s="58" t="str">
         <f t="shared" si="12"/>
         <v>i̊</v>
       </c>
-      <c r="AL13" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z13, 【調】韻母標調!AJ$1, "/", AA13, "/")</f>
+      <c r="AM13" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA13, 【調】韻母標調!AJ$1, "/", AB13, "/")</f>
         <v xml:space="preserve">    - xform/》i1/i/</v>
       </c>
-      <c r="AM13" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z13, 【調】韻母標調!AK$1, "/", AB13, "/")</f>
+      <c r="AN13" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA13, 【調】韻母標調!AK$1, "/", AC13, "/")</f>
         <v xml:space="preserve">    - xform/》i2/í/</v>
       </c>
-      <c r="AN13" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z13, 【調】韻母標調!AL$1, "/", AC13, "/")</f>
+      <c r="AO13" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA13, 【調】韻母標調!AL$1, "/", AD13, "/")</f>
         <v xml:space="preserve">    - xform/》i3/ì/</v>
       </c>
-      <c r="AO13" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z13, 【調】韻母標調!AM$1, "/", AD13, "/")</f>
+      <c r="AP13" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA13, 【調】韻母標調!AM$1, "/", AE13, "/")</f>
         <v xml:space="preserve">    - xform/》i4/i/</v>
       </c>
-      <c r="AP13" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z13, 【調】韻母標調!AN$1, "/", AE13, "/")</f>
+      <c r="AQ13" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA13, 【調】韻母標調!AN$1, "/", AF13, "/")</f>
         <v xml:space="preserve">    - xform/》i5/ǐ/</v>
       </c>
-      <c r="AQ13" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z13, 【調】韻母標調!AO$1, "/", AF13, "/")</f>
+      <c r="AR13" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA13, 【調】韻母標調!AO$1, "/", AG13, "/")</f>
         <v xml:space="preserve">    - xform/》i6/í/</v>
       </c>
-      <c r="AR13" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z13, 【調】韻母標調!AP$1, "/", AG13, "/")</f>
+      <c r="AS13" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA13, 【調】韻母標調!AP$1, "/", AH13, "/")</f>
         <v xml:space="preserve">    - xform/》i7/ī/</v>
       </c>
-      <c r="AS13" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z13, 【調】韻母標調!AQ$1, "/", AH13, "/")</f>
+      <c r="AT13" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA13, 【調】韻母標調!AQ$1, "/", AI13, "/")</f>
         <v xml:space="preserve">    - xform/》i8/i̍/</v>
       </c>
-      <c r="AT13" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z13, 【調】韻母標調!AR$1, "/", AI13, "/")</f>
+      <c r="AU13" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA13, 【調】韻母標調!AR$1, "/", AJ13, "/")</f>
         <v xml:space="preserve">    - xform/》i9/i̋/</v>
       </c>
-      <c r="AU13" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z13, 【調】韻母標調!AS$1, "/", AJ13, "/")</f>
+      <c r="AV13" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA13, 【調】韻母標調!AS$1, "/", AK13, "/")</f>
         <v xml:space="preserve">    - xform/》i9/i̊/</v>
       </c>
-      <c r="AV13" s="58"/>
       <c r="AW13" s="58"/>
-      <c r="AX13" s="55"/>
-    </row>
-    <row r="14" spans="1:50" ht="27.75" thickBot="1">
+      <c r="AX13" s="58"/>
+      <c r="AY13" s="55"/>
+    </row>
+    <row r="14" spans="1:51" ht="27.75" thickBot="1">
       <c r="A14" s="101">
         <f t="shared" si="8"/>
         <v>11</v>
@@ -14018,133 +14111,137 @@
       <c r="K14" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L14" s="18" t="s">
+      <c r="L14" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>監（促）</v>
+      </c>
+      <c r="M14" s="18" t="s">
         <v>306</v>
       </c>
-      <c r="M14" s="61" t="s">
+      <c r="N14" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N14" s="18">
+      <c r="O14" s="18">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="O14" s="26"/>
-      <c r="P14" s="21" t="str">
+      <c r="P14" s="26"/>
+      <c r="Q14" s="21" t="str">
         <f t="shared" si="1"/>
         <v>annh</v>
       </c>
-      <c r="Q14" s="21" t="str">
+      <c r="R14" s="21" t="str">
         <f t="shared" si="2"/>
         <v>annh</v>
       </c>
-      <c r="S14" s="47" t="str">
-        <f t="shared" ref="S14:S84" si="13" xml:space="preserve"> _xlfn.CONCAT(P14, "(\d)")</f>
+      <c r="T14" s="47" t="str">
+        <f t="shared" ref="T14:T84" si="13" xml:space="preserve"> _xlfn.CONCAT(Q14, "(\d)")</f>
         <v>annh(\d)</v>
       </c>
-      <c r="T14" s="50" t="s">
+      <c r="U14" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U14" s="50">
-        <f t="shared" ref="U14:U84" si="14" xml:space="preserve"> IFERROR( IF(T14="", "", SEARCH(T14, $P14)), "")</f>
+      <c r="V14" s="50">
+        <f t="shared" ref="V14:V84" si="14" xml:space="preserve"> IFERROR( IF(U14="", "", SEARCH(U14, $Q14)), "")</f>
         <v>1</v>
       </c>
-      <c r="V14" s="47" t="str">
-        <f t="shared" ref="V14:V88" si="15" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P14,U14-1), "》", MID(P14,U14,1), "${1}", RIGHT(P14, LEN(P14)-U14)), "" )</f>
+      <c r="W14" s="47" t="str">
+        <f t="shared" ref="W14:W88" si="15" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q14,V14-1), "》", MID(Q14,V14,1), "${1}", RIGHT(Q14, LEN(Q14)-V14)), "" )</f>
         <v>》a${1}nnh</v>
       </c>
-      <c r="W14" s="19"/>
-      <c r="X14" s="20" t="str">
-        <f t="shared" ref="X14:X84" si="16" xml:space="preserve"> IF(AND(Q14&lt;&gt;"", P14&lt;&gt;""), "    - xform/》" &amp; S14 &amp;  "/"  &amp; V14 &amp;  "/", "")</f>
+      <c r="X14" s="19"/>
+      <c r="Y14" s="20" t="str">
+        <f t="shared" ref="Y14:Y84" si="16" xml:space="preserve"> IF(AND(R14&lt;&gt;"", Q14&lt;&gt;""), "    - xform/》" &amp; T14 &amp;  "/"  &amp; W14 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》annh(\d)/》a${1}nnh/</v>
       </c>
-      <c r="Z14" s="55" t="s">
+      <c r="AA14" s="55" t="s">
         <v>981</v>
       </c>
-      <c r="AA14" s="58" t="str">
-        <f t="shared" ref="AA14:AJ14" si="17" xml:space="preserve"> _xlfn.CONCAT($Z14, IF(AA$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(AA$3,4)))))</f>
+      <c r="AB14" s="58" t="str">
+        <f t="shared" ref="AB14:AK14" si="17" xml:space="preserve"> _xlfn.CONCAT($AA14, IF(AB$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(AB$3,4)))))</f>
         <v>e</v>
       </c>
-      <c r="AB14" s="58" t="str">
+      <c r="AC14" s="58" t="str">
         <f t="shared" si="17"/>
         <v>é</v>
       </c>
-      <c r="AC14" s="58" t="str">
+      <c r="AD14" s="58" t="str">
         <f t="shared" si="17"/>
         <v>è</v>
       </c>
-      <c r="AD14" s="58" t="str">
+      <c r="AE14" s="58" t="str">
         <f t="shared" si="17"/>
         <v>e</v>
       </c>
-      <c r="AE14" s="58" t="str">
+      <c r="AF14" s="58" t="str">
         <f t="shared" si="17"/>
         <v>ě</v>
       </c>
-      <c r="AF14" s="58" t="str">
+      <c r="AG14" s="58" t="str">
         <f t="shared" si="17"/>
         <v>é</v>
       </c>
-      <c r="AG14" s="58" t="str">
+      <c r="AH14" s="58" t="str">
         <f t="shared" si="17"/>
         <v>ē</v>
       </c>
-      <c r="AH14" s="58" t="str">
+      <c r="AI14" s="58" t="str">
         <f t="shared" si="17"/>
         <v>e̍</v>
       </c>
-      <c r="AI14" s="58" t="str">
+      <c r="AJ14" s="58" t="str">
         <f t="shared" si="17"/>
         <v>e̋</v>
       </c>
-      <c r="AJ14" s="58" t="str">
+      <c r="AK14" s="58" t="str">
         <f t="shared" si="17"/>
         <v>e̊</v>
       </c>
-      <c r="AL14" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z14, 【調】韻母標調!AJ$1, "/", AA14, "/")</f>
+      <c r="AM14" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA14, 【調】韻母標調!AJ$1, "/", AB14, "/")</f>
         <v xml:space="preserve">    - xform/》e1/e/</v>
       </c>
-      <c r="AM14" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z14, 【調】韻母標調!AK$1, "/", AB14, "/")</f>
+      <c r="AN14" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA14, 【調】韻母標調!AK$1, "/", AC14, "/")</f>
         <v xml:space="preserve">    - xform/》e2/é/</v>
       </c>
-      <c r="AN14" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z14, 【調】韻母標調!AL$1, "/", AC14, "/")</f>
+      <c r="AO14" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA14, 【調】韻母標調!AL$1, "/", AD14, "/")</f>
         <v xml:space="preserve">    - xform/》e3/è/</v>
       </c>
-      <c r="AO14" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z14, 【調】韻母標調!AM$1, "/", AD14, "/")</f>
+      <c r="AP14" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA14, 【調】韻母標調!AM$1, "/", AE14, "/")</f>
         <v xml:space="preserve">    - xform/》e4/e/</v>
       </c>
-      <c r="AP14" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z14, 【調】韻母標調!AN$1, "/", AE14, "/")</f>
+      <c r="AQ14" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA14, 【調】韻母標調!AN$1, "/", AF14, "/")</f>
         <v xml:space="preserve">    - xform/》e5/ě/</v>
       </c>
-      <c r="AQ14" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z14, 【調】韻母標調!AO$1, "/", AF14, "/")</f>
+      <c r="AR14" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA14, 【調】韻母標調!AO$1, "/", AG14, "/")</f>
         <v xml:space="preserve">    - xform/》e6/é/</v>
       </c>
-      <c r="AR14" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z14, 【調】韻母標調!AP$1, "/", AG14, "/")</f>
+      <c r="AS14" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA14, 【調】韻母標調!AP$1, "/", AH14, "/")</f>
         <v xml:space="preserve">    - xform/》e7/ē/</v>
       </c>
-      <c r="AS14" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z14, 【調】韻母標調!AQ$1, "/", AH14, "/")</f>
+      <c r="AT14" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA14, 【調】韻母標調!AQ$1, "/", AI14, "/")</f>
         <v xml:space="preserve">    - xform/》e8/e̍/</v>
       </c>
-      <c r="AT14" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z14, 【調】韻母標調!AR$1, "/", AI14, "/")</f>
+      <c r="AU14" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA14, 【調】韻母標調!AR$1, "/", AJ14, "/")</f>
         <v xml:space="preserve">    - xform/》e9/e̋/</v>
       </c>
-      <c r="AU14" s="60" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $Z14, 【調】韻母標調!AS$1, "/", AJ14, "/")</f>
+      <c r="AV14" s="60" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $AA14, 【調】韻母標調!AS$1, "/", AK14, "/")</f>
         <v xml:space="preserve">    - xform/》e9/e̊/</v>
       </c>
-      <c r="AV14" s="58"/>
       <c r="AW14" s="58"/>
-      <c r="AX14" s="55"/>
-    </row>
-    <row r="15" spans="1:50" ht="27.75" thickBot="1">
+      <c r="AX14" s="58"/>
+      <c r="AY14" s="55"/>
+    </row>
+    <row r="15" spans="1:51" ht="27.75" thickBot="1">
       <c r="A15" s="101">
         <f t="shared" si="8"/>
         <v>12</v>
@@ -14181,45 +14278,49 @@
       <c r="K15" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="L15" s="18" t="s">
+      <c r="L15" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>甘（促）</v>
+      </c>
+      <c r="M15" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="M15" s="21"/>
-      <c r="N15" s="18">
+      <c r="N15" s="21"/>
+      <c r="O15" s="18">
         <f xml:space="preserve"> LEN(D15)</f>
         <v>2</v>
       </c>
-      <c r="O15" s="26"/>
-      <c r="P15" s="21" t="str">
-        <f t="shared" ref="P15:Q18" si="18">C15</f>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="21" t="str">
+        <f>C15</f>
         <v>ap</v>
       </c>
-      <c r="Q15" s="21" t="str">
-        <f t="shared" si="18"/>
+      <c r="R15" s="21" t="str">
+        <f>D15</f>
         <v>ap</v>
       </c>
-      <c r="S15" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P15, "(\d)")</f>
+      <c r="T15" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q15, "(\d)")</f>
         <v>ap(\d)</v>
       </c>
-      <c r="T15" s="50" t="s">
+      <c r="U15" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U15" s="50">
-        <f xml:space="preserve"> IFERROR( IF(T15="", "", SEARCH(T15, $P15)), "")</f>
+      <c r="V15" s="50">
+        <f xml:space="preserve"> IFERROR( IF(U15="", "", SEARCH(U15, $Q15)), "")</f>
         <v>1</v>
       </c>
-      <c r="V15" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P15,U15-1), "》", MID(P15,U15,1), "${1}", RIGHT(P15, LEN(P15)-U15)), "" )</f>
+      <c r="W15" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q15,V15-1), "》", MID(Q15,V15,1), "${1}", RIGHT(Q15, LEN(Q15)-V15)), "" )</f>
         <v>》a${1}p</v>
       </c>
-      <c r="W15" s="19"/>
-      <c r="X15" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q15&lt;&gt;"", P15&lt;&gt;""), "    - xform/》" &amp; S15 &amp;  "/"  &amp; V15 &amp;  "/", "")</f>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R15&lt;&gt;"", Q15&lt;&gt;""), "    - xform/》" &amp; T15 &amp;  "/"  &amp; W15 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》ap(\d)/》a${1}p/</v>
       </c>
     </row>
-    <row r="16" spans="1:50" ht="27.75" thickBot="1">
+    <row r="16" spans="1:51" ht="27.75" thickBot="1">
       <c r="A16" s="101">
         <f t="shared" si="8"/>
         <v>13</v>
@@ -14256,45 +14357,49 @@
       <c r="K16" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="L16" s="18" t="s">
+      <c r="L16" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>干（促）</v>
+      </c>
+      <c r="M16" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="M16" s="21"/>
-      <c r="N16" s="18">
+      <c r="N16" s="21"/>
+      <c r="O16" s="18">
         <f xml:space="preserve"> LEN(D16)</f>
         <v>2</v>
       </c>
-      <c r="O16" s="26"/>
-      <c r="P16" s="21" t="str">
-        <f t="shared" si="18"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="21" t="str">
+        <f>C16</f>
         <v>at</v>
       </c>
-      <c r="Q16" s="21" t="str">
-        <f t="shared" si="18"/>
+      <c r="R16" s="21" t="str">
+        <f>D16</f>
         <v>at</v>
       </c>
-      <c r="S16" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P16, "(\d)")</f>
+      <c r="T16" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q16, "(\d)")</f>
         <v>at(\d)</v>
       </c>
-      <c r="T16" s="50" t="s">
+      <c r="U16" s="50" t="s">
         <v>1016</v>
       </c>
-      <c r="U16" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T16="", "", SEARCH(T16, $P16)), "")</f>
+      <c r="V16" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U16="", "", SEARCH(U16, $Q16)), "")</f>
         <v/>
       </c>
-      <c r="V16" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P16,U16-1), "》", MID(P16,U16,1), "${1}", RIGHT(P16, LEN(P16)-U16)), "" )</f>
+      <c r="W16" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q16,V16-1), "》", MID(Q16,V16,1), "${1}", RIGHT(Q16, LEN(Q16)-V16)), "" )</f>
         <v/>
       </c>
-      <c r="W16" s="19"/>
-      <c r="X16" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q16&lt;&gt;"", P16&lt;&gt;""), "    - xform/》" &amp; S16 &amp;  "/"  &amp; V16 &amp;  "/", "")</f>
+      <c r="X16" s="19"/>
+      <c r="Y16" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R16&lt;&gt;"", Q16&lt;&gt;""), "    - xform/》" &amp; T16 &amp;  "/"  &amp; W16 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》at(\d)//</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="27.75" thickBot="1">
+    <row r="17" spans="1:25" ht="27.75" thickBot="1">
       <c r="A17" s="101">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -14330,45 +14435,49 @@
       <c r="K17" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="L17" s="18" t="s">
+      <c r="L17" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>交（舒）</v>
+      </c>
+      <c r="M17" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="M17" s="21"/>
-      <c r="N17" s="18">
+      <c r="N17" s="21"/>
+      <c r="O17" s="18">
         <f xml:space="preserve"> LEN(D17)</f>
         <v>2</v>
       </c>
-      <c r="O17" s="26"/>
-      <c r="P17" s="21" t="str">
-        <f t="shared" si="18"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="21" t="str">
+        <f>C17</f>
         <v>au</v>
       </c>
-      <c r="Q17" s="21" t="str">
-        <f t="shared" si="18"/>
+      <c r="R17" s="21" t="str">
+        <f>D17</f>
         <v>au</v>
       </c>
-      <c r="S17" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P17, "(\d)")</f>
+      <c r="T17" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q17, "(\d)")</f>
         <v>au(\d)</v>
       </c>
-      <c r="T17" s="50" t="s">
+      <c r="U17" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U17" s="50">
-        <f xml:space="preserve"> IFERROR( IF(T17="", "", SEARCH(T17, $P17)), "")</f>
+      <c r="V17" s="50">
+        <f xml:space="preserve"> IFERROR( IF(U17="", "", SEARCH(U17, $Q17)), "")</f>
         <v>1</v>
       </c>
-      <c r="V17" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P17,U17-1), "》", MID(P17,U17,1), "${1}", RIGHT(P17, LEN(P17)-U17)), "" )</f>
+      <c r="W17" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q17,V17-1), "》", MID(Q17,V17,1), "${1}", RIGHT(Q17, LEN(Q17)-V17)), "" )</f>
         <v>》a${1}u</v>
       </c>
-      <c r="W17" s="19"/>
-      <c r="X17" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q17&lt;&gt;"", P17&lt;&gt;""), "    - xform/》" &amp; S17 &amp;  "/"  &amp; V17 &amp;  "/", "")</f>
+      <c r="X17" s="19"/>
+      <c r="Y17" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R17&lt;&gt;"", Q17&lt;&gt;""), "    - xform/》" &amp; T17 &amp;  "/"  &amp; W17 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》au(\d)/》a${1}u/</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="30.75" thickBot="1">
+    <row r="18" spans="1:25" ht="30.75" thickBot="1">
       <c r="A18" s="101">
         <f t="shared" si="8"/>
         <v>15</v>
@@ -14404,45 +14513,49 @@
       <c r="K18" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="L18" s="18" t="s">
+      <c r="L18" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>交（促）</v>
+      </c>
+      <c r="M18" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="M18" s="21"/>
-      <c r="N18" s="18">
+      <c r="N18" s="21"/>
+      <c r="O18" s="18">
         <f xml:space="preserve"> LEN(D18)</f>
         <v>3</v>
       </c>
-      <c r="O18" s="26"/>
-      <c r="P18" s="21" t="str">
-        <f t="shared" si="18"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="21" t="str">
+        <f>C18</f>
         <v>auh</v>
       </c>
-      <c r="Q18" s="21" t="str">
-        <f t="shared" si="18"/>
+      <c r="R18" s="21" t="str">
+        <f>D18</f>
         <v>auh</v>
       </c>
-      <c r="S18" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P18, "(\d)")</f>
+      <c r="T18" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q18, "(\d)")</f>
         <v>auh(\d)</v>
       </c>
-      <c r="T18" s="50" t="s">
+      <c r="U18" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U18" s="50">
-        <f xml:space="preserve"> IFERROR( IF(T18="", "", SEARCH(T18, $P18)), "")</f>
+      <c r="V18" s="50">
+        <f xml:space="preserve"> IFERROR( IF(U18="", "", SEARCH(U18, $Q18)), "")</f>
         <v>1</v>
       </c>
-      <c r="V18" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P18,U18-1), "》", MID(P18,U18,1), "${1}", RIGHT(P18, LEN(P18)-U18)), "" )</f>
+      <c r="W18" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q18,V18-1), "》", MID(Q18,V18,1), "${1}", RIGHT(Q18, LEN(Q18)-V18)), "" )</f>
         <v>》a${1}uh</v>
       </c>
-      <c r="W18" s="19"/>
-      <c r="X18" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q18&lt;&gt;"", P18&lt;&gt;""), "    - xform/》" &amp; S18 &amp;  "/"  &amp; V18 &amp;  "/", "")</f>
+      <c r="X18" s="19"/>
+      <c r="Y18" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R18&lt;&gt;"", Q18&lt;&gt;""), "    - xform/》" &amp; T18 &amp;  "/"  &amp; W18 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》auh(\d)/》a${1}uh/</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="27.75" thickBot="1">
+    <row r="19" spans="1:25" ht="27.75" thickBot="1">
       <c r="A19" s="101">
         <f t="shared" si="8"/>
         <v>16</v>
@@ -14478,47 +14591,51 @@
       <c r="K19" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="L19" s="18" t="s">
+      <c r="L19" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>稽（舒）</v>
+      </c>
+      <c r="M19" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="M19" s="21"/>
-      <c r="N19" s="18">
+      <c r="N19" s="21"/>
+      <c r="O19" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O19" s="26"/>
-      <c r="P19" s="21" t="str">
+      <c r="P19" s="26"/>
+      <c r="Q19" s="21" t="str">
         <f>C27</f>
         <v>i</v>
       </c>
-      <c r="Q19" s="21" t="str">
+      <c r="R19" s="21" t="str">
         <f>D27</f>
         <v>i</v>
       </c>
-      <c r="S19" s="47" t="str">
+      <c r="T19" s="47" t="str">
         <f t="shared" si="13"/>
         <v>i(\d)</v>
       </c>
-      <c r="T19" s="50" t="s">
+      <c r="U19" s="50" t="s">
         <v>1016</v>
       </c>
-      <c r="U19" s="50" t="str">
+      <c r="V19" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V19" s="47" t="str">
+      <c r="W19" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W19" s="19"/>
-      <c r="X19" s="20" t="str">
+      <c r="X19" s="19"/>
+      <c r="Y19" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》i(\d)//</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="27.75" thickBot="1">
+    <row r="20" spans="1:25" ht="27.75" thickBot="1">
       <c r="A20" s="101">
-        <f t="shared" ref="A20:A21" si="19" xml:space="preserve"> ROW() - 3</f>
+        <f t="shared" ref="A20:A21" si="18" xml:space="preserve"> ROW() - 3</f>
         <v>17</v>
       </c>
       <c r="B20" s="63" t="s">
@@ -14546,47 +14663,51 @@
       <c r="K20" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="L20" s="69" t="s">
+      <c r="L20" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>嘉（舒）</v>
+      </c>
+      <c r="M20" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="M20" s="21"/>
-      <c r="N20" s="18">
-        <f t="shared" ref="N20:N21" si="20" xml:space="preserve"> LEN(D20)</f>
+      <c r="N20" s="21"/>
+      <c r="O20" s="18">
+        <f t="shared" ref="O20:O21" si="19" xml:space="preserve"> LEN(D20)</f>
         <v>2</v>
       </c>
-      <c r="O20" s="26"/>
-      <c r="P20" s="21" t="str">
+      <c r="P20" s="26"/>
+      <c r="Q20" s="21" t="str">
         <f>C19</f>
         <v>e</v>
       </c>
-      <c r="Q20" s="21" t="str">
+      <c r="R20" s="21" t="str">
         <f>D19</f>
         <v>ei</v>
       </c>
-      <c r="S20" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P20, "(\d)")</f>
+      <c r="T20" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q20, "(\d)")</f>
         <v>e(\d)</v>
       </c>
-      <c r="T20" s="50" t="s">
+      <c r="U20" s="50" t="s">
         <v>1029</v>
       </c>
-      <c r="U20" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T20="", "", SEARCH(T20, $P20)), "")</f>
+      <c r="V20" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U20="", "", SEARCH(U20, $Q20)), "")</f>
         <v/>
       </c>
-      <c r="V20" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P20,U20-1), "》", MID(P20,U20,1), "${1}", RIGHT(P20, LEN(P20)-U20)), "" )</f>
+      <c r="W20" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q20,V20-1), "》", MID(Q20,V20,1), "${1}", RIGHT(Q20, LEN(Q20)-V20)), "" )</f>
         <v/>
       </c>
-      <c r="W20" s="19"/>
-      <c r="X20" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q20&lt;&gt;"", P20&lt;&gt;""), "    - xform/》" &amp; S20 &amp;  "/"  &amp; V20 &amp;  "/", "")</f>
+      <c r="X20" s="19"/>
+      <c r="Y20" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R20&lt;&gt;"", Q20&lt;&gt;""), "    - xform/》" &amp; T20 &amp;  "/"  &amp; W20 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》e(\d)//</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="27.75" thickBot="1">
+    <row r="21" spans="1:25" ht="27.75" thickBot="1">
       <c r="A21" s="101">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>18</v>
       </c>
       <c r="B21" s="63" t="str">
@@ -14615,45 +14736,49 @@
       <c r="K21" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="L21" s="69" t="s">
+      <c r="L21" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>嘉（促）</v>
+      </c>
+      <c r="M21" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="M21" s="21"/>
-      <c r="N21" s="18">
-        <f t="shared" si="20"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="18">
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="O21" s="26"/>
-      <c r="P21" s="21" t="str">
+      <c r="P21" s="26"/>
+      <c r="Q21" s="21" t="str">
         <f>C25</f>
         <v>enn</v>
       </c>
-      <c r="Q21" s="21" t="str">
+      <c r="R21" s="21" t="str">
         <f>D25</f>
         <v>enn</v>
       </c>
-      <c r="S21" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P21, "(\d)")</f>
+      <c r="T21" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q21, "(\d)")</f>
         <v>enn(\d)</v>
       </c>
-      <c r="T21" s="50" t="s">
+      <c r="U21" s="50" t="s">
         <v>1029</v>
       </c>
-      <c r="U21" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T21="", "", SEARCH(T21, $P21)), "")</f>
+      <c r="V21" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U21="", "", SEARCH(U21, $Q21)), "")</f>
         <v/>
       </c>
-      <c r="V21" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P21,U21-1), "》", MID(P21,U21,1), "${1}", RIGHT(P21, LEN(P21)-U21)), "" )</f>
+      <c r="W21" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q21,V21-1), "》", MID(Q21,V21,1), "${1}", RIGHT(Q21, LEN(Q21)-V21)), "" )</f>
         <v/>
       </c>
-      <c r="W21" s="19"/>
-      <c r="X21" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q21&lt;&gt;"", P21&lt;&gt;""), "    - xform/》" &amp; S21 &amp;  "/"  &amp; V21 &amp;  "/", "")</f>
+      <c r="X21" s="19"/>
+      <c r="Y21" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R21&lt;&gt;"", Q21&lt;&gt;""), "    - xform/》" &amp; T21 &amp;  "/"  &amp; W21 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》enn(\d)//</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="27.75" thickBot="1">
+    <row r="22" spans="1:25" ht="27.75" thickBot="1">
       <c r="A22" s="101">
         <f t="shared" si="8"/>
         <v>19</v>
@@ -14689,47 +14814,51 @@
       <c r="K22" s="18" t="s">
         <v>412</v>
       </c>
-      <c r="L22" s="18" t="s">
+      <c r="L22" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>伽（促）</v>
+      </c>
+      <c r="M22" s="18" t="s">
         <v>413</v>
       </c>
-      <c r="M22" s="21"/>
-      <c r="N22" s="18">
+      <c r="N22" s="21"/>
+      <c r="O22" s="18">
         <f xml:space="preserve"> LEN(D22)</f>
         <v>2</v>
       </c>
-      <c r="O22" s="26"/>
-      <c r="P22" s="21" t="str">
+      <c r="P22" s="26"/>
+      <c r="Q22" s="21" t="str">
         <f>C41</f>
         <v>ih</v>
       </c>
-      <c r="Q22" s="21" t="str">
+      <c r="R22" s="21" t="str">
         <f>D41</f>
         <v>ih</v>
       </c>
-      <c r="S22" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P22, "(\d)")</f>
+      <c r="T22" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q22, "(\d)")</f>
         <v>ih(\d)</v>
       </c>
-      <c r="T22" s="50" t="s">
+      <c r="U22" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U22" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T22="", "", SEARCH(T22, $P22)), "")</f>
+      <c r="V22" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U22="", "", SEARCH(U22, $Q22)), "")</f>
         <v/>
       </c>
-      <c r="V22" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P22,U22-1), "》", MID(P22,U22,1), "${1}", RIGHT(P22, LEN(P22)-U22)), "" )</f>
+      <c r="W22" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q22,V22-1), "》", MID(Q22,V22,1), "${1}", RIGHT(Q22, LEN(Q22)-V22)), "" )</f>
         <v/>
       </c>
-      <c r="W22" s="19"/>
-      <c r="X22" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q22&lt;&gt;"", P22&lt;&gt;""), "    - xform/》" &amp; S22 &amp;  "/"  &amp; V22 &amp;  "/", "")</f>
+      <c r="X22" s="19"/>
+      <c r="Y22" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R22&lt;&gt;"", Q22&lt;&gt;""), "    - xform/》" &amp; T22 &amp;  "/"  &amp; W22 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》ih(\d)//</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="27.75" thickBot="1">
+    <row r="23" spans="1:25" ht="27.75" thickBot="1">
       <c r="A23" s="101">
-        <f t="shared" ref="A23:A24" si="21" xml:space="preserve"> ROW() - 3</f>
+        <f t="shared" ref="A23:A24" si="20" xml:space="preserve"> ROW() - 3</f>
         <v>20</v>
       </c>
       <c r="B23" s="63" t="str">
@@ -14758,47 +14887,51 @@
       <c r="K23" s="18" t="s">
         <v>2071</v>
       </c>
-      <c r="L23" s="69" t="s">
+      <c r="L23" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>經（促）</v>
+      </c>
+      <c r="M23" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="M23" s="21"/>
-      <c r="N23" s="18">
+      <c r="N23" s="21"/>
+      <c r="O23" s="18">
         <f xml:space="preserve"> LEN(D23)</f>
         <v>2</v>
       </c>
-      <c r="O23" s="26"/>
-      <c r="P23" s="21" t="str">
+      <c r="P23" s="26"/>
+      <c r="Q23" s="21" t="str">
         <f>C26</f>
         <v>ennh</v>
       </c>
-      <c r="Q23" s="21" t="str">
+      <c r="R23" s="21" t="str">
         <f>D26</f>
         <v>ennh</v>
       </c>
-      <c r="S23" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P23, "(\d)")</f>
+      <c r="T23" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q23, "(\d)")</f>
         <v>ennh(\d)</v>
       </c>
-      <c r="T23" s="50" t="s">
+      <c r="U23" s="50" t="s">
         <v>1029</v>
       </c>
-      <c r="U23" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T23="", "", SEARCH(T23, $P23)), "")</f>
+      <c r="V23" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U23="", "", SEARCH(U23, $Q23)), "")</f>
         <v/>
       </c>
-      <c r="V23" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P23,U23-1), "》", MID(P23,U23,1), "${1}", RIGHT(P23, LEN(P23)-U23)), "" )</f>
+      <c r="W23" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q23,V23-1), "》", MID(Q23,V23,1), "${1}", RIGHT(Q23, LEN(Q23)-V23)), "" )</f>
         <v/>
       </c>
-      <c r="W23" s="19"/>
-      <c r="X23" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q23&lt;&gt;"", P23&lt;&gt;""), "    - xform/》" &amp; S23 &amp;  "/"  &amp; V23 &amp;  "/", "")</f>
+      <c r="X23" s="19"/>
+      <c r="Y23" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R23&lt;&gt;"", Q23&lt;&gt;""), "    - xform/》" &amp; T23 &amp;  "/"  &amp; W23 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》ennh(\d)//</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="27.75" thickBot="1">
+    <row r="24" spans="1:25" ht="27.75" thickBot="1">
       <c r="A24" s="101">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>21</v>
       </c>
       <c r="B24" s="63" t="str">
@@ -14827,45 +14960,49 @@
       <c r="K24" s="18" t="s">
         <v>2071</v>
       </c>
-      <c r="L24" s="69" t="s">
+      <c r="L24" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>經（舒）</v>
+      </c>
+      <c r="M24" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="M24" s="21"/>
-      <c r="N24" s="18">
-        <f t="shared" ref="N24" si="22" xml:space="preserve"> LEN(D24)</f>
+      <c r="N24" s="21"/>
+      <c r="O24" s="18">
+        <f t="shared" ref="O24" si="21" xml:space="preserve"> LEN(D24)</f>
         <v>3</v>
       </c>
-      <c r="O24" s="26"/>
-      <c r="P24" s="21" t="str">
+      <c r="P24" s="26"/>
+      <c r="Q24" s="21" t="str">
         <f>C22</f>
         <v>eh</v>
       </c>
-      <c r="Q24" s="21" t="str">
+      <c r="R24" s="21" t="str">
         <f>D22</f>
         <v>eh</v>
       </c>
-      <c r="S24" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P24, "(\d)")</f>
+      <c r="T24" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q24, "(\d)")</f>
         <v>eh(\d)</v>
       </c>
-      <c r="T24" s="50" t="s">
+      <c r="U24" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U24" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T24="", "", SEARCH(T24, $P24)), "")</f>
+      <c r="V24" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U24="", "", SEARCH(U24, $Q24)), "")</f>
         <v/>
       </c>
-      <c r="V24" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P24,U24-1), "》", MID(P24,U24,1), "${1}", RIGHT(P24, LEN(P24)-U24)), "" )</f>
+      <c r="W24" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q24,V24-1), "》", MID(Q24,V24,1), "${1}", RIGHT(Q24, LEN(Q24)-V24)), "" )</f>
         <v/>
       </c>
-      <c r="W24" s="19"/>
-      <c r="X24" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q24&lt;&gt;"", P24&lt;&gt;""), "    - xform/》" &amp; S24 &amp;  "/"  &amp; V24 &amp;  "/", "")</f>
+      <c r="X24" s="19"/>
+      <c r="Y24" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R24&lt;&gt;"", Q24&lt;&gt;""), "    - xform/》" &amp; T24 &amp;  "/"  &amp; W24 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》eh(\d)//</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="27.75" thickBot="1">
+    <row r="25" spans="1:25" ht="27.75" thickBot="1">
       <c r="A25" s="101">
         <f t="shared" si="8"/>
         <v>22</v>
@@ -14901,47 +15038,51 @@
       <c r="K25" s="18" t="s">
         <v>336</v>
       </c>
-      <c r="L25" s="18" t="s">
+      <c r="L25" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>更（舒）</v>
+      </c>
+      <c r="M25" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="M25" s="61" t="s">
+      <c r="N25" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N25" s="18">
+      <c r="O25" s="18">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="O25" s="26"/>
-      <c r="P25" s="21" t="str">
+      <c r="P25" s="26"/>
+      <c r="Q25" s="21" t="str">
         <f>C46</f>
         <v>inn</v>
       </c>
-      <c r="Q25" s="21" t="str">
+      <c r="R25" s="21" t="str">
         <f>D46</f>
         <v>inn</v>
       </c>
-      <c r="S25" s="47" t="str">
+      <c r="T25" s="47" t="str">
         <f t="shared" si="13"/>
         <v>inn(\d)</v>
       </c>
-      <c r="T25" s="50" t="s">
+      <c r="U25" s="50" t="s">
         <v>1016</v>
       </c>
-      <c r="U25" s="50" t="str">
+      <c r="V25" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V25" s="47" t="str">
+      <c r="W25" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W25" s="19"/>
-      <c r="X25" s="20" t="str">
+      <c r="X25" s="19"/>
+      <c r="Y25" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》inn(\d)//</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="30.75" thickBot="1">
+    <row r="26" spans="1:25" ht="30.75" thickBot="1">
       <c r="A26" s="101">
         <f t="shared" si="8"/>
         <v>23</v>
@@ -14977,47 +15118,51 @@
       <c r="K26" s="18" t="s">
         <v>344</v>
       </c>
-      <c r="L26" s="70" t="s">
+      <c r="L26" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>更（促）</v>
+      </c>
+      <c r="M26" s="70" t="s">
         <v>347</v>
       </c>
-      <c r="M26" s="61" t="s">
+      <c r="N26" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N26" s="18">
+      <c r="O26" s="18">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="O26" s="26"/>
-      <c r="P26" s="21" t="str">
+      <c r="P26" s="26"/>
+      <c r="Q26" s="21" t="str">
         <f>C43</f>
         <v>im</v>
       </c>
-      <c r="Q26" s="21" t="str">
+      <c r="R26" s="21" t="str">
         <f>D43</f>
         <v>im</v>
       </c>
-      <c r="S26" s="47" t="str">
+      <c r="T26" s="47" t="str">
         <f t="shared" si="13"/>
         <v>im(\d)</v>
       </c>
-      <c r="T26" s="50" t="s">
+      <c r="U26" s="50" t="s">
         <v>981</v>
       </c>
-      <c r="U26" s="50" t="str">
+      <c r="V26" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V26" s="47" t="str">
+      <c r="W26" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W26" s="19"/>
-      <c r="X26" s="20" t="str">
+      <c r="X26" s="19"/>
+      <c r="Y26" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》im(\d)//</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="27.75" thickBot="1">
+    <row r="27" spans="1:25" ht="27.75" thickBot="1">
       <c r="A27" s="101">
         <f t="shared" si="8"/>
         <v>24</v>
@@ -15053,45 +15198,49 @@
       <c r="K27" s="18" t="s">
         <v>323</v>
       </c>
-      <c r="L27" s="18" t="s">
+      <c r="L27" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>居（舒）</v>
+      </c>
+      <c r="M27" s="18" t="s">
         <v>327</v>
       </c>
-      <c r="M27" s="21"/>
-      <c r="N27" s="18">
+      <c r="N27" s="21"/>
+      <c r="O27" s="18">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O27" s="26"/>
-      <c r="P27" s="21" t="str">
+      <c r="P27" s="26"/>
+      <c r="Q27" s="21" t="str">
         <f>C44</f>
         <v>in</v>
       </c>
-      <c r="Q27" s="21" t="str">
+      <c r="R27" s="21" t="str">
         <f>D44</f>
         <v>in</v>
       </c>
-      <c r="S27" s="47" t="str">
+      <c r="T27" s="47" t="str">
         <f t="shared" si="13"/>
         <v>in(\d)</v>
       </c>
-      <c r="T27" s="50" t="s">
+      <c r="U27" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U27" s="50" t="str">
+      <c r="V27" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V27" s="47" t="str">
+      <c r="W27" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W27" s="19"/>
-      <c r="X27" s="20" t="str">
+      <c r="X27" s="19"/>
+      <c r="Y27" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》in(\d)//</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="27.75" thickBot="1">
+    <row r="28" spans="1:25" ht="27.75" thickBot="1">
       <c r="A28" s="101">
         <f t="shared" si="8"/>
         <v>25</v>
@@ -15127,45 +15276,49 @@
       <c r="K28" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="L28" s="18" t="s">
+      <c r="L28" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>迦（舒）</v>
+      </c>
+      <c r="M28" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="M28" s="21"/>
-      <c r="N28" s="18">
-        <f t="shared" ref="N28:N42" si="23" xml:space="preserve"> LEN(D28)</f>
+      <c r="N28" s="21"/>
+      <c r="O28" s="18">
+        <f t="shared" ref="O28:O42" si="22" xml:space="preserve"> LEN(D28)</f>
         <v>2</v>
       </c>
-      <c r="O28" s="26"/>
-      <c r="P28" s="21" t="str">
+      <c r="P28" s="26"/>
+      <c r="Q28" s="21" t="str">
         <f>C31</f>
         <v>iam</v>
       </c>
-      <c r="Q28" s="21" t="str">
+      <c r="R28" s="21" t="str">
         <f>D31</f>
         <v>iam</v>
       </c>
-      <c r="S28" s="47" t="str">
-        <f t="shared" ref="S28:S42" si="24" xml:space="preserve"> _xlfn.CONCAT(P28, "(\d)")</f>
+      <c r="T28" s="47" t="str">
+        <f t="shared" ref="T28:T42" si="23" xml:space="preserve"> _xlfn.CONCAT(Q28, "(\d)")</f>
         <v>iam(\d)</v>
       </c>
-      <c r="T28" s="50" t="s">
+      <c r="U28" s="50" t="s">
         <v>1029</v>
       </c>
-      <c r="U28" s="50">
-        <f t="shared" ref="U28:U42" si="25" xml:space="preserve"> IFERROR( IF(T28="", "", SEARCH(T28, $P28)), "")</f>
+      <c r="V28" s="50">
+        <f t="shared" ref="V28:V42" si="24" xml:space="preserve"> IFERROR( IF(U28="", "", SEARCH(U28, $Q28)), "")</f>
         <v>1</v>
       </c>
-      <c r="V28" s="47" t="str">
-        <f t="shared" ref="V28:V42" si="26" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P28,U28-1), "》", MID(P28,U28,1), "${1}", RIGHT(P28, LEN(P28)-U28)), "" )</f>
+      <c r="W28" s="47" t="str">
+        <f t="shared" ref="W28:W42" si="25" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q28,V28-1), "》", MID(Q28,V28,1), "${1}", RIGHT(Q28, LEN(Q28)-V28)), "" )</f>
         <v>》i${1}am</v>
       </c>
-      <c r="W28" s="19"/>
-      <c r="X28" s="20" t="str">
-        <f t="shared" ref="X28:X42" si="27" xml:space="preserve"> IF(AND(Q28&lt;&gt;"", P28&lt;&gt;""), "    - xform/》" &amp; S28 &amp;  "/"  &amp; V28 &amp;  "/", "")</f>
+      <c r="X28" s="19"/>
+      <c r="Y28" s="20" t="str">
+        <f t="shared" ref="Y28:Y42" si="26" xml:space="preserve"> IF(AND(R28&lt;&gt;"", Q28&lt;&gt;""), "    - xform/》" &amp; T28 &amp;  "/"  &amp; W28 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》iam(\d)/》i${1}am/</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="27.75" thickBot="1">
+    <row r="29" spans="1:25" ht="27.75" thickBot="1">
       <c r="A29" s="101">
         <f t="shared" si="8"/>
         <v>26</v>
@@ -15202,45 +15355,49 @@
       <c r="K29" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="L29" s="18" t="s">
+      <c r="L29" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>迦（促）</v>
+      </c>
+      <c r="M29" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="M29" s="21"/>
-      <c r="N29" s="18">
-        <f t="shared" si="23"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="18">
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
-      <c r="O29" s="26"/>
-      <c r="P29" s="21" t="str">
+      <c r="P29" s="26"/>
+      <c r="Q29" s="21" t="str">
         <f>C33</f>
         <v>iang</v>
       </c>
-      <c r="Q29" s="21" t="str">
+      <c r="R29" s="21" t="str">
         <f>D33</f>
         <v>iang</v>
       </c>
-      <c r="S29" s="47" t="str">
+      <c r="T29" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>iang(\d)</v>
+      </c>
+      <c r="U29" s="50" t="s">
+        <v>1029</v>
+      </c>
+      <c r="V29" s="50">
         <f t="shared" si="24"/>
-        <v>iang(\d)</v>
-      </c>
-      <c r="T29" s="50" t="s">
-        <v>1029</v>
-      </c>
-      <c r="U29" s="50">
+        <v>1</v>
+      </c>
+      <c r="W29" s="47" t="str">
         <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="V29" s="47" t="str">
+        <v>》i${1}ang</v>
+      </c>
+      <c r="X29" s="19"/>
+      <c r="Y29" s="20" t="str">
         <f t="shared" si="26"/>
-        <v>》i${1}ang</v>
-      </c>
-      <c r="W29" s="19"/>
-      <c r="X29" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》iang(\d)/》i${1}ang/</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="27.75" thickBot="1">
+    <row r="30" spans="1:25" ht="27.75" thickBot="1">
       <c r="A30" s="101">
         <f t="shared" si="8"/>
         <v>27</v>
@@ -15276,45 +15433,49 @@
       <c r="K30" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="L30" s="18" t="s">
+      <c r="L30" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>姜（促）</v>
+      </c>
+      <c r="M30" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="M30" s="21"/>
-      <c r="N30" s="18">
-        <f t="shared" si="23"/>
+      <c r="N30" s="21"/>
+      <c r="O30" s="18">
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
-      <c r="O30" s="26"/>
-      <c r="P30" s="21" t="str">
+      <c r="P30" s="26"/>
+      <c r="Q30" s="21" t="str">
         <f>C47</f>
         <v>io</v>
       </c>
-      <c r="Q30" s="21" t="str">
+      <c r="R30" s="21" t="str">
         <f>D47</f>
         <v>io</v>
       </c>
-      <c r="S30" s="47" t="str">
+      <c r="T30" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>io(\d)</v>
+      </c>
+      <c r="U30" s="50" t="s">
+        <v>1028</v>
+      </c>
+      <c r="V30" s="50" t="str">
         <f t="shared" si="24"/>
-        <v>io(\d)</v>
-      </c>
-      <c r="T30" s="50" t="s">
-        <v>1028</v>
-      </c>
-      <c r="U30" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W30" s="47" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="V30" s="47" t="str">
+      <c r="X30" s="19"/>
+      <c r="Y30" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="W30" s="19"/>
-      <c r="X30" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》io(\d)//</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="27.75" thickBot="1">
+    <row r="31" spans="1:25" ht="27.75" thickBot="1">
       <c r="A31" s="101">
         <f t="shared" si="8"/>
         <v>28</v>
@@ -15350,45 +15511,49 @@
       <c r="K31" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="L31" s="18" t="s">
+      <c r="L31" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>兼（舒）</v>
+      </c>
+      <c r="M31" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="M31" s="21"/>
-      <c r="N31" s="18">
-        <f t="shared" si="23"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="18">
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
-      <c r="O31" s="26"/>
-      <c r="P31" s="21" t="str">
+      <c r="P31" s="26"/>
+      <c r="Q31" s="21" t="str">
         <f>C37</f>
         <v>iat</v>
       </c>
-      <c r="Q31" s="21" t="str">
+      <c r="R31" s="21" t="str">
         <f>D37</f>
         <v>iat</v>
       </c>
-      <c r="S31" s="47" t="str">
+      <c r="T31" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>iat(\d)</v>
+      </c>
+      <c r="U31" s="50" t="s">
+        <v>981</v>
+      </c>
+      <c r="V31" s="50" t="str">
         <f t="shared" si="24"/>
-        <v>iat(\d)</v>
-      </c>
-      <c r="T31" s="50" t="s">
-        <v>981</v>
-      </c>
-      <c r="U31" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W31" s="47" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="V31" s="47" t="str">
+      <c r="X31" s="19"/>
+      <c r="Y31" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="W31" s="19"/>
-      <c r="X31" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》iat(\d)//</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="27.75" thickBot="1">
+    <row r="32" spans="1:25" ht="27.75" thickBot="1">
       <c r="A32" s="101">
         <f t="shared" si="8"/>
         <v>29</v>
@@ -15424,45 +15589,49 @@
       <c r="K32" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="L32" s="18" t="s">
+      <c r="L32" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>堅（舒）</v>
+      </c>
+      <c r="M32" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="M32" s="21"/>
-      <c r="N32" s="18">
-        <f t="shared" si="23"/>
+      <c r="N32" s="21"/>
+      <c r="O32" s="18">
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
-      <c r="O32" s="26"/>
-      <c r="P32" s="21" t="str">
+      <c r="P32" s="26"/>
+      <c r="Q32" s="21" t="str">
         <f>C30</f>
         <v>iak</v>
       </c>
-      <c r="Q32" s="21" t="str">
+      <c r="R32" s="21" t="str">
         <f>D30</f>
         <v>iak</v>
       </c>
-      <c r="S32" s="47" t="str">
+      <c r="T32" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>iak(\d)</v>
+      </c>
+      <c r="U32" s="50" t="s">
+        <v>1086</v>
+      </c>
+      <c r="V32" s="50" t="str">
         <f t="shared" si="24"/>
-        <v>iak(\d)</v>
-      </c>
-      <c r="T32" s="50" t="s">
-        <v>1086</v>
-      </c>
-      <c r="U32" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W32" s="47" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="V32" s="47" t="str">
+      <c r="X32" s="19"/>
+      <c r="Y32" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="W32" s="19"/>
-      <c r="X32" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》iak(\d)//</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="27.75" thickBot="1">
+    <row r="33" spans="1:25" ht="27.75" thickBot="1">
       <c r="A33" s="101">
         <f t="shared" si="8"/>
         <v>30</v>
@@ -15498,45 +15667,49 @@
       <c r="K33" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="L33" s="18" t="s">
+      <c r="L33" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>姜（舒）</v>
+      </c>
+      <c r="M33" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="M33" s="21"/>
-      <c r="N33" s="18">
-        <f t="shared" si="23"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="18">
+        <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="O33" s="26"/>
-      <c r="P33" s="21" t="str">
+      <c r="P33" s="26"/>
+      <c r="Q33" s="21" t="str">
         <f>C38</f>
         <v>iau</v>
       </c>
-      <c r="Q33" s="21" t="str">
+      <c r="R33" s="21" t="str">
         <f>D38</f>
         <v>iau</v>
       </c>
-      <c r="S33" s="47" t="str">
+      <c r="T33" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>iau(\d)</v>
+      </c>
+      <c r="U33" s="50" t="s">
+        <v>1016</v>
+      </c>
+      <c r="V33" s="50" t="str">
         <f t="shared" si="24"/>
-        <v>iau(\d)</v>
-      </c>
-      <c r="T33" s="50" t="s">
-        <v>1016</v>
-      </c>
-      <c r="U33" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W33" s="47" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="V33" s="47" t="str">
+      <c r="X33" s="19"/>
+      <c r="Y33" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="W33" s="19"/>
-      <c r="X33" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》iau(\d)//</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="27.75" thickBot="1">
+    <row r="34" spans="1:25" ht="27.75" thickBot="1">
       <c r="A34" s="101">
         <f t="shared" si="8"/>
         <v>31</v>
@@ -15573,47 +15746,51 @@
       <c r="K34" s="18" t="s">
         <v>2071</v>
       </c>
-      <c r="L34" s="18" t="s">
+      <c r="L34" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>驚（舒）</v>
+      </c>
+      <c r="M34" s="18" t="s">
         <v>395</v>
       </c>
-      <c r="M34" s="61" t="s">
+      <c r="N34" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N34" s="18">
-        <f t="shared" si="23"/>
+      <c r="O34" s="18">
+        <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="O34" s="26"/>
-      <c r="P34" s="21" t="str">
+      <c r="P34" s="26"/>
+      <c r="Q34" s="21" t="str">
         <f>C32</f>
         <v>ian</v>
       </c>
-      <c r="Q34" s="21" t="str">
+      <c r="R34" s="21" t="str">
         <f>D32</f>
         <v>ian</v>
       </c>
-      <c r="S34" s="47" t="str">
+      <c r="T34" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>ian(\d)</v>
+      </c>
+      <c r="U34" s="50" t="s">
+        <v>1029</v>
+      </c>
+      <c r="V34" s="50">
         <f t="shared" si="24"/>
-        <v>ian(\d)</v>
-      </c>
-      <c r="T34" s="50" t="s">
-        <v>1029</v>
-      </c>
-      <c r="U34" s="50">
+        <v>1</v>
+      </c>
+      <c r="W34" s="47" t="str">
         <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="V34" s="47" t="str">
+        <v>》i${1}an</v>
+      </c>
+      <c r="X34" s="19"/>
+      <c r="Y34" s="20" t="str">
         <f t="shared" si="26"/>
-        <v>》i${1}an</v>
-      </c>
-      <c r="W34" s="19"/>
-      <c r="X34" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》ian(\d)/》i${1}an/</v>
       </c>
     </row>
-    <row r="35" spans="1:24" ht="30.75" thickBot="1">
+    <row r="35" spans="1:25" ht="30.75" thickBot="1">
       <c r="A35" s="101">
         <f t="shared" si="8"/>
         <v>32</v>
@@ -15650,47 +15827,51 @@
       <c r="K35" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="L35" s="70" t="s">
+      <c r="L35" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>迦（促）</v>
+      </c>
+      <c r="M35" s="70" t="s">
         <v>279</v>
       </c>
-      <c r="M35" s="61" t="s">
+      <c r="N35" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N35" s="18">
-        <f t="shared" si="23"/>
+      <c r="O35" s="18">
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
-      <c r="O35" s="26"/>
-      <c r="P35" s="21" t="str">
+      <c r="P35" s="26"/>
+      <c r="Q35" s="21" t="str">
         <f>C36</f>
         <v>iap</v>
       </c>
-      <c r="Q35" s="21" t="str">
+      <c r="R35" s="21" t="str">
         <f>D36</f>
         <v>iap</v>
       </c>
-      <c r="S35" s="47" t="str">
+      <c r="T35" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>iap(\d)</v>
+      </c>
+      <c r="U35" s="50" t="s">
+        <v>1029</v>
+      </c>
+      <c r="V35" s="50">
         <f t="shared" si="24"/>
-        <v>iap(\d)</v>
-      </c>
-      <c r="T35" s="50" t="s">
-        <v>1029</v>
-      </c>
-      <c r="U35" s="50">
+        <v>1</v>
+      </c>
+      <c r="W35" s="47" t="str">
         <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="V35" s="47" t="str">
+        <v>》i${1}ap</v>
+      </c>
+      <c r="X35" s="19"/>
+      <c r="Y35" s="20" t="str">
         <f t="shared" si="26"/>
-        <v>》i${1}ap</v>
-      </c>
-      <c r="W35" s="19"/>
-      <c r="X35" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》iap(\d)/》i${1}ap/</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="27.75" thickBot="1">
+    <row r="36" spans="1:25" ht="27.75" thickBot="1">
       <c r="A36" s="101">
         <f t="shared" si="8"/>
         <v>33</v>
@@ -15726,45 +15907,49 @@
       <c r="K36" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="L36" s="18" t="s">
+      <c r="L36" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>兼（促）</v>
+      </c>
+      <c r="M36" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="M36" s="21"/>
-      <c r="N36" s="18">
-        <f t="shared" si="23"/>
+      <c r="N36" s="21"/>
+      <c r="O36" s="18">
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
-      <c r="O36" s="26"/>
-      <c r="P36" s="21" t="str">
+      <c r="P36" s="26"/>
+      <c r="Q36" s="21" t="str">
         <f>C40</f>
         <v>iaunn</v>
       </c>
-      <c r="Q36" s="21" t="str">
+      <c r="R36" s="21" t="str">
         <f>D40</f>
         <v>iaunn</v>
       </c>
-      <c r="S36" s="47" t="str">
+      <c r="T36" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>iaunn(\d)</v>
+      </c>
+      <c r="U36" s="50" t="s">
+        <v>1016</v>
+      </c>
+      <c r="V36" s="50" t="str">
         <f t="shared" si="24"/>
-        <v>iaunn(\d)</v>
-      </c>
-      <c r="T36" s="50" t="s">
-        <v>1016</v>
-      </c>
-      <c r="U36" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W36" s="47" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="V36" s="47" t="str">
+      <c r="X36" s="19"/>
+      <c r="Y36" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="W36" s="19"/>
-      <c r="X36" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》iaunn(\d)//</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="27.75" thickBot="1">
+    <row r="37" spans="1:25" ht="27.75" thickBot="1">
       <c r="A37" s="101">
         <f t="shared" si="8"/>
         <v>34</v>
@@ -15800,45 +15985,49 @@
       <c r="K37" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="L37" s="18" t="s">
+      <c r="L37" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>堅（促）</v>
+      </c>
+      <c r="M37" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="M37" s="21"/>
-      <c r="N37" s="18">
-        <f t="shared" si="23"/>
+      <c r="N37" s="21"/>
+      <c r="O37" s="18">
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
-      <c r="O37" s="26"/>
-      <c r="P37" s="21" t="str">
+      <c r="P37" s="26"/>
+      <c r="Q37" s="21" t="str">
         <f>C39</f>
         <v>iauh</v>
       </c>
-      <c r="Q37" s="21" t="str">
+      <c r="R37" s="21" t="str">
         <f>D39</f>
         <v>iauh</v>
       </c>
-      <c r="S37" s="47" t="str">
+      <c r="T37" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>iauh(\d)</v>
+      </c>
+      <c r="U37" s="50" t="s">
+        <v>1016</v>
+      </c>
+      <c r="V37" s="50" t="str">
         <f t="shared" si="24"/>
-        <v>iauh(\d)</v>
-      </c>
-      <c r="T37" s="50" t="s">
-        <v>1016</v>
-      </c>
-      <c r="U37" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W37" s="47" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="V37" s="47" t="str">
+      <c r="X37" s="19"/>
+      <c r="Y37" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="W37" s="19"/>
-      <c r="X37" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》iauh(\d)//</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="27.75" thickBot="1">
+    <row r="38" spans="1:25" ht="27.75" thickBot="1">
       <c r="A38" s="101">
         <f t="shared" si="8"/>
         <v>35</v>
@@ -15874,45 +16063,49 @@
       <c r="K38" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="L38" s="18" t="s">
+      <c r="L38" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>嬌（舒）</v>
+      </c>
+      <c r="M38" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="M38" s="21"/>
-      <c r="N38" s="18">
-        <f t="shared" si="23"/>
+      <c r="N38" s="21"/>
+      <c r="O38" s="18">
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
-      <c r="O38" s="26"/>
-      <c r="P38" s="21" t="str">
+      <c r="P38" s="26"/>
+      <c r="Q38" s="21" t="str">
         <f>C53</f>
         <v>ionn</v>
       </c>
-      <c r="Q38" s="21" t="str">
+      <c r="R38" s="21" t="str">
         <f>D53</f>
         <v>ionn</v>
       </c>
-      <c r="S38" s="47" t="str">
+      <c r="T38" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>ionn(\d)</v>
+      </c>
+      <c r="U38" s="50" t="s">
+        <v>1028</v>
+      </c>
+      <c r="V38" s="50" t="str">
         <f t="shared" si="24"/>
-        <v>ionn(\d)</v>
-      </c>
-      <c r="T38" s="50" t="s">
-        <v>1028</v>
-      </c>
-      <c r="U38" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W38" s="47" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="V38" s="47" t="str">
+      <c r="X38" s="19"/>
+      <c r="Y38" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="W38" s="19"/>
-      <c r="X38" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》ionn(\d)//</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="27.75" thickBot="1">
+    <row r="39" spans="1:25" ht="27.75" thickBot="1">
       <c r="A39" s="101">
         <f t="shared" si="8"/>
         <v>36</v>
@@ -15949,45 +16142,49 @@
       <c r="K39" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="L39" s="18" t="s">
+      <c r="L39" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>嬌（促）</v>
+      </c>
+      <c r="M39" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="M39" s="21"/>
-      <c r="N39" s="18">
-        <f t="shared" si="23"/>
+      <c r="N39" s="21"/>
+      <c r="O39" s="18">
+        <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="O39" s="26"/>
-      <c r="P39" s="21" t="str">
+      <c r="P39" s="26"/>
+      <c r="Q39" s="21" t="str">
         <f>C50</f>
         <v>iong</v>
       </c>
-      <c r="Q39" s="21" t="str">
+      <c r="R39" s="21" t="str">
         <f>D50</f>
         <v>iong</v>
       </c>
-      <c r="S39" s="47" t="str">
+      <c r="T39" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>iong(\d)</v>
+      </c>
+      <c r="U39" s="50" t="s">
+        <v>1028</v>
+      </c>
+      <c r="V39" s="50" t="str">
         <f t="shared" si="24"/>
-        <v>iong(\d)</v>
-      </c>
-      <c r="T39" s="50" t="s">
-        <v>1028</v>
-      </c>
-      <c r="U39" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W39" s="47" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="V39" s="47" t="str">
+      <c r="X39" s="19"/>
+      <c r="Y39" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="W39" s="19"/>
-      <c r="X39" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》iong(\d)//</v>
       </c>
     </row>
-    <row r="40" spans="1:24" ht="27.75" thickBot="1">
+    <row r="40" spans="1:25" ht="27.75" thickBot="1">
       <c r="A40" s="101">
         <f t="shared" si="8"/>
         <v>37</v>
@@ -16024,47 +16221,51 @@
       <c r="K40" s="18" t="s">
         <v>462</v>
       </c>
-      <c r="L40" s="18" t="s">
+      <c r="L40" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>嘄（舒）</v>
+      </c>
+      <c r="M40" s="18" t="s">
         <v>468</v>
       </c>
-      <c r="M40" s="61" t="s">
+      <c r="N40" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N40" s="18">
-        <f t="shared" si="23"/>
+      <c r="O40" s="18">
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
-      <c r="O40" s="26"/>
-      <c r="P40" s="21" t="str">
+      <c r="P40" s="26"/>
+      <c r="Q40" s="21" t="str">
         <f>C48</f>
         <v>ioh</v>
       </c>
-      <c r="Q40" s="21" t="str">
+      <c r="R40" s="21" t="str">
         <f>D48</f>
         <v>ioh</v>
       </c>
-      <c r="S40" s="47" t="str">
+      <c r="T40" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>ioh(\d)</v>
+      </c>
+      <c r="U40" s="50" t="s">
+        <v>1028</v>
+      </c>
+      <c r="V40" s="50" t="str">
         <f t="shared" si="24"/>
-        <v>ioh(\d)</v>
-      </c>
-      <c r="T40" s="50" t="s">
-        <v>1028</v>
-      </c>
-      <c r="U40" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W40" s="47" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="V40" s="47" t="str">
+      <c r="X40" s="19"/>
+      <c r="Y40" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="W40" s="19"/>
-      <c r="X40" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》ioh(\d)//</v>
       </c>
     </row>
-    <row r="41" spans="1:24" ht="27.75" thickBot="1">
+    <row r="41" spans="1:25" ht="27.75" thickBot="1">
       <c r="A41" s="101">
         <f t="shared" si="8"/>
         <v>38</v>
@@ -16100,45 +16301,49 @@
       <c r="K41" s="18" t="s">
         <v>328</v>
       </c>
-      <c r="L41" s="18" t="s">
+      <c r="L41" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>居（促）</v>
+      </c>
+      <c r="M41" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="M41" s="21"/>
-      <c r="N41" s="18">
-        <f t="shared" si="23"/>
+      <c r="N41" s="21"/>
+      <c r="O41" s="18">
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
-      <c r="O41" s="26"/>
-      <c r="P41" s="21" t="str">
+      <c r="P41" s="26"/>
+      <c r="Q41" s="21" t="str">
         <f>C51</f>
         <v>ip</v>
       </c>
-      <c r="Q41" s="21" t="str">
+      <c r="R41" s="21" t="str">
         <f>D51</f>
         <v>ip</v>
       </c>
-      <c r="S41" s="47" t="str">
+      <c r="T41" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>ip(\d)</v>
+      </c>
+      <c r="U41" s="50" t="s">
+        <v>1028</v>
+      </c>
+      <c r="V41" s="50" t="str">
         <f t="shared" si="24"/>
-        <v>ip(\d)</v>
-      </c>
-      <c r="T41" s="50" t="s">
-        <v>1028</v>
-      </c>
-      <c r="U41" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W41" s="47" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="V41" s="47" t="str">
+      <c r="X41" s="19"/>
+      <c r="Y41" s="20" t="str">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="W41" s="19"/>
-      <c r="X41" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》ip(\d)//</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="27.75" thickBot="1">
+    <row r="42" spans="1:25" ht="27.75" thickBot="1">
       <c r="A42" s="101">
         <f t="shared" si="8"/>
         <v>39</v>
@@ -16174,45 +16379,49 @@
       <c r="K42" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="L42" s="18" t="s">
+      <c r="L42" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>經（促）</v>
+      </c>
+      <c r="M42" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="M42" s="21"/>
-      <c r="N42" s="18">
-        <f t="shared" si="23"/>
+      <c r="N42" s="21"/>
+      <c r="O42" s="18">
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
-      <c r="O42" s="26"/>
-      <c r="P42" s="21" t="str">
+      <c r="P42" s="26"/>
+      <c r="Q42" s="21" t="str">
         <f>C35</f>
         <v>iannh</v>
       </c>
-      <c r="Q42" s="21" t="str">
+      <c r="R42" s="21" t="str">
         <f>D35</f>
         <v>iannh</v>
       </c>
-      <c r="S42" s="47" t="str">
+      <c r="T42" s="47" t="str">
+        <f t="shared" si="23"/>
+        <v>iannh(\d)</v>
+      </c>
+      <c r="U42" s="50" t="s">
+        <v>1028</v>
+      </c>
+      <c r="V42" s="50">
         <f t="shared" si="24"/>
-        <v>iannh(\d)</v>
-      </c>
-      <c r="T42" s="50" t="s">
-        <v>1028</v>
-      </c>
-      <c r="U42" s="50">
+        <v>2</v>
+      </c>
+      <c r="W42" s="47" t="str">
         <f t="shared" si="25"/>
-        <v>2</v>
-      </c>
-      <c r="V42" s="47" t="str">
+        <v>i》a${1}nnh</v>
+      </c>
+      <c r="X42" s="19"/>
+      <c r="Y42" s="20" t="str">
         <f t="shared" si="26"/>
-        <v>i》a${1}nnh</v>
-      </c>
-      <c r="W42" s="19"/>
-      <c r="X42" s="20" t="str">
-        <f t="shared" si="27"/>
         <v xml:space="preserve">    - xform/》iannh(\d)/i》a${1}nnh/</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="27.75" thickBot="1">
+    <row r="43" spans="1:25" ht="27.75" thickBot="1">
       <c r="A43" s="101">
         <f t="shared" si="8"/>
         <v>40</v>
@@ -16248,45 +16457,49 @@
       <c r="K43" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="L43" s="18" t="s">
+      <c r="L43" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>金（舒）</v>
+      </c>
+      <c r="M43" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="M43" s="21"/>
-      <c r="N43" s="18">
+      <c r="N43" s="21"/>
+      <c r="O43" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O43" s="26"/>
-      <c r="P43" s="21" t="str">
-        <f t="shared" ref="P43" si="28">C52</f>
+      <c r="P43" s="26"/>
+      <c r="Q43" s="21" t="str">
+        <f t="shared" ref="Q43" si="27">C52</f>
         <v>it</v>
       </c>
-      <c r="Q43" s="21" t="str">
-        <f t="shared" ref="Q43" si="29">D52</f>
+      <c r="R43" s="21" t="str">
+        <f t="shared" ref="R43" si="28">D52</f>
         <v>it</v>
       </c>
-      <c r="S43" s="47" t="str">
+      <c r="T43" s="47" t="str">
         <f t="shared" si="13"/>
         <v>it(\d)</v>
       </c>
-      <c r="T43" s="50" t="s">
+      <c r="U43" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U43" s="50" t="str">
+      <c r="V43" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V43" s="47" t="str">
+      <c r="W43" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W43" s="19"/>
-      <c r="X43" s="20" t="str">
+      <c r="X43" s="19"/>
+      <c r="Y43" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》it(\d)//</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="27.75" thickBot="1">
+    <row r="44" spans="1:25" ht="27.75" thickBot="1">
       <c r="A44" s="101">
         <f t="shared" si="8"/>
         <v>41</v>
@@ -16322,45 +16535,49 @@
       <c r="K44" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="L44" s="18" t="s">
+      <c r="L44" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>巾（舒）</v>
+      </c>
+      <c r="M44" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="M44" s="21"/>
-      <c r="N44" s="18">
+      <c r="N44" s="21"/>
+      <c r="O44" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O44" s="26"/>
-      <c r="P44" s="21" t="str">
+      <c r="P44" s="26"/>
+      <c r="Q44" s="21" t="str">
         <f>C42</f>
         <v>ik</v>
       </c>
-      <c r="Q44" s="21" t="str">
+      <c r="R44" s="21" t="str">
         <f>D42</f>
         <v>ik</v>
       </c>
-      <c r="S44" s="47" t="str">
+      <c r="T44" s="47" t="str">
         <f t="shared" si="13"/>
         <v>ik(\d)</v>
       </c>
-      <c r="T44" s="50" t="s">
+      <c r="U44" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U44" s="50" t="str">
+      <c r="V44" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V44" s="47" t="str">
+      <c r="W44" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W44" s="19"/>
-      <c r="X44" s="20" t="str">
+      <c r="X44" s="19"/>
+      <c r="Y44" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》ik(\d)//</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="27.75" thickBot="1">
+    <row r="45" spans="1:25" ht="27.75" thickBot="1">
       <c r="A45" s="101">
         <f t="shared" si="8"/>
         <v>42</v>
@@ -16396,45 +16613,49 @@
       <c r="K45" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="L45" s="18" t="s">
+      <c r="L45" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>經（舒）</v>
+      </c>
+      <c r="M45" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="M45" s="21"/>
-      <c r="N45" s="18">
+      <c r="N45" s="21"/>
+      <c r="O45" s="18">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="O45" s="26"/>
-      <c r="P45" s="21" t="str">
+      <c r="P45" s="26"/>
+      <c r="Q45" s="21" t="str">
         <f>C28</f>
         <v>ia</v>
       </c>
-      <c r="Q45" s="21" t="str">
+      <c r="R45" s="21" t="str">
         <f>D28</f>
         <v>ia</v>
       </c>
-      <c r="S45" s="47" t="str">
+      <c r="T45" s="47" t="str">
         <f t="shared" si="13"/>
         <v>ia(\d)</v>
       </c>
-      <c r="T45" s="50" t="s">
+      <c r="U45" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U45" s="50">
+      <c r="V45" s="50">
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="V45" s="47" t="str">
+      <c r="W45" s="47" t="str">
         <f t="shared" si="15"/>
         <v>i》a${1}</v>
       </c>
-      <c r="W45" s="19"/>
-      <c r="X45" s="20" t="str">
+      <c r="X45" s="19"/>
+      <c r="Y45" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》ia(\d)/i》a${1}/</v>
       </c>
     </row>
-    <row r="46" spans="1:24" ht="27.75" thickBot="1">
+    <row r="46" spans="1:25" ht="27.75" thickBot="1">
       <c r="A46" s="101">
         <f t="shared" si="8"/>
         <v>43</v>
@@ -16470,47 +16691,51 @@
       <c r="K46" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="L46" s="18" t="s">
+      <c r="L46" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>梔（舒）</v>
+      </c>
+      <c r="M46" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="M46" s="61" t="s">
+      <c r="N46" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N46" s="18">
+      <c r="O46" s="18">
         <f xml:space="preserve"> LEN(D46)</f>
         <v>3</v>
       </c>
-      <c r="O46" s="26"/>
-      <c r="P46" s="21" t="str">
+      <c r="P46" s="26"/>
+      <c r="Q46" s="21" t="str">
         <f>C45</f>
         <v>ing</v>
       </c>
-      <c r="Q46" s="21" t="str">
+      <c r="R46" s="21" t="str">
         <f>D45</f>
         <v>ing</v>
       </c>
-      <c r="S46" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P46, "(\d)")</f>
+      <c r="T46" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q46, "(\d)")</f>
         <v>ing(\d)</v>
       </c>
-      <c r="T46" s="50" t="s">
+      <c r="U46" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U46" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T46="", "", SEARCH(T46, $P46)), "")</f>
+      <c r="V46" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U46="", "", SEARCH(U46, $Q46)), "")</f>
         <v/>
       </c>
-      <c r="V46" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P46,U46-1), "》", MID(P46,U46,1), "${1}", RIGHT(P46, LEN(P46)-U46)), "" )</f>
+      <c r="W46" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q46,V46-1), "》", MID(Q46,V46,1), "${1}", RIGHT(Q46, LEN(Q46)-V46)), "" )</f>
         <v/>
       </c>
-      <c r="W46" s="19"/>
-      <c r="X46" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q46&lt;&gt;"", P46&lt;&gt;""), "    - xform/》" &amp; S46 &amp;  "/"  &amp; V46 &amp;  "/", "")</f>
+      <c r="X46" s="19"/>
+      <c r="Y46" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R46&lt;&gt;"", Q46&lt;&gt;""), "    - xform/》" &amp; T46 &amp;  "/"  &amp; W46 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》ing(\d)//</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="27.75" thickBot="1">
+    <row r="47" spans="1:25" ht="27.75" thickBot="1">
       <c r="A47" s="101">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -16546,45 +16771,49 @@
       <c r="K47" s="18" t="s">
         <v>356</v>
       </c>
-      <c r="L47" s="18" t="s">
+      <c r="L47" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>茄（舒）</v>
+      </c>
+      <c r="M47" s="18" t="s">
         <v>361</v>
       </c>
-      <c r="M47" s="21"/>
-      <c r="N47" s="18">
+      <c r="N47" s="21"/>
+      <c r="O47" s="18">
         <f xml:space="preserve"> LEN(D47)</f>
         <v>2</v>
       </c>
-      <c r="O47" s="26"/>
-      <c r="P47" s="21" t="str">
+      <c r="P47" s="26"/>
+      <c r="Q47" s="21" t="str">
         <f>C49</f>
         <v>iok</v>
       </c>
-      <c r="Q47" s="21" t="str">
+      <c r="R47" s="21" t="str">
         <f>D49</f>
         <v>iok</v>
       </c>
-      <c r="S47" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P47, "(\d)")</f>
+      <c r="T47" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q47, "(\d)")</f>
         <v>iok(\d)</v>
       </c>
-      <c r="T47" s="50" t="s">
+      <c r="U47" s="50" t="s">
         <v>981</v>
       </c>
-      <c r="U47" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T47="", "", SEARCH(T47, $P47)), "")</f>
+      <c r="V47" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U47="", "", SEARCH(U47, $Q47)), "")</f>
         <v/>
       </c>
-      <c r="V47" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P47,U47-1), "》", MID(P47,U47,1), "${1}", RIGHT(P47, LEN(P47)-U47)), "" )</f>
+      <c r="W47" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q47,V47-1), "》", MID(Q47,V47,1), "${1}", RIGHT(Q47, LEN(Q47)-V47)), "" )</f>
         <v/>
       </c>
-      <c r="W47" s="19"/>
-      <c r="X47" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q47&lt;&gt;"", P47&lt;&gt;""), "    - xform/》" &amp; S47 &amp;  "/"  &amp; V47 &amp;  "/", "")</f>
+      <c r="X47" s="19"/>
+      <c r="Y47" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R47&lt;&gt;"", Q47&lt;&gt;""), "    - xform/》" &amp; T47 &amp;  "/"  &amp; W47 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》iok(\d)//</v>
       </c>
     </row>
-    <row r="48" spans="1:24" ht="27.75" thickBot="1">
+    <row r="48" spans="1:25" ht="27.75" thickBot="1">
       <c r="A48" s="101">
         <f t="shared" si="8"/>
         <v>45</v>
@@ -16620,45 +16849,49 @@
       <c r="K48" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="L48" s="18" t="s">
+      <c r="L48" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>茄（促）</v>
+      </c>
+      <c r="M48" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="M48" s="21"/>
-      <c r="N48" s="18">
+      <c r="N48" s="21"/>
+      <c r="O48" s="18">
         <f xml:space="preserve"> LEN(D48)</f>
         <v>3</v>
       </c>
-      <c r="O48" s="26"/>
-      <c r="P48" s="21" t="str">
+      <c r="P48" s="26"/>
+      <c r="Q48" s="21" t="str">
         <f>C55</f>
         <v>iunn</v>
       </c>
-      <c r="Q48" s="21" t="str">
+      <c r="R48" s="21" t="str">
         <f>D55</f>
         <v>iunn</v>
       </c>
-      <c r="S48" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P48, "(\d)")</f>
+      <c r="T48" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q48, "(\d)")</f>
         <v>iunn(\d)</v>
       </c>
-      <c r="T48" s="50" t="s">
+      <c r="U48" s="50" t="s">
         <v>1029</v>
       </c>
-      <c r="U48" s="50">
-        <f xml:space="preserve"> IFERROR( IF(T48="", "", SEARCH(T48, $P48)), "")</f>
+      <c r="V48" s="50">
+        <f xml:space="preserve"> IFERROR( IF(U48="", "", SEARCH(U48, $Q48)), "")</f>
         <v>1</v>
       </c>
-      <c r="V48" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P48,U48-1), "》", MID(P48,U48,1), "${1}", RIGHT(P48, LEN(P48)-U48)), "" )</f>
+      <c r="W48" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q48,V48-1), "》", MID(Q48,V48,1), "${1}", RIGHT(Q48, LEN(Q48)-V48)), "" )</f>
         <v>》i${1}unn</v>
       </c>
-      <c r="W48" s="19"/>
-      <c r="X48" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q48&lt;&gt;"", P48&lt;&gt;""), "    - xform/》" &amp; S48 &amp;  "/"  &amp; V48 &amp;  "/", "")</f>
+      <c r="X48" s="19"/>
+      <c r="Y48" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R48&lt;&gt;"", Q48&lt;&gt;""), "    - xform/》" &amp; T48 &amp;  "/"  &amp; W48 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》iunn(\d)/》i${1}unn/</v>
       </c>
     </row>
-    <row r="49" spans="1:24" ht="27.75" thickBot="1">
+    <row r="49" spans="1:25" ht="27.75" thickBot="1">
       <c r="A49" s="101">
         <f t="shared" si="8"/>
         <v>46</v>
@@ -16694,45 +16927,49 @@
       <c r="K49" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="L49" s="18" t="s">
+      <c r="L49" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>恭（促）</v>
+      </c>
+      <c r="M49" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="M49" s="21"/>
-      <c r="N49" s="18">
+      <c r="N49" s="21"/>
+      <c r="O49" s="18">
         <f xml:space="preserve"> LEN(D49)</f>
         <v>3</v>
       </c>
-      <c r="O49" s="26"/>
-      <c r="P49" s="21" t="str">
+      <c r="P49" s="26"/>
+      <c r="Q49" s="21" t="str">
         <f>C61</f>
         <v>o</v>
       </c>
-      <c r="Q49" s="21" t="str">
+      <c r="R49" s="21" t="str">
         <f>D61</f>
         <v>o</v>
       </c>
-      <c r="S49" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P49, "(\d)")</f>
+      <c r="T49" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q49, "(\d)")</f>
         <v>o(\d)</v>
       </c>
-      <c r="T49" s="50" t="s">
+      <c r="U49" s="50" t="s">
         <v>1029</v>
       </c>
-      <c r="U49" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T49="", "", SEARCH(T49, $P49)), "")</f>
+      <c r="V49" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U49="", "", SEARCH(U49, $Q49)), "")</f>
         <v/>
       </c>
-      <c r="V49" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P49,U49-1), "》", MID(P49,U49,1), "${1}", RIGHT(P49, LEN(P49)-U49)), "" )</f>
+      <c r="W49" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q49,V49-1), "》", MID(Q49,V49,1), "${1}", RIGHT(Q49, LEN(Q49)-V49)), "" )</f>
         <v/>
       </c>
-      <c r="W49" s="19"/>
-      <c r="X49" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q49&lt;&gt;"", P49&lt;&gt;""), "    - xform/》" &amp; S49 &amp;  "/"  &amp; V49 &amp;  "/", "")</f>
+      <c r="X49" s="19"/>
+      <c r="Y49" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R49&lt;&gt;"", Q49&lt;&gt;""), "    - xform/》" &amp; T49 &amp;  "/"  &amp; W49 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》o(\d)//</v>
       </c>
     </row>
-    <row r="50" spans="1:24" ht="27.75" thickBot="1">
+    <row r="50" spans="1:25" ht="27.75" thickBot="1">
       <c r="A50" s="101">
         <f t="shared" si="8"/>
         <v>47</v>
@@ -16768,45 +17005,49 @@
       <c r="K50" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="L50" s="18" t="s">
+      <c r="L50" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>恭（舒）</v>
+      </c>
+      <c r="M50" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="M50" s="21"/>
-      <c r="N50" s="18">
+      <c r="N50" s="21"/>
+      <c r="O50" s="18">
         <f xml:space="preserve"> LEN(D50)</f>
         <v>4</v>
       </c>
-      <c r="O50" s="26"/>
-      <c r="P50" s="21" t="str">
+      <c r="P50" s="26"/>
+      <c r="Q50" s="21" t="str">
         <f>C56</f>
         <v>iunnh</v>
       </c>
-      <c r="Q50" s="21" t="str">
+      <c r="R50" s="21" t="str">
         <f>D56</f>
         <v>iunnh</v>
       </c>
-      <c r="S50" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P50, "(\d)")</f>
+      <c r="T50" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q50, "(\d)")</f>
         <v>iunnh(\d)</v>
       </c>
-      <c r="T50" s="50" t="s">
+      <c r="U50" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U50" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T50="", "", SEARCH(T50, $P50)), "")</f>
+      <c r="V50" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U50="", "", SEARCH(U50, $Q50)), "")</f>
         <v/>
       </c>
-      <c r="V50" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P50,U50-1), "》", MID(P50,U50,1), "${1}", RIGHT(P50, LEN(P50)-U50)), "" )</f>
+      <c r="W50" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q50,V50-1), "》", MID(Q50,V50,1), "${1}", RIGHT(Q50, LEN(Q50)-V50)), "" )</f>
         <v/>
       </c>
-      <c r="W50" s="19"/>
-      <c r="X50" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q50&lt;&gt;"", P50&lt;&gt;""), "    - xform/》" &amp; S50 &amp;  "/"  &amp; V50 &amp;  "/", "")</f>
+      <c r="X50" s="19"/>
+      <c r="Y50" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R50&lt;&gt;"", Q50&lt;&gt;""), "    - xform/》" &amp; T50 &amp;  "/"  &amp; W50 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》iunnh(\d)//</v>
       </c>
     </row>
-    <row r="51" spans="1:24" ht="27.75" thickBot="1">
+    <row r="51" spans="1:25" ht="27.75" thickBot="1">
       <c r="A51" s="101">
         <f t="shared" si="8"/>
         <v>48</v>
@@ -16842,45 +17083,49 @@
       <c r="K51" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="L51" s="18" t="s">
+      <c r="L51" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>金（促）</v>
+      </c>
+      <c r="M51" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="M51" s="21"/>
-      <c r="N51" s="18">
+      <c r="N51" s="21"/>
+      <c r="O51" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O51" s="26"/>
-      <c r="P51" s="21" t="str">
+      <c r="P51" s="26"/>
+      <c r="Q51" s="21" t="str">
         <f>C34</f>
         <v>iann</v>
       </c>
-      <c r="Q51" s="21" t="str">
+      <c r="R51" s="21" t="str">
         <f>D34</f>
         <v>iann</v>
       </c>
-      <c r="S51" s="47" t="str">
+      <c r="T51" s="47" t="str">
         <f t="shared" si="13"/>
         <v>iann(\d)</v>
       </c>
-      <c r="T51" s="50" t="s">
+      <c r="U51" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U51" s="50">
+      <c r="V51" s="50">
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="V51" s="47" t="str">
+      <c r="W51" s="47" t="str">
         <f t="shared" si="15"/>
         <v>i》a${1}nn</v>
       </c>
-      <c r="W51" s="19"/>
-      <c r="X51" s="20" t="str">
+      <c r="X51" s="19"/>
+      <c r="Y51" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》iann(\d)/i》a${1}nn/</v>
       </c>
     </row>
-    <row r="52" spans="1:24" ht="27.75" thickBot="1">
+    <row r="52" spans="1:25" ht="27.75" thickBot="1">
       <c r="A52" s="101">
         <f t="shared" si="8"/>
         <v>49</v>
@@ -16916,45 +17161,49 @@
       <c r="K52" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="L52" s="18" t="s">
+      <c r="L52" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>巾（促）</v>
+      </c>
+      <c r="M52" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="M52" s="21"/>
-      <c r="N52" s="18">
+      <c r="N52" s="21"/>
+      <c r="O52" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O52" s="26"/>
-      <c r="P52" s="21" t="str">
+      <c r="P52" s="26"/>
+      <c r="Q52" s="21" t="str">
         <f>C29</f>
         <v>iah</v>
       </c>
-      <c r="Q52" s="21" t="str">
+      <c r="R52" s="21" t="str">
         <f>D29</f>
         <v>iah</v>
       </c>
-      <c r="S52" s="47" t="str">
+      <c r="T52" s="47" t="str">
         <f t="shared" si="13"/>
         <v>iah(\d)</v>
       </c>
-      <c r="T52" s="50" t="s">
+      <c r="U52" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U52" s="50">
+      <c r="V52" s="50">
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="V52" s="47" t="str">
+      <c r="W52" s="47" t="str">
         <f t="shared" si="15"/>
         <v>i》a${1}h</v>
       </c>
-      <c r="W52" s="19"/>
-      <c r="X52" s="20" t="str">
+      <c r="X52" s="19"/>
+      <c r="Y52" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》iah(\d)/i》a${1}h/</v>
       </c>
     </row>
-    <row r="53" spans="1:24" ht="27.75" thickBot="1">
+    <row r="53" spans="1:25" ht="27.75" thickBot="1">
       <c r="A53" s="101">
         <f t="shared" si="8"/>
         <v>50</v>
@@ -16990,47 +17239,51 @@
       <c r="K53" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="L53" s="18" t="s">
+      <c r="L53" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>薑（舒）</v>
+      </c>
+      <c r="M53" s="18" t="s">
         <v>387</v>
       </c>
-      <c r="M53" s="61" t="s">
+      <c r="N53" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N53" s="18">
+      <c r="O53" s="18">
         <f xml:space="preserve"> LEN(D53)</f>
         <v>4</v>
       </c>
-      <c r="O53" s="26"/>
-      <c r="P53" s="21" t="str">
+      <c r="P53" s="26"/>
+      <c r="Q53" s="21" t="str">
         <f>C54</f>
         <v>iu</v>
       </c>
-      <c r="Q53" s="21" t="str">
+      <c r="R53" s="21" t="str">
         <f>D54</f>
         <v>iu</v>
       </c>
-      <c r="S53" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P53, "(\d)")</f>
+      <c r="T53" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q53, "(\d)")</f>
         <v>iu(\d)</v>
       </c>
-      <c r="T53" s="50" t="s">
+      <c r="U53" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U53" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T53="", "", SEARCH(T53, $P53)), "")</f>
+      <c r="V53" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U53="", "", SEARCH(U53, $Q53)), "")</f>
         <v/>
       </c>
-      <c r="V53" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P53,U53-1), "》", MID(P53,U53,1), "${1}", RIGHT(P53, LEN(P53)-U53)), "" )</f>
+      <c r="W53" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q53,V53-1), "》", MID(Q53,V53,1), "${1}", RIGHT(Q53, LEN(Q53)-V53)), "" )</f>
         <v/>
       </c>
-      <c r="W53" s="19"/>
-      <c r="X53" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q53&lt;&gt;"", P53&lt;&gt;""), "    - xform/》" &amp; S53 &amp;  "/"  &amp; V53 &amp;  "/", "")</f>
+      <c r="X53" s="19"/>
+      <c r="Y53" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R53&lt;&gt;"", Q53&lt;&gt;""), "    - xform/》" &amp; T53 &amp;  "/"  &amp; W53 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》iu(\d)//</v>
       </c>
     </row>
-    <row r="54" spans="1:24" ht="27.75" thickBot="1">
+    <row r="54" spans="1:25" ht="27.75" thickBot="1">
       <c r="A54" s="101">
         <f t="shared" si="8"/>
         <v>51</v>
@@ -17067,45 +17320,49 @@
       <c r="K54" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="L54" s="18" t="s">
+      <c r="L54" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>丩（舒）</v>
+      </c>
+      <c r="M54" s="18" t="s">
         <v>335</v>
       </c>
-      <c r="M54" s="21"/>
-      <c r="N54" s="18">
-        <f t="shared" ref="N54:N89" si="30" xml:space="preserve"> LEN(D54)</f>
+      <c r="N54" s="21"/>
+      <c r="O54" s="18">
+        <f t="shared" ref="O54:O89" si="29" xml:space="preserve"> LEN(D54)</f>
         <v>2</v>
       </c>
-      <c r="O54" s="26"/>
-      <c r="P54" s="21" t="str">
+      <c r="P54" s="26"/>
+      <c r="Q54" s="21" t="str">
         <f>C68</f>
         <v>oo</v>
       </c>
-      <c r="Q54" s="21" t="str">
+      <c r="R54" s="21" t="str">
         <f>D68</f>
         <v>oo</v>
       </c>
-      <c r="S54" s="47" t="str">
+      <c r="T54" s="47" t="str">
         <f t="shared" si="13"/>
         <v>oo(\d)</v>
       </c>
-      <c r="T54" s="50" t="s">
+      <c r="U54" s="50" t="s">
         <v>981</v>
       </c>
-      <c r="U54" s="50" t="str">
+      <c r="V54" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V54" s="47" t="str">
+      <c r="W54" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W54" s="19"/>
-      <c r="X54" s="20" t="str">
+      <c r="X54" s="19"/>
+      <c r="Y54" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》oo(\d)//</v>
       </c>
     </row>
-    <row r="55" spans="1:24" ht="27.75" thickBot="1">
+    <row r="55" spans="1:25" ht="27.75" thickBot="1">
       <c r="A55" s="101">
         <f t="shared" si="8"/>
         <v>52</v>
@@ -17142,47 +17399,51 @@
       <c r="K55" s="18" t="s">
         <v>501</v>
       </c>
-      <c r="L55" s="18" t="s">
+      <c r="L55" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>牛（舒）</v>
+      </c>
+      <c r="M55" s="18" t="s">
         <v>507</v>
       </c>
-      <c r="M55" s="61" t="s">
+      <c r="N55" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N55" s="18">
-        <f t="shared" si="30"/>
+      <c r="O55" s="18">
+        <f t="shared" si="29"/>
         <v>4</v>
       </c>
-      <c r="O55" s="26"/>
-      <c r="P55" s="21" t="str">
+      <c r="P55" s="26"/>
+      <c r="Q55" s="21" t="str">
         <f>C66</f>
         <v>onn</v>
       </c>
-      <c r="Q55" s="21" t="str">
+      <c r="R55" s="21" t="str">
         <f>D66</f>
         <v>onn</v>
       </c>
-      <c r="S55" s="47" t="str">
+      <c r="T55" s="47" t="str">
         <f t="shared" si="13"/>
         <v>onn(\d)</v>
       </c>
-      <c r="T55" s="50" t="s">
+      <c r="U55" s="50" t="s">
         <v>981</v>
       </c>
-      <c r="U55" s="50" t="str">
+      <c r="V55" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V55" s="47" t="str">
+      <c r="W55" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W55" s="19"/>
-      <c r="X55" s="20" t="str">
+      <c r="X55" s="19"/>
+      <c r="Y55" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》onn(\d)//</v>
       </c>
     </row>
-    <row r="56" spans="1:24" ht="30.75" thickBot="1">
+    <row r="56" spans="1:25" ht="30.75" thickBot="1">
       <c r="A56" s="101">
         <f t="shared" si="8"/>
         <v>53</v>
@@ -17219,49 +17480,53 @@
       <c r="K56" s="18" t="s">
         <v>2071</v>
       </c>
-      <c r="L56" s="70" t="s">
+      <c r="L56" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>牛（促）</v>
+      </c>
+      <c r="M56" s="70" t="s">
         <v>1947</v>
       </c>
-      <c r="M56" s="61" t="s">
+      <c r="N56" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N56" s="18">
-        <f t="shared" si="30"/>
+      <c r="O56" s="18">
+        <f t="shared" si="29"/>
         <v>5</v>
       </c>
-      <c r="O56" s="26"/>
-      <c r="P56" s="21" t="str">
+      <c r="P56" s="26"/>
+      <c r="Q56" s="21" t="str">
         <f>C62</f>
         <v>oh</v>
       </c>
-      <c r="Q56" s="21" t="str">
+      <c r="R56" s="21" t="str">
         <f>D62</f>
         <v>oh</v>
       </c>
-      <c r="S56" s="47" t="str">
+      <c r="T56" s="47" t="str">
         <f t="shared" si="13"/>
         <v>oh(\d)</v>
       </c>
-      <c r="T56" s="50" t="s">
+      <c r="U56" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U56" s="50" t="str">
+      <c r="V56" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V56" s="47" t="str">
+      <c r="W56" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W56" s="19"/>
-      <c r="X56" s="20" t="str">
+      <c r="X56" s="19"/>
+      <c r="Y56" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》oh(\d)//</v>
       </c>
     </row>
-    <row r="57" spans="1:24" ht="27.75" thickBot="1">
+    <row r="57" spans="1:25" ht="27.75" thickBot="1">
       <c r="A57" s="101">
-        <f t="shared" ref="A57:A87" si="31" xml:space="preserve"> ROW() - 3</f>
+        <f t="shared" ref="A57:A87" si="30" xml:space="preserve"> ROW() - 3</f>
         <v>54</v>
       </c>
       <c r="B57" s="63" t="s">
@@ -17295,18 +17560,22 @@
       <c r="K57" s="18" t="s">
         <v>428</v>
       </c>
-      <c r="L57" s="18" t="s">
+      <c r="L57" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>姆（舒）</v>
+      </c>
+      <c r="M57" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="M57" s="21"/>
-      <c r="N57" s="18">
+      <c r="N57" s="21"/>
+      <c r="O57" s="18">
         <f xml:space="preserve"> LEN(D57)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:24" ht="27.75" thickBot="1">
+    <row r="58" spans="1:25" ht="27.75" thickBot="1">
       <c r="A58" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>55</v>
       </c>
       <c r="B58" s="63" t="s">
@@ -17340,18 +17609,22 @@
       <c r="K58" s="18" t="s">
         <v>2071</v>
       </c>
-      <c r="L58" s="69" t="s">
+      <c r="L58" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>姆（促）</v>
+      </c>
+      <c r="M58" s="69" t="s">
         <v>1942</v>
       </c>
-      <c r="M58" s="21"/>
-      <c r="N58" s="18">
+      <c r="N58" s="21"/>
+      <c r="O58" s="18">
         <f xml:space="preserve"> LEN(D58)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:24" ht="27.75" thickBot="1">
+    <row r="59" spans="1:25" ht="27.75" thickBot="1">
       <c r="A59" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>56</v>
       </c>
       <c r="B59" s="63" t="s">
@@ -17385,18 +17658,22 @@
       <c r="K59" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="L59" s="18" t="s">
+      <c r="L59" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>鋼（舒）</v>
+      </c>
+      <c r="M59" s="18" t="s">
         <v>408</v>
       </c>
-      <c r="M59" s="21"/>
-      <c r="N59" s="18">
+      <c r="N59" s="21"/>
+      <c r="O59" s="18">
         <f xml:space="preserve"> LEN(D59)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:24" ht="27.75" thickBot="1">
+    <row r="60" spans="1:25" ht="27.75" thickBot="1">
       <c r="A60" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>57</v>
       </c>
       <c r="B60" s="63" t="s">
@@ -17430,16 +17707,20 @@
       <c r="K60" s="18" t="s">
         <v>2071</v>
       </c>
-      <c r="L60" s="69" t="s">
+      <c r="L60" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>鋼（促）</v>
+      </c>
+      <c r="M60" s="69" t="s">
         <v>1944</v>
       </c>
-      <c r="M60" s="21"/>
-      <c r="N60" s="18">
+      <c r="N60" s="21"/>
+      <c r="O60" s="18">
         <f xml:space="preserve"> LEN(D60)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:24" ht="27.75" thickBot="1">
+    <row r="61" spans="1:25" ht="27.75" thickBot="1">
       <c r="A61" s="101">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -17475,45 +17756,49 @@
       <c r="K61" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="L61" s="18" t="s">
+      <c r="L61" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>高（舒）</v>
+      </c>
+      <c r="M61" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="M61" s="21"/>
-      <c r="N61" s="18">
-        <f t="shared" si="30"/>
+      <c r="N61" s="21"/>
+      <c r="O61" s="18">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
-      <c r="O61" s="26"/>
-      <c r="P61" s="21" t="str">
+      <c r="P61" s="26"/>
+      <c r="Q61" s="21" t="str">
         <f>C69</f>
         <v>ooh</v>
       </c>
-      <c r="Q61" s="21" t="str">
+      <c r="R61" s="21" t="str">
         <f>D69</f>
         <v>ooh</v>
       </c>
-      <c r="S61" s="47" t="str">
+      <c r="T61" s="47" t="str">
         <f t="shared" si="13"/>
         <v>ooh(\d)</v>
       </c>
-      <c r="T61" s="50" t="s">
+      <c r="U61" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U61" s="50" t="str">
+      <c r="V61" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V61" s="47" t="str">
+      <c r="W61" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W61" s="19"/>
-      <c r="X61" s="20" t="str">
+      <c r="X61" s="19"/>
+      <c r="Y61" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》ooh(\d)//</v>
       </c>
     </row>
-    <row r="62" spans="1:24" ht="27.75" thickBot="1">
+    <row r="62" spans="1:25" ht="27.75" thickBot="1">
       <c r="A62" s="101">
         <f t="shared" si="8"/>
         <v>59</v>
@@ -17549,45 +17834,49 @@
       <c r="K62" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="L62" s="18" t="s">
+      <c r="L62" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>高（促）</v>
+      </c>
+      <c r="M62" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="M62" s="21"/>
-      <c r="N62" s="18">
-        <f t="shared" ref="N62:N67" si="32" xml:space="preserve"> LEN(D62)</f>
+      <c r="N62" s="21"/>
+      <c r="O62" s="18">
+        <f t="shared" ref="O62:O67" si="31" xml:space="preserve"> LEN(D62)</f>
         <v>2</v>
       </c>
-      <c r="O62" s="26"/>
-      <c r="P62" s="21" t="str">
+      <c r="P62" s="26"/>
+      <c r="Q62" s="21" t="str">
         <f>C65</f>
         <v>ong</v>
       </c>
-      <c r="Q62" s="21" t="str">
+      <c r="R62" s="21" t="str">
         <f>D65</f>
         <v>ong</v>
       </c>
-      <c r="S62" s="47" t="str">
-        <f t="shared" ref="S62:S67" si="33" xml:space="preserve"> _xlfn.CONCAT(P62, "(\d)")</f>
+      <c r="T62" s="47" t="str">
+        <f t="shared" ref="T62:T67" si="32" xml:space="preserve"> _xlfn.CONCAT(Q62, "(\d)")</f>
         <v>ong(\d)</v>
       </c>
-      <c r="T62" s="50" t="s">
+      <c r="U62" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U62" s="50" t="str">
-        <f t="shared" ref="U62:U67" si="34" xml:space="preserve"> IFERROR( IF(T62="", "", SEARCH(T62, $P62)), "")</f>
+      <c r="V62" s="50" t="str">
+        <f t="shared" ref="V62:V67" si="33" xml:space="preserve"> IFERROR( IF(U62="", "", SEARCH(U62, $Q62)), "")</f>
         <v/>
       </c>
-      <c r="V62" s="47" t="str">
-        <f t="shared" ref="V62:V67" si="35" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P62,U62-1), "》", MID(P62,U62,1), "${1}", RIGHT(P62, LEN(P62)-U62)), "" )</f>
+      <c r="W62" s="47" t="str">
+        <f t="shared" ref="W62:W67" si="34" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q62,V62-1), "》", MID(Q62,V62,1), "${1}", RIGHT(Q62, LEN(Q62)-V62)), "" )</f>
         <v/>
       </c>
-      <c r="W62" s="19"/>
-      <c r="X62" s="20" t="str">
-        <f t="shared" ref="X62:X67" si="36" xml:space="preserve"> IF(AND(Q62&lt;&gt;"", P62&lt;&gt;""), "    - xform/》" &amp; S62 &amp;  "/"  &amp; V62 &amp;  "/", "")</f>
+      <c r="X62" s="19"/>
+      <c r="Y62" s="20" t="str">
+        <f t="shared" ref="Y62:Y67" si="35" xml:space="preserve"> IF(AND(R62&lt;&gt;"", Q62&lt;&gt;""), "    - xform/》" &amp; T62 &amp;  "/"  &amp; W62 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》ong(\d)//</v>
       </c>
     </row>
-    <row r="63" spans="1:24" ht="27.75" thickBot="1">
+    <row r="63" spans="1:25" ht="27.75" thickBot="1">
       <c r="A63" s="101">
         <f t="shared" si="8"/>
         <v>60</v>
@@ -17623,45 +17912,49 @@
       <c r="K63" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="L63" s="18" t="s">
+      <c r="L63" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>公（促）</v>
+      </c>
+      <c r="M63" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="M63" s="21"/>
-      <c r="N63" s="18">
-        <f t="shared" si="32"/>
+      <c r="N63" s="21"/>
+      <c r="O63" s="18">
+        <f t="shared" si="31"/>
         <v>2</v>
       </c>
-      <c r="O63" s="26"/>
-      <c r="P63" s="21" t="str">
+      <c r="P63" s="26"/>
+      <c r="Q63" s="21" t="str">
         <f>C89</f>
         <v>ut</v>
       </c>
-      <c r="Q63" s="21" t="str">
+      <c r="R63" s="21" t="str">
         <f>D89</f>
         <v>ut</v>
       </c>
-      <c r="S63" s="47" t="str">
+      <c r="T63" s="47" t="str">
+        <f t="shared" si="32"/>
+        <v>ut(\d)</v>
+      </c>
+      <c r="U63" s="50" t="s">
+        <v>1028</v>
+      </c>
+      <c r="V63" s="50" t="str">
         <f t="shared" si="33"/>
-        <v>ut(\d)</v>
-      </c>
-      <c r="T63" s="50" t="s">
-        <v>1028</v>
-      </c>
-      <c r="U63" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W63" s="47" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="V63" s="47" t="str">
+      <c r="X63" s="19"/>
+      <c r="Y63" s="20" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="W63" s="19"/>
-      <c r="X63" s="20" t="str">
-        <f t="shared" si="36"/>
         <v xml:space="preserve">    - xform/》ut(\d)//</v>
       </c>
     </row>
-    <row r="64" spans="1:24" ht="27.75" thickBot="1">
+    <row r="64" spans="1:25" ht="27.75" thickBot="1">
       <c r="A64" s="101">
         <f t="shared" si="8"/>
         <v>61</v>
@@ -17697,45 +17990,49 @@
       <c r="K64" s="18" t="s">
         <v>473</v>
       </c>
-      <c r="L64" s="18" t="s">
+      <c r="L64" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>箴（舒）</v>
+      </c>
+      <c r="M64" s="18" t="s">
         <v>479</v>
       </c>
-      <c r="M64" s="21"/>
-      <c r="N64" s="18">
-        <f t="shared" si="32"/>
+      <c r="N64" s="21"/>
+      <c r="O64" s="18">
+        <f t="shared" si="31"/>
         <v>2</v>
       </c>
-      <c r="O64" s="26"/>
-      <c r="P64" s="21" t="str">
+      <c r="P64" s="26"/>
+      <c r="Q64" s="21" t="str">
         <f>C71</f>
         <v>u</v>
       </c>
-      <c r="Q64" s="21" t="str">
+      <c r="R64" s="21" t="str">
         <f>D71</f>
         <v>u</v>
       </c>
-      <c r="S64" s="47" t="str">
+      <c r="T64" s="47" t="str">
+        <f t="shared" si="32"/>
+        <v>u(\d)</v>
+      </c>
+      <c r="U64" s="50" t="s">
+        <v>1028</v>
+      </c>
+      <c r="V64" s="50" t="str">
         <f t="shared" si="33"/>
-        <v>u(\d)</v>
-      </c>
-      <c r="T64" s="50" t="s">
-        <v>1028</v>
-      </c>
-      <c r="U64" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W64" s="47" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="V64" s="47" t="str">
+      <c r="X64" s="19"/>
+      <c r="Y64" s="20" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="W64" s="19"/>
-      <c r="X64" s="20" t="str">
-        <f t="shared" si="36"/>
         <v xml:space="preserve">    - xform/》u(\d)//</v>
       </c>
     </row>
-    <row r="65" spans="1:24" ht="27.75" thickBot="1">
+    <row r="65" spans="1:25" ht="27.75" thickBot="1">
       <c r="A65" s="101">
         <f t="shared" si="8"/>
         <v>62</v>
@@ -17771,45 +18068,49 @@
       <c r="K65" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="L65" s="18" t="s">
+      <c r="L65" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>公（舒）</v>
+      </c>
+      <c r="M65" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="M65" s="21"/>
-      <c r="N65" s="18">
-        <f t="shared" si="32"/>
+      <c r="N65" s="21"/>
+      <c r="O65" s="18">
+        <f t="shared" si="31"/>
         <v>3</v>
       </c>
-      <c r="O65" s="26"/>
-      <c r="P65" s="21" t="str">
+      <c r="P65" s="26"/>
+      <c r="Q65" s="21" t="str">
         <f>C84</f>
         <v>uh</v>
       </c>
-      <c r="Q65" s="21" t="str">
+      <c r="R65" s="21" t="str">
         <f>D84</f>
         <v>uh</v>
       </c>
-      <c r="S65" s="47" t="str">
+      <c r="T65" s="47" t="str">
+        <f t="shared" si="32"/>
+        <v>uh(\d)</v>
+      </c>
+      <c r="U65" s="50" t="s">
+        <v>981</v>
+      </c>
+      <c r="V65" s="50" t="str">
         <f t="shared" si="33"/>
-        <v>uh(\d)</v>
-      </c>
-      <c r="T65" s="50" t="s">
-        <v>981</v>
-      </c>
-      <c r="U65" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W65" s="47" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="V65" s="47" t="str">
+      <c r="X65" s="19"/>
+      <c r="Y65" s="20" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="W65" s="19"/>
-      <c r="X65" s="20" t="str">
-        <f t="shared" si="36"/>
         <v xml:space="preserve">    - xform/》uh(\d)//</v>
       </c>
     </row>
-    <row r="66" spans="1:24" ht="27.75" thickBot="1">
+    <row r="66" spans="1:25" ht="27.75" thickBot="1">
       <c r="A66" s="101">
         <f t="shared" si="8"/>
         <v>63</v>
@@ -17845,45 +18146,49 @@
       <c r="K66" s="18" t="s">
         <v>421</v>
       </c>
-      <c r="L66" s="18" t="s">
+      <c r="L66" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>姑（舒）</v>
+      </c>
+      <c r="M66" s="18" t="s">
         <v>427</v>
       </c>
-      <c r="M66" s="21"/>
-      <c r="N66" s="18">
-        <f t="shared" si="32"/>
+      <c r="N66" s="21"/>
+      <c r="O66" s="18">
+        <f t="shared" si="31"/>
         <v>3</v>
       </c>
-      <c r="O66" s="26"/>
-      <c r="P66" s="21" t="str">
+      <c r="P66" s="26"/>
+      <c r="Q66" s="21" t="str">
         <f>C64</f>
         <v>om</v>
       </c>
-      <c r="Q66" s="21" t="str">
+      <c r="R66" s="21" t="str">
         <f>D64</f>
         <v>om</v>
       </c>
-      <c r="S66" s="47" t="str">
+      <c r="T66" s="47" t="str">
+        <f t="shared" si="32"/>
+        <v>om(\d)</v>
+      </c>
+      <c r="U66" s="50" t="s">
+        <v>1028</v>
+      </c>
+      <c r="V66" s="50" t="str">
         <f t="shared" si="33"/>
-        <v>om(\d)</v>
-      </c>
-      <c r="T66" s="50" t="s">
-        <v>1028</v>
-      </c>
-      <c r="U66" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W66" s="47" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="V66" s="47" t="str">
+      <c r="X66" s="19"/>
+      <c r="Y66" s="20" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="W66" s="19"/>
-      <c r="X66" s="20" t="str">
-        <f t="shared" si="36"/>
         <v xml:space="preserve">    - xform/》om(\d)//</v>
       </c>
     </row>
-    <row r="67" spans="1:24" ht="27.75" thickBot="1">
+    <row r="67" spans="1:25" ht="27.75" thickBot="1">
       <c r="A67" s="101">
         <f t="shared" si="8"/>
         <v>64</v>
@@ -17919,47 +18224,51 @@
       <c r="K67" s="18" t="s">
         <v>2071</v>
       </c>
-      <c r="L67" s="18" t="s">
+      <c r="L67" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>扛（促）</v>
+      </c>
+      <c r="M67" s="18" t="s">
         <v>500</v>
       </c>
-      <c r="M67" s="61" t="s">
+      <c r="N67" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N67" s="18">
-        <f t="shared" si="32"/>
+      <c r="O67" s="18">
+        <f t="shared" si="31"/>
         <v>4</v>
       </c>
-      <c r="O67" s="26"/>
-      <c r="P67" s="21" t="str">
+      <c r="P67" s="26"/>
+      <c r="Q67" s="21" t="str">
         <f>C63</f>
         <v>ok</v>
       </c>
-      <c r="Q67" s="21" t="str">
+      <c r="R67" s="21" t="str">
         <f>D63</f>
         <v>ok</v>
       </c>
-      <c r="S67" s="47" t="str">
+      <c r="T67" s="47" t="str">
+        <f t="shared" si="32"/>
+        <v>ok(\d)</v>
+      </c>
+      <c r="U67" s="50" t="s">
+        <v>1028</v>
+      </c>
+      <c r="V67" s="50" t="str">
         <f t="shared" si="33"/>
-        <v>ok(\d)</v>
-      </c>
-      <c r="T67" s="50" t="s">
-        <v>1028</v>
-      </c>
-      <c r="U67" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W67" s="47" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="V67" s="47" t="str">
+      <c r="X67" s="19"/>
+      <c r="Y67" s="20" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="W67" s="19"/>
-      <c r="X67" s="20" t="str">
-        <f t="shared" si="36"/>
         <v xml:space="preserve">    - xform/》ok(\d)//</v>
       </c>
     </row>
-    <row r="68" spans="1:24" ht="27.75" thickBot="1">
+    <row r="68" spans="1:25" ht="27.75" thickBot="1">
       <c r="A68" s="101">
         <f t="shared" si="8"/>
         <v>65</v>
@@ -17995,45 +18304,49 @@
       <c r="K68" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="L68" s="18" t="s">
+      <c r="L68" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>沽（舒）</v>
+      </c>
+      <c r="M68" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="M68" s="21"/>
-      <c r="N68" s="18">
-        <f t="shared" si="30"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="18">
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
-      <c r="O68" s="26"/>
-      <c r="P68" s="21" t="str">
+      <c r="P68" s="26"/>
+      <c r="Q68" s="21" t="str">
         <f>C67</f>
         <v>onnh</v>
       </c>
-      <c r="Q68" s="21" t="str">
+      <c r="R68" s="21" t="str">
         <f>D67</f>
         <v>ohnn</v>
       </c>
-      <c r="S68" s="47" t="str">
+      <c r="T68" s="47" t="str">
         <f t="shared" si="13"/>
         <v>onnh(\d)</v>
       </c>
-      <c r="T68" s="50" t="s">
+      <c r="U68" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U68" s="50" t="str">
+      <c r="V68" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V68" s="47" t="str">
+      <c r="W68" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W68" s="19"/>
-      <c r="X68" s="20" t="str">
+      <c r="X68" s="19"/>
+      <c r="Y68" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》onnh(\d)//</v>
       </c>
     </row>
-    <row r="69" spans="1:24" ht="30.75" thickBot="1">
+    <row r="69" spans="1:25" ht="30.75" thickBot="1">
       <c r="A69" s="101">
         <f t="shared" si="8"/>
         <v>66</v>
@@ -18069,45 +18382,49 @@
       <c r="K69" s="18" t="s">
         <v>2071</v>
       </c>
-      <c r="L69" s="70" t="s">
+      <c r="L69" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>沽（促）</v>
+      </c>
+      <c r="M69" s="70" t="s">
         <v>1946</v>
       </c>
-      <c r="M69" s="21"/>
-      <c r="N69" s="18">
-        <f t="shared" si="30"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="18">
+        <f t="shared" si="29"/>
         <v>3</v>
       </c>
-      <c r="O69" s="26"/>
-      <c r="P69" s="21" t="str">
+      <c r="P69" s="26"/>
+      <c r="Q69" s="21" t="str">
         <f>C70</f>
         <v>op</v>
       </c>
-      <c r="Q69" s="21" t="str">
+      <c r="R69" s="21" t="str">
         <f>D70</f>
         <v>op</v>
       </c>
-      <c r="S69" s="47" t="str">
+      <c r="T69" s="47" t="str">
         <f t="shared" si="13"/>
         <v>op(\d)</v>
       </c>
-      <c r="T69" s="50" t="s">
+      <c r="U69" s="50" t="s">
         <v>1028</v>
       </c>
-      <c r="U69" s="50" t="str">
+      <c r="V69" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V69" s="47" t="str">
+      <c r="W69" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W69" s="19"/>
-      <c r="X69" s="20" t="str">
+      <c r="X69" s="19"/>
+      <c r="Y69" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》op(\d)//</v>
       </c>
     </row>
-    <row r="70" spans="1:24" ht="27.75" thickBot="1">
+    <row r="70" spans="1:25" ht="27.75" thickBot="1">
       <c r="A70" s="101">
         <f t="shared" si="8"/>
         <v>67</v>
@@ -18143,45 +18460,49 @@
       <c r="K70" s="18" t="s">
         <v>480</v>
       </c>
-      <c r="L70" s="18" t="s">
+      <c r="L70" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>箴（促）</v>
+      </c>
+      <c r="M70" s="18" t="s">
         <v>485</v>
       </c>
-      <c r="M70" s="21"/>
-      <c r="N70" s="18">
-        <f t="shared" si="30"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="18">
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
-      <c r="O70" s="26"/>
-      <c r="P70" s="21" t="str">
+      <c r="P70" s="26"/>
+      <c r="Q70" s="21" t="str">
         <f>C88</f>
         <v>un</v>
       </c>
-      <c r="Q70" s="21" t="str">
+      <c r="R70" s="21" t="str">
         <f>D88</f>
         <v>un</v>
       </c>
-      <c r="S70" s="47" t="str">
+      <c r="T70" s="47" t="str">
         <f t="shared" si="13"/>
         <v>un(\d)</v>
       </c>
-      <c r="T70" s="50" t="s">
+      <c r="U70" s="50" t="s">
         <v>1029</v>
       </c>
-      <c r="U70" s="50" t="str">
+      <c r="V70" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V70" s="47" t="str">
+      <c r="W70" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W70" s="19"/>
-      <c r="X70" s="20" t="str">
+      <c r="X70" s="19"/>
+      <c r="Y70" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》un(\d)//</v>
       </c>
     </row>
-    <row r="71" spans="1:24" ht="27.75" thickBot="1">
+    <row r="71" spans="1:25" ht="27.75" thickBot="1">
       <c r="A71" s="101">
         <f t="shared" si="8"/>
         <v>68</v>
@@ -18217,45 +18538,49 @@
       <c r="K71" s="18" t="s">
         <v>307</v>
       </c>
-      <c r="L71" s="18" t="s">
+      <c r="L71" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>艍（舒）</v>
+      </c>
+      <c r="M71" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="M71" s="21"/>
-      <c r="N71" s="18">
-        <f t="shared" si="30"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="18">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
-      <c r="O71" s="26"/>
-      <c r="P71" s="21" t="str">
+      <c r="P71" s="26"/>
+      <c r="Q71" s="21" t="str">
         <f>C72</f>
         <v>ua</v>
       </c>
-      <c r="Q71" s="21" t="str">
+      <c r="R71" s="21" t="str">
         <f>D72</f>
         <v>ua</v>
       </c>
-      <c r="S71" s="47" t="str">
+      <c r="T71" s="47" t="str">
         <f t="shared" si="13"/>
         <v>ua(\d)</v>
       </c>
-      <c r="T71" s="50" t="s">
+      <c r="U71" s="50" t="s">
         <v>981</v>
       </c>
-      <c r="U71" s="50" t="str">
+      <c r="V71" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V71" s="47" t="str">
+      <c r="W71" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W71" s="19"/>
-      <c r="X71" s="20" t="str">
+      <c r="X71" s="19"/>
+      <c r="Y71" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》ua(\d)//</v>
       </c>
     </row>
-    <row r="72" spans="1:24" ht="27.75" thickBot="1">
+    <row r="72" spans="1:25" ht="27.75" thickBot="1">
       <c r="A72" s="101">
         <f t="shared" si="8"/>
         <v>69</v>
@@ -18291,47 +18616,51 @@
       <c r="K72" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="L72" s="18" t="s">
+      <c r="L72" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>瓜（舒）</v>
+      </c>
+      <c r="M72" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="M72" s="21"/>
-      <c r="N72" s="18">
-        <f t="shared" ref="N72:N83" si="37" xml:space="preserve"> LEN(D72)</f>
+      <c r="N72" s="21"/>
+      <c r="O72" s="18">
+        <f t="shared" ref="O72:O83" si="36" xml:space="preserve"> LEN(D72)</f>
         <v>2</v>
       </c>
-      <c r="O72" s="26"/>
-      <c r="P72" s="21" t="str">
+      <c r="P72" s="26"/>
+      <c r="Q72" s="21" t="str">
         <f>C79</f>
         <v>uang</v>
       </c>
-      <c r="Q72" s="21" t="str">
+      <c r="R72" s="21" t="str">
         <f>D79</f>
         <v>uang</v>
       </c>
-      <c r="S72" s="47" t="str">
-        <f t="shared" ref="S72:S83" si="38" xml:space="preserve"> _xlfn.CONCAT(P72, "(\d)")</f>
+      <c r="T72" s="47" t="str">
+        <f t="shared" ref="T72:T83" si="37" xml:space="preserve"> _xlfn.CONCAT(Q72, "(\d)")</f>
         <v>uang(\d)</v>
       </c>
-      <c r="T72" s="50" t="s">
+      <c r="U72" s="50" t="s">
         <v>1029</v>
       </c>
-      <c r="U72" s="50" t="str">
-        <f t="shared" ref="U72:U83" si="39" xml:space="preserve"> IFERROR( IF(T72="", "", SEARCH(T72, $P72)), "")</f>
+      <c r="V72" s="50" t="str">
+        <f t="shared" ref="V72:V83" si="38" xml:space="preserve"> IFERROR( IF(U72="", "", SEARCH(U72, $Q72)), "")</f>
         <v/>
       </c>
-      <c r="V72" s="47" t="str">
-        <f t="shared" ref="V72:V83" si="40" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P72,U72-1), "》", MID(P72,U72,1), "${1}", RIGHT(P72, LEN(P72)-U72)), "" )</f>
+      <c r="W72" s="47" t="str">
+        <f t="shared" ref="W72:W83" si="39" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q72,V72-1), "》", MID(Q72,V72,1), "${1}", RIGHT(Q72, LEN(Q72)-V72)), "" )</f>
         <v/>
       </c>
-      <c r="W72" s="19"/>
-      <c r="X72" s="20" t="str">
-        <f t="shared" ref="X72:X83" si="41" xml:space="preserve"> IF(AND(Q72&lt;&gt;"", P72&lt;&gt;""), "    - xform/》" &amp; S72 &amp;  "/"  &amp; V72 &amp;  "/", "")</f>
+      <c r="X72" s="19"/>
+      <c r="Y72" s="20" t="str">
+        <f t="shared" ref="Y72:Y83" si="40" xml:space="preserve"> IF(AND(R72&lt;&gt;"", Q72&lt;&gt;""), "    - xform/》" &amp; T72 &amp;  "/"  &amp; W72 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》uang(\d)//</v>
       </c>
     </row>
-    <row r="73" spans="1:24" ht="27.75" thickBot="1">
+    <row r="73" spans="1:25" ht="27.75" thickBot="1">
       <c r="A73" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>70</v>
       </c>
       <c r="B73" s="63" t="s">
@@ -18365,47 +18694,51 @@
       <c r="K73" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="L73" s="18" t="s">
+      <c r="L73" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>瓜（促）</v>
+      </c>
+      <c r="M73" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="M73" s="21"/>
-      <c r="N73" s="18">
-        <f t="shared" si="37"/>
+      <c r="N73" s="21"/>
+      <c r="O73" s="18">
+        <f t="shared" si="36"/>
         <v>3</v>
       </c>
-      <c r="O73" s="26"/>
-      <c r="P73" s="21" t="str">
+      <c r="P73" s="26"/>
+      <c r="Q73" s="21" t="str">
         <f>C74</f>
         <v>uai</v>
       </c>
-      <c r="Q73" s="21" t="str">
+      <c r="R73" s="21" t="str">
         <f>D74</f>
         <v>uai</v>
       </c>
-      <c r="S73" s="47" t="str">
+      <c r="T73" s="47" t="str">
+        <f t="shared" si="37"/>
+        <v>uai(\d)</v>
+      </c>
+      <c r="U73" s="50" t="s">
+        <v>1029</v>
+      </c>
+      <c r="V73" s="50">
         <f t="shared" si="38"/>
-        <v>uai(\d)</v>
-      </c>
-      <c r="T73" s="50" t="s">
-        <v>1029</v>
-      </c>
-      <c r="U73" s="50">
+        <v>3</v>
+      </c>
+      <c r="W73" s="47" t="str">
         <f t="shared" si="39"/>
-        <v>3</v>
-      </c>
-      <c r="V73" s="47" t="str">
+        <v>ua》i${1}</v>
+      </c>
+      <c r="X73" s="19"/>
+      <c r="Y73" s="20" t="str">
         <f t="shared" si="40"/>
-        <v>ua》i${1}</v>
-      </c>
-      <c r="W73" s="19"/>
-      <c r="X73" s="20" t="str">
-        <f t="shared" si="41"/>
         <v xml:space="preserve">    - xform/》uai(\d)/ua》i${1}/</v>
       </c>
     </row>
-    <row r="74" spans="1:24" ht="27.75" thickBot="1">
+    <row r="74" spans="1:25" ht="27.75" thickBot="1">
       <c r="A74" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>71</v>
       </c>
       <c r="B74" s="63" t="s">
@@ -18439,47 +18772,51 @@
       <c r="K74" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="L74" s="18" t="s">
+      <c r="L74" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>乖（舒）</v>
+      </c>
+      <c r="M74" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="M74" s="21"/>
-      <c r="N74" s="18">
-        <f t="shared" si="37"/>
+      <c r="N74" s="21"/>
+      <c r="O74" s="18">
+        <f t="shared" si="36"/>
         <v>3</v>
       </c>
-      <c r="O74" s="26"/>
-      <c r="P74" s="21" t="str">
+      <c r="P74" s="26"/>
+      <c r="Q74" s="21" t="str">
         <f>C82</f>
         <v>ue</v>
       </c>
-      <c r="Q74" s="21" t="str">
+      <c r="R74" s="21" t="str">
         <f>D82</f>
         <v>ue</v>
       </c>
-      <c r="S74" s="47" t="str">
+      <c r="T74" s="47" t="str">
+        <f t="shared" si="37"/>
+        <v>ue(\d)</v>
+      </c>
+      <c r="U74" s="50" t="s">
+        <v>1086</v>
+      </c>
+      <c r="V74" s="50" t="str">
         <f t="shared" si="38"/>
-        <v>ue(\d)</v>
-      </c>
-      <c r="T74" s="50" t="s">
-        <v>1086</v>
-      </c>
-      <c r="U74" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W74" s="47" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="V74" s="47" t="str">
+      <c r="X74" s="19"/>
+      <c r="Y74" s="20" t="str">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="W74" s="19"/>
-      <c r="X74" s="20" t="str">
-        <f t="shared" si="41"/>
         <v xml:space="preserve">    - xform/》ue(\d)//</v>
       </c>
     </row>
-    <row r="75" spans="1:24" ht="27.75" thickBot="1">
+    <row r="75" spans="1:25" ht="27.75" thickBot="1">
       <c r="A75" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>72</v>
       </c>
       <c r="B75" s="63" t="s">
@@ -18513,49 +18850,53 @@
       <c r="K75" s="18" t="s">
         <v>445</v>
       </c>
-      <c r="L75" s="18" t="s">
+      <c r="L75" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>閂（舒）</v>
+      </c>
+      <c r="M75" s="18" t="s">
         <v>451</v>
       </c>
-      <c r="M75" s="61" t="s">
+      <c r="N75" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N75" s="18">
-        <f t="shared" si="37"/>
+      <c r="O75" s="18">
+        <f t="shared" si="36"/>
         <v>5</v>
       </c>
-      <c r="O75" s="26"/>
-      <c r="P75" s="21" t="str">
+      <c r="P75" s="26"/>
+      <c r="Q75" s="21" t="str">
         <f>C83</f>
         <v>ueh</v>
       </c>
-      <c r="Q75" s="21" t="str">
+      <c r="R75" s="21" t="str">
         <f>D83</f>
         <v>ueh</v>
       </c>
-      <c r="S75" s="47" t="str">
+      <c r="T75" s="47" t="str">
+        <f t="shared" si="37"/>
+        <v>ueh(\d)</v>
+      </c>
+      <c r="U75" s="50" t="s">
+        <v>1016</v>
+      </c>
+      <c r="V75" s="50" t="str">
         <f t="shared" si="38"/>
-        <v>ueh(\d)</v>
-      </c>
-      <c r="T75" s="50" t="s">
-        <v>1016</v>
-      </c>
-      <c r="U75" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W75" s="47" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="V75" s="47" t="str">
+      <c r="X75" s="19"/>
+      <c r="Y75" s="20" t="str">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="W75" s="19"/>
-      <c r="X75" s="20" t="str">
-        <f t="shared" si="41"/>
         <v xml:space="preserve">    - xform/》ueh(\d)//</v>
       </c>
     </row>
-    <row r="76" spans="1:24" ht="27.75" thickBot="1">
+    <row r="76" spans="1:25" ht="27.75" thickBot="1">
       <c r="A76" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>73</v>
       </c>
       <c r="B76" s="63" t="s">
@@ -18589,47 +18930,51 @@
       <c r="K76" s="18" t="s">
         <v>2071</v>
       </c>
-      <c r="L76" s="18" t="s">
+      <c r="L76" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>乖（促）</v>
+      </c>
+      <c r="M76" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="M76" s="21"/>
-      <c r="N76" s="18">
-        <f t="shared" si="37"/>
+      <c r="N76" s="21"/>
+      <c r="O76" s="18">
+        <f t="shared" si="36"/>
         <v>4</v>
       </c>
-      <c r="O76" s="26"/>
-      <c r="P76" s="21" t="str">
+      <c r="P76" s="26"/>
+      <c r="Q76" s="21" t="str">
         <f>C85</f>
         <v>ui</v>
       </c>
-      <c r="Q76" s="21" t="str">
+      <c r="R76" s="21" t="str">
         <f>D85</f>
         <v>ui</v>
       </c>
-      <c r="S76" s="47" t="str">
+      <c r="T76" s="47" t="str">
+        <f t="shared" si="37"/>
+        <v>ui(\d)</v>
+      </c>
+      <c r="U76" s="50" t="s">
+        <v>1016</v>
+      </c>
+      <c r="V76" s="50" t="str">
         <f t="shared" si="38"/>
-        <v>ui(\d)</v>
-      </c>
-      <c r="T76" s="50" t="s">
-        <v>1016</v>
-      </c>
-      <c r="U76" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W76" s="47" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="V76" s="47" t="str">
+      <c r="X76" s="19"/>
+      <c r="Y76" s="20" t="str">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="W76" s="19"/>
-      <c r="X76" s="20" t="str">
-        <f t="shared" si="41"/>
         <v xml:space="preserve">    - xform/》ui(\d)//</v>
       </c>
     </row>
-    <row r="77" spans="1:24" ht="27.75" thickBot="1">
+    <row r="77" spans="1:25" ht="27.75" thickBot="1">
       <c r="A77" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>74</v>
       </c>
       <c r="B77" s="63" t="s">
@@ -18663,49 +19008,53 @@
       <c r="K77" s="18" t="s">
         <v>452</v>
       </c>
-      <c r="L77" s="18" t="s">
+      <c r="L77" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>閂（促）</v>
+      </c>
+      <c r="M77" s="18" t="s">
         <v>456</v>
       </c>
-      <c r="M77" s="61" t="s">
+      <c r="N77" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N77" s="18">
-        <f t="shared" si="37"/>
+      <c r="O77" s="18">
+        <f t="shared" si="36"/>
         <v>6</v>
       </c>
-      <c r="O77" s="26"/>
-      <c r="P77" s="21" t="str">
+      <c r="P77" s="26"/>
+      <c r="Q77" s="21" t="str">
         <f>C87</f>
         <v>uinn</v>
       </c>
-      <c r="Q77" s="21" t="str">
+      <c r="R77" s="21" t="str">
         <f>D87</f>
         <v>uinn</v>
       </c>
-      <c r="S77" s="47" t="str">
+      <c r="T77" s="47" t="str">
+        <f t="shared" si="37"/>
+        <v>uinn(\d)</v>
+      </c>
+      <c r="U77" s="50" t="s">
+        <v>1016</v>
+      </c>
+      <c r="V77" s="50" t="str">
         <f t="shared" si="38"/>
-        <v>uinn(\d)</v>
-      </c>
-      <c r="T77" s="50" t="s">
-        <v>1016</v>
-      </c>
-      <c r="U77" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W77" s="47" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="V77" s="47" t="str">
+      <c r="X77" s="19"/>
+      <c r="Y77" s="20" t="str">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="W77" s="19"/>
-      <c r="X77" s="20" t="str">
-        <f t="shared" si="41"/>
         <v xml:space="preserve">    - xform/》uinn(\d)//</v>
       </c>
     </row>
-    <row r="78" spans="1:24" ht="27.75" thickBot="1">
+    <row r="78" spans="1:25" ht="27.75" thickBot="1">
       <c r="A78" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>75</v>
       </c>
       <c r="B78" s="63" t="s">
@@ -18739,47 +19088,51 @@
       <c r="K78" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="L78" s="18" t="s">
+      <c r="L78" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>觀（舒）</v>
+      </c>
+      <c r="M78" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="M78" s="21"/>
-      <c r="N78" s="18">
-        <f t="shared" si="37"/>
+      <c r="N78" s="21"/>
+      <c r="O78" s="18">
+        <f t="shared" si="36"/>
         <v>3</v>
       </c>
-      <c r="O78" s="26"/>
-      <c r="P78" s="21" t="str">
+      <c r="P78" s="26"/>
+      <c r="Q78" s="21" t="str">
         <f>C75</f>
         <v>uainn</v>
       </c>
-      <c r="Q78" s="21" t="str">
+      <c r="R78" s="21" t="str">
         <f>D75</f>
         <v>uainn</v>
       </c>
-      <c r="S78" s="47" t="str">
+      <c r="T78" s="47" t="str">
+        <f t="shared" si="37"/>
+        <v>uainn(\d)</v>
+      </c>
+      <c r="U78" s="50" t="s">
+        <v>1029</v>
+      </c>
+      <c r="V78" s="50">
         <f t="shared" si="38"/>
-        <v>uainn(\d)</v>
-      </c>
-      <c r="T78" s="50" t="s">
-        <v>1029</v>
-      </c>
-      <c r="U78" s="50">
+        <v>3</v>
+      </c>
+      <c r="W78" s="47" t="str">
         <f t="shared" si="39"/>
-        <v>3</v>
-      </c>
-      <c r="V78" s="47" t="str">
+        <v>ua》i${1}nn</v>
+      </c>
+      <c r="X78" s="19"/>
+      <c r="Y78" s="20" t="str">
         <f t="shared" si="40"/>
-        <v>ua》i${1}nn</v>
-      </c>
-      <c r="W78" s="19"/>
-      <c r="X78" s="20" t="str">
-        <f t="shared" si="41"/>
         <v xml:space="preserve">    - xform/》uainn(\d)/ua》i${1}nn/</v>
       </c>
     </row>
-    <row r="79" spans="1:24" ht="27.75" thickBot="1">
+    <row r="79" spans="1:25" ht="27.75" thickBot="1">
       <c r="A79" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>76</v>
       </c>
       <c r="B79" s="63" t="s">
@@ -18813,45 +19166,49 @@
       <c r="K79" s="18" t="s">
         <v>433</v>
       </c>
-      <c r="L79" s="18" t="s">
+      <c r="L79" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>光（舒）</v>
+      </c>
+      <c r="M79" s="18" t="s">
         <v>438</v>
       </c>
-      <c r="M79" s="21"/>
-      <c r="N79" s="18">
-        <f t="shared" si="37"/>
+      <c r="N79" s="21"/>
+      <c r="O79" s="18">
+        <f t="shared" si="36"/>
         <v>4</v>
       </c>
-      <c r="O79" s="26"/>
-      <c r="P79" s="21" t="str">
+      <c r="P79" s="26"/>
+      <c r="Q79" s="21" t="str">
         <f>C76</f>
         <v>uaih</v>
       </c>
-      <c r="Q79" s="21" t="str">
+      <c r="R79" s="21" t="str">
         <f>D76</f>
         <v>uaih</v>
       </c>
-      <c r="S79" s="47" t="str">
+      <c r="T79" s="47" t="str">
+        <f t="shared" si="37"/>
+        <v>uaih(\d)</v>
+      </c>
+      <c r="U79" s="50" t="s">
+        <v>1029</v>
+      </c>
+      <c r="V79" s="50">
         <f t="shared" si="38"/>
-        <v>uaih(\d)</v>
-      </c>
-      <c r="T79" s="50" t="s">
-        <v>1029</v>
-      </c>
-      <c r="U79" s="50">
+        <v>3</v>
+      </c>
+      <c r="W79" s="47" t="str">
         <f t="shared" si="39"/>
-        <v>3</v>
-      </c>
-      <c r="V79" s="47" t="str">
+        <v>ua》i${1}h</v>
+      </c>
+      <c r="X79" s="19"/>
+      <c r="Y79" s="20" t="str">
         <f t="shared" si="40"/>
-        <v>ua》i${1}h</v>
-      </c>
-      <c r="W79" s="19"/>
-      <c r="X79" s="20" t="str">
-        <f t="shared" si="41"/>
         <v xml:space="preserve">    - xform/》uaih(\d)/ua》i${1}h/</v>
       </c>
     </row>
-    <row r="80" spans="1:24" ht="27.75" thickBot="1">
+    <row r="80" spans="1:25" ht="27.75" thickBot="1">
       <c r="A80" s="101">
         <f t="shared" si="8"/>
         <v>77</v>
@@ -18887,47 +19244,51 @@
       <c r="K80" s="18" t="s">
         <v>396</v>
       </c>
-      <c r="L80" s="18" t="s">
+      <c r="L80" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>官（舒）</v>
+      </c>
+      <c r="M80" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="M80" s="21"/>
-      <c r="N80" s="18">
-        <f t="shared" si="37"/>
+      <c r="N80" s="21"/>
+      <c r="O80" s="18">
+        <f t="shared" si="36"/>
         <v>4</v>
       </c>
-      <c r="O80" s="26"/>
-      <c r="P80" s="21" t="str">
+      <c r="P80" s="26"/>
+      <c r="Q80" s="21" t="str">
         <f>C81</f>
         <v>uat</v>
       </c>
-      <c r="Q80" s="21" t="str">
+      <c r="R80" s="21" t="str">
         <f>D81</f>
         <v>uat</v>
       </c>
-      <c r="S80" s="47" t="str">
+      <c r="T80" s="47" t="str">
+        <f t="shared" si="37"/>
+        <v>uat(\d)</v>
+      </c>
+      <c r="U80" s="50" t="s">
+        <v>1029</v>
+      </c>
+      <c r="V80" s="50" t="str">
         <f t="shared" si="38"/>
-        <v>uat(\d)</v>
-      </c>
-      <c r="T80" s="50" t="s">
-        <v>1029</v>
-      </c>
-      <c r="U80" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W80" s="47" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="V80" s="47" t="str">
+      <c r="X80" s="19"/>
+      <c r="Y80" s="20" t="str">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="W80" s="19"/>
-      <c r="X80" s="20" t="str">
-        <f t="shared" si="41"/>
         <v xml:space="preserve">    - xform/》uat(\d)//</v>
       </c>
     </row>
-    <row r="81" spans="1:24" ht="27.75" thickBot="1">
+    <row r="81" spans="1:25" ht="27.75" thickBot="1">
       <c r="A81" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>78</v>
       </c>
       <c r="B81" s="63" t="s">
@@ -18961,47 +19322,51 @@
       <c r="K81" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="L81" s="18" t="s">
+      <c r="L81" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>觀（促）</v>
+      </c>
+      <c r="M81" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="M81" s="21"/>
-      <c r="N81" s="18">
-        <f t="shared" si="37"/>
+      <c r="N81" s="21"/>
+      <c r="O81" s="18">
+        <f t="shared" si="36"/>
         <v>3</v>
       </c>
-      <c r="O81" s="26"/>
-      <c r="P81" s="21" t="str">
+      <c r="P81" s="26"/>
+      <c r="Q81" s="21" t="str">
         <f>C77</f>
         <v>uainnh</v>
       </c>
-      <c r="Q81" s="21" t="str">
+      <c r="R81" s="21" t="str">
         <f>D77</f>
         <v>uaihnn</v>
       </c>
-      <c r="S81" s="47" t="str">
+      <c r="T81" s="47" t="str">
+        <f t="shared" si="37"/>
+        <v>uainnh(\d)</v>
+      </c>
+      <c r="U81" s="50" t="s">
+        <v>1087</v>
+      </c>
+      <c r="V81" s="50" t="str">
         <f t="shared" si="38"/>
-        <v>uainnh(\d)</v>
-      </c>
-      <c r="T81" s="50" t="s">
-        <v>1087</v>
-      </c>
-      <c r="U81" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W81" s="47" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="V81" s="47" t="str">
+      <c r="X81" s="19"/>
+      <c r="Y81" s="20" t="str">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="W81" s="19"/>
-      <c r="X81" s="20" t="str">
-        <f t="shared" si="41"/>
         <v xml:space="preserve">    - xform/》uainnh(\d)//</v>
       </c>
     </row>
-    <row r="82" spans="1:24" ht="27.75" thickBot="1">
+    <row r="82" spans="1:25" ht="27.75" thickBot="1">
       <c r="A82" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>79</v>
       </c>
       <c r="B82" s="63" t="s">
@@ -19035,47 +19400,51 @@
       <c r="K82" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="L82" s="18" t="s">
+      <c r="L82" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>檜（舒）</v>
+      </c>
+      <c r="M82" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="M82" s="21"/>
-      <c r="N82" s="18">
-        <f t="shared" si="37"/>
+      <c r="N82" s="21"/>
+      <c r="O82" s="18">
+        <f t="shared" si="36"/>
         <v>2</v>
       </c>
-      <c r="O82" s="26"/>
-      <c r="P82" s="21" t="str">
+      <c r="P82" s="26"/>
+      <c r="Q82" s="21" t="str">
         <f>C86</f>
         <v>uih</v>
       </c>
-      <c r="Q82" s="21" t="str">
+      <c r="R82" s="21" t="str">
         <f>D86</f>
         <v>uih</v>
       </c>
-      <c r="S82" s="47" t="str">
+      <c r="T82" s="47" t="str">
+        <f t="shared" si="37"/>
+        <v>uih(\d)</v>
+      </c>
+      <c r="U82" s="50" t="s">
+        <v>1016</v>
+      </c>
+      <c r="V82" s="50" t="str">
         <f t="shared" si="38"/>
-        <v>uih(\d)</v>
-      </c>
-      <c r="T82" s="50" t="s">
-        <v>1016</v>
-      </c>
-      <c r="U82" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W82" s="47" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="V82" s="47" t="str">
+      <c r="X82" s="19"/>
+      <c r="Y82" s="20" t="str">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="W82" s="19"/>
-      <c r="X82" s="20" t="str">
-        <f t="shared" si="41"/>
         <v xml:space="preserve">    - xform/》uih(\d)//</v>
       </c>
     </row>
-    <row r="83" spans="1:24" ht="27.75" thickBot="1">
+    <row r="83" spans="1:25" ht="27.75" thickBot="1">
       <c r="A83" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>80</v>
       </c>
       <c r="B83" s="63" t="s">
@@ -19109,45 +19478,49 @@
       <c r="K83" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="L83" s="18" t="s">
+      <c r="L83" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>檜（促）</v>
+      </c>
+      <c r="M83" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="M83" s="21"/>
-      <c r="N83" s="18">
-        <f t="shared" si="37"/>
+      <c r="N83" s="21"/>
+      <c r="O83" s="18">
+        <f t="shared" si="36"/>
         <v>3</v>
       </c>
-      <c r="O83" s="26"/>
-      <c r="P83" s="21" t="str">
+      <c r="P83" s="26"/>
+      <c r="Q83" s="21" t="str">
         <f>C57</f>
         <v>m</v>
       </c>
-      <c r="Q83" s="21" t="str">
+      <c r="R83" s="21" t="str">
         <f>D57</f>
         <v>m</v>
       </c>
-      <c r="S83" s="47" t="str">
+      <c r="T83" s="47" t="str">
+        <f t="shared" si="37"/>
+        <v>m(\d)</v>
+      </c>
+      <c r="U83" s="50" t="s">
+        <v>1027</v>
+      </c>
+      <c r="V83" s="50" t="str">
         <f t="shared" si="38"/>
-        <v>m(\d)</v>
-      </c>
-      <c r="T83" s="50" t="s">
-        <v>1027</v>
-      </c>
-      <c r="U83" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W83" s="47" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="V83" s="47" t="str">
+      <c r="X83" s="19"/>
+      <c r="Y83" s="20" t="str">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="W83" s="19"/>
-      <c r="X83" s="20" t="str">
-        <f t="shared" si="41"/>
         <v xml:space="preserve">    - xform/》m(\d)//</v>
       </c>
     </row>
-    <row r="84" spans="1:24" ht="27.75" thickBot="1">
+    <row r="84" spans="1:25" ht="27.75" thickBot="1">
       <c r="A84" s="101">
         <f t="shared" si="8"/>
         <v>81</v>
@@ -19183,47 +19556,51 @@
       <c r="K84" s="18" t="s">
         <v>312</v>
       </c>
-      <c r="L84" s="18" t="s">
+      <c r="L84" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>艍（促）</v>
+      </c>
+      <c r="M84" s="18" t="s">
         <v>314</v>
       </c>
-      <c r="M84" s="21"/>
-      <c r="N84" s="18">
-        <f t="shared" si="30"/>
+      <c r="N84" s="21"/>
+      <c r="O84" s="18">
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
-      <c r="O84" s="26"/>
-      <c r="P84" s="21" t="str">
+      <c r="P84" s="26"/>
+      <c r="Q84" s="21" t="str">
         <f>C80</f>
         <v>uann</v>
       </c>
-      <c r="Q84" s="21" t="str">
+      <c r="R84" s="21" t="str">
         <f>D80</f>
         <v>uann</v>
       </c>
-      <c r="S84" s="47" t="str">
+      <c r="T84" s="47" t="str">
         <f t="shared" si="13"/>
         <v>uann(\d)</v>
       </c>
-      <c r="T84" s="50" t="s">
+      <c r="U84" s="50" t="s">
         <v>1029</v>
       </c>
-      <c r="U84" s="50" t="str">
+      <c r="V84" s="50" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V84" s="47" t="str">
+      <c r="W84" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W84" s="19"/>
-      <c r="X84" s="20" t="str">
+      <c r="X84" s="19"/>
+      <c r="Y84" s="20" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">    - xform/》uann(\d)//</v>
       </c>
     </row>
-    <row r="85" spans="1:24" ht="27.75" thickBot="1">
+    <row r="85" spans="1:25" ht="27.75" thickBot="1">
       <c r="A85" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>82</v>
       </c>
       <c r="B85" s="63" t="s">
@@ -19257,47 +19634,51 @@
       <c r="K85" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="L85" s="18" t="s">
+      <c r="L85" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>規（舒）</v>
+      </c>
+      <c r="M85" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="M85" s="21"/>
-      <c r="N85" s="18">
+      <c r="N85" s="21"/>
+      <c r="O85" s="18">
         <f xml:space="preserve"> LEN(D85)</f>
         <v>2</v>
       </c>
-      <c r="O85" s="26"/>
-      <c r="P85" s="21" t="str">
+      <c r="P85" s="26"/>
+      <c r="Q85" s="21" t="str">
         <f>C58</f>
         <v>mh</v>
       </c>
-      <c r="Q85" s="21" t="str">
+      <c r="R85" s="21" t="str">
         <f>D58</f>
         <v>mh</v>
       </c>
-      <c r="S85" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P85, "(\d)")</f>
+      <c r="T85" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q85, "(\d)")</f>
         <v>mh(\d)</v>
       </c>
-      <c r="T85" s="50" t="s">
+      <c r="U85" s="50" t="s">
         <v>1027</v>
       </c>
-      <c r="U85" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T85="", "", SEARCH(T85, $P85)), "")</f>
+      <c r="V85" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U85="", "", SEARCH(U85, $Q85)), "")</f>
         <v/>
       </c>
-      <c r="V85" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P85,U85-1), "》", MID(P85,U85,1), "${1}", RIGHT(P85, LEN(P85)-U85)), "" )</f>
+      <c r="W85" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q85,V85-1), "》", MID(Q85,V85,1), "${1}", RIGHT(Q85, LEN(Q85)-V85)), "" )</f>
         <v/>
       </c>
-      <c r="W85" s="19"/>
-      <c r="X85" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q85&lt;&gt;"", P85&lt;&gt;""), "    - xform/》" &amp; S85 &amp;  "/"  &amp; V85 &amp;  "/", "")</f>
+      <c r="X85" s="19"/>
+      <c r="Y85" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R85&lt;&gt;"", Q85&lt;&gt;""), "    - xform/》" &amp; T85 &amp;  "/"  &amp; W85 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》mh(\d)//</v>
       </c>
     </row>
-    <row r="86" spans="1:24" ht="27.75" thickBot="1">
+    <row r="86" spans="1:25" ht="27.75" thickBot="1">
       <c r="A86" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>83</v>
       </c>
       <c r="B86" s="63" t="s">
@@ -19331,49 +19712,53 @@
       <c r="K86" s="18" t="s">
         <v>2071</v>
       </c>
-      <c r="L86" s="69" t="s">
+      <c r="L86" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>褌（促）</v>
+      </c>
+      <c r="M86" s="69" t="s">
         <v>1943</v>
       </c>
-      <c r="M86" s="61" t="s">
+      <c r="N86" s="61" t="s">
         <v>1091</v>
       </c>
-      <c r="N86" s="18">
+      <c r="O86" s="18">
         <f xml:space="preserve"> LEN(D86)</f>
         <v>3</v>
       </c>
-      <c r="O86" s="26"/>
-      <c r="P86" s="21" t="str">
+      <c r="P86" s="26"/>
+      <c r="Q86" s="21" t="str">
         <f>C60</f>
         <v>ngh</v>
       </c>
-      <c r="Q86" s="21" t="str">
+      <c r="R86" s="21" t="str">
         <f>D60</f>
         <v>ngh</v>
       </c>
-      <c r="S86" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P86, "(\d)")</f>
+      <c r="T86" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q86, "(\d)")</f>
         <v>ngh(\d)</v>
       </c>
-      <c r="T86" s="50" t="s">
+      <c r="U86" s="50" t="s">
         <v>1027</v>
       </c>
-      <c r="U86" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T86="", "", SEARCH(T86, $P86)), "")</f>
+      <c r="V86" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U86="", "", SEARCH(U86, $Q86)), "")</f>
         <v/>
       </c>
-      <c r="V86" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P86,U86-1), "》", MID(P86,U86,1), "${1}", RIGHT(P86, LEN(P86)-U86)), "" )</f>
+      <c r="W86" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q86,V86-1), "》", MID(Q86,V86,1), "${1}", RIGHT(Q86, LEN(Q86)-V86)), "" )</f>
         <v/>
       </c>
-      <c r="W86" s="19"/>
-      <c r="X86" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q86&lt;&gt;"", P86&lt;&gt;""), "    - xform/》" &amp; S86 &amp;  "/"  &amp; V86 &amp;  "/", "")</f>
+      <c r="X86" s="19"/>
+      <c r="Y86" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R86&lt;&gt;"", Q86&lt;&gt;""), "    - xform/》" &amp; T86 &amp;  "/"  &amp; W86 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》ngh(\d)//</v>
       </c>
     </row>
-    <row r="87" spans="1:24" ht="27.75" thickBot="1">
+    <row r="87" spans="1:25" ht="27.75" thickBot="1">
       <c r="A87" s="101">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>84</v>
       </c>
       <c r="B87" s="63" t="s">
@@ -19407,45 +19792,49 @@
       <c r="K87" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="L87" s="18" t="s">
+      <c r="L87" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>褌（舒）</v>
+      </c>
+      <c r="M87" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="M87" s="21"/>
-      <c r="N87" s="18">
-        <f t="shared" ref="N87" si="42" xml:space="preserve"> LEN(D87)</f>
+      <c r="N87" s="21"/>
+      <c r="O87" s="18">
+        <f t="shared" ref="O87" si="41" xml:space="preserve"> LEN(D87)</f>
         <v>4</v>
       </c>
-      <c r="O87" s="26"/>
-      <c r="P87" s="21" t="str">
+      <c r="P87" s="26"/>
+      <c r="Q87" s="21" t="str">
         <f>C59</f>
         <v>ng</v>
       </c>
-      <c r="Q87" s="21" t="str">
+      <c r="R87" s="21" t="str">
         <f>D59</f>
         <v>ng</v>
       </c>
-      <c r="S87" s="47" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P87, "(\d)")</f>
+      <c r="T87" s="47" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q87, "(\d)")</f>
         <v>ng(\d)</v>
       </c>
-      <c r="T87" s="50" t="s">
+      <c r="U87" s="50" t="s">
         <v>1027</v>
       </c>
-      <c r="U87" s="50" t="str">
-        <f xml:space="preserve"> IFERROR( IF(T87="", "", SEARCH(T87, $P87)), "")</f>
+      <c r="V87" s="50" t="str">
+        <f xml:space="preserve"> IFERROR( IF(U87="", "", SEARCH(U87, $Q87)), "")</f>
         <v/>
       </c>
-      <c r="V87" s="47" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P87,U87-1), "》", MID(P87,U87,1), "${1}", RIGHT(P87, LEN(P87)-U87)), "" )</f>
+      <c r="W87" s="47" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q87,V87-1), "》", MID(Q87,V87,1), "${1}", RIGHT(Q87, LEN(Q87)-V87)), "" )</f>
         <v/>
       </c>
-      <c r="W87" s="19"/>
-      <c r="X87" s="20" t="str">
-        <f xml:space="preserve"> IF(AND(Q87&lt;&gt;"", P87&lt;&gt;""), "    - xform/》" &amp; S87 &amp;  "/"  &amp; V87 &amp;  "/", "")</f>
+      <c r="X87" s="19"/>
+      <c r="Y87" s="20" t="str">
+        <f xml:space="preserve"> IF(AND(R87&lt;&gt;"", Q87&lt;&gt;""), "    - xform/》" &amp; T87 &amp;  "/"  &amp; W87 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》ng(\d)//</v>
       </c>
     </row>
-    <row r="88" spans="1:24" ht="27.75" thickBot="1">
+    <row r="88" spans="1:25" ht="27.75" thickBot="1">
       <c r="A88" s="101">
         <f t="shared" si="8"/>
         <v>85</v>
@@ -19481,45 +19870,49 @@
       <c r="K88" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="L88" s="18" t="s">
+      <c r="L88" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>君（舒）</v>
+      </c>
+      <c r="M88" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="M88" s="21"/>
-      <c r="N88" s="18">
-        <f t="shared" si="30"/>
+      <c r="N88" s="21"/>
+      <c r="O88" s="18">
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
-      <c r="O88" s="26"/>
-      <c r="P88" s="21" t="str">
+      <c r="P88" s="26"/>
+      <c r="Q88" s="21" t="str">
         <f>C73</f>
         <v>uah</v>
       </c>
-      <c r="Q88" s="21" t="str">
+      <c r="R88" s="21" t="str">
         <f>D73</f>
         <v>uah</v>
       </c>
-      <c r="S88" s="47" t="str">
-        <f t="shared" ref="S88:S89" si="43" xml:space="preserve"> _xlfn.CONCAT(P88, "(\d)")</f>
+      <c r="T88" s="47" t="str">
+        <f t="shared" ref="T88:T89" si="42" xml:space="preserve"> _xlfn.CONCAT(Q88, "(\d)")</f>
         <v>uah(\d)</v>
       </c>
-      <c r="T88" s="50" t="s">
+      <c r="U88" s="50" t="s">
         <v>1029</v>
       </c>
-      <c r="U88" s="50" t="str">
-        <f t="shared" ref="U88:U89" si="44" xml:space="preserve"> IFERROR( IF(T88="", "", SEARCH(T88, $P88)), "")</f>
+      <c r="V88" s="50" t="str">
+        <f t="shared" ref="V88:V89" si="43" xml:space="preserve"> IFERROR( IF(U88="", "", SEARCH(U88, $Q88)), "")</f>
         <v/>
       </c>
-      <c r="V88" s="47" t="str">
+      <c r="W88" s="47" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W88" s="19"/>
-      <c r="X88" s="20" t="str">
-        <f t="shared" ref="X88:X89" si="45" xml:space="preserve"> IF(AND(Q88&lt;&gt;"", P88&lt;&gt;""), "    - xform/》" &amp; S88 &amp;  "/"  &amp; V88 &amp;  "/", "")</f>
+      <c r="X88" s="19"/>
+      <c r="Y88" s="20" t="str">
+        <f t="shared" ref="Y88:Y89" si="44" xml:space="preserve"> IF(AND(R88&lt;&gt;"", Q88&lt;&gt;""), "    - xform/》" &amp; T88 &amp;  "/"  &amp; W88 &amp;  "/", "")</f>
         <v xml:space="preserve">    - xform/》uah(\d)//</v>
       </c>
     </row>
-    <row r="89" spans="1:24" ht="27.75" thickBot="1">
+    <row r="89" spans="1:25" ht="27.75" thickBot="1">
       <c r="A89" s="101">
         <f t="shared" si="8"/>
         <v>86</v>
@@ -19555,46 +19948,50 @@
       <c r="K89" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="L89" s="18" t="s">
+      <c r="L89" s="18" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(LEFT(韻母對照表[[#This Row],[十五音識別碼2]],1), "（", RIGHT(韻母對照表[[#This Row],[十五音識別碼2]],1), "）")</f>
+        <v>君（促）</v>
+      </c>
+      <c r="M89" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M89" s="21"/>
-      <c r="N89" s="18">
-        <f t="shared" si="30"/>
+      <c r="N89" s="21"/>
+      <c r="O89" s="18">
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
-      <c r="O89" s="26"/>
-      <c r="P89" s="21" t="str">
+      <c r="P89" s="26"/>
+      <c r="Q89" s="21" t="str">
         <f>C78</f>
         <v>uan</v>
       </c>
-      <c r="Q89" s="21" t="str">
+      <c r="R89" s="21" t="str">
         <f>D78</f>
         <v>uan</v>
       </c>
-      <c r="S89" s="47" t="str">
+      <c r="T89" s="47" t="str">
+        <f t="shared" si="42"/>
+        <v>uan(\d)</v>
+      </c>
+      <c r="U89" s="50" t="s">
+        <v>1029</v>
+      </c>
+      <c r="V89" s="50" t="str">
         <f t="shared" si="43"/>
-        <v>uan(\d)</v>
-      </c>
-      <c r="T89" s="50" t="s">
-        <v>1029</v>
-      </c>
-      <c r="U89" s="50" t="str">
+        <v/>
+      </c>
+      <c r="W89" s="47" t="str">
+        <f t="shared" ref="W89" si="45" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(Q89,V89-1), "》", MID(Q89,V89,1), "${1}", RIGHT(Q89, LEN(Q89)-V89)), "" )</f>
+        <v/>
+      </c>
+      <c r="X89" s="19"/>
+      <c r="Y89" s="20" t="str">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="V89" s="47" t="str">
-        <f t="shared" ref="V89" si="46" xml:space="preserve"> IFERROR( _xlfn.CONCAT(LEFT(P89,U89-1), "》", MID(P89,U89,1), "${1}", RIGHT(P89, LEN(P89)-U89)), "" )</f>
-        <v/>
-      </c>
-      <c r="W89" s="19"/>
-      <c r="X89" s="20" t="str">
-        <f t="shared" si="45"/>
         <v xml:space="preserve">    - xform/》uan(\d)//</v>
       </c>
     </row>
-    <row r="90" spans="1:24" ht="27" thickBot="1"/>
-    <row r="91" spans="1:24" ht="48.75" thickBot="1">
+    <row r="90" spans="1:25" ht="27" thickBot="1"/>
+    <row r="91" spans="1:25" ht="48.75" thickBot="1">
       <c r="B91" s="22" t="s">
         <v>1092</v>
       </c>
@@ -19605,7 +20002,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="92" spans="1:24" ht="27.75" thickBot="1">
+    <row r="92" spans="1:25" ht="27.75" thickBot="1">
       <c r="B92" s="21" t="s">
         <v>1093</v>
       </c>
@@ -19618,7 +20015,7 @@
         <v>ã</v>
       </c>
     </row>
-    <row r="93" spans="1:24" ht="27.75" thickBot="1">
+    <row r="93" spans="1:25" ht="27.75" thickBot="1">
       <c r="B93" s="21" t="s">
         <v>1094</v>
       </c>
@@ -19631,8 +20028,8 @@
         <v>aʔ</v>
       </c>
     </row>
-    <row r="94" spans="1:24" ht="27" thickBot="1"/>
-    <row r="95" spans="1:24" ht="27" thickBot="1">
+    <row r="94" spans="1:25" ht="27" thickBot="1"/>
+    <row r="95" spans="1:25" ht="27" thickBot="1">
       <c r="B95" s="22" t="s">
         <v>1096</v>
       </c>
@@ -19645,7 +20042,7 @@
         <v>o͘</v>
       </c>
     </row>
-    <row r="96" spans="1:24" ht="27" thickBot="1">
+    <row r="96" spans="1:25" ht="27" thickBot="1">
       <c r="B96" s="22" t="s">
         <v>1095</v>
       </c>
@@ -40071,18 +40468,18 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="P2:X85">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula xml:space="preserve"> MOD($P2,2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="6">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula xml:space="preserve"> MOD($P2,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R86:Z101">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula xml:space="preserve"> MOD($R86,2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula xml:space="preserve"> MOD($R86,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44053,19 +44450,19 @@
   <sheetFormatPr defaultRowHeight="25.5"/>
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" thickBot="1">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="219" t="s">
         <v>736</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
+      <c r="B1" s="220"/>
+      <c r="C1" s="220"/>
+      <c r="D1" s="220"/>
+      <c r="E1" s="220"/>
+      <c r="F1" s="220"/>
+      <c r="G1" s="220"/>
+      <c r="H1" s="220"/>
+      <c r="I1" s="220"/>
+      <c r="J1" s="220"/>
+      <c r="K1" s="220"/>
     </row>
     <row r="2" spans="1:11" ht="26.25" thickBot="1">
       <c r="A2" s="28" t="s">
@@ -53001,43 +53398,43 @@
       </c>
     </row>
     <row r="23" spans="1:16" ht="29.25">
-      <c r="A23" s="201">
+      <c r="A23" s="199">
         <v>22</v>
       </c>
-      <c r="B23" s="202">
+      <c r="B23" s="200">
         <v>21</v>
       </c>
-      <c r="C23" s="203" t="s">
+      <c r="C23" s="201" t="s">
         <v>613</v>
       </c>
-      <c r="D23" s="202" t="s">
+      <c r="D23" s="200" t="s">
         <v>615</v>
       </c>
-      <c r="E23" s="202" t="s">
+      <c r="E23" s="200" t="s">
         <v>615</v>
       </c>
-      <c r="F23" s="204" t="s">
+      <c r="F23" s="202" t="s">
         <v>2232</v>
       </c>
-      <c r="G23" s="202" t="s">
+      <c r="G23" s="200" t="s">
         <v>615</v>
       </c>
-      <c r="H23" s="202" t="s">
+      <c r="H23" s="200" t="s">
         <v>615</v>
       </c>
-      <c r="I23" s="203" t="s">
+      <c r="I23" s="201" t="s">
         <v>2060</v>
       </c>
-      <c r="J23" s="203" t="s">
+      <c r="J23" s="201" t="s">
         <v>614</v>
       </c>
-      <c r="K23" s="205" t="s">
+      <c r="K23" s="203" t="s">
         <v>560</v>
       </c>
-      <c r="L23" s="205" t="s">
+      <c r="L23" s="203" t="s">
         <v>612</v>
       </c>
-      <c r="M23" s="203" t="s">
+      <c r="M23" s="201" t="s">
         <v>619</v>
       </c>
       <c r="N23" s="82">
@@ -53137,10 +53534,10 @@
       <c r="H2" s="1">
         <v>1</v>
       </c>
-      <c r="I2" s="211" t="s">
+      <c r="I2" s="209" t="s">
         <v>518</v>
       </c>
-      <c r="J2" s="211" t="s">
+      <c r="J2" s="209" t="s">
         <v>518</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -53179,10 +53576,10 @@
       <c r="H3" s="1">
         <v>2</v>
       </c>
-      <c r="I3" s="211" t="s">
+      <c r="I3" s="209" t="s">
         <v>538</v>
       </c>
-      <c r="J3" s="211" t="s">
+      <c r="J3" s="209" t="s">
         <v>538</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -53219,10 +53616,10 @@
       <c r="H4" s="1">
         <v>3</v>
       </c>
-      <c r="I4" s="211" t="s">
+      <c r="I4" s="209" t="s">
         <v>583</v>
       </c>
-      <c r="J4" s="211" t="s">
+      <c r="J4" s="209" t="s">
         <v>583</v>
       </c>
       <c r="K4" s="1" t="s">
@@ -53259,10 +53656,10 @@
       <c r="H5" s="1">
         <v>4</v>
       </c>
-      <c r="I5" s="211" t="s">
+      <c r="I5" s="209" t="s">
         <v>566</v>
       </c>
-      <c r="J5" s="215" t="s">
+      <c r="J5" s="213" t="s">
         <v>1978</v>
       </c>
       <c r="K5" s="1" t="s">
@@ -53299,10 +53696,10 @@
       <c r="H6" s="1">
         <v>5</v>
       </c>
-      <c r="I6" s="211" t="s">
+      <c r="I6" s="209" t="s">
         <v>533</v>
       </c>
-      <c r="J6" s="211" t="s">
+      <c r="J6" s="209" t="s">
         <v>533</v>
       </c>
       <c r="K6" s="1" t="s">
@@ -53339,10 +53736,10 @@
       <c r="H7" s="1">
         <v>6</v>
       </c>
-      <c r="I7" s="211" t="s">
+      <c r="I7" s="209" t="s">
         <v>543</v>
       </c>
-      <c r="J7" s="211" t="s">
+      <c r="J7" s="209" t="s">
         <v>543</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -53379,10 +53776,10 @@
       <c r="H8" s="1">
         <v>7</v>
       </c>
-      <c r="I8" s="211" t="s">
+      <c r="I8" s="209" t="s">
         <v>588</v>
       </c>
-      <c r="J8" s="211" t="s">
+      <c r="J8" s="209" t="s">
         <v>588</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -53419,10 +53816,10 @@
       <c r="H9" s="1">
         <v>8</v>
       </c>
-      <c r="I9" s="211" t="s">
+      <c r="I9" s="209" t="s">
         <v>514</v>
       </c>
-      <c r="J9" s="211" t="s">
+      <c r="J9" s="209" t="s">
         <v>514</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -53459,10 +53856,10 @@
       <c r="H10" s="1">
         <v>9</v>
       </c>
-      <c r="I10" s="211" t="s">
+      <c r="I10" s="209" t="s">
         <v>523</v>
       </c>
-      <c r="J10" s="211" t="s">
+      <c r="J10" s="209" t="s">
         <v>523</v>
       </c>
       <c r="K10" s="1" t="s">
@@ -53499,10 +53896,10 @@
       <c r="H11" s="1">
         <v>10</v>
       </c>
-      <c r="I11" s="211" t="s">
+      <c r="I11" s="209" t="s">
         <v>528</v>
       </c>
-      <c r="J11" s="211" t="s">
+      <c r="J11" s="209" t="s">
         <v>528</v>
       </c>
       <c r="K11" s="1" t="s">
@@ -53539,10 +53936,10 @@
       <c r="H12" s="1">
         <v>11</v>
       </c>
-      <c r="I12" s="211" t="s">
+      <c r="I12" s="209" t="s">
         <v>593</v>
       </c>
-      <c r="J12" s="215" t="s">
+      <c r="J12" s="213" t="s">
         <v>1980</v>
       </c>
       <c r="K12" s="1" t="s">
@@ -53579,10 +53976,10 @@
       <c r="H13" s="1">
         <v>12</v>
       </c>
-      <c r="I13" s="211" t="s">
+      <c r="I13" s="209" t="s">
         <v>571</v>
       </c>
-      <c r="J13" s="215" t="s">
+      <c r="J13" s="213" t="s">
         <v>593</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -53619,10 +54016,10 @@
       <c r="H14" s="1">
         <v>13</v>
       </c>
-      <c r="I14" s="211" t="s">
+      <c r="I14" s="209" t="s">
         <v>548</v>
       </c>
-      <c r="J14" s="211" t="s">
+      <c r="J14" s="209" t="s">
         <v>548</v>
       </c>
       <c r="K14" s="1" t="s">
@@ -53661,10 +54058,10 @@
       <c r="H15" s="1">
         <v>14</v>
       </c>
-      <c r="I15" s="211" t="s">
+      <c r="I15" s="209" t="s">
         <v>620</v>
       </c>
-      <c r="J15" s="211" t="s">
+      <c r="J15" s="209" t="s">
         <v>1979</v>
       </c>
       <c r="K15" s="1" t="s">
@@ -53701,10 +54098,10 @@
       <c r="H16" s="1">
         <v>15</v>
       </c>
-      <c r="I16" s="211" t="s">
+      <c r="I16" s="209" t="s">
         <v>618</v>
       </c>
-      <c r="J16" s="211" t="s">
+      <c r="J16" s="209" t="s">
         <v>1977</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -53743,10 +54140,10 @@
       <c r="H17" s="1">
         <v>16</v>
       </c>
-      <c r="I17" s="211" t="s">
+      <c r="I17" s="209" t="s">
         <v>555</v>
       </c>
-      <c r="J17" s="215" t="s">
+      <c r="J17" s="213" t="s">
         <v>1976</v>
       </c>
       <c r="K17" s="1" t="s">
@@ -53783,10 +54180,10 @@
       <c r="H18" s="1">
         <v>17</v>
       </c>
-      <c r="I18" s="211" t="s">
+      <c r="I18" s="209" t="s">
         <v>581</v>
       </c>
-      <c r="J18" s="211" t="s">
+      <c r="J18" s="209" t="s">
         <v>581</v>
       </c>
       <c r="K18" s="1" t="s">
@@ -53823,25 +54220,25 @@
       <c r="H19" s="1">
         <v>18</v>
       </c>
-      <c r="I19" s="219" t="s">
+      <c r="I19" s="217" t="s">
         <v>563</v>
       </c>
-      <c r="J19" s="220" t="s">
+      <c r="J19" s="218" t="s">
         <v>563</v>
       </c>
-      <c r="K19" s="217" t="s">
+      <c r="K19" s="215" t="s">
         <v>563</v>
       </c>
-      <c r="L19" s="217" t="s">
+      <c r="L19" s="215" t="s">
         <v>563</v>
       </c>
-      <c r="M19" s="217" t="s">
+      <c r="M19" s="215" t="s">
         <v>563</v>
       </c>
-      <c r="N19" s="218" t="s">
+      <c r="N19" s="216" t="s">
         <v>563</v>
       </c>
-      <c r="O19" s="217" t="s">
+      <c r="O19" s="215" t="s">
         <v>563</v>
       </c>
       <c r="P19" s="1" t="s">
@@ -53867,10 +54264,10 @@
       <c r="H20" s="9">
         <v>19</v>
       </c>
-      <c r="I20" s="212" t="s">
+      <c r="I20" s="210" t="s">
         <v>2058</v>
       </c>
-      <c r="J20" s="212" t="s">
+      <c r="J20" s="210" t="s">
         <v>602</v>
       </c>
       <c r="K20" s="9" t="s">
@@ -53911,10 +54308,10 @@
       <c r="H21" s="9">
         <v>20</v>
       </c>
-      <c r="I21" s="212" t="s">
+      <c r="I21" s="210" t="s">
         <v>2059</v>
       </c>
-      <c r="J21" s="212" t="s">
+      <c r="J21" s="210" t="s">
         <v>608</v>
       </c>
       <c r="K21" s="9" t="s">
@@ -53955,72 +54352,72 @@
       <c r="H22" s="9">
         <v>21</v>
       </c>
-      <c r="I22" s="213" t="s">
+      <c r="I22" s="211" t="s">
         <v>2060</v>
       </c>
-      <c r="J22" s="213" t="s">
+      <c r="J22" s="211" t="s">
         <v>614</v>
       </c>
-      <c r="K22" s="202" t="s">
+      <c r="K22" s="200" t="s">
         <v>615</v>
       </c>
-      <c r="L22" s="202" t="s">
+      <c r="L22" s="200" t="s">
         <v>615</v>
       </c>
-      <c r="M22" s="202" t="s">
+      <c r="M22" s="200" t="s">
         <v>615</v>
       </c>
-      <c r="N22" s="204" t="s">
+      <c r="N22" s="202" t="s">
         <v>2232</v>
       </c>
-      <c r="O22" s="202" t="s">
+      <c r="O22" s="200" t="s">
         <v>615</v>
       </c>
-      <c r="P22" s="203" t="s">
+      <c r="P22" s="201" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="39">
-      <c r="A23" s="209">
+      <c r="A23" s="207">
         <v>22</v>
       </c>
-      <c r="B23" s="210" t="s">
+      <c r="B23" s="208" t="s">
         <v>560</v>
       </c>
-      <c r="C23" s="210" t="s">
+      <c r="C23" s="208" t="s">
         <v>612</v>
       </c>
-      <c r="D23" s="208" t="s">
+      <c r="D23" s="206" t="s">
         <v>613</v>
       </c>
-      <c r="E23" s="208" t="s">
+      <c r="E23" s="206" t="s">
         <v>619</v>
       </c>
       <c r="H23" s="9">
         <v>22</v>
       </c>
-      <c r="I23" s="214" t="s">
+      <c r="I23" s="212" t="s">
         <v>597</v>
       </c>
-      <c r="J23" s="216" t="s">
+      <c r="J23" s="214" t="s">
         <v>1976</v>
       </c>
-      <c r="K23" s="206" t="s">
+      <c r="K23" s="204" t="s">
         <v>598</v>
       </c>
-      <c r="L23" s="206" t="s">
+      <c r="L23" s="204" t="s">
         <v>598</v>
       </c>
-      <c r="M23" s="206" t="s">
+      <c r="M23" s="204" t="s">
         <v>598</v>
       </c>
-      <c r="N23" s="207" t="s">
+      <c r="N23" s="205" t="s">
         <v>2229</v>
       </c>
-      <c r="O23" s="206" t="s">
+      <c r="O23" s="204" t="s">
         <v>599</v>
       </c>
-      <c r="P23" s="208" t="s">
+      <c r="P23" s="206" t="s">
         <v>616</v>
       </c>
     </row>
